--- a/docs/arb_stiffness.xlsx
+++ b/docs/arb_stiffness.xlsx
@@ -468,7 +468,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -535,6 +535,12 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" numFmtId="1" fontId="1" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" numFmtId="1" fontId="1" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -641,13 +647,13 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>2.2698401224037079</c:v>
+                  <c:v>2.2853924564370129</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.5466251912557931</c:v>
+                  <c:v>3.5709257131828327</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.4886975076831144</c:v>
+                  <c:v>4.5194528557470228</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>4.8261413511642468</c:v>
@@ -659,13 +665,13 @@
                   <c:v>9.54388304307383</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.8050375657307463</c:v>
+                  <c:v>8.883105307657285</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>13.757871196454293</c:v>
+                  <c:v>13.879852043214509</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>17.412305733012463</c:v>
+                  <c:v>17.566687742193366</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -730,13 +736,13 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>5.6582903686974513</c:v>
+                  <c:v>5.6824163988087895</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.2177274322502765</c:v>
+                  <c:v>8.252766485843928</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.6760113405536323</c:v>
+                  <c:v>9.7172682796197645</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>11.686377648349833</c:v>
@@ -748,13 +754,13 @@
                   <c:v>19.984397280314212</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>19.53163899581299</c:v>
+                  <c:v>19.680770253067951</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>28.36646320956666</c:v>
+                  <c:v>28.583051603568116</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>33.400258401123992</c:v>
+                  <c:v>33.655281675364719</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -990,13 +996,13 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>2.6727912991374931</c:v>
+                  <c:v>2.6911045462579462</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.8488194707579906</c:v>
+                  <c:v>3.8751905466114427</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.6168378685509683</c:v>
+                  <c:v>4.6484711999035211</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>5.6828974360270976</c:v>
@@ -1008,13 +1014,13 @@
                   <c:v>9.8163354894966037</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>10.368143360397529</c:v>
+                  <c:v>10.460070002853563</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>14.93012643897244</c:v>
+                  <c:v>15.062500804109128</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>17.909380694368298</c:v>
+                  <c:v>18.068169898806641</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1079,13 +1085,13 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>5.4532242223578775</c:v>
+                  <c:v>5.4764758837643539</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.7889300165861197</c:v>
+                  <c:v>7.8221407477205336</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.459608466624374</c:v>
+                  <c:v>9.4999426990225206</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>11.262843281454536</c:v>
@@ -1097,13 +1103,13 @@
                   <c:v>19.537448547722441</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>18.823778903880459</c:v>
+                  <c:v>18.967505388627945</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>26.886313592038661</c:v>
+                  <c:v>27.091600498569726</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>32.653265487040706</c:v>
+                  <c:v>32.902585195264187</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2552,8 +2558,9 @@
       <c r="D7" s="4">
         <v>14.6</v>
       </c>
-      <c r="E7" s="5">
-        <v>935</v>
+      <c r="E7" s="23">
+        <f>$E$8*(D7/$D$8)^4</f>
+        <v>941.40636852684645</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -2590,8 +2597,9 @@
       <c r="D9" s="4">
         <v>20.5</v>
       </c>
-      <c r="E9" s="5">
-        <v>3627</v>
+      <c r="E9" s="23">
+        <f>$E$8*(D9/$D$8)^4</f>
+        <v>3659.1579207191103</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -2609,8 +2617,9 @@
       <c r="D10" s="4">
         <v>16.2</v>
       </c>
-      <c r="E10" s="5">
-        <v>1423</v>
+      <c r="E10" s="24">
+        <f>$E$11*(D10/$D$11)^4</f>
+        <v>1429.0674406245321</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -2647,8 +2656,9 @@
       <c r="D12" s="4">
         <v>22.1</v>
       </c>
-      <c r="E12" s="5">
-        <v>4912</v>
+      <c r="E12" s="24">
+        <f>$E$11*(D12/$D$11)^4</f>
+        <v>4949.5049290944507</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -3358,11 +3368,11 @@
       </c>
       <c r="K6" s="9">
         <f>Parameters!E7</f>
-        <v>935</v>
+        <v>941.40636852684645</v>
       </c>
       <c r="L6" s="13">
         <f t="shared" ref="L6:L41" si="1">1000*K6*I6^2/J6^2</f>
-        <v>2.6727912991374931</v>
+        <v>2.6911045462579462</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>37</v>
@@ -3411,11 +3421,11 @@
       </c>
       <c r="K7" s="10">
         <f>Parameters!E7</f>
-        <v>935</v>
+        <v>941.40636852684645</v>
       </c>
       <c r="L7" s="16">
         <f t="shared" si="1"/>
-        <v>3.8488194707579906</v>
+        <v>3.8751905466114427</v>
       </c>
       <c r="M7" s="6" t="s">
         <v>39</v>
@@ -3464,11 +3474,11 @@
       </c>
       <c r="K8" s="9">
         <f>Parameters!E7</f>
-        <v>935</v>
+        <v>941.40636852684645</v>
       </c>
       <c r="L8" s="13">
         <f t="shared" si="1"/>
-        <v>4.6168378685509683</v>
+        <v>4.6484711999035211</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>41</v>
@@ -3676,11 +3686,11 @@
       </c>
       <c r="K12" s="9">
         <f>Parameters!E9</f>
-        <v>3627</v>
+        <v>3659.1579207191103</v>
       </c>
       <c r="L12" s="13">
         <f t="shared" si="1"/>
-        <v>10.368143360397529</v>
+        <v>10.460070002853563</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>49</v>
@@ -3729,11 +3739,11 @@
       </c>
       <c r="K13" s="10">
         <f>Parameters!E9</f>
-        <v>3627</v>
+        <v>3659.1579207191103</v>
       </c>
       <c r="L13" s="16">
         <f t="shared" si="1"/>
-        <v>14.93012643897244</v>
+        <v>15.062500804109128</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>51</v>
@@ -3782,11 +3792,11 @@
       </c>
       <c r="K14" s="9">
         <f>Parameters!E9</f>
-        <v>3627</v>
+        <v>3659.1579207191103</v>
       </c>
       <c r="L14" s="13">
         <f t="shared" si="1"/>
-        <v>17.909380694368298</v>
+        <v>18.068169898806641</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>53</v>
@@ -3809,7 +3819,7 @@
       </c>
       <c r="F15" s="14">
         <f>Parameters!D10</f>
-        <v>16.2</v>
+        <v>16.199999999999999</v>
       </c>
       <c r="G15" s="14">
         <f>Parameters!E20</f>
@@ -3829,11 +3839,11 @@
       </c>
       <c r="K15" s="10">
         <f>Parameters!E10</f>
-        <v>1423</v>
+        <v>1429.0674406245321</v>
       </c>
       <c r="L15" s="16">
         <f t="shared" si="1"/>
-        <v>5.4532242223578775</v>
+        <v>5.4764758837643539</v>
       </c>
       <c r="M15" s="6" t="s">
         <v>54</v>
@@ -3856,7 +3866,7 @@
       </c>
       <c r="F16" s="11">
         <f>Parameters!D10</f>
-        <v>16.2</v>
+        <v>16.199999999999999</v>
       </c>
       <c r="G16" s="11">
         <f>Parameters!E21</f>
@@ -3876,11 +3886,11 @@
       </c>
       <c r="K16" s="9">
         <f>Parameters!E10</f>
-        <v>1423</v>
+        <v>1429.0674406245321</v>
       </c>
       <c r="L16" s="13">
         <f t="shared" si="1"/>
-        <v>7.7889300165861197</v>
+        <v>7.8221407477205336</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>55</v>
@@ -3903,7 +3913,7 @@
       </c>
       <c r="F17" s="14">
         <f>Parameters!D10</f>
-        <v>16.2</v>
+        <v>16.199999999999999</v>
       </c>
       <c r="G17" s="14">
         <f>Parameters!E22</f>
@@ -3923,11 +3933,11 @@
       </c>
       <c r="K17" s="10">
         <f>Parameters!E10</f>
-        <v>1423</v>
+        <v>1429.0674406245321</v>
       </c>
       <c r="L17" s="16">
         <f t="shared" si="1"/>
-        <v>9.459608466624374</v>
+        <v>9.4999426990225206</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>56</v>
@@ -4091,7 +4101,7 @@
       </c>
       <c r="F21" s="14">
         <f>Parameters!D12</f>
-        <v>22.1</v>
+        <v>22.100000000000001</v>
       </c>
       <c r="G21" s="14">
         <f>Parameters!E20</f>
@@ -4111,11 +4121,11 @@
       </c>
       <c r="K21" s="10">
         <f>Parameters!E12</f>
-        <v>4912</v>
+        <v>4949.5049290944507</v>
       </c>
       <c r="L21" s="16">
         <f t="shared" si="1"/>
-        <v>18.823778903880459</v>
+        <v>18.967505388627945</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>60</v>
@@ -4138,7 +4148,7 @@
       </c>
       <c r="F22" s="11">
         <f>Parameters!D12</f>
-        <v>22.1</v>
+        <v>22.100000000000001</v>
       </c>
       <c r="G22" s="11">
         <f>Parameters!E21</f>
@@ -4158,11 +4168,11 @@
       </c>
       <c r="K22" s="9">
         <f>Parameters!E12</f>
-        <v>4912</v>
+        <v>4949.5049290944507</v>
       </c>
       <c r="L22" s="13">
         <f t="shared" si="1"/>
-        <v>26.886313592038661</v>
+        <v>27.091600498569726</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>61</v>
@@ -4185,7 +4195,7 @@
       </c>
       <c r="F23" s="14">
         <f>Parameters!D12</f>
-        <v>22.1</v>
+        <v>22.100000000000001</v>
       </c>
       <c r="G23" s="14">
         <f>Parameters!E22</f>
@@ -4205,11 +4215,11 @@
       </c>
       <c r="K23" s="10">
         <f>Parameters!E12</f>
-        <v>4912</v>
+        <v>4949.5049290944507</v>
       </c>
       <c r="L23" s="16">
         <f t="shared" si="1"/>
-        <v>32.653265487040706</v>
+        <v>32.902585195264187</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>62</v>
@@ -4252,11 +4262,11 @@
       </c>
       <c r="K24" s="9">
         <f>Parameters!E7</f>
-        <v>935</v>
+        <v>941.40636852684645</v>
       </c>
       <c r="L24" s="13">
         <f t="shared" si="1"/>
-        <v>2.2698401224037079</v>
+        <v>2.2853924564370129</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>63</v>
@@ -4299,11 +4309,11 @@
       </c>
       <c r="K25" s="10">
         <f>Parameters!E7</f>
-        <v>935</v>
+        <v>941.40636852684645</v>
       </c>
       <c r="L25" s="16">
         <f t="shared" si="1"/>
-        <v>3.5466251912557931</v>
+        <v>3.5709257131828327</v>
       </c>
       <c r="M25" s="6" t="s">
         <v>64</v>
@@ -4346,11 +4356,11 @@
       </c>
       <c r="K26" s="9">
         <f>Parameters!E7</f>
-        <v>935</v>
+        <v>941.40636852684645</v>
       </c>
       <c r="L26" s="13">
         <f t="shared" si="1"/>
-        <v>4.4886975076831144</v>
+        <v>4.5194528557470228</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>65</v>
@@ -4534,11 +4544,11 @@
       </c>
       <c r="K30" s="9">
         <f>Parameters!E9</f>
-        <v>3627</v>
+        <v>3659.1579207191103</v>
       </c>
       <c r="L30" s="13">
         <f t="shared" si="1"/>
-        <v>8.8050375657307463</v>
+        <v>8.883105307657285</v>
       </c>
       <c r="M30" s="3" t="s">
         <v>69</v>
@@ -4581,11 +4591,11 @@
       </c>
       <c r="K31" s="10">
         <f>Parameters!E9</f>
-        <v>3627</v>
+        <v>3659.1579207191103</v>
       </c>
       <c r="L31" s="16">
         <f t="shared" si="1"/>
-        <v>13.757871196454293</v>
+        <v>13.879852043214509</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>70</v>
@@ -4628,11 +4638,11 @@
       </c>
       <c r="K32" s="9">
         <f>Parameters!E9</f>
-        <v>3627</v>
+        <v>3659.1579207191103</v>
       </c>
       <c r="L32" s="13">
         <f t="shared" si="1"/>
-        <v>17.412305733012463</v>
+        <v>17.566687742193366</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>71</v>
@@ -4655,7 +4665,7 @@
       </c>
       <c r="F33" s="14">
         <f>Parameters!D10</f>
-        <v>16.2</v>
+        <v>16.199999999999999</v>
       </c>
       <c r="G33" s="14">
         <f>Parameters!E26</f>
@@ -4675,11 +4685,11 @@
       </c>
       <c r="K33" s="10">
         <f>Parameters!E10</f>
-        <v>1423</v>
+        <v>1429.0674406245321</v>
       </c>
       <c r="L33" s="16">
         <f t="shared" si="1"/>
-        <v>5.6582903686974513</v>
+        <v>5.6824163988087895</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>72</v>
@@ -4702,7 +4712,7 @@
       </c>
       <c r="F34" s="11">
         <f>Parameters!D10</f>
-        <v>16.2</v>
+        <v>16.199999999999999</v>
       </c>
       <c r="G34" s="11">
         <f>Parameters!E27</f>
@@ -4722,11 +4732,11 @@
       </c>
       <c r="K34" s="9">
         <f>Parameters!E10</f>
-        <v>1423</v>
+        <v>1429.0674406245321</v>
       </c>
       <c r="L34" s="13">
         <f t="shared" si="1"/>
-        <v>8.2177274322502765</v>
+        <v>8.252766485843928</v>
       </c>
       <c r="M34" s="3" t="s">
         <v>73</v>
@@ -4749,7 +4759,7 @@
       </c>
       <c r="F35" s="14">
         <f>Parameters!D10</f>
-        <v>16.2</v>
+        <v>16.199999999999999</v>
       </c>
       <c r="G35" s="14">
         <f>Parameters!E28</f>
@@ -4769,11 +4779,11 @@
       </c>
       <c r="K35" s="10">
         <f>Parameters!E10</f>
-        <v>1423</v>
+        <v>1429.0674406245321</v>
       </c>
       <c r="L35" s="16">
         <f t="shared" si="1"/>
-        <v>9.6760113405536323</v>
+        <v>9.7172682796197645</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>74</v>
@@ -4937,7 +4947,7 @@
       </c>
       <c r="F39" s="14">
         <f>Parameters!D12</f>
-        <v>22.1</v>
+        <v>22.100000000000001</v>
       </c>
       <c r="G39" s="14">
         <f>Parameters!E26</f>
@@ -4957,11 +4967,11 @@
       </c>
       <c r="K39" s="10">
         <f>Parameters!E12</f>
-        <v>4912</v>
+        <v>4949.5049290944507</v>
       </c>
       <c r="L39" s="16">
         <f t="shared" si="1"/>
-        <v>19.53163899581299</v>
+        <v>19.680770253067951</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>78</v>
@@ -4984,7 +4994,7 @@
       </c>
       <c r="F40" s="11">
         <f>Parameters!D12</f>
-        <v>22.1</v>
+        <v>22.100000000000001</v>
       </c>
       <c r="G40" s="11">
         <f>Parameters!E27</f>
@@ -5004,11 +5014,11 @@
       </c>
       <c r="K40" s="9">
         <f>Parameters!E12</f>
-        <v>4912</v>
+        <v>4949.5049290944507</v>
       </c>
       <c r="L40" s="13">
         <f t="shared" si="1"/>
-        <v>28.36646320956666</v>
+        <v>28.583051603568116</v>
       </c>
       <c r="M40" s="3" t="s">
         <v>79</v>
@@ -5031,7 +5041,7 @@
       </c>
       <c r="F41" s="14">
         <f>Parameters!D12</f>
-        <v>22.1</v>
+        <v>22.100000000000001</v>
       </c>
       <c r="G41" s="14">
         <f>Parameters!E28</f>
@@ -5051,11 +5061,11 @@
       </c>
       <c r="K41" s="10">
         <f>Parameters!E12</f>
-        <v>4912</v>
+        <v>4949.5049290944507</v>
       </c>
       <c r="L41" s="16">
         <f t="shared" si="1"/>
-        <v>33.400258401123992</v>
+        <v>33.655281675364719</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>80</v>
@@ -5141,11 +5151,11 @@
       </c>
       <c r="C46" s="13">
         <f t="shared" ref="C46:C54" si="2">L24</f>
-        <v>2.2698401224037079</v>
+        <v>2.2853924564370129</v>
       </c>
       <c r="D46" s="13">
         <f t="shared" ref="D46:D54" si="3">L33</f>
-        <v>5.6582903686974513</v>
+        <v>5.6824163988087895</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
@@ -5165,11 +5175,11 @@
       </c>
       <c r="C47" s="16">
         <f t="shared" si="2"/>
-        <v>3.5466251912557931</v>
+        <v>3.5709257131828327</v>
       </c>
       <c r="D47" s="16">
         <f t="shared" si="3"/>
-        <v>8.2177274322502765</v>
+        <v>8.252766485843928</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
@@ -5189,11 +5199,11 @@
       </c>
       <c r="C48" s="13">
         <f t="shared" si="2"/>
-        <v>4.4886975076831144</v>
+        <v>4.5194528557470228</v>
       </c>
       <c r="D48" s="13">
         <f t="shared" si="3"/>
-        <v>9.6760113405536323</v>
+        <v>9.7172682796197645</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -5285,11 +5295,11 @@
       </c>
       <c r="C52" s="13">
         <f t="shared" si="2"/>
-        <v>8.8050375657307463</v>
+        <v>8.883105307657285</v>
       </c>
       <c r="D52" s="13">
         <f t="shared" si="3"/>
-        <v>19.53163899581299</v>
+        <v>19.680770253067951</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -5309,11 +5319,11 @@
       </c>
       <c r="C53" s="16">
         <f t="shared" si="2"/>
-        <v>13.757871196454293</v>
+        <v>13.879852043214509</v>
       </c>
       <c r="D53" s="16">
         <f t="shared" si="3"/>
-        <v>28.36646320956666</v>
+        <v>28.583051603568116</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -5333,11 +5343,11 @@
       </c>
       <c r="C54" s="13">
         <f t="shared" si="2"/>
-        <v>17.412305733012463</v>
+        <v>17.566687742193366</v>
       </c>
       <c r="D54" s="13">
         <f t="shared" si="3"/>
-        <v>33.400258401123992</v>
+        <v>33.655281675364719</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
@@ -5445,11 +5455,11 @@
       </c>
       <c r="C60" s="13">
         <f t="shared" ref="C60:C68" si="4">L6</f>
-        <v>2.6727912991374931</v>
+        <v>2.6911045462579462</v>
       </c>
       <c r="D60" s="13">
         <f t="shared" ref="D60:D68" si="5">L15</f>
-        <v>5.4532242223578775</v>
+        <v>5.4764758837643539</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
@@ -5469,11 +5479,11 @@
       </c>
       <c r="C61" s="16">
         <f t="shared" si="4"/>
-        <v>3.8488194707579906</v>
+        <v>3.8751905466114427</v>
       </c>
       <c r="D61" s="16">
         <f t="shared" si="5"/>
-        <v>7.7889300165861197</v>
+        <v>7.8221407477205336</v>
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
@@ -5493,11 +5503,11 @@
       </c>
       <c r="C62" s="13">
         <f t="shared" si="4"/>
-        <v>4.6168378685509683</v>
+        <v>4.6484711999035211</v>
       </c>
       <c r="D62" s="13">
         <f t="shared" si="5"/>
-        <v>9.459608466624374</v>
+        <v>9.4999426990225206</v>
       </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
@@ -5589,11 +5599,11 @@
       </c>
       <c r="C66" s="13">
         <f t="shared" si="4"/>
-        <v>10.368143360397529</v>
+        <v>10.460070002853563</v>
       </c>
       <c r="D66" s="13">
         <f t="shared" si="5"/>
-        <v>18.823778903880459</v>
+        <v>18.967505388627945</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
@@ -5613,11 +5623,11 @@
       </c>
       <c r="C67" s="16">
         <f t="shared" si="4"/>
-        <v>14.93012643897244</v>
+        <v>15.062500804109128</v>
       </c>
       <c r="D67" s="16">
         <f t="shared" si="5"/>
-        <v>26.886313592038661</v>
+        <v>27.091600498569726</v>
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
@@ -5637,11 +5647,11 @@
       </c>
       <c r="C68" s="13">
         <f t="shared" si="4"/>
-        <v>17.909380694368298</v>
+        <v>18.068169898806641</v>
       </c>
       <c r="D68" s="13">
         <f t="shared" si="5"/>
-        <v>32.653265487040706</v>
+        <v>32.902585195264187</v>
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>

--- a/docs/arb_stiffness.xlsx
+++ b/docs/arb_stiffness.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\UserSpace\Games\Steam_Library\common\BeamNG_Userdata\current\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="11_507BD9252E54F25ED5866DE2E3AD0A0E2C0D3175" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comparison" sheetId="1" r:id="rId1"/>
@@ -321,10 +321,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="178" formatCode="0.0"/>
-    <numFmt numFmtId="179" formatCode="0.0000"/>
+    <numFmt numFmtId="176" formatCode="0.0"/>
+    <numFmt numFmtId="177" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -396,10 +396,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
@@ -464,88 +460,80 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" numFmtId="1" fontId="1" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" numFmtId="1" fontId="1" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -563,7 +551,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -912,7 +900,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -1534,7 +1522,7 @@
     <tabColor rgb="FF243B53"/>
   </sheetPr>
   <dimension ref="A1:O48"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.75" customWidth="1"/>
     <col min="2" max="14" width="10" customWidth="1"/>
@@ -1542,25 +1530,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="12" customHeight="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-    </row>
-    <row r="2" spans="1:15" ht="35" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="17" t="s">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+    </row>
+    <row r="2" spans="1:15" ht="35.1" customHeight="1">
+      <c r="A2" s="2"/>
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="18" t="s">
@@ -1599,10 +1587,10 @@
       <c r="N2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="O2" s="1"/>
+      <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" ht="12" customHeight="1">
-      <c r="A3" s="1"/>
+      <c r="A3" s="2"/>
       <c r="B3" s="18" t="s">
         <v>0</v>
       </c>
@@ -1642,10 +1630,10 @@
       <c r="N3" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="O3" s="1"/>
+      <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" ht="24" customHeight="1">
-      <c r="A4" s="1"/>
+      <c r="A4" s="2"/>
       <c r="B4" s="19" t="s">
         <v>1</v>
       </c>
@@ -1685,749 +1673,749 @@
       <c r="N4" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="O4" s="1"/>
+      <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" ht="24" customHeight="1">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="24" customHeight="1">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
     </row>
     <row r="7" spans="1:15" ht="24" customHeight="1">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" ht="24" customHeight="1">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" ht="24" customHeight="1">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="24" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
     </row>
     <row r="11" spans="1:15" ht="24" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
     </row>
     <row r="12" spans="1:15" ht="24" customHeight="1">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
     </row>
     <row r="13" spans="1:15" ht="24" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
     </row>
     <row r="14" spans="1:15" ht="24" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
     </row>
     <row r="15" spans="1:15" ht="24" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
     </row>
     <row r="16" spans="1:15" ht="24" customHeight="1">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
     </row>
     <row r="17" spans="1:15" ht="24" customHeight="1">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
     </row>
     <row r="18" spans="1:15" ht="24" customHeight="1">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
     </row>
     <row r="19" spans="1:15" ht="24" customHeight="1">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
     </row>
     <row r="20" spans="1:15" ht="24" customHeight="1">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
     </row>
     <row r="21" spans="1:15" ht="24" customHeight="1">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
     </row>
     <row r="22" spans="1:15" ht="24" customHeight="1">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
     </row>
     <row r="23" spans="1:15" ht="24" customHeight="1">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
     </row>
     <row r="24" spans="1:15" ht="24" customHeight="1">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
     </row>
     <row r="25" spans="1:15" ht="24" customHeight="1">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
     </row>
     <row r="26" spans="1:15" ht="24" customHeight="1">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
     </row>
     <row r="27" spans="1:15" ht="24" customHeight="1">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
     </row>
     <row r="28" spans="1:15" ht="24" customHeight="1">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
     </row>
     <row r="29" spans="1:15" ht="24" customHeight="1">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
     </row>
     <row r="30" spans="1:15" ht="24" customHeight="1">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
     </row>
     <row r="31" spans="1:15" ht="24" customHeight="1">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
     </row>
     <row r="32" spans="1:15" ht="24" customHeight="1">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
     </row>
     <row r="33" spans="1:15" ht="24" customHeight="1">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
     </row>
     <row r="34" spans="1:15" ht="24" customHeight="1">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
     </row>
     <row r="35" spans="1:15" ht="24" customHeight="1">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
     </row>
     <row r="36" spans="1:15" ht="24" customHeight="1">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
     </row>
     <row r="37" spans="1:15" ht="24" customHeight="1">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
     </row>
     <row r="38" spans="1:15" ht="24" customHeight="1">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
     </row>
     <row r="39" spans="1:15" ht="24" customHeight="1">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
     </row>
     <row r="40" spans="1:15" ht="24" customHeight="1">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
     </row>
     <row r="41" spans="1:15" ht="24" customHeight="1">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
     </row>
     <row r="42" spans="1:15" ht="24" customHeight="1">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
     </row>
     <row r="43" spans="1:15" ht="24" customHeight="1">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
     </row>
     <row r="44" spans="1:15" ht="24" customHeight="1">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
     </row>
     <row r="45" spans="1:15" ht="24" customHeight="1">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
     </row>
     <row r="46" spans="1:15" ht="24" customHeight="1">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
     </row>
     <row r="47" spans="1:15" ht="24" customHeight="1">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
     </row>
     <row r="48" spans="1:15" ht="24" customHeight="1">
-      <c r="A48" s="1"/>
-      <c r="O48" s="1"/>
+      <c r="A48" s="2"/>
+      <c r="O48" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:N3"/>
     <mergeCell ref="B4:N4"/>
   </mergeCells>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2439,11 +2427,11 @@
     <tabColor rgb="FF243B53"/>
   </sheetPr>
   <dimension ref="A1:I56"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.75" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="12.9140625" customWidth="1"/>
+    <col min="3" max="3" width="12.875" customWidth="1"/>
     <col min="4" max="4" width="16.75" customWidth="1"/>
     <col min="5" max="7" width="18.5" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
@@ -2453,19 +2441,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="12" customHeight="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:9" ht="35" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="17" t="s">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:9" ht="35.1" customHeight="1">
+      <c r="A2" s="2"/>
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="18" t="s">
@@ -2486,10 +2474,10 @@
       <c r="H2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="1"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:9" ht="12" customHeight="1">
-      <c r="A3" s="1"/>
+      <c r="A3" s="2"/>
       <c r="B3" s="18" t="s">
         <v>3</v>
       </c>
@@ -2511,173 +2499,173 @@
       <c r="H3" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="1"/>
+      <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9" ht="24" customHeight="1">
-      <c r="A4" s="1"/>
-      <c r="I4" s="1"/>
+      <c r="A4" s="2"/>
+      <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9" ht="24" customHeight="1">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:9" ht="32" customHeight="1">
-      <c r="A6" s="1"/>
-      <c r="B6" s="2" t="s">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" ht="32.1" customHeight="1">
+      <c r="A6" s="2"/>
+      <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="1:9" ht="31" customHeight="1">
-      <c r="A7" s="1"/>
-      <c r="B7" s="3" t="s">
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A7" s="2"/>
+      <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <v>14.6</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="10">
         <f>$E$8*(D7/$D$8)^4</f>
         <v>941.40636852684645</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" ht="31" customHeight="1">
-      <c r="A8" s="1"/>
-      <c r="B8" s="6" t="s">
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A8" s="2"/>
+      <c r="B8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="5">
         <v>17.600000000000001</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="6">
         <v>1988</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" spans="1:9" ht="31" customHeight="1">
-      <c r="A9" s="1"/>
-      <c r="B9" s="3" t="s">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A9" s="2"/>
+      <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="5">
         <v>20.5</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="10">
         <f>$E$8*(D9/$D$8)^4</f>
         <v>3659.1579207191103</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" spans="1:9" ht="31" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="6" t="s">
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A10" s="2"/>
+      <c r="B10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="5">
         <v>16.2</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="11">
         <f>$E$11*(D10/$D$11)^4</f>
         <v>1429.0674406245321</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" spans="1:9" ht="31" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="3" t="s">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A11" s="2"/>
+      <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <v>19.399999999999999</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="6">
         <v>2939</v>
       </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="1:9" ht="31" customHeight="1">
-      <c r="A12" s="1"/>
-      <c r="B12" s="6" t="s">
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A12" s="2"/>
+      <c r="B12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="5">
         <v>22.1</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="11">
         <f>$E$11*(D12/$D$11)^4</f>
         <v>4949.5049290944507</v>
       </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9" ht="24" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9" ht="24" customHeight="1">
-      <c r="A14" s="1"/>
+      <c r="A14" s="2"/>
       <c r="B14" s="21" t="s">
         <v>13</v>
       </c>
@@ -2699,450 +2687,450 @@
       <c r="H14" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="I14" s="1"/>
+      <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:9" ht="24" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-    </row>
-    <row r="16" spans="1:9" ht="40" customHeight="1">
-      <c r="A16" s="1"/>
-      <c r="B16" s="2" t="s">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" spans="1:9" ht="39.950000000000003" customHeight="1">
+      <c r="A16" s="2"/>
+      <c r="B16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-    </row>
-    <row r="17" spans="1:9" ht="31" customHeight="1">
-      <c r="A17" s="1"/>
-      <c r="B17" s="3" t="s">
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A17" s="2"/>
+      <c r="B17" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="5">
         <v>127</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="5">
         <v>35</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="5">
         <v>163</v>
       </c>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" spans="1:9" ht="31" customHeight="1">
-      <c r="A18" s="1"/>
-      <c r="B18" s="6" t="s">
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A18" s="2"/>
+      <c r="B18" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="5">
         <v>127</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="5">
         <v>42</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="5">
         <v>163</v>
       </c>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" spans="1:9" ht="31" customHeight="1">
-      <c r="A19" s="1"/>
-      <c r="B19" s="3" t="s">
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A19" s="2"/>
+      <c r="B19" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="5">
         <v>127</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="5">
         <v>46</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="5">
         <v>163</v>
       </c>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="20" spans="1:9" ht="31" customHeight="1">
-      <c r="A20" s="1"/>
-      <c r="B20" s="6" t="s">
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A20" s="2"/>
+      <c r="B20" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="5">
         <v>136</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="5">
         <v>41</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="5">
         <v>154</v>
       </c>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" spans="1:9" ht="31" customHeight="1">
-      <c r="A21" s="1"/>
-      <c r="B21" s="3" t="s">
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A21" s="2"/>
+      <c r="B21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="5">
         <v>136</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="5">
         <v>49</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="5">
         <v>154</v>
       </c>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" spans="1:9" ht="31" customHeight="1">
-      <c r="A22" s="1"/>
-      <c r="B22" s="6" t="s">
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A22" s="2"/>
+      <c r="B22" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="5">
         <v>136</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="5">
         <v>54</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G22" s="5">
         <v>154</v>
       </c>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" spans="1:9" ht="31" customHeight="1">
-      <c r="A23" s="1"/>
-      <c r="B23" s="3" t="s">
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A23" s="2"/>
+      <c r="B23" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="5">
         <v>126</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="5">
         <v>32</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G23" s="5">
         <v>163</v>
       </c>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-    </row>
-    <row r="24" spans="1:9" ht="31" customHeight="1">
-      <c r="A24" s="1"/>
-      <c r="B24" s="6" t="s">
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A24" s="2"/>
+      <c r="B24" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="5">
         <v>126</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="5">
         <v>40</v>
       </c>
-      <c r="G24" s="4">
+      <c r="G24" s="5">
         <v>163</v>
       </c>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-    </row>
-    <row r="25" spans="1:9" ht="31" customHeight="1">
-      <c r="A25" s="1"/>
-      <c r="B25" s="3" t="s">
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A25" s="2"/>
+      <c r="B25" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="5">
         <v>126</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="5">
         <v>45</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G25" s="5">
         <v>163</v>
       </c>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-    </row>
-    <row r="26" spans="1:9" ht="31" customHeight="1">
-      <c r="A26" s="1"/>
-      <c r="B26" s="6" t="s">
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A26" s="2"/>
+      <c r="B26" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="5">
         <v>127</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="5">
         <v>39</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G26" s="5">
         <v>154</v>
       </c>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-    </row>
-    <row r="27" spans="1:9" ht="31" customHeight="1">
-      <c r="A27" s="1"/>
-      <c r="B27" s="3" t="s">
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+    </row>
+    <row r="27" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A27" s="2"/>
+      <c r="B27" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="5">
         <v>127</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="5">
         <v>47</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G27" s="5">
         <v>154</v>
       </c>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-    </row>
-    <row r="28" spans="1:9" ht="31" customHeight="1">
-      <c r="A28" s="1"/>
-      <c r="B28" s="6" t="s">
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+    </row>
+    <row r="28" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A28" s="2"/>
+      <c r="B28" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="5">
         <v>127</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="5">
         <v>51</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G28" s="5">
         <v>154</v>
       </c>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
     </row>
     <row r="29" spans="1:9" ht="24" customHeight="1">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
     </row>
     <row r="30" spans="1:9" ht="24" customHeight="1">
-      <c r="A30" s="1"/>
-      <c r="I30" s="1"/>
+      <c r="A30" s="2"/>
+      <c r="I30" s="2"/>
     </row>
     <row r="31" spans="1:9" ht="24" customHeight="1">
-      <c r="A31" s="1"/>
-      <c r="I31" s="1"/>
+      <c r="A31" s="2"/>
+      <c r="I31" s="2"/>
     </row>
     <row r="32" spans="1:9" ht="24" customHeight="1">
-      <c r="A32" s="1"/>
-      <c r="I32" s="1"/>
+      <c r="A32" s="2"/>
+      <c r="I32" s="2"/>
     </row>
     <row r="33" spans="1:9" ht="24" customHeight="1">
-      <c r="A33" s="1"/>
-      <c r="I33" s="1"/>
+      <c r="A33" s="2"/>
+      <c r="I33" s="2"/>
     </row>
     <row r="34" spans="1:9" ht="24" customHeight="1">
-      <c r="A34" s="1"/>
-      <c r="I34" s="1"/>
+      <c r="A34" s="2"/>
+      <c r="I34" s="2"/>
     </row>
     <row r="35" spans="1:9" ht="24" customHeight="1">
-      <c r="A35" s="1"/>
-      <c r="I35" s="1"/>
+      <c r="A35" s="2"/>
+      <c r="I35" s="2"/>
     </row>
     <row r="36" spans="1:9" ht="24" customHeight="1">
-      <c r="A36" s="1"/>
-      <c r="I36" s="1"/>
+      <c r="A36" s="2"/>
+      <c r="I36" s="2"/>
     </row>
     <row r="37" spans="1:9" ht="24" customHeight="1">
-      <c r="A37" s="1"/>
-      <c r="I37" s="1"/>
+      <c r="A37" s="2"/>
+      <c r="I37" s="2"/>
     </row>
     <row r="38" spans="1:9" ht="24" customHeight="1">
-      <c r="A38" s="1"/>
-      <c r="I38" s="1"/>
-    </row>
-    <row r="39" spans="1:9" ht="32" customHeight="1">
-      <c r="A39" s="1"/>
-      <c r="I39" s="1"/>
-    </row>
-    <row r="40" spans="1:9" ht="31" customHeight="1">
-      <c r="A40" s="1"/>
-      <c r="I40" s="1"/>
-    </row>
-    <row r="41" spans="1:9" ht="31" customHeight="1">
-      <c r="A41" s="1"/>
-      <c r="I41" s="1"/>
-    </row>
-    <row r="42" spans="1:9" ht="31" customHeight="1">
-      <c r="A42" s="1"/>
-      <c r="I42" s="1"/>
-    </row>
-    <row r="43" spans="1:9" ht="31" customHeight="1">
-      <c r="A43" s="1"/>
-      <c r="I43" s="1"/>
-    </row>
-    <row r="44" spans="1:9" ht="31" customHeight="1">
-      <c r="A44" s="1"/>
-      <c r="I44" s="1"/>
-    </row>
-    <row r="45" spans="1:9" ht="31" customHeight="1">
-      <c r="A45" s="1"/>
-      <c r="I45" s="1"/>
-    </row>
-    <row r="46" spans="1:9" ht="31" customHeight="1">
-      <c r="A46" s="1"/>
-      <c r="I46" s="1"/>
-    </row>
-    <row r="47" spans="1:9" ht="31" customHeight="1">
-      <c r="A47" s="1"/>
-      <c r="I47" s="1"/>
+      <c r="A38" s="2"/>
+      <c r="I38" s="2"/>
+    </row>
+    <row r="39" spans="1:9" ht="32.1" customHeight="1">
+      <c r="A39" s="2"/>
+      <c r="I39" s="2"/>
+    </row>
+    <row r="40" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A40" s="2"/>
+      <c r="I40" s="2"/>
+    </row>
+    <row r="41" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A41" s="2"/>
+      <c r="I41" s="2"/>
+    </row>
+    <row r="42" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A42" s="2"/>
+      <c r="I42" s="2"/>
+    </row>
+    <row r="43" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A43" s="2"/>
+      <c r="I43" s="2"/>
+    </row>
+    <row r="44" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A44" s="2"/>
+      <c r="I44" s="2"/>
+    </row>
+    <row r="45" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A45" s="2"/>
+      <c r="I45" s="2"/>
+    </row>
+    <row r="46" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A46" s="2"/>
+      <c r="I46" s="2"/>
+    </row>
+    <row r="47" spans="1:9" ht="30.95" customHeight="1">
+      <c r="A47" s="2"/>
+      <c r="I47" s="2"/>
     </row>
     <row r="48" spans="1:9" ht="24" customHeight="1">
-      <c r="A48" s="1"/>
-      <c r="I48" s="1"/>
+      <c r="A48" s="2"/>
+      <c r="I48" s="2"/>
     </row>
     <row r="49" spans="1:9" ht="24" customHeight="1">
-      <c r="A49" s="1"/>
-      <c r="I49" s="1"/>
+      <c r="A49" s="2"/>
+      <c r="I49" s="2"/>
     </row>
     <row r="50" spans="1:9" ht="24" customHeight="1">
-      <c r="A50" s="1"/>
-      <c r="I50" s="1"/>
+      <c r="A50" s="2"/>
+      <c r="I50" s="2"/>
     </row>
     <row r="51" spans="1:9" ht="24" customHeight="1">
-      <c r="A51" s="1"/>
-      <c r="I51" s="1"/>
+      <c r="A51" s="2"/>
+      <c r="I51" s="2"/>
     </row>
     <row r="52" spans="1:9" ht="24" customHeight="1">
-      <c r="A52" s="1"/>
-      <c r="I52" s="1"/>
+      <c r="A52" s="2"/>
+      <c r="I52" s="2"/>
     </row>
     <row r="53" spans="1:9" ht="24" customHeight="1">
-      <c r="A53" s="1"/>
-      <c r="I53" s="1"/>
+      <c r="A53" s="2"/>
+      <c r="I53" s="2"/>
     </row>
     <row r="54" spans="1:9" ht="24" customHeight="1">
-      <c r="A54" s="1"/>
-      <c r="I54" s="1"/>
+      <c r="A54" s="2"/>
+      <c r="I54" s="2"/>
     </row>
     <row r="55" spans="1:9" ht="24" customHeight="1">
-      <c r="A55" s="1"/>
-      <c r="I55" s="1"/>
+      <c r="A55" s="2"/>
+      <c r="I55" s="2"/>
     </row>
     <row r="56" spans="1:9" ht="24" customHeight="1">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:H3"/>
     <mergeCell ref="B14:H14"/>
   </mergeCells>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3153,11 +3141,11 @@
     <tabColor rgb="FF243B53"/>
   </sheetPr>
   <dimension ref="A1:Q157"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.75" customWidth="1"/>
-    <col min="2" max="2" width="18.1640625" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="2" max="2" width="18.125" customWidth="1"/>
+    <col min="3" max="3" width="9.625" customWidth="1"/>
     <col min="4" max="5" width="10.25" customWidth="1"/>
     <col min="6" max="8" width="12.25" customWidth="1"/>
     <col min="9" max="9" width="11.25" customWidth="1"/>
@@ -3172,24 +3160,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="12" customHeight="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-    </row>
-    <row r="2" spans="1:17" ht="35" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="17" t="s">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+    </row>
+    <row r="2" spans="1:17" ht="35.1" customHeight="1">
+      <c r="A2" s="2"/>
+      <c r="B2" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C2" s="18" t="s">
@@ -3225,10 +3213,10 @@
       <c r="M2" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="1"/>
+      <c r="N2" s="2"/>
     </row>
     <row r="3" spans="1:17" ht="12" customHeight="1">
-      <c r="A3" s="1"/>
+      <c r="A3" s="2"/>
       <c r="B3" s="18" t="s">
         <v>25</v>
       </c>
@@ -3265,2544 +3253,2544 @@
       <c r="M3" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="1"/>
+      <c r="N3" s="2"/>
     </row>
     <row r="4" spans="1:17" ht="24" customHeight="1">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="P4" s="7" t="s">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="P4" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="42" customHeight="1">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2" t="s">
+      <c r="A5" s="2"/>
+      <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="L5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="N5" s="1"/>
-      <c r="P5" s="2" t="s">
+      <c r="N5" s="2"/>
+      <c r="P5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="Q5" s="2" t="s">
+      <c r="Q5" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="31" customHeight="1">
-      <c r="A6" s="1"/>
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:17" ht="30.95" customHeight="1">
+      <c r="A6" s="2"/>
+      <c r="B6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="12">
         <f>Parameters!D7</f>
         <v>14.6</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="12">
         <f>Parameters!E17</f>
         <v>127</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="12">
         <f>Parameters!F17</f>
         <v>35</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="13">
         <f t="shared" ref="I6:I41" si="0">H6/G6</f>
         <v>0.27559055118110237</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="12">
         <f>Parameters!G17</f>
         <v>163</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="10">
         <f>Parameters!E7</f>
         <v>941.40636852684645</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="14">
         <f t="shared" ref="L6:L41" si="1">1000*K6*I6^2/J6^2</f>
         <v>2.6911045462579462</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="M6" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="N6" s="1"/>
-      <c r="P6" s="3" t="s">
+      <c r="N6" s="2"/>
+      <c r="P6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="Q6" s="9">
+      <c r="Q6" s="10">
         <v>223</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="31" customHeight="1">
-      <c r="A7" s="1"/>
-      <c r="B7" s="6" t="s">
+    <row r="7" spans="1:17" ht="30.95" customHeight="1">
+      <c r="A7" s="2"/>
+      <c r="B7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="15">
         <f>Parameters!D7</f>
         <v>14.6</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="15">
         <f>Parameters!E18</f>
         <v>127</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="15">
         <f>Parameters!F18</f>
         <v>42</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="16">
         <f t="shared" si="0"/>
         <v>0.33070866141732286</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="15">
         <f>Parameters!G18</f>
         <v>163</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="11">
         <f>Parameters!E7</f>
         <v>941.40636852684645</v>
       </c>
-      <c r="L7" s="16">
+      <c r="L7" s="17">
         <f t="shared" si="1"/>
         <v>3.8751905466114427</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="M7" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="N7" s="1"/>
-      <c r="P7" s="6" t="s">
+      <c r="N7" s="2"/>
+      <c r="P7" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="Q7" s="10">
+      <c r="Q7" s="11">
         <v>267</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="31" customHeight="1">
-      <c r="A8" s="1"/>
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="1:17" ht="30.95" customHeight="1">
+      <c r="A8" s="2"/>
+      <c r="B8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="12">
         <f>Parameters!D7</f>
         <v>14.6</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="12">
         <f>Parameters!E19</f>
         <v>127</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="12">
         <f>Parameters!F19</f>
         <v>46</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="13">
         <f t="shared" si="0"/>
         <v>0.36220472440944884</v>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="12">
         <f>Parameters!G19</f>
         <v>163</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="10">
         <f>Parameters!E7</f>
         <v>941.40636852684645</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="14">
         <f t="shared" si="1"/>
         <v>4.6484711999035211</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="M8" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="N8" s="1"/>
-      <c r="P8" s="3" t="s">
+      <c r="N8" s="2"/>
+      <c r="P8" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="Q8" s="9">
+      <c r="Q8" s="10">
         <v>236</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="31" customHeight="1">
-      <c r="A9" s="1"/>
-      <c r="B9" s="6" t="s">
+    <row r="9" spans="1:17" ht="30.95" customHeight="1">
+      <c r="A9" s="2"/>
+      <c r="B9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="15">
         <f>Parameters!D8</f>
         <v>17.600000000000001</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="15">
         <f>Parameters!E17</f>
         <v>127</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="15">
         <f>Parameters!F17</f>
         <v>35</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I9" s="16">
         <f t="shared" si="0"/>
         <v>0.27559055118110237</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="15">
         <f>Parameters!G17</f>
         <v>163</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="11">
         <f>Parameters!E8</f>
         <v>1988</v>
       </c>
-      <c r="L9" s="16">
+      <c r="L9" s="17">
         <f t="shared" si="1"/>
         <v>5.6828974360270976</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="M9" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="N9" s="1"/>
-      <c r="P9" s="6" t="s">
+      <c r="N9" s="2"/>
+      <c r="P9" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="Q9" s="10">
+      <c r="Q9" s="11">
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="31" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="1:17" ht="30.95" customHeight="1">
+      <c r="A10" s="2"/>
+      <c r="B10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="12">
         <f>Parameters!D8</f>
         <v>17.600000000000001</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="12">
         <f>Parameters!E18</f>
         <v>127</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="12">
         <f>Parameters!F18</f>
         <v>42</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="13">
         <f t="shared" si="0"/>
         <v>0.33070866141732286</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="12">
         <f>Parameters!G18</f>
         <v>163</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="10">
         <f>Parameters!E8</f>
         <v>1988</v>
       </c>
-      <c r="L10" s="13">
+      <c r="L10" s="14">
         <f t="shared" si="1"/>
         <v>8.1833723078790221</v>
       </c>
-      <c r="M10" s="3" t="s">
+      <c r="M10" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N10" s="1"/>
-      <c r="P10" s="3" t="s">
+      <c r="N10" s="2"/>
+      <c r="P10" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="Q10" s="9">
+      <c r="Q10" s="10">
         <v>279</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="31" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="6" t="s">
+    <row r="11" spans="1:17" ht="30.95" customHeight="1">
+      <c r="A11" s="2"/>
+      <c r="B11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="15">
         <f>Parameters!D8</f>
         <v>17.600000000000001</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="15">
         <f>Parameters!E19</f>
         <v>127</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="15">
         <f>Parameters!F19</f>
         <v>46</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I11" s="16">
         <f t="shared" si="0"/>
         <v>0.36220472440944884</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J11" s="15">
         <f>Parameters!G19</f>
         <v>163</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="11">
         <f>Parameters!E8</f>
         <v>1988</v>
       </c>
-      <c r="L11" s="16">
+      <c r="L11" s="17">
         <f t="shared" si="1"/>
         <v>9.8163354894966037</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="M11" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="N11" s="1"/>
-      <c r="P11" s="6" t="s">
+      <c r="N11" s="2"/>
+      <c r="P11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="Q11" s="10">
+      <c r="Q11" s="11">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="31" customHeight="1">
-      <c r="A12" s="1"/>
-      <c r="B12" s="3" t="s">
+    <row r="12" spans="1:17" ht="30.95" customHeight="1">
+      <c r="A12" s="2"/>
+      <c r="B12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="12">
         <f>Parameters!D9</f>
         <v>20.5</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="12">
         <f>Parameters!E17</f>
         <v>127</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="12">
         <f>Parameters!F17</f>
         <v>35</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="13">
         <f t="shared" si="0"/>
         <v>0.27559055118110237</v>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="12">
         <f>Parameters!G17</f>
         <v>163</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="10">
         <f>Parameters!E9</f>
         <v>3659.1579207191103</v>
       </c>
-      <c r="L12" s="13">
+      <c r="L12" s="14">
         <f t="shared" si="1"/>
         <v>10.460070002853563</v>
       </c>
-      <c r="M12" s="3" t="s">
+      <c r="M12" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="N12" s="1"/>
-      <c r="P12" s="3" t="s">
+      <c r="N12" s="2"/>
+      <c r="P12" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="Q12" s="9">
+      <c r="Q12" s="10">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="31" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="6" t="s">
+    <row r="13" spans="1:17" ht="30.95" customHeight="1">
+      <c r="A13" s="2"/>
+      <c r="B13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="15">
         <f>Parameters!D9</f>
         <v>20.5</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="15">
         <f>Parameters!E18</f>
         <v>127</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="15">
         <f>Parameters!F18</f>
         <v>42</v>
       </c>
-      <c r="I13" s="15">
+      <c r="I13" s="16">
         <f t="shared" si="0"/>
         <v>0.33070866141732286</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="15">
         <f>Parameters!G18</f>
         <v>163</v>
       </c>
-      <c r="K13" s="10">
+      <c r="K13" s="11">
         <f>Parameters!E9</f>
         <v>3659.1579207191103</v>
       </c>
-      <c r="L13" s="16">
+      <c r="L13" s="17">
         <f t="shared" si="1"/>
         <v>15.062500804109128</v>
       </c>
-      <c r="M13" s="6" t="s">
+      <c r="M13" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="N13" s="1"/>
-      <c r="P13" s="6" t="s">
+      <c r="N13" s="2"/>
+      <c r="P13" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="Q13" s="10">
+      <c r="Q13" s="11">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="31" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="3" t="s">
+    <row r="14" spans="1:17" ht="30.95" customHeight="1">
+      <c r="A14" s="2"/>
+      <c r="B14" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="12">
         <f>Parameters!D9</f>
         <v>20.5</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="12">
         <f>Parameters!E19</f>
         <v>127</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="12">
         <f>Parameters!F19</f>
         <v>46</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="13">
         <f t="shared" si="0"/>
         <v>0.36220472440944884</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="12">
         <f>Parameters!G19</f>
         <v>163</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="10">
         <f>Parameters!E9</f>
         <v>3659.1579207191103</v>
       </c>
-      <c r="L14" s="13">
+      <c r="L14" s="14">
         <f t="shared" si="1"/>
         <v>18.068169898806641</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="M14" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="N14" s="1"/>
-    </row>
-    <row r="15" spans="1:17" ht="31" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="6" t="s">
+      <c r="N14" s="2"/>
+    </row>
+    <row r="15" spans="1:17" ht="30.95" customHeight="1">
+      <c r="A15" s="2"/>
+      <c r="B15" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="15">
         <f>Parameters!D10</f>
-        <v>16.199999999999999</v>
-      </c>
-      <c r="G15" s="14">
+        <v>16.2</v>
+      </c>
+      <c r="G15" s="15">
         <f>Parameters!E20</f>
         <v>136</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="15">
         <f>Parameters!F20</f>
         <v>41</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="16">
         <f t="shared" si="0"/>
         <v>0.3014705882352941</v>
       </c>
-      <c r="J15" s="14">
+      <c r="J15" s="15">
         <f>Parameters!G20</f>
         <v>154</v>
       </c>
-      <c r="K15" s="10">
+      <c r="K15" s="11">
         <f>Parameters!E10</f>
         <v>1429.0674406245321</v>
       </c>
-      <c r="L15" s="16">
+      <c r="L15" s="17">
         <f t="shared" si="1"/>
         <v>5.4764758837643539</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="M15" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="N15" s="1"/>
-    </row>
-    <row r="16" spans="1:17" ht="31" customHeight="1">
-      <c r="A16" s="1"/>
-      <c r="B16" s="3" t="s">
+      <c r="N15" s="2"/>
+    </row>
+    <row r="16" spans="1:17" ht="30.95" customHeight="1">
+      <c r="A16" s="2"/>
+      <c r="B16" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="12">
         <f>Parameters!D10</f>
-        <v>16.199999999999999</v>
-      </c>
-      <c r="G16" s="11">
+        <v>16.2</v>
+      </c>
+      <c r="G16" s="12">
         <f>Parameters!E21</f>
         <v>136</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="12">
         <f>Parameters!F21</f>
         <v>49</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="13">
         <f t="shared" si="0"/>
         <v>0.36029411764705882</v>
       </c>
-      <c r="J16" s="11">
+      <c r="J16" s="12">
         <f>Parameters!G21</f>
         <v>154</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="10">
         <f>Parameters!E10</f>
         <v>1429.0674406245321</v>
       </c>
-      <c r="L16" s="13">
+      <c r="L16" s="14">
         <f t="shared" si="1"/>
         <v>7.8221407477205336</v>
       </c>
-      <c r="M16" s="3" t="s">
+      <c r="M16" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="N16" s="1"/>
-    </row>
-    <row r="17" spans="1:14" ht="31" customHeight="1">
-      <c r="A17" s="1"/>
-      <c r="B17" s="6" t="s">
+      <c r="N16" s="2"/>
+    </row>
+    <row r="17" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A17" s="2"/>
+      <c r="B17" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="15">
         <f>Parameters!D10</f>
-        <v>16.199999999999999</v>
-      </c>
-      <c r="G17" s="14">
+        <v>16.2</v>
+      </c>
+      <c r="G17" s="15">
         <f>Parameters!E22</f>
         <v>136</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="15">
         <f>Parameters!F22</f>
         <v>54</v>
       </c>
-      <c r="I17" s="15">
+      <c r="I17" s="16">
         <f t="shared" si="0"/>
         <v>0.39705882352941174</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="15">
         <f>Parameters!G22</f>
         <v>154</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K17" s="11">
         <f>Parameters!E10</f>
         <v>1429.0674406245321</v>
       </c>
-      <c r="L17" s="16">
+      <c r="L17" s="17">
         <f t="shared" si="1"/>
         <v>9.4999426990225206</v>
       </c>
-      <c r="M17" s="6" t="s">
+      <c r="M17" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="N17" s="1"/>
-    </row>
-    <row r="18" spans="1:14" ht="31" customHeight="1">
-      <c r="A18" s="1"/>
-      <c r="B18" s="3" t="s">
+      <c r="N17" s="2"/>
+    </row>
+    <row r="18" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A18" s="2"/>
+      <c r="B18" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="12">
         <f>Parameters!D11</f>
         <v>19.399999999999999</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="12">
         <f>Parameters!E20</f>
         <v>136</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="12">
         <f>Parameters!F20</f>
         <v>41</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="13">
         <f t="shared" si="0"/>
         <v>0.3014705882352941</v>
       </c>
-      <c r="J18" s="11">
+      <c r="J18" s="12">
         <f>Parameters!G20</f>
         <v>154</v>
       </c>
-      <c r="K18" s="9">
+      <c r="K18" s="10">
         <f>Parameters!E11</f>
         <v>2939</v>
       </c>
-      <c r="L18" s="13">
+      <c r="L18" s="14">
         <f t="shared" si="1"/>
         <v>11.262843281454536</v>
       </c>
-      <c r="M18" s="3" t="s">
+      <c r="M18" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="N18" s="1"/>
-    </row>
-    <row r="19" spans="1:14" ht="31" customHeight="1">
-      <c r="A19" s="1"/>
-      <c r="B19" s="6" t="s">
+      <c r="N18" s="2"/>
+    </row>
+    <row r="19" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A19" s="2"/>
+      <c r="B19" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="15">
         <f>Parameters!D11</f>
         <v>19.399999999999999</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="15">
         <f>Parameters!E21</f>
         <v>136</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="15">
         <f>Parameters!F21</f>
         <v>49</v>
       </c>
-      <c r="I19" s="15">
+      <c r="I19" s="16">
         <f t="shared" si="0"/>
         <v>0.36029411764705882</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19" s="15">
         <f>Parameters!G21</f>
         <v>154</v>
       </c>
-      <c r="K19" s="10">
+      <c r="K19" s="11">
         <f>Parameters!E11</f>
         <v>2939</v>
       </c>
-      <c r="L19" s="16">
+      <c r="L19" s="17">
         <f t="shared" si="1"/>
         <v>16.086904651262547</v>
       </c>
-      <c r="M19" s="6" t="s">
+      <c r="M19" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="N19" s="1"/>
-    </row>
-    <row r="20" spans="1:14" ht="31" customHeight="1">
-      <c r="A20" s="1"/>
-      <c r="B20" s="3" t="s">
+      <c r="N19" s="2"/>
+    </row>
+    <row r="20" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A20" s="2"/>
+      <c r="B20" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="12">
         <f>Parameters!D11</f>
         <v>19.399999999999999</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="12">
         <f>Parameters!E22</f>
         <v>136</v>
       </c>
-      <c r="H20" s="11">
+      <c r="H20" s="12">
         <f>Parameters!F22</f>
         <v>54</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="13">
         <f t="shared" si="0"/>
         <v>0.39705882352941174</v>
       </c>
-      <c r="J20" s="11">
+      <c r="J20" s="12">
         <f>Parameters!G22</f>
         <v>154</v>
       </c>
-      <c r="K20" s="9">
+      <c r="K20" s="10">
         <f>Parameters!E11</f>
         <v>2939</v>
       </c>
-      <c r="L20" s="13">
+      <c r="L20" s="14">
         <f t="shared" si="1"/>
         <v>19.537448547722441</v>
       </c>
-      <c r="M20" s="3" t="s">
+      <c r="M20" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="N20" s="1"/>
-    </row>
-    <row r="21" spans="1:14" ht="31" customHeight="1">
-      <c r="A21" s="1"/>
-      <c r="B21" s="6" t="s">
+      <c r="N20" s="2"/>
+    </row>
+    <row r="21" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A21" s="2"/>
+      <c r="B21" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="15">
         <f>Parameters!D12</f>
-        <v>22.100000000000001</v>
-      </c>
-      <c r="G21" s="14">
+        <v>22.1</v>
+      </c>
+      <c r="G21" s="15">
         <f>Parameters!E20</f>
         <v>136</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="15">
         <f>Parameters!F20</f>
         <v>41</v>
       </c>
-      <c r="I21" s="15">
+      <c r="I21" s="16">
         <f t="shared" si="0"/>
         <v>0.3014705882352941</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="15">
         <f>Parameters!G20</f>
         <v>154</v>
       </c>
-      <c r="K21" s="10">
+      <c r="K21" s="11">
         <f>Parameters!E12</f>
         <v>4949.5049290944507</v>
       </c>
-      <c r="L21" s="16">
+      <c r="L21" s="17">
         <f t="shared" si="1"/>
         <v>18.967505388627945</v>
       </c>
-      <c r="M21" s="6" t="s">
+      <c r="M21" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="N21" s="1"/>
-    </row>
-    <row r="22" spans="1:14" ht="31" customHeight="1">
-      <c r="A22" s="1"/>
-      <c r="B22" s="3" t="s">
+      <c r="N21" s="2"/>
+    </row>
+    <row r="22" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A22" s="2"/>
+      <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="12">
         <f>Parameters!D12</f>
-        <v>22.100000000000001</v>
-      </c>
-      <c r="G22" s="11">
+        <v>22.1</v>
+      </c>
+      <c r="G22" s="12">
         <f>Parameters!E21</f>
         <v>136</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="12">
         <f>Parameters!F21</f>
         <v>49</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="13">
         <f t="shared" si="0"/>
         <v>0.36029411764705882</v>
       </c>
-      <c r="J22" s="11">
+      <c r="J22" s="12">
         <f>Parameters!G21</f>
         <v>154</v>
       </c>
-      <c r="K22" s="9">
+      <c r="K22" s="10">
         <f>Parameters!E12</f>
         <v>4949.5049290944507</v>
       </c>
-      <c r="L22" s="13">
+      <c r="L22" s="14">
         <f t="shared" si="1"/>
         <v>27.091600498569726</v>
       </c>
-      <c r="M22" s="3" t="s">
+      <c r="M22" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="N22" s="1"/>
-    </row>
-    <row r="23" spans="1:14" ht="31" customHeight="1">
-      <c r="A23" s="1"/>
-      <c r="B23" s="6" t="s">
+      <c r="N22" s="2"/>
+    </row>
+    <row r="23" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A23" s="2"/>
+      <c r="B23" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F23" s="14">
+      <c r="F23" s="15">
         <f>Parameters!D12</f>
-        <v>22.100000000000001</v>
-      </c>
-      <c r="G23" s="14">
+        <v>22.1</v>
+      </c>
+      <c r="G23" s="15">
         <f>Parameters!E22</f>
         <v>136</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H23" s="15">
         <f>Parameters!F22</f>
         <v>54</v>
       </c>
-      <c r="I23" s="15">
+      <c r="I23" s="16">
         <f t="shared" si="0"/>
         <v>0.39705882352941174</v>
       </c>
-      <c r="J23" s="14">
+      <c r="J23" s="15">
         <f>Parameters!G22</f>
         <v>154</v>
       </c>
-      <c r="K23" s="10">
+      <c r="K23" s="11">
         <f>Parameters!E12</f>
         <v>4949.5049290944507</v>
       </c>
-      <c r="L23" s="16">
+      <c r="L23" s="17">
         <f t="shared" si="1"/>
         <v>32.902585195264187</v>
       </c>
-      <c r="M23" s="6" t="s">
+      <c r="M23" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="N23" s="1"/>
-    </row>
-    <row r="24" spans="1:14" ht="31" customHeight="1">
-      <c r="A24" s="1"/>
-      <c r="B24" s="3" t="s">
+      <c r="N23" s="2"/>
+    </row>
+    <row r="24" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A24" s="2"/>
+      <c r="B24" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="12">
         <f>Parameters!D7</f>
         <v>14.6</v>
       </c>
-      <c r="G24" s="11">
+      <c r="G24" s="12">
         <f>Parameters!E23</f>
         <v>126</v>
       </c>
-      <c r="H24" s="11">
+      <c r="H24" s="12">
         <f>Parameters!F23</f>
         <v>32</v>
       </c>
-      <c r="I24" s="12">
+      <c r="I24" s="13">
         <f t="shared" si="0"/>
         <v>0.25396825396825395</v>
       </c>
-      <c r="J24" s="11">
+      <c r="J24" s="12">
         <f>Parameters!G23</f>
         <v>163</v>
       </c>
-      <c r="K24" s="9">
+      <c r="K24" s="10">
         <f>Parameters!E7</f>
         <v>941.40636852684645</v>
       </c>
-      <c r="L24" s="13">
+      <c r="L24" s="14">
         <f t="shared" si="1"/>
         <v>2.2853924564370129</v>
       </c>
-      <c r="M24" s="3" t="s">
+      <c r="M24" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="N24" s="1"/>
-    </row>
-    <row r="25" spans="1:14" ht="31" customHeight="1">
-      <c r="A25" s="1"/>
-      <c r="B25" s="6" t="s">
+      <c r="N24" s="2"/>
+    </row>
+    <row r="25" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A25" s="2"/>
+      <c r="B25" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F25" s="15">
         <f>Parameters!D7</f>
         <v>14.6</v>
       </c>
-      <c r="G25" s="14">
+      <c r="G25" s="15">
         <f>Parameters!E24</f>
         <v>126</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="15">
         <f>Parameters!F24</f>
         <v>40</v>
       </c>
-      <c r="I25" s="15">
+      <c r="I25" s="16">
         <f t="shared" si="0"/>
         <v>0.31746031746031744</v>
       </c>
-      <c r="J25" s="14">
+      <c r="J25" s="15">
         <f>Parameters!G24</f>
         <v>163</v>
       </c>
-      <c r="K25" s="10">
+      <c r="K25" s="11">
         <f>Parameters!E7</f>
         <v>941.40636852684645</v>
       </c>
-      <c r="L25" s="16">
+      <c r="L25" s="17">
         <f t="shared" si="1"/>
         <v>3.5709257131828327</v>
       </c>
-      <c r="M25" s="6" t="s">
+      <c r="M25" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="N25" s="1"/>
-    </row>
-    <row r="26" spans="1:14" ht="31" customHeight="1">
-      <c r="A26" s="1"/>
-      <c r="B26" s="3" t="s">
+      <c r="N25" s="2"/>
+    </row>
+    <row r="26" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A26" s="2"/>
+      <c r="B26" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F26" s="11">
+      <c r="F26" s="12">
         <f>Parameters!D7</f>
         <v>14.6</v>
       </c>
-      <c r="G26" s="11">
+      <c r="G26" s="12">
         <f>Parameters!E25</f>
         <v>126</v>
       </c>
-      <c r="H26" s="11">
+      <c r="H26" s="12">
         <f>Parameters!F25</f>
         <v>45</v>
       </c>
-      <c r="I26" s="12">
+      <c r="I26" s="13">
         <f t="shared" si="0"/>
         <v>0.35714285714285715</v>
       </c>
-      <c r="J26" s="11">
+      <c r="J26" s="12">
         <f>Parameters!G25</f>
         <v>163</v>
       </c>
-      <c r="K26" s="9">
+      <c r="K26" s="10">
         <f>Parameters!E7</f>
         <v>941.40636852684645</v>
       </c>
-      <c r="L26" s="13">
+      <c r="L26" s="14">
         <f t="shared" si="1"/>
         <v>4.5194528557470228</v>
       </c>
-      <c r="M26" s="3" t="s">
+      <c r="M26" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="N26" s="1"/>
-    </row>
-    <row r="27" spans="1:14" ht="31" customHeight="1">
-      <c r="A27" s="1"/>
-      <c r="B27" s="6" t="s">
+      <c r="N26" s="2"/>
+    </row>
+    <row r="27" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A27" s="2"/>
+      <c r="B27" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="14">
+      <c r="F27" s="15">
         <f>Parameters!D8</f>
         <v>17.600000000000001</v>
       </c>
-      <c r="G27" s="14">
+      <c r="G27" s="15">
         <f>Parameters!E23</f>
         <v>126</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="15">
         <f>Parameters!F23</f>
         <v>32</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="16">
         <f t="shared" si="0"/>
         <v>0.25396825396825395</v>
       </c>
-      <c r="J27" s="14">
+      <c r="J27" s="15">
         <f>Parameters!G23</f>
         <v>163</v>
       </c>
-      <c r="K27" s="10">
+      <c r="K27" s="11">
         <f>Parameters!E8</f>
         <v>1988</v>
       </c>
-      <c r="L27" s="16">
+      <c r="L27" s="17">
         <f t="shared" si="1"/>
         <v>4.8261413511642468</v>
       </c>
-      <c r="M27" s="6" t="s">
+      <c r="M27" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="N27" s="1"/>
-    </row>
-    <row r="28" spans="1:14" ht="31" customHeight="1">
-      <c r="A28" s="1"/>
-      <c r="B28" s="3" t="s">
+      <c r="N27" s="2"/>
+    </row>
+    <row r="28" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A28" s="2"/>
+      <c r="B28" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F28" s="12">
         <f>Parameters!D8</f>
         <v>17.600000000000001</v>
       </c>
-      <c r="G28" s="11">
+      <c r="G28" s="12">
         <f>Parameters!E24</f>
         <v>126</v>
       </c>
-      <c r="H28" s="11">
+      <c r="H28" s="12">
         <f>Parameters!F24</f>
         <v>40</v>
       </c>
-      <c r="I28" s="12">
+      <c r="I28" s="13">
         <f t="shared" si="0"/>
         <v>0.31746031746031744</v>
       </c>
-      <c r="J28" s="11">
+      <c r="J28" s="12">
         <f>Parameters!G24</f>
         <v>163</v>
       </c>
-      <c r="K28" s="9">
+      <c r="K28" s="10">
         <f>Parameters!E8</f>
         <v>1988</v>
       </c>
-      <c r="L28" s="13">
+      <c r="L28" s="14">
         <f t="shared" si="1"/>
         <v>7.5408458611941356</v>
       </c>
-      <c r="M28" s="3" t="s">
+      <c r="M28" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="N28" s="1"/>
-    </row>
-    <row r="29" spans="1:14" ht="31" customHeight="1">
-      <c r="A29" s="1"/>
-      <c r="B29" s="6" t="s">
+      <c r="N28" s="2"/>
+    </row>
+    <row r="29" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A29" s="2"/>
+      <c r="B29" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F29" s="14">
+      <c r="F29" s="15">
         <f>Parameters!D8</f>
         <v>17.600000000000001</v>
       </c>
-      <c r="G29" s="14">
+      <c r="G29" s="15">
         <f>Parameters!E25</f>
         <v>126</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H29" s="15">
         <f>Parameters!F25</f>
         <v>45</v>
       </c>
-      <c r="I29" s="15">
+      <c r="I29" s="16">
         <f t="shared" si="0"/>
         <v>0.35714285714285715</v>
       </c>
-      <c r="J29" s="14">
+      <c r="J29" s="15">
         <f>Parameters!G25</f>
         <v>163</v>
       </c>
-      <c r="K29" s="10">
+      <c r="K29" s="11">
         <f>Parameters!E8</f>
         <v>1988</v>
       </c>
-      <c r="L29" s="16">
+      <c r="L29" s="17">
         <f t="shared" si="1"/>
         <v>9.54388304307383</v>
       </c>
-      <c r="M29" s="6" t="s">
+      <c r="M29" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="N29" s="1"/>
-    </row>
-    <row r="30" spans="1:14" ht="31" customHeight="1">
-      <c r="A30" s="1"/>
-      <c r="B30" s="3" t="s">
+      <c r="N29" s="2"/>
+    </row>
+    <row r="30" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A30" s="2"/>
+      <c r="B30" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="12">
         <f>Parameters!D9</f>
         <v>20.5</v>
       </c>
-      <c r="G30" s="11">
+      <c r="G30" s="12">
         <f>Parameters!E23</f>
         <v>126</v>
       </c>
-      <c r="H30" s="11">
+      <c r="H30" s="12">
         <f>Parameters!F23</f>
         <v>32</v>
       </c>
-      <c r="I30" s="12">
+      <c r="I30" s="13">
         <f t="shared" si="0"/>
         <v>0.25396825396825395</v>
       </c>
-      <c r="J30" s="11">
+      <c r="J30" s="12">
         <f>Parameters!G23</f>
         <v>163</v>
       </c>
-      <c r="K30" s="9">
+      <c r="K30" s="10">
         <f>Parameters!E9</f>
         <v>3659.1579207191103</v>
       </c>
-      <c r="L30" s="13">
+      <c r="L30" s="14">
         <f t="shared" si="1"/>
         <v>8.883105307657285</v>
       </c>
-      <c r="M30" s="3" t="s">
+      <c r="M30" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="N30" s="1"/>
-    </row>
-    <row r="31" spans="1:14" ht="31" customHeight="1">
-      <c r="A31" s="1"/>
-      <c r="B31" s="6" t="s">
+      <c r="N30" s="2"/>
+    </row>
+    <row r="31" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A31" s="2"/>
+      <c r="B31" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="15">
         <f>Parameters!D9</f>
         <v>20.5</v>
       </c>
-      <c r="G31" s="14">
+      <c r="G31" s="15">
         <f>Parameters!E24</f>
         <v>126</v>
       </c>
-      <c r="H31" s="14">
+      <c r="H31" s="15">
         <f>Parameters!F24</f>
         <v>40</v>
       </c>
-      <c r="I31" s="15">
+      <c r="I31" s="16">
         <f t="shared" si="0"/>
         <v>0.31746031746031744</v>
       </c>
-      <c r="J31" s="14">
+      <c r="J31" s="15">
         <f>Parameters!G24</f>
         <v>163</v>
       </c>
-      <c r="K31" s="10">
+      <c r="K31" s="11">
         <f>Parameters!E9</f>
         <v>3659.1579207191103</v>
       </c>
-      <c r="L31" s="16">
+      <c r="L31" s="17">
         <f t="shared" si="1"/>
         <v>13.879852043214509</v>
       </c>
-      <c r="M31" s="6" t="s">
+      <c r="M31" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="N31" s="1"/>
-    </row>
-    <row r="32" spans="1:14" ht="31" customHeight="1">
-      <c r="A32" s="1"/>
-      <c r="B32" s="3" t="s">
+      <c r="N31" s="2"/>
+    </row>
+    <row r="32" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A32" s="2"/>
+      <c r="B32" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F32" s="11">
+      <c r="F32" s="12">
         <f>Parameters!D9</f>
         <v>20.5</v>
       </c>
-      <c r="G32" s="11">
+      <c r="G32" s="12">
         <f>Parameters!E25</f>
         <v>126</v>
       </c>
-      <c r="H32" s="11">
+      <c r="H32" s="12">
         <f>Parameters!F25</f>
         <v>45</v>
       </c>
-      <c r="I32" s="12">
+      <c r="I32" s="13">
         <f t="shared" si="0"/>
         <v>0.35714285714285715</v>
       </c>
-      <c r="J32" s="11">
+      <c r="J32" s="12">
         <f>Parameters!G25</f>
         <v>163</v>
       </c>
-      <c r="K32" s="9">
+      <c r="K32" s="10">
         <f>Parameters!E9</f>
         <v>3659.1579207191103</v>
       </c>
-      <c r="L32" s="13">
+      <c r="L32" s="14">
         <f t="shared" si="1"/>
         <v>17.566687742193366</v>
       </c>
-      <c r="M32" s="3" t="s">
+      <c r="M32" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="N32" s="1"/>
-    </row>
-    <row r="33" spans="1:14" ht="31" customHeight="1">
-      <c r="A33" s="1"/>
-      <c r="B33" s="6" t="s">
+      <c r="N32" s="2"/>
+    </row>
+    <row r="33" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A33" s="2"/>
+      <c r="B33" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="15">
         <f>Parameters!D10</f>
-        <v>16.199999999999999</v>
-      </c>
-      <c r="G33" s="14">
+        <v>16.2</v>
+      </c>
+      <c r="G33" s="15">
         <f>Parameters!E26</f>
         <v>127</v>
       </c>
-      <c r="H33" s="14">
+      <c r="H33" s="15">
         <f>Parameters!F26</f>
         <v>39</v>
       </c>
-      <c r="I33" s="15">
+      <c r="I33" s="16">
         <f t="shared" si="0"/>
         <v>0.30708661417322836</v>
       </c>
-      <c r="J33" s="14">
+      <c r="J33" s="15">
         <f>Parameters!G26</f>
         <v>154</v>
       </c>
-      <c r="K33" s="10">
+      <c r="K33" s="11">
         <f>Parameters!E10</f>
         <v>1429.0674406245321</v>
       </c>
-      <c r="L33" s="16">
+      <c r="L33" s="17">
         <f t="shared" si="1"/>
         <v>5.6824163988087895</v>
       </c>
-      <c r="M33" s="6" t="s">
+      <c r="M33" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="N33" s="1"/>
-    </row>
-    <row r="34" spans="1:14" ht="31" customHeight="1">
-      <c r="A34" s="1"/>
-      <c r="B34" s="3" t="s">
+      <c r="N33" s="2"/>
+    </row>
+    <row r="34" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A34" s="2"/>
+      <c r="B34" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F34" s="11">
+      <c r="F34" s="12">
         <f>Parameters!D10</f>
-        <v>16.199999999999999</v>
-      </c>
-      <c r="G34" s="11">
+        <v>16.2</v>
+      </c>
+      <c r="G34" s="12">
         <f>Parameters!E27</f>
         <v>127</v>
       </c>
-      <c r="H34" s="11">
+      <c r="H34" s="12">
         <f>Parameters!F27</f>
         <v>47</v>
       </c>
-      <c r="I34" s="12">
+      <c r="I34" s="13">
         <f t="shared" si="0"/>
         <v>0.37007874015748032</v>
       </c>
-      <c r="J34" s="11">
+      <c r="J34" s="12">
         <f>Parameters!G27</f>
         <v>154</v>
       </c>
-      <c r="K34" s="9">
+      <c r="K34" s="10">
         <f>Parameters!E10</f>
         <v>1429.0674406245321</v>
       </c>
-      <c r="L34" s="13">
+      <c r="L34" s="14">
         <f t="shared" si="1"/>
         <v>8.252766485843928</v>
       </c>
-      <c r="M34" s="3" t="s">
+      <c r="M34" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="N34" s="1"/>
-    </row>
-    <row r="35" spans="1:14" ht="31" customHeight="1">
-      <c r="A35" s="1"/>
-      <c r="B35" s="6" t="s">
+      <c r="N34" s="2"/>
+    </row>
+    <row r="35" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A35" s="2"/>
+      <c r="B35" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="15">
         <f>Parameters!D10</f>
-        <v>16.199999999999999</v>
-      </c>
-      <c r="G35" s="14">
+        <v>16.2</v>
+      </c>
+      <c r="G35" s="15">
         <f>Parameters!E28</f>
         <v>127</v>
       </c>
-      <c r="H35" s="14">
+      <c r="H35" s="15">
         <f>Parameters!F28</f>
         <v>51</v>
       </c>
-      <c r="I35" s="15">
+      <c r="I35" s="16">
         <f t="shared" si="0"/>
         <v>0.40157480314960631</v>
       </c>
-      <c r="J35" s="14">
+      <c r="J35" s="15">
         <f>Parameters!G28</f>
         <v>154</v>
       </c>
-      <c r="K35" s="10">
+      <c r="K35" s="11">
         <f>Parameters!E10</f>
         <v>1429.0674406245321</v>
       </c>
-      <c r="L35" s="16">
+      <c r="L35" s="17">
         <f t="shared" si="1"/>
         <v>9.7172682796197645</v>
       </c>
-      <c r="M35" s="6" t="s">
+      <c r="M35" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="N35" s="1"/>
-    </row>
-    <row r="36" spans="1:14" ht="31" customHeight="1">
-      <c r="A36" s="1"/>
-      <c r="B36" s="3" t="s">
+      <c r="N35" s="2"/>
+    </row>
+    <row r="36" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A36" s="2"/>
+      <c r="B36" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F36" s="11">
+      <c r="F36" s="12">
         <f>Parameters!D11</f>
         <v>19.399999999999999</v>
       </c>
-      <c r="G36" s="11">
+      <c r="G36" s="12">
         <f>Parameters!E26</f>
         <v>127</v>
       </c>
-      <c r="H36" s="11">
+      <c r="H36" s="12">
         <f>Parameters!F26</f>
         <v>39</v>
       </c>
-      <c r="I36" s="12">
+      <c r="I36" s="13">
         <f t="shared" si="0"/>
         <v>0.30708661417322836</v>
       </c>
-      <c r="J36" s="11">
+      <c r="J36" s="12">
         <f>Parameters!G26</f>
         <v>154</v>
       </c>
-      <c r="K36" s="9">
+      <c r="K36" s="10">
         <f>Parameters!E11</f>
         <v>2939</v>
       </c>
-      <c r="L36" s="13">
+      <c r="L36" s="14">
         <f t="shared" si="1"/>
         <v>11.686377648349833</v>
       </c>
-      <c r="M36" s="3" t="s">
+      <c r="M36" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="N36" s="1"/>
-    </row>
-    <row r="37" spans="1:14" ht="31" customHeight="1">
-      <c r="A37" s="1"/>
-      <c r="B37" s="6" t="s">
+      <c r="N36" s="2"/>
+    </row>
+    <row r="37" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A37" s="2"/>
+      <c r="B37" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E37" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F37" s="14">
+      <c r="F37" s="15">
         <f>Parameters!D11</f>
         <v>19.399999999999999</v>
       </c>
-      <c r="G37" s="14">
+      <c r="G37" s="15">
         <f>Parameters!E27</f>
         <v>127</v>
       </c>
-      <c r="H37" s="14">
+      <c r="H37" s="15">
         <f>Parameters!F27</f>
         <v>47</v>
       </c>
-      <c r="I37" s="15">
+      <c r="I37" s="16">
         <f t="shared" si="0"/>
         <v>0.37007874015748032</v>
       </c>
-      <c r="J37" s="14">
+      <c r="J37" s="15">
         <f>Parameters!G27</f>
         <v>154</v>
       </c>
-      <c r="K37" s="10">
+      <c r="K37" s="11">
         <f>Parameters!E11</f>
         <v>2939</v>
       </c>
-      <c r="L37" s="16">
+      <c r="L37" s="17">
         <f t="shared" si="1"/>
         <v>16.972523487971586</v>
       </c>
-      <c r="M37" s="6" t="s">
+      <c r="M37" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N37" s="1"/>
-    </row>
-    <row r="38" spans="1:14" ht="31" customHeight="1">
-      <c r="A38" s="1"/>
-      <c r="B38" s="3" t="s">
+      <c r="N37" s="2"/>
+    </row>
+    <row r="38" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A38" s="2"/>
+      <c r="B38" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F38" s="11">
+      <c r="F38" s="12">
         <f>Parameters!D11</f>
         <v>19.399999999999999</v>
       </c>
-      <c r="G38" s="11">
+      <c r="G38" s="12">
         <f>Parameters!E28</f>
         <v>127</v>
       </c>
-      <c r="H38" s="11">
+      <c r="H38" s="12">
         <f>Parameters!F28</f>
         <v>51</v>
       </c>
-      <c r="I38" s="12">
+      <c r="I38" s="13">
         <f t="shared" si="0"/>
         <v>0.40157480314960631</v>
       </c>
-      <c r="J38" s="11">
+      <c r="J38" s="12">
         <f>Parameters!G28</f>
         <v>154</v>
       </c>
-      <c r="K38" s="9">
+      <c r="K38" s="10">
         <f>Parameters!E11</f>
         <v>2939</v>
       </c>
-      <c r="L38" s="13">
+      <c r="L38" s="14">
         <f t="shared" si="1"/>
         <v>19.984397280314212</v>
       </c>
-      <c r="M38" s="3" t="s">
+      <c r="M38" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="N38" s="1"/>
-    </row>
-    <row r="39" spans="1:14" ht="31" customHeight="1">
-      <c r="A39" s="1"/>
-      <c r="B39" s="6" t="s">
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A39" s="2"/>
+      <c r="B39" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F39" s="14">
+      <c r="F39" s="15">
         <f>Parameters!D12</f>
-        <v>22.100000000000001</v>
-      </c>
-      <c r="G39" s="14">
+        <v>22.1</v>
+      </c>
+      <c r="G39" s="15">
         <f>Parameters!E26</f>
         <v>127</v>
       </c>
-      <c r="H39" s="14">
+      <c r="H39" s="15">
         <f>Parameters!F26</f>
         <v>39</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="16">
         <f t="shared" si="0"/>
         <v>0.30708661417322836</v>
       </c>
-      <c r="J39" s="14">
+      <c r="J39" s="15">
         <f>Parameters!G26</f>
         <v>154</v>
       </c>
-      <c r="K39" s="10">
+      <c r="K39" s="11">
         <f>Parameters!E12</f>
         <v>4949.5049290944507</v>
       </c>
-      <c r="L39" s="16">
+      <c r="L39" s="17">
         <f t="shared" si="1"/>
         <v>19.680770253067951</v>
       </c>
-      <c r="M39" s="6" t="s">
+      <c r="M39" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="N39" s="1"/>
-    </row>
-    <row r="40" spans="1:14" ht="31" customHeight="1">
-      <c r="A40" s="1"/>
-      <c r="B40" s="3" t="s">
+      <c r="N39" s="2"/>
+    </row>
+    <row r="40" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A40" s="2"/>
+      <c r="B40" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E40" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F40" s="11">
+      <c r="F40" s="12">
         <f>Parameters!D12</f>
-        <v>22.100000000000001</v>
-      </c>
-      <c r="G40" s="11">
+        <v>22.1</v>
+      </c>
+      <c r="G40" s="12">
         <f>Parameters!E27</f>
         <v>127</v>
       </c>
-      <c r="H40" s="11">
+      <c r="H40" s="12">
         <f>Parameters!F27</f>
         <v>47</v>
       </c>
-      <c r="I40" s="12">
+      <c r="I40" s="13">
         <f t="shared" si="0"/>
         <v>0.37007874015748032</v>
       </c>
-      <c r="J40" s="11">
+      <c r="J40" s="12">
         <f>Parameters!G27</f>
         <v>154</v>
       </c>
-      <c r="K40" s="9">
+      <c r="K40" s="10">
         <f>Parameters!E12</f>
         <v>4949.5049290944507</v>
       </c>
-      <c r="L40" s="13">
+      <c r="L40" s="14">
         <f t="shared" si="1"/>
         <v>28.583051603568116</v>
       </c>
-      <c r="M40" s="3" t="s">
+      <c r="M40" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="N40" s="1"/>
-    </row>
-    <row r="41" spans="1:14" ht="31" customHeight="1">
-      <c r="A41" s="1"/>
-      <c r="B41" s="6" t="s">
+      <c r="N40" s="2"/>
+    </row>
+    <row r="41" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A41" s="2"/>
+      <c r="B41" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F41" s="14">
+      <c r="F41" s="15">
         <f>Parameters!D12</f>
-        <v>22.100000000000001</v>
-      </c>
-      <c r="G41" s="14">
+        <v>22.1</v>
+      </c>
+      <c r="G41" s="15">
         <f>Parameters!E28</f>
         <v>127</v>
       </c>
-      <c r="H41" s="14">
+      <c r="H41" s="15">
         <f>Parameters!F28</f>
         <v>51</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="16">
         <f t="shared" si="0"/>
         <v>0.40157480314960631</v>
       </c>
-      <c r="J41" s="14">
+      <c r="J41" s="15">
         <f>Parameters!G28</f>
         <v>154</v>
       </c>
-      <c r="K41" s="10">
+      <c r="K41" s="11">
         <f>Parameters!E12</f>
         <v>4949.5049290944507</v>
       </c>
-      <c r="L41" s="16">
+      <c r="L41" s="17">
         <f t="shared" si="1"/>
         <v>33.655281675364719</v>
       </c>
-      <c r="M41" s="6" t="s">
+      <c r="M41" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="N41" s="1"/>
+      <c r="N41" s="2"/>
     </row>
     <row r="42" spans="1:14" ht="24" customHeight="1">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
     </row>
     <row r="43" spans="1:14" ht="24" customHeight="1">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
     </row>
     <row r="44" spans="1:14" ht="24" customHeight="1">
-      <c r="A44" s="1"/>
-      <c r="B44" s="8" t="s">
+      <c r="A44" s="2"/>
+      <c r="B44" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-    </row>
-    <row r="45" spans="1:14" ht="32" customHeight="1">
-      <c r="A45" s="1"/>
-      <c r="B45" s="2" t="s">
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+      <c r="N44" s="2"/>
+    </row>
+    <row r="45" spans="1:14" ht="32.1" customHeight="1">
+      <c r="A45" s="2"/>
+      <c r="B45" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-    </row>
-    <row r="46" spans="1:14" ht="31" customHeight="1">
-      <c r="A46" s="1"/>
-      <c r="B46" s="3" t="s">
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+      <c r="N45" s="2"/>
+    </row>
+    <row r="46" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A46" s="2"/>
+      <c r="B46" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C46" s="13">
+      <c r="C46" s="14">
         <f t="shared" ref="C46:C54" si="2">L24</f>
         <v>2.2853924564370129</v>
       </c>
-      <c r="D46" s="13">
+      <c r="D46" s="14">
         <f t="shared" ref="D46:D54" si="3">L33</f>
         <v>5.6824163988087895</v>
       </c>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-    </row>
-    <row r="47" spans="1:14" ht="31" customHeight="1">
-      <c r="A47" s="1"/>
-      <c r="B47" s="6" t="s">
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
+      <c r="N46" s="2"/>
+    </row>
+    <row r="47" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A47" s="2"/>
+      <c r="B47" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C47" s="16">
+      <c r="C47" s="17">
         <f t="shared" si="2"/>
         <v>3.5709257131828327</v>
       </c>
-      <c r="D47" s="16">
+      <c r="D47" s="17">
         <f t="shared" si="3"/>
         <v>8.252766485843928</v>
       </c>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-    </row>
-    <row r="48" spans="1:14" ht="31" customHeight="1">
-      <c r="A48" s="1"/>
-      <c r="B48" s="3" t="s">
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2"/>
+    </row>
+    <row r="48" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A48" s="2"/>
+      <c r="B48" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C48" s="13">
+      <c r="C48" s="14">
         <f t="shared" si="2"/>
         <v>4.5194528557470228</v>
       </c>
-      <c r="D48" s="13">
+      <c r="D48" s="14">
         <f t="shared" si="3"/>
         <v>9.7172682796197645</v>
       </c>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-    </row>
-    <row r="49" spans="1:14" ht="31" customHeight="1">
-      <c r="A49" s="1"/>
-      <c r="B49" s="6" t="s">
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2"/>
+      <c r="N48" s="2"/>
+    </row>
+    <row r="49" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A49" s="2"/>
+      <c r="B49" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C49" s="16">
+      <c r="C49" s="17">
         <f t="shared" si="2"/>
         <v>4.8261413511642468</v>
       </c>
-      <c r="D49" s="16">
+      <c r="D49" s="17">
         <f t="shared" si="3"/>
         <v>11.686377648349833</v>
       </c>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
-      <c r="N49" s="1"/>
-    </row>
-    <row r="50" spans="1:14" ht="31" customHeight="1">
-      <c r="A50" s="1"/>
-      <c r="B50" s="3" t="s">
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2"/>
+    </row>
+    <row r="50" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A50" s="2"/>
+      <c r="B50" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C50" s="13">
+      <c r="C50" s="14">
         <f t="shared" si="2"/>
         <v>7.5408458611941356</v>
       </c>
-      <c r="D50" s="13">
+      <c r="D50" s="14">
         <f t="shared" si="3"/>
         <v>16.972523487971586</v>
       </c>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-      <c r="M50" s="1"/>
-      <c r="N50" s="1"/>
-    </row>
-    <row r="51" spans="1:14" ht="31" customHeight="1">
-      <c r="A51" s="1"/>
-      <c r="B51" s="6" t="s">
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
+    </row>
+    <row r="51" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A51" s="2"/>
+      <c r="B51" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C51" s="16">
+      <c r="C51" s="17">
         <f t="shared" si="2"/>
         <v>9.54388304307383</v>
       </c>
-      <c r="D51" s="16">
+      <c r="D51" s="17">
         <f t="shared" si="3"/>
         <v>19.984397280314212</v>
       </c>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-      <c r="M51" s="1"/>
-      <c r="N51" s="1"/>
-    </row>
-    <row r="52" spans="1:14" ht="31" customHeight="1">
-      <c r="A52" s="1"/>
-      <c r="B52" s="3" t="s">
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
+      <c r="N51" s="2"/>
+    </row>
+    <row r="52" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A52" s="2"/>
+      <c r="B52" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C52" s="13">
+      <c r="C52" s="14">
         <f t="shared" si="2"/>
         <v>8.883105307657285</v>
       </c>
-      <c r="D52" s="13">
+      <c r="D52" s="14">
         <f t="shared" si="3"/>
         <v>19.680770253067951</v>
       </c>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
-      <c r="N52" s="1"/>
-    </row>
-    <row r="53" spans="1:14" ht="31" customHeight="1">
-      <c r="A53" s="1"/>
-      <c r="B53" s="6" t="s">
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2"/>
+    </row>
+    <row r="53" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A53" s="2"/>
+      <c r="B53" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C53" s="16">
+      <c r="C53" s="17">
         <f t="shared" si="2"/>
         <v>13.879852043214509</v>
       </c>
-      <c r="D53" s="16">
+      <c r="D53" s="17">
         <f t="shared" si="3"/>
         <v>28.583051603568116</v>
       </c>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="1"/>
-      <c r="M53" s="1"/>
-      <c r="N53" s="1"/>
-    </row>
-    <row r="54" spans="1:14" ht="31" customHeight="1">
-      <c r="A54" s="1"/>
-      <c r="B54" s="3" t="s">
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
+    </row>
+    <row r="54" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A54" s="2"/>
+      <c r="B54" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C54" s="13">
+      <c r="C54" s="14">
         <f t="shared" si="2"/>
         <v>17.566687742193366</v>
       </c>
-      <c r="D54" s="13">
+      <c r="D54" s="14">
         <f t="shared" si="3"/>
         <v>33.655281675364719</v>
       </c>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
-      <c r="M54" s="1"/>
-      <c r="N54" s="1"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
+      <c r="M54" s="2"/>
+      <c r="N54" s="2"/>
     </row>
     <row r="55" spans="1:14" ht="24" customHeight="1">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="1"/>
-      <c r="M55" s="1"/>
-      <c r="N55" s="1"/>
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2"/>
     </row>
     <row r="56" spans="1:14" ht="24" customHeight="1">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
-      <c r="M56" s="1"/>
-      <c r="N56" s="1"/>
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
     </row>
     <row r="57" spans="1:14" ht="24" customHeight="1">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
-      <c r="M57" s="1"/>
-      <c r="N57" s="1"/>
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
     </row>
     <row r="58" spans="1:14" ht="24" customHeight="1">
-      <c r="A58" s="1"/>
-      <c r="B58" s="8" t="s">
+      <c r="A58" s="2"/>
+      <c r="B58" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
-      <c r="M58" s="1"/>
-      <c r="N58" s="1"/>
-    </row>
-    <row r="59" spans="1:14" ht="32" customHeight="1">
-      <c r="A59" s="1"/>
-      <c r="B59" s="2" t="s">
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
+      <c r="M58" s="2"/>
+      <c r="N58" s="2"/>
+    </row>
+    <row r="59" spans="1:14" ht="32.1" customHeight="1">
+      <c r="A59" s="2"/>
+      <c r="B59" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D59" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
-      <c r="L59" s="1"/>
-      <c r="M59" s="1"/>
-      <c r="N59" s="1"/>
-    </row>
-    <row r="60" spans="1:14" ht="31" customHeight="1">
-      <c r="A60" s="1"/>
-      <c r="B60" s="3" t="s">
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
+    </row>
+    <row r="60" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A60" s="2"/>
+      <c r="B60" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C60" s="13">
+      <c r="C60" s="14">
         <f t="shared" ref="C60:C68" si="4">L6</f>
         <v>2.6911045462579462</v>
       </c>
-      <c r="D60" s="13">
+      <c r="D60" s="14">
         <f t="shared" ref="D60:D68" si="5">L15</f>
         <v>5.4764758837643539</v>
       </c>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
-      <c r="M60" s="1"/>
-      <c r="N60" s="1"/>
-    </row>
-    <row r="61" spans="1:14" ht="31" customHeight="1">
-      <c r="A61" s="1"/>
-      <c r="B61" s="6" t="s">
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
+      <c r="M60" s="2"/>
+      <c r="N60" s="2"/>
+    </row>
+    <row r="61" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A61" s="2"/>
+      <c r="B61" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C61" s="16">
+      <c r="C61" s="17">
         <f t="shared" si="4"/>
         <v>3.8751905466114427</v>
       </c>
-      <c r="D61" s="16">
+      <c r="D61" s="17">
         <f t="shared" si="5"/>
         <v>7.8221407477205336</v>
       </c>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
-      <c r="L61" s="1"/>
-      <c r="M61" s="1"/>
-      <c r="N61" s="1"/>
-    </row>
-    <row r="62" spans="1:14" ht="31" customHeight="1">
-      <c r="A62" s="1"/>
-      <c r="B62" s="3" t="s">
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
+      <c r="M61" s="2"/>
+      <c r="N61" s="2"/>
+    </row>
+    <row r="62" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A62" s="2"/>
+      <c r="B62" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C62" s="13">
+      <c r="C62" s="14">
         <f t="shared" si="4"/>
         <v>4.6484711999035211</v>
       </c>
-      <c r="D62" s="13">
+      <c r="D62" s="14">
         <f t="shared" si="5"/>
         <v>9.4999426990225206</v>
       </c>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
-      <c r="M62" s="1"/>
-      <c r="N62" s="1"/>
-    </row>
-    <row r="63" spans="1:14" ht="31" customHeight="1">
-      <c r="A63" s="1"/>
-      <c r="B63" s="6" t="s">
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+    </row>
+    <row r="63" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A63" s="2"/>
+      <c r="B63" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C63" s="16">
+      <c r="C63" s="17">
         <f t="shared" si="4"/>
         <v>5.6828974360270976</v>
       </c>
-      <c r="D63" s="16">
+      <c r="D63" s="17">
         <f t="shared" si="5"/>
         <v>11.262843281454536</v>
       </c>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1"/>
-      <c r="K63" s="1"/>
-      <c r="L63" s="1"/>
-      <c r="M63" s="1"/>
-      <c r="N63" s="1"/>
-    </row>
-    <row r="64" spans="1:14" ht="31" customHeight="1">
-      <c r="A64" s="1"/>
-      <c r="B64" s="3" t="s">
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2"/>
+    </row>
+    <row r="64" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A64" s="2"/>
+      <c r="B64" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C64" s="13">
+      <c r="C64" s="14">
         <f t="shared" si="4"/>
         <v>8.1833723078790221</v>
       </c>
-      <c r="D64" s="13">
+      <c r="D64" s="14">
         <f t="shared" si="5"/>
         <v>16.086904651262547</v>
       </c>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
-      <c r="L64" s="1"/>
-      <c r="M64" s="1"/>
-      <c r="N64" s="1"/>
-    </row>
-    <row r="65" spans="1:14" ht="31" customHeight="1">
-      <c r="A65" s="1"/>
-      <c r="B65" s="6" t="s">
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2"/>
+      <c r="L64" s="2"/>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2"/>
+    </row>
+    <row r="65" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A65" s="2"/>
+      <c r="B65" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C65" s="16">
+      <c r="C65" s="17">
         <f t="shared" si="4"/>
         <v>9.8163354894966037</v>
       </c>
-      <c r="D65" s="16">
+      <c r="D65" s="17">
         <f t="shared" si="5"/>
         <v>19.537448547722441</v>
       </c>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1"/>
-      <c r="K65" s="1"/>
-      <c r="L65" s="1"/>
-      <c r="M65" s="1"/>
-      <c r="N65" s="1"/>
-    </row>
-    <row r="66" spans="1:14" ht="31" customHeight="1">
-      <c r="A66" s="1"/>
-      <c r="B66" s="3" t="s">
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
+    </row>
+    <row r="66" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A66" s="2"/>
+      <c r="B66" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C66" s="13">
+      <c r="C66" s="14">
         <f t="shared" si="4"/>
         <v>10.460070002853563</v>
       </c>
-      <c r="D66" s="13">
+      <c r="D66" s="14">
         <f t="shared" si="5"/>
         <v>18.967505388627945</v>
       </c>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="1"/>
-      <c r="M66" s="1"/>
-      <c r="N66" s="1"/>
-    </row>
-    <row r="67" spans="1:14" ht="31" customHeight="1">
-      <c r="A67" s="1"/>
-      <c r="B67" s="6" t="s">
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+      <c r="L66" s="2"/>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
+    </row>
+    <row r="67" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A67" s="2"/>
+      <c r="B67" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C67" s="16">
+      <c r="C67" s="17">
         <f t="shared" si="4"/>
         <v>15.062500804109128</v>
       </c>
-      <c r="D67" s="16">
+      <c r="D67" s="17">
         <f t="shared" si="5"/>
         <v>27.091600498569726</v>
       </c>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
-      <c r="L67" s="1"/>
-      <c r="M67" s="1"/>
-      <c r="N67" s="1"/>
-    </row>
-    <row r="68" spans="1:14" ht="31" customHeight="1">
-      <c r="A68" s="1"/>
-      <c r="B68" s="3" t="s">
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
+      <c r="M67" s="2"/>
+      <c r="N67" s="2"/>
+    </row>
+    <row r="68" spans="1:14" ht="30.95" customHeight="1">
+      <c r="A68" s="2"/>
+      <c r="B68" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C68" s="13">
+      <c r="C68" s="14">
         <f t="shared" si="4"/>
         <v>18.068169898806641</v>
       </c>
-      <c r="D68" s="13">
+      <c r="D68" s="14">
         <f t="shared" si="5"/>
         <v>32.902585195264187</v>
       </c>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
-      <c r="M68" s="1"/>
-      <c r="N68" s="1"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
     </row>
     <row r="69" spans="1:14" ht="24" customHeight="1">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="1"/>
-      <c r="M69" s="1"/>
-      <c r="N69" s="1"/>
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
+      <c r="M69" s="2"/>
+      <c r="N69" s="2"/>
     </row>
     <row r="70" spans="1:14" ht="24" customHeight="1">
-      <c r="A70" s="1"/>
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
-      <c r="L70" s="1"/>
-      <c r="M70" s="1"/>
-      <c r="N70" s="1"/>
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
+      <c r="L70" s="2"/>
+      <c r="M70" s="2"/>
+      <c r="N70" s="2"/>
     </row>
     <row r="71" spans="1:14" ht="24" customHeight="1">
-      <c r="A71" s="1"/>
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
-      <c r="K71" s="1"/>
-      <c r="L71" s="1"/>
-      <c r="M71" s="1"/>
-      <c r="N71" s="1"/>
-    </row>
-    <row r="72" spans="1:14" ht="22" customHeight="1"/>
-    <row r="73" spans="1:14" ht="22" customHeight="1"/>
-    <row r="74" spans="1:14" ht="22" customHeight="1"/>
-    <row r="75" spans="1:14" ht="22" customHeight="1"/>
-    <row r="76" spans="1:14" ht="22" customHeight="1"/>
-    <row r="77" spans="1:14" ht="22" customHeight="1"/>
-    <row r="78" spans="1:14" ht="22" customHeight="1"/>
-    <row r="79" spans="1:14" ht="22" customHeight="1"/>
-    <row r="80" spans="1:14" ht="22" customHeight="1"/>
-    <row r="81" ht="22" customHeight="1"/>
-    <row r="82" ht="22" customHeight="1"/>
-    <row r="83" ht="22" customHeight="1"/>
-    <row r="84" ht="35" customHeight="1"/>
-    <row r="85" ht="22" customHeight="1"/>
-    <row r="86" ht="22" customHeight="1"/>
-    <row r="87" ht="22" customHeight="1"/>
-    <row r="88" ht="22" customHeight="1"/>
-    <row r="89" ht="22" customHeight="1"/>
-    <row r="90" ht="22" customHeight="1"/>
-    <row r="91" ht="22" customHeight="1"/>
-    <row r="92" ht="22" customHeight="1"/>
-    <row r="93" ht="22" customHeight="1"/>
-    <row r="94" ht="22" customHeight="1"/>
-    <row r="95" ht="22" customHeight="1"/>
-    <row r="96" ht="22" customHeight="1"/>
-    <row r="97" ht="22" customHeight="1"/>
-    <row r="98" ht="22" customHeight="1"/>
-    <row r="99" ht="22" customHeight="1"/>
-    <row r="100" ht="22" customHeight="1"/>
-    <row r="101" ht="22" customHeight="1"/>
-    <row r="102" ht="22" customHeight="1"/>
-    <row r="103" ht="22" customHeight="1"/>
-    <row r="104" ht="22" customHeight="1"/>
-    <row r="105" ht="22" customHeight="1"/>
-    <row r="106" ht="22" customHeight="1"/>
-    <row r="107" ht="22" customHeight="1"/>
-    <row r="108" ht="22" customHeight="1"/>
-    <row r="109" ht="22" customHeight="1"/>
-    <row r="110" ht="22" customHeight="1"/>
-    <row r="111" ht="22" customHeight="1"/>
-    <row r="112" ht="22" customHeight="1"/>
-    <row r="113" ht="22" customHeight="1"/>
-    <row r="114" ht="22" customHeight="1"/>
-    <row r="115" ht="22" customHeight="1"/>
-    <row r="116" ht="22" customHeight="1"/>
-    <row r="117" ht="22" customHeight="1"/>
-    <row r="118" ht="22" customHeight="1"/>
-    <row r="119" ht="22" customHeight="1"/>
-    <row r="120" ht="22" customHeight="1"/>
-    <row r="121" ht="22" customHeight="1"/>
-    <row r="122" ht="22" customHeight="1"/>
-    <row r="123" ht="22" customHeight="1"/>
-    <row r="124" ht="35" customHeight="1"/>
-    <row r="125" ht="22" customHeight="1"/>
-    <row r="126" ht="22" customHeight="1"/>
-    <row r="127" ht="22" customHeight="1"/>
-    <row r="128" ht="22" customHeight="1"/>
-    <row r="129" ht="22" customHeight="1"/>
-    <row r="130" ht="22" customHeight="1"/>
-    <row r="131" ht="22" customHeight="1"/>
-    <row r="132" ht="22" customHeight="1"/>
-    <row r="133" ht="22" customHeight="1"/>
-    <row r="134" ht="22" customHeight="1"/>
-    <row r="135" ht="22" customHeight="1"/>
-    <row r="136" ht="22" customHeight="1"/>
-    <row r="137" ht="22" customHeight="1"/>
-    <row r="138" ht="22" customHeight="1"/>
-    <row r="139" ht="22" customHeight="1"/>
-    <row r="140" ht="22" customHeight="1"/>
-    <row r="141" ht="22" customHeight="1"/>
-    <row r="142" ht="22" customHeight="1"/>
-    <row r="143" ht="22" customHeight="1"/>
-    <row r="144" ht="22" customHeight="1"/>
-    <row r="145" ht="22" customHeight="1"/>
-    <row r="146" ht="22" customHeight="1"/>
-    <row r="147" ht="22" customHeight="1"/>
-    <row r="148" ht="22" customHeight="1"/>
-    <row r="149" ht="22" customHeight="1"/>
-    <row r="150" ht="22" customHeight="1"/>
-    <row r="151" ht="22" customHeight="1"/>
-    <row r="152" ht="22" customHeight="1"/>
-    <row r="153" ht="22" customHeight="1"/>
-    <row r="154" ht="22" customHeight="1"/>
-    <row r="155" ht="22" customHeight="1"/>
-    <row r="156" ht="22" customHeight="1"/>
-    <row r="157" ht="22" customHeight="1"/>
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+      <c r="L71" s="2"/>
+      <c r="M71" s="2"/>
+      <c r="N71" s="2"/>
+    </row>
+    <row r="72" spans="1:14" ht="21.95" customHeight="1"/>
+    <row r="73" spans="1:14" ht="21.95" customHeight="1"/>
+    <row r="74" spans="1:14" ht="21.95" customHeight="1"/>
+    <row r="75" spans="1:14" ht="21.95" customHeight="1"/>
+    <row r="76" spans="1:14" ht="21.95" customHeight="1"/>
+    <row r="77" spans="1:14" ht="21.95" customHeight="1"/>
+    <row r="78" spans="1:14" ht="21.95" customHeight="1"/>
+    <row r="79" spans="1:14" ht="21.95" customHeight="1"/>
+    <row r="80" spans="1:14" ht="21.95" customHeight="1"/>
+    <row r="81" ht="21.95" customHeight="1"/>
+    <row r="82" ht="21.95" customHeight="1"/>
+    <row r="83" ht="21.95" customHeight="1"/>
+    <row r="84" ht="35.1" customHeight="1"/>
+    <row r="85" ht="21.95" customHeight="1"/>
+    <row r="86" ht="21.95" customHeight="1"/>
+    <row r="87" ht="21.95" customHeight="1"/>
+    <row r="88" ht="21.95" customHeight="1"/>
+    <row r="89" ht="21.95" customHeight="1"/>
+    <row r="90" ht="21.95" customHeight="1"/>
+    <row r="91" ht="21.95" customHeight="1"/>
+    <row r="92" ht="21.95" customHeight="1"/>
+    <row r="93" ht="21.95" customHeight="1"/>
+    <row r="94" ht="21.95" customHeight="1"/>
+    <row r="95" ht="21.95" customHeight="1"/>
+    <row r="96" ht="21.95" customHeight="1"/>
+    <row r="97" ht="21.95" customHeight="1"/>
+    <row r="98" ht="21.95" customHeight="1"/>
+    <row r="99" ht="21.95" customHeight="1"/>
+    <row r="100" ht="21.95" customHeight="1"/>
+    <row r="101" ht="21.95" customHeight="1"/>
+    <row r="102" ht="21.95" customHeight="1"/>
+    <row r="103" ht="21.95" customHeight="1"/>
+    <row r="104" ht="21.95" customHeight="1"/>
+    <row r="105" ht="21.95" customHeight="1"/>
+    <row r="106" ht="21.95" customHeight="1"/>
+    <row r="107" ht="21.95" customHeight="1"/>
+    <row r="108" ht="21.95" customHeight="1"/>
+    <row r="109" ht="21.95" customHeight="1"/>
+    <row r="110" ht="21.95" customHeight="1"/>
+    <row r="111" ht="21.95" customHeight="1"/>
+    <row r="112" ht="21.95" customHeight="1"/>
+    <row r="113" ht="21.95" customHeight="1"/>
+    <row r="114" ht="21.95" customHeight="1"/>
+    <row r="115" ht="21.95" customHeight="1"/>
+    <row r="116" ht="21.95" customHeight="1"/>
+    <row r="117" ht="21.95" customHeight="1"/>
+    <row r="118" ht="21.95" customHeight="1"/>
+    <row r="119" ht="21.95" customHeight="1"/>
+    <row r="120" ht="21.95" customHeight="1"/>
+    <row r="121" ht="21.95" customHeight="1"/>
+    <row r="122" ht="21.95" customHeight="1"/>
+    <row r="123" ht="21.95" customHeight="1"/>
+    <row r="124" ht="35.1" customHeight="1"/>
+    <row r="125" ht="21.95" customHeight="1"/>
+    <row r="126" ht="21.95" customHeight="1"/>
+    <row r="127" ht="21.95" customHeight="1"/>
+    <row r="128" ht="21.95" customHeight="1"/>
+    <row r="129" ht="21.95" customHeight="1"/>
+    <row r="130" ht="21.95" customHeight="1"/>
+    <row r="131" ht="21.95" customHeight="1"/>
+    <row r="132" ht="21.95" customHeight="1"/>
+    <row r="133" ht="21.95" customHeight="1"/>
+    <row r="134" ht="21.95" customHeight="1"/>
+    <row r="135" ht="21.95" customHeight="1"/>
+    <row r="136" ht="21.95" customHeight="1"/>
+    <row r="137" ht="21.95" customHeight="1"/>
+    <row r="138" ht="21.95" customHeight="1"/>
+    <row r="139" ht="21.95" customHeight="1"/>
+    <row r="140" ht="21.95" customHeight="1"/>
+    <row r="141" ht="21.95" customHeight="1"/>
+    <row r="142" ht="21.95" customHeight="1"/>
+    <row r="143" ht="21.95" customHeight="1"/>
+    <row r="144" ht="21.95" customHeight="1"/>
+    <row r="145" ht="21.95" customHeight="1"/>
+    <row r="146" ht="21.95" customHeight="1"/>
+    <row r="147" ht="21.95" customHeight="1"/>
+    <row r="148" ht="21.95" customHeight="1"/>
+    <row r="149" ht="21.95" customHeight="1"/>
+    <row r="150" ht="21.95" customHeight="1"/>
+    <row r="151" ht="21.95" customHeight="1"/>
+    <row r="152" ht="21.95" customHeight="1"/>
+    <row r="153" ht="21.95" customHeight="1"/>
+    <row r="154" ht="21.95" customHeight="1"/>
+    <row r="155" ht="21.95" customHeight="1"/>
+    <row r="156" ht="21.95" customHeight="1"/>
+    <row r="157" ht="21.95" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:M3"/>
   </mergeCells>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/arb_stiffness.xlsx
+++ b/docs/arb_stiffness.xlsx
@@ -6,6 +6,7 @@
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="5" r:id="R8c987114657e4a23"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Samples" sheetId="7" r:id="R638dabceae96445b"/>
   </x:sheets>
+  <x:calcPr fullCalcOnLoad="1" forceFullCalc="1" calcMode="auto"/>
 </x:workbook>
 </file>
 
@@ -15,15 +16,21 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="12">
     <x:numFmt numFmtId="176" formatCode="0.0"/>
     <x:numFmt numFmtId="177" formatCode="0.0000"/>
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.000"/>
     <x:numFmt numFmtId="203" formatCode="0.000000"/>
+    <x:numFmt numFmtId="204" formatCode="0.0"/>
+    <x:numFmt numFmtId="205" formatCode="0.0000"/>
+    <x:numFmt numFmtId="206" formatCode="0"/>
+    <x:numFmt numFmtId="207" formatCode="0.00"/>
+    <x:numFmt numFmtId="208" formatCode="0.000"/>
+    <x:numFmt numFmtId="209" formatCode="0.000000"/>
   </x:numFmts>
-  <x:fonts count="21">
+  <x:fonts count="44">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -147,8 +154,141 @@
       <x:color rgb="FF667B91"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF283C50"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="20"/>
+      <x:color rgb="FF283C50"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF667B91"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF195DB1"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF243B53"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="22"/>
+      <x:color rgb="FF243B53"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF627D98"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF283C50"/>
+      <x:name val="微软雅黑"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF283C50"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:name val="宋体"/>
+      <x:family val="3"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF283C50"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="20"/>
+      <x:color rgb="FF283C50"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF667B91"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF667B91"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF195DB1"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="12"/>
+      <x:color rgb="FF667B91"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="12"/>
+      <x:color rgb="FF667B91"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF667B91"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF667B91"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF667B91"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="12">
+  <x:fills count="29">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -205,8 +345,112 @@
         <x:fgColor rgb="FFEDF2F7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="none"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF31475E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F7FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEDF2F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF31475E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F7FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEDF2F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF31475E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F7FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEDF2F7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="3">
+  <x:borders count="6">
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom style="thin">
+        <x:color rgb="FFDCE4EB"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
     <x:border>
       <x:left/>
       <x:right/>
@@ -231,10 +475,11 @@
       <x:diagonal/>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="1">
+  <x:cellStyleXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <x:xf numFmtId="0" fontId="21" fillId="12" borderId="3"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="62">
+  <x:cellXfs count="151">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -413,6 +658,263 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="20" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="12" borderId="3" xfId="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="16" borderId="3" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="16" borderId="3" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="14" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="17" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="25" fillId="15" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="25" fillId="15" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="16" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="18" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="18" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="22" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="22" fillId="16" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="22" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="22" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="2" fontId="22" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="22" fillId="16" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="22" fillId="16" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="2" fontId="22" fillId="16" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="16" borderId="3" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="16" borderId="3" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="16" borderId="3" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="18" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="18" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="19" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="33" fillId="19" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="33" fillId="19" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="19" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="35" fillId="19" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="36" fillId="19" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="20" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="37" fillId="20" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="37" fillId="20" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="37" fillId="20" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="21" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="21" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="19" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="22" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="38" fillId="22" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="38" fillId="22" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="38" fillId="22" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="38" fillId="22" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="33" fillId="21" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="33" fillId="19" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="39" fillId="19" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="39" fillId="23" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="22" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="38" fillId="22" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="38" fillId="22" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="38" fillId="22" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="38" fillId="22" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="33" fillId="19" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="33" fillId="21" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="33" fillId="19" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="33" fillId="21" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="40" fillId="19" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="40" fillId="23" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="33" fillId="19" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="33" fillId="21" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="33" fillId="19" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="33" fillId="21" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="41" fillId="19" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="41" fillId="21" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="24" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="33" fillId="24" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="33" fillId="24" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="24" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="42" fillId="24" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="25" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="37" fillId="25" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="37" fillId="25" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="37" fillId="25" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="26" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="26" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="24" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="27" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="38" fillId="27" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="38" fillId="27" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="38" fillId="27" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="38" fillId="27" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="33" fillId="26" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="33" fillId="24" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="40" fillId="24" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="40" fillId="28" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="43" fillId="24" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="38" fillId="27" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="33" fillId="26" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="33" fillId="24" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="33" fillId="26" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="33" fillId="24" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -488,8 +990,8 @@
             <c:numRef>
               <c:f>'Samples'!$C$23:$C$31</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="0"/>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -518,8 +1020,8 @@
             <c:numRef>
               <c:f>'Samples'!$D$23:$D$31</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="0"/>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -703,8 +1205,8 @@
             <c:numRef>
               <c:f>'Samples'!$C$36:$C$44</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="0"/>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -733,8 +1235,8 @@
             <c:numRef>
               <c:f>'Samples'!$D$36:$D$44</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="0"/>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2093,2188 +2595,1936 @@
   <x:sheetFormatPr defaultRowHeight="14.25"/>
   <x:cols>
     <x:col min="1" max="1" width="2.75" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13.5" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15.5" hidden="0" customWidth="1"/>
     <x:col min="5" max="7" width="18.5" customWidth="1"/>
-    <x:col min="8" max="8" width="16.25" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="2.75" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="10" max="14" width="10" customWidth="1"/>
     <x:col min="15" max="15" width="10.5" customWidth="1"/>
-    <x:col min="5" max="5" width="18.5" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16.25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18.1299991607666" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16.5" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16.5" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="2.75" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="25"/>
-      <x:c r="B1" s="25"/>
-      <x:c r="C1" s="25"/>
-      <x:c r="D1" s="25"/>
-      <x:c r="E1" s="25"/>
-      <x:c r="F1" s="25"/>
-      <x:c r="G1" s="25"/>
-      <x:c r="H1" s="25"/>
-      <x:c r="I1" s="25"/>
-    </x:row>
-    <x:row r="2" ht="26" customHeight="1">
-      <x:c r="A2" s="25"/>
-      <x:c r="B2" s="26" t="str">
+    <x:row r="1" ht="27" customHeight="1">
+      <x:c r="A1" s="126"/>
+      <x:c r="B1" s="126"/>
+      <x:c r="C1" s="126"/>
+      <x:c r="D1" s="126"/>
+      <x:c r="E1" s="126"/>
+      <x:c r="F1" s="126"/>
+      <x:c r="G1" s="126"/>
+      <x:c r="H1" s="126"/>
+      <x:c r="I1" s="126"/>
+      <x:c r="J1" s="126"/>
+    </x:row>
+    <x:row r="2" ht="27" customHeight="1">
+      <x:c r="A2" s="126"/>
+      <x:c r="B2" s="127" t="str">
         <x:v>Astral · ARB Parameters</x:v>
       </x:c>
-      <x:c r="C2" s="26" t="str">
+      <x:c r="C2" s="127" t="str">
         <x:v>Astral · ARB Parameters</x:v>
       </x:c>
-      <x:c r="D2" s="26" t="str">
+      <x:c r="D2" s="127" t="str">
         <x:v>Astral · ARB Parameters</x:v>
       </x:c>
-      <x:c r="E2" s="26" t="str">
+      <x:c r="E2" s="127" t="str">
         <x:v>Astral · ARB Parameters</x:v>
       </x:c>
-      <x:c r="F2" s="26" t="str">
+      <x:c r="F2" s="127" t="str">
         <x:v>Astral · ARB Parameters</x:v>
       </x:c>
-      <x:c r="G2" s="26" t="str">
+      <x:c r="G2" s="127" t="str">
         <x:v>Astral · ARB Parameters</x:v>
       </x:c>
-      <x:c r="H2" s="26" t="str">
+      <x:c r="H2" s="127" t="str">
         <x:v>Astral · ARB Parameters</x:v>
       </x:c>
-      <x:c r="I2" s="25"/>
-    </x:row>
-    <x:row r="3" ht="26" customHeight="1">
-      <x:c r="A3" s="25"/>
-      <x:c r="B3" s="26" t="str">
+      <x:c r="I2" s="127" t="str">
         <x:v>Astral · ARB Parameters</x:v>
       </x:c>
-      <x:c r="C3" s="26" t="str">
+      <x:c r="J2" s="126"/>
+    </x:row>
+    <x:row r="3" ht="27" customHeight="1">
+      <x:c r="A3" s="126"/>
+      <x:c r="B3" s="127" t="str">
         <x:v>Astral · ARB Parameters</x:v>
       </x:c>
-      <x:c r="D3" s="26" t="str">
+      <x:c r="C3" s="127" t="str">
         <x:v>Astral · ARB Parameters</x:v>
       </x:c>
-      <x:c r="E3" s="26" t="str">
+      <x:c r="D3" s="127" t="str">
         <x:v>Astral · ARB Parameters</x:v>
       </x:c>
-      <x:c r="F3" s="26" t="str">
+      <x:c r="E3" s="127" t="str">
         <x:v>Astral · ARB Parameters</x:v>
       </x:c>
-      <x:c r="G3" s="26" t="str">
+      <x:c r="F3" s="127" t="str">
         <x:v>Astral · ARB Parameters</x:v>
       </x:c>
-      <x:c r="H3" s="26" t="str">
+      <x:c r="G3" s="127" t="str">
         <x:v>Astral · ARB Parameters</x:v>
       </x:c>
-      <x:c r="I3" s="25"/>
-    </x:row>
-    <x:row r="4" ht="26" customHeight="1">
-      <x:c r="A4" s="25"/>
-      <x:c r="B4" s="27" t="str">
+      <x:c r="H3" s="127" t="str">
+        <x:v>Astral · ARB Parameters</x:v>
+      </x:c>
+      <x:c r="I3" s="127" t="str">
+        <x:v>Astral · ARB Parameters</x:v>
+      </x:c>
+      <x:c r="J3" s="126"/>
+    </x:row>
+    <x:row r="4" ht="27" customHeight="1">
+      <x:c r="A4" s="126"/>
+      <x:c r="B4" s="128" t="str">
         <x:v>黄色单元格为手动输入。</x:v>
       </x:c>
-      <x:c r="C4" s="27" t="str">
+      <x:c r="C4" s="128" t="str">
         <x:v>黄色单元格为手动输入。</x:v>
       </x:c>
-      <x:c r="D4" s="27" t="str">
+      <x:c r="D4" s="128" t="str">
         <x:v>黄色单元格为手动输入。</x:v>
       </x:c>
-      <x:c r="E4" s="27" t="str">
+      <x:c r="E4" s="128" t="str">
         <x:v>黄色单元格为手动输入。</x:v>
       </x:c>
-      <x:c r="F4" s="27" t="str">
+      <x:c r="F4" s="128" t="str">
         <x:v>黄色单元格为手动输入。</x:v>
       </x:c>
-      <x:c r="G4" s="27" t="str">
+      <x:c r="G4" s="128" t="str">
         <x:v>黄色单元格为手动输入。</x:v>
       </x:c>
-      <x:c r="H4" s="27" t="str">
+      <x:c r="H4" s="128" t="str">
         <x:v>黄色单元格为手动输入。</x:v>
       </x:c>
-      <x:c r="I4" s="25"/>
-    </x:row>
-    <x:row r="5" ht="26" customHeight="1">
-      <x:c r="A5" s="25"/>
-      <x:c r="B5" s="25"/>
-      <x:c r="C5" s="25"/>
-      <x:c r="D5" s="25"/>
-      <x:c r="E5" s="25"/>
-      <x:c r="F5" s="25"/>
-      <x:c r="G5" s="25"/>
-      <x:c r="H5" s="25"/>
-      <x:c r="I5" s="25"/>
-    </x:row>
-    <x:row r="6" ht="40" customHeight="1">
-      <x:c r="A6" s="25"/>
-      <x:c r="B6" s="32" t="str">
+      <x:c r="I4" s="128" t="str">
+        <x:v>黄色单元格为手动输入。</x:v>
+      </x:c>
+      <x:c r="J4" s="126"/>
+    </x:row>
+    <x:row r="5" ht="27" customHeight="1">
+      <x:c r="A5" s="126"/>
+      <x:c r="B5" s="126"/>
+      <x:c r="C5" s="126"/>
+      <x:c r="D5" s="126"/>
+      <x:c r="E5" s="126"/>
+      <x:c r="F5" s="126"/>
+      <x:c r="G5" s="126"/>
+      <x:c r="H5" s="126"/>
+      <x:c r="I5" s="126"/>
+      <x:c r="J5" s="126"/>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="126"/>
+      <x:c r="B6" s="132" t="str">
         <x:v>Axle</x:v>
       </x:c>
-      <x:c r="C6" s="32" t="str">
+      <x:c r="C6" s="132" t="str">
         <x:v>Bar</x:v>
       </x:c>
-      <x:c r="D6" s="32" t="str">
+      <x:c r="D6" s="132" t="str">
         <x:v>Diameter
 (mm)</x:v>
       </x:c>
-      <x:c r="E6" s="32" t="str">
+      <x:c r="E6" s="132" t="str">
         <x:v>Torsion
 (N·m/rad)</x:v>
       </x:c>
-      <x:c r="F6" s="25"/>
-      <x:c r="G6" s="25"/>
-      <x:c r="H6" s="25"/>
-      <x:c r="I6" s="25"/>
-    </x:row>
-    <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="25"/>
-      <x:c r="B7" s="34" t="str">
+      <x:c r="F6" s="126"/>
+      <x:c r="G6" s="126"/>
+      <x:c r="H6" s="126"/>
+      <x:c r="I6" s="126"/>
+      <x:c r="J6" s="126"/>
+    </x:row>
+    <x:row r="7" ht="27" customHeight="1">
+      <x:c r="A7" s="126"/>
+      <x:c r="B7" s="134" t="str">
         <x:v>Front</x:v>
       </x:c>
-      <x:c r="C7" s="34" t="str">
+      <x:c r="C7" s="134" t="str">
         <x:v>Soft</x:v>
       </x:c>
-      <x:c r="D7" s="39" t="n">
+      <x:c r="D7" s="139" t="n">
         <x:v>14.6</x:v>
       </x:c>
-      <x:c r="E7" s="41">
+      <x:c r="E7" s="141">
         <x:f>$E$8*(D7/$D$8)^4</x:f>
         <x:v>941.4063685268464</x:v>
       </x:c>
-      <x:c r="F7" s="25"/>
-      <x:c r="G7" s="25"/>
-      <x:c r="H7" s="25"/>
-      <x:c r="I7" s="25"/>
-    </x:row>
-    <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="25"/>
-      <x:c r="B8" s="35" t="str">
+      <x:c r="F7" s="126"/>
+      <x:c r="G7" s="126"/>
+      <x:c r="H7" s="126"/>
+      <x:c r="I7" s="126"/>
+      <x:c r="J7" s="126"/>
+    </x:row>
+    <x:row r="8" ht="27" customHeight="1">
+      <x:c r="A8" s="126"/>
+      <x:c r="B8" s="135" t="str">
         <x:v>Front</x:v>
       </x:c>
-      <x:c r="C8" s="35" t="str">
+      <x:c r="C8" s="135" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="D8" s="39" t="n">
+      <x:c r="D8" s="139" t="n">
         <x:v>17.6</x:v>
       </x:c>
-      <x:c r="E8" s="40" t="n">
+      <x:c r="E8" s="140" t="n">
         <x:v>1988</x:v>
       </x:c>
-      <x:c r="F8" s="25"/>
-      <x:c r="G8" s="25"/>
-      <x:c r="H8" s="25"/>
-      <x:c r="I8" s="25"/>
-    </x:row>
-    <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="25"/>
-      <x:c r="B9" s="34" t="str">
+      <x:c r="F8" s="126"/>
+      <x:c r="G8" s="126"/>
+      <x:c r="H8" s="126"/>
+      <x:c r="I8" s="126"/>
+      <x:c r="J8" s="126"/>
+    </x:row>
+    <x:row r="9" ht="27" customHeight="1">
+      <x:c r="A9" s="126"/>
+      <x:c r="B9" s="134" t="str">
         <x:v>Front</x:v>
       </x:c>
-      <x:c r="C9" s="34" t="str">
+      <x:c r="C9" s="134" t="str">
         <x:v>Hard</x:v>
       </x:c>
-      <x:c r="D9" s="39" t="n">
+      <x:c r="D9" s="139" t="n">
         <x:v>20.5</x:v>
       </x:c>
-      <x:c r="E9" s="41">
+      <x:c r="E9" s="141">
         <x:f>$E$8*(D9/$D$8)^4</x:f>
         <x:v>3659.1579207191103</x:v>
       </x:c>
-      <x:c r="F9" s="25"/>
-      <x:c r="G9" s="25"/>
-      <x:c r="H9" s="25"/>
-      <x:c r="I9" s="25"/>
-    </x:row>
-    <x:row r="10" ht="26" customHeight="1">
-      <x:c r="A10" s="25"/>
-      <x:c r="B10" s="35" t="str">
+      <x:c r="F9" s="126"/>
+      <x:c r="G9" s="126"/>
+      <x:c r="H9" s="126"/>
+      <x:c r="I9" s="126"/>
+      <x:c r="J9" s="126"/>
+    </x:row>
+    <x:row r="10" ht="27" customHeight="1">
+      <x:c r="A10" s="126"/>
+      <x:c r="B10" s="135" t="str">
         <x:v>Rear</x:v>
       </x:c>
-      <x:c r="C10" s="35" t="str">
+      <x:c r="C10" s="135" t="str">
         <x:v>Soft</x:v>
       </x:c>
-      <x:c r="D10" s="39" t="n">
+      <x:c r="D10" s="139" t="n">
         <x:v>16.2</x:v>
       </x:c>
-      <x:c r="E10" s="42">
+      <x:c r="E10" s="142">
         <x:f>$E$11*(D10/$D$11)^4</x:f>
         <x:v>1429.067440624532</x:v>
       </x:c>
-      <x:c r="F10" s="25"/>
-      <x:c r="G10" s="25"/>
-      <x:c r="H10" s="25"/>
-      <x:c r="I10" s="25"/>
-    </x:row>
-    <x:row r="11" ht="26" customHeight="1">
-      <x:c r="A11" s="25"/>
-      <x:c r="B11" s="34" t="str">
+      <x:c r="F10" s="126"/>
+      <x:c r="G10" s="126"/>
+      <x:c r="H10" s="126"/>
+      <x:c r="I10" s="126"/>
+      <x:c r="J10" s="126"/>
+    </x:row>
+    <x:row r="11" ht="27" customHeight="1">
+      <x:c r="A11" s="126"/>
+      <x:c r="B11" s="134" t="str">
         <x:v>Rear</x:v>
       </x:c>
-      <x:c r="C11" s="34" t="str">
+      <x:c r="C11" s="134" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="D11" s="39" t="n">
+      <x:c r="D11" s="139" t="n">
         <x:v>19.4</x:v>
       </x:c>
-      <x:c r="E11" s="40" t="n">
+      <x:c r="E11" s="140" t="n">
         <x:v>2939</x:v>
       </x:c>
-      <x:c r="F11" s="25"/>
-      <x:c r="G11" s="25"/>
-      <x:c r="H11" s="25"/>
-      <x:c r="I11" s="25"/>
-    </x:row>
-    <x:row r="12" ht="26" customHeight="1">
-      <x:c r="A12" s="25"/>
-      <x:c r="B12" s="35" t="str">
+      <x:c r="F11" s="126"/>
+      <x:c r="G11" s="126"/>
+      <x:c r="H11" s="126"/>
+      <x:c r="I11" s="126"/>
+      <x:c r="J11" s="126"/>
+    </x:row>
+    <x:row r="12" ht="27" customHeight="1">
+      <x:c r="A12" s="126"/>
+      <x:c r="B12" s="135" t="str">
         <x:v>Rear</x:v>
       </x:c>
-      <x:c r="C12" s="35" t="str">
+      <x:c r="C12" s="135" t="str">
         <x:v>Hard</x:v>
       </x:c>
-      <x:c r="D12" s="39" t="n">
+      <x:c r="D12" s="139" t="n">
         <x:v>22.1</x:v>
       </x:c>
-      <x:c r="E12" s="42">
+      <x:c r="E12" s="142">
         <x:f>$E$11*(D12/$D$11)^4</x:f>
         <x:v>4949.504929094451</x:v>
       </x:c>
-      <x:c r="F12" s="25"/>
-      <x:c r="G12" s="25"/>
-      <x:c r="H12" s="25"/>
-      <x:c r="I12" s="25"/>
-    </x:row>
-    <x:row r="13" ht="26" customHeight="1">
-      <x:c r="A13" s="25"/>
-      <x:c r="B13" s="25"/>
-      <x:c r="C13" s="25"/>
-      <x:c r="D13" s="25"/>
-      <x:c r="E13" s="25"/>
-      <x:c r="F13" s="25"/>
-      <x:c r="G13" s="25"/>
-      <x:c r="H13" s="25"/>
-      <x:c r="I13" s="25"/>
-    </x:row>
-    <x:row r="14" ht="26" customHeight="1">
-      <x:c r="A14" s="25"/>
-      <x:c r="B14" s="28" t="str">
-        <x:v>同侧 arb1 / arb2：车身相对坐标（m），按当前横向转轴计算。</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="str">
-        <x:v>同侧 arb1 / arb2：车身相对坐标（m），按当前横向转轴计算。</x:v>
-      </x:c>
-      <x:c r="D14" s="28" t="str">
-        <x:v>同侧 arb1 / arb2：车身相对坐标（m），按当前横向转轴计算。</x:v>
-      </x:c>
-      <x:c r="E14" s="28" t="str">
-        <x:v>同侧 arb1 / arb2：车身相对坐标（m），按当前横向转轴计算。</x:v>
-      </x:c>
-      <x:c r="F14" s="28" t="str">
-        <x:v>同侧 arb1 / arb2：车身相对坐标（m），按当前横向转轴计算。</x:v>
-      </x:c>
-      <x:c r="G14" s="28" t="str">
-        <x:v>同侧 arb1 / arb2：车身相对坐标（m），按当前横向转轴计算。</x:v>
-      </x:c>
-      <x:c r="H14" s="28" t="str">
-        <x:v>同侧 arb1 / arb2：车身相对坐标（m），按当前横向转轴计算。</x:v>
-      </x:c>
-      <x:c r="I14" s="25"/>
-    </x:row>
-    <x:row r="15" ht="26" customHeight="1">
-      <x:c r="A15" s="25"/>
-      <x:c r="B15" s="28" t="str">
-        <x:v>轮行程：同一测量区间的轮心 Z 变化（mm）。</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="str">
-        <x:v>轮行程：同一测量区间的轮心 Z 变化（mm）。</x:v>
-      </x:c>
-      <x:c r="D15" s="28" t="str">
-        <x:v>轮行程：同一测量区间的轮心 Z 变化（mm）。</x:v>
-      </x:c>
-      <x:c r="E15" s="28" t="str">
-        <x:v>轮行程：同一测量区间的轮心 Z 变化（mm）。</x:v>
-      </x:c>
-      <x:c r="F15" s="28" t="str">
-        <x:v>轮行程：同一测量区间的轮心 Z 变化（mm）。</x:v>
-      </x:c>
-      <x:c r="G15" s="28" t="str">
-        <x:v>轮行程：同一测量区间的轮心 Z 变化（mm）。</x:v>
-      </x:c>
-      <x:c r="H15" s="28" t="str">
-        <x:v>轮行程：同一测量区间的轮心 Z 变化（mm）。</x:v>
-      </x:c>
-      <x:c r="I15" s="25"/>
-    </x:row>
-    <x:row r="16" ht="26" customHeight="1">
-      <x:c r="A16" s="25"/>
-      <x:c r="B16" s="25"/>
-      <x:c r="C16" s="25"/>
-      <x:c r="D16" s="25"/>
-      <x:c r="E16" s="25"/>
-      <x:c r="F16" s="25"/>
-      <x:c r="G16" s="25"/>
-      <x:c r="H16" s="25"/>
-      <x:c r="I16" s="25"/>
-    </x:row>
-    <x:row r="17" ht="26" customHeight="1">
-      <x:c r="A17" s="25"/>
-      <x:c r="B17" s="44" t="str">
-        <x:v>Tarmac / Front / Inner</x:v>
-      </x:c>
-      <x:c r="C17" s="44" t="str">
-        <x:v>Tarmac / Front / Inner</x:v>
-      </x:c>
-      <x:c r="D17" s="44" t="str">
-        <x:v>Tarmac / Front / Inner</x:v>
-      </x:c>
-      <x:c r="E17" s="44" t="str">
-        <x:v>Tarmac / Front / Inner</x:v>
-      </x:c>
-      <x:c r="F17" s="44" t="str">
-        <x:v>Tarmac / Front / Inner</x:v>
-      </x:c>
-      <x:c r="G17" s="44" t="str">
-        <x:v>Tarmac / Front / Inner</x:v>
-      </x:c>
-      <x:c r="H17" s="44" t="str">
-        <x:v>Tarmac / Front / Inner</x:v>
-      </x:c>
-      <x:c r="I17" s="25"/>
-    </x:row>
-    <x:row r="18" ht="26" customHeight="1">
-      <x:c r="A18" s="25"/>
-      <x:c r="B18" s="25" t="str">
-        <x:v>Wheel ΔZ (mm)</x:v>
-      </x:c>
-      <x:c r="C18" s="48" t="n">
+      <x:c r="F12" s="126"/>
+      <x:c r="G12" s="126"/>
+      <x:c r="H12" s="126"/>
+      <x:c r="I12" s="126"/>
+      <x:c r="J12" s="126"/>
+    </x:row>
+    <x:row r="13" ht="27" customHeight="1">
+      <x:c r="A13" s="126"/>
+      <x:c r="B13" s="126"/>
+      <x:c r="C13" s="126"/>
+      <x:c r="D13" s="126"/>
+      <x:c r="E13" s="126"/>
+      <x:c r="F13" s="126"/>
+      <x:c r="G13" s="126"/>
+      <x:c r="H13" s="126"/>
+      <x:c r="I13" s="126"/>
+      <x:c r="J13" s="126"/>
+    </x:row>
+    <x:row r="14" ht="27" customHeight="1">
+      <x:c r="A14" s="126"/>
+      <x:c r="B14" s="144" t="str">
+        <x:v>固定几何 · 生成位置 / 转轴</x:v>
+      </x:c>
+      <x:c r="C14" s="144" t="str">
+        <x:v>固定几何 · 生成位置 / 转轴</x:v>
+      </x:c>
+      <x:c r="D14" s="144" t="str">
+        <x:v>固定几何 · 生成位置 / 转轴</x:v>
+      </x:c>
+      <x:c r="E14" s="144" t="str">
+        <x:v>固定几何 · 生成位置 / 转轴</x:v>
+      </x:c>
+      <x:c r="F14" s="144" t="str">
+        <x:v>固定几何 · 生成位置 / 转轴</x:v>
+      </x:c>
+      <x:c r="G14" s="144" t="str">
+        <x:v>固定几何 · 生成位置 / 转轴</x:v>
+      </x:c>
+      <x:c r="H14" s="144" t="str">
+        <x:v>固定几何 · 生成位置 / 转轴</x:v>
+      </x:c>
+      <x:c r="I14" s="144" t="str">
+        <x:v>固定几何 · 生成位置 / 转轴</x:v>
+      </x:c>
+      <x:c r="J14" s="126"/>
+    </x:row>
+    <x:row r="15" ht="27" customHeight="1">
+      <x:c r="A15" s="126"/>
+      <x:c r="B15" s="145" t="str">
+        <x:v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</x:v>
+      </x:c>
+      <x:c r="C15" s="145" t="str">
+        <x:v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</x:v>
+      </x:c>
+      <x:c r="D15" s="145" t="str">
+        <x:v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</x:v>
+      </x:c>
+      <x:c r="E15" s="145" t="str">
+        <x:v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</x:v>
+      </x:c>
+      <x:c r="F15" s="145" t="str">
+        <x:v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</x:v>
+      </x:c>
+      <x:c r="G15" s="145" t="str">
+        <x:v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</x:v>
+      </x:c>
+      <x:c r="H15" s="145" t="str">
+        <x:v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</x:v>
+      </x:c>
+      <x:c r="I15" s="145" t="str">
+        <x:v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</x:v>
+      </x:c>
+      <x:c r="J15" s="126"/>
+    </x:row>
+    <x:row r="16" ht="42" customHeight="1">
+      <x:c r="A16" s="126"/>
+      <x:c r="B16" s="132" t="str">
+        <x:v>Axle</x:v>
+      </x:c>
+      <x:c r="C16" s="132" t="str">
+        <x:v>arb1 Start Y
+(m)</x:v>
+      </x:c>
+      <x:c r="D16" s="132" t="str">
+        <x:v>arb1 Start Z
+(m)</x:v>
+      </x:c>
+      <x:c r="E16" s="132" t="str">
+        <x:v>arb2 Y
+(m)</x:v>
+      </x:c>
+      <x:c r="F16" s="132" t="str">
+        <x:v>arb2 Z
+(m)</x:v>
+      </x:c>
+      <x:c r="G16" s="132" t="str">
+        <x:v>Start angle
+(°)</x:v>
+      </x:c>
+      <x:c r="H16" s="132" t="str">
+        <x:v>Radius
+(mm)</x:v>
+      </x:c>
+      <x:c r="I16" s="126"/>
+      <x:c r="J16" s="126"/>
+    </x:row>
+    <x:row r="17" ht="27" customHeight="1">
+      <x:c r="A17" s="126"/>
+      <x:c r="B17" s="134" t="str">
+        <x:v>Front</x:v>
+      </x:c>
+      <x:c r="C17" s="146" t="n">
+        <x:v>-1.061</x:v>
+      </x:c>
+      <x:c r="D17" s="146" t="n">
+        <x:v>0.195</x:v>
+      </x:c>
+      <x:c r="E17" s="146" t="n">
+        <x:v>-0.899</x:v>
+      </x:c>
+      <x:c r="F17" s="146" t="n">
+        <x:v>0.185</x:v>
+      </x:c>
+      <x:c r="G17" s="147">
+        <x:f>IF(COUNT(C17:F17)&lt;4,"",IF(H17=0,"无效半径",IF(D17&lt;F17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E17-C17)*1000/H17))))))</x:f>
+        <x:v>3.532294583890938</x:v>
+      </x:c>
+      <x:c r="H17" s="149">
+        <x:f>IF(COUNT(C17:F17)&lt;4,"",1000*SQRT((C17-E17)^2+(D17-F17)^2))</x:f>
+        <x:v>162.30834852218777</x:v>
+      </x:c>
+      <x:c r="I17" s="126"/>
+      <x:c r="J17" s="126"/>
+    </x:row>
+    <x:row r="18" ht="27" customHeight="1">
+      <x:c r="A18" s="126"/>
+      <x:c r="B18" s="135" t="str">
+        <x:v>Rear</x:v>
+      </x:c>
+      <x:c r="C18" s="146" t="n">
+        <x:v>1.321</x:v>
+      </x:c>
+      <x:c r="D18" s="146" t="n">
+        <x:v>0.186</x:v>
+      </x:c>
+      <x:c r="E18" s="146" t="n">
+        <x:v>1.455</x:v>
+      </x:c>
+      <x:c r="F18" s="146" t="n">
+        <x:v>0.261</x:v>
+      </x:c>
+      <x:c r="G18" s="148">
+        <x:f>IF(COUNT(C18:F18)&lt;4,"",IF(H18=0,"无效半径",IF(D18&lt;F18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E18-C18)*1000/H18))))))</x:f>
+        <x:v>-29.235804568699994</x:v>
+      </x:c>
+      <x:c r="H18" s="150">
+        <x:f>IF(COUNT(C18:F18)&lt;4,"",1000*SQRT((C18-E18)^2+(D18-F18)^2))</x:f>
+        <x:v>153.5610627730872</x:v>
+      </x:c>
+      <x:c r="I18" s="126"/>
+      <x:c r="J18" s="126"/>
+    </x:row>
+    <x:row r="19" ht="27" customHeight="1">
+      <x:c r="A19" s="126"/>
+      <x:c r="B19" s="126"/>
+      <x:c r="C19" s="126"/>
+      <x:c r="D19" s="126"/>
+      <x:c r="E19" s="126"/>
+      <x:c r="F19" s="126"/>
+      <x:c r="G19" s="126"/>
+      <x:c r="H19" s="126"/>
+      <x:c r="I19" s="126"/>
+      <x:c r="J19" s="126"/>
+    </x:row>
+    <x:row r="20" ht="27" customHeight="1">
+      <x:c r="A20" s="126"/>
+      <x:c r="B20" s="144" t="str">
+        <x:v>测量 · 每组填写轮行程和 arb1 终点</x:v>
+      </x:c>
+      <x:c r="C20" s="144" t="str">
+        <x:v>测量 · 每组填写轮行程和 arb1 终点</x:v>
+      </x:c>
+      <x:c r="D20" s="144" t="str">
+        <x:v>测量 · 每组填写轮行程和 arb1 终点</x:v>
+      </x:c>
+      <x:c r="E20" s="144" t="str">
+        <x:v>测量 · 每组填写轮行程和 arb1 终点</x:v>
+      </x:c>
+      <x:c r="F20" s="144" t="str">
+        <x:v>测量 · 每组填写轮行程和 arb1 终点</x:v>
+      </x:c>
+      <x:c r="G20" s="144" t="str">
+        <x:v>测量 · 每组填写轮行程和 arb1 终点</x:v>
+      </x:c>
+      <x:c r="H20" s="144" t="str">
+        <x:v>测量 · 每组填写轮行程和 arb1 终点</x:v>
+      </x:c>
+      <x:c r="I20" s="144" t="str">
+        <x:v>测量 · 每组填写轮行程和 arb1 终点</x:v>
+      </x:c>
+      <x:c r="J20" s="126"/>
+    </x:row>
+    <x:row r="21" ht="27" customHeight="1">
+      <x:c r="A21" s="126"/>
+      <x:c r="B21" s="126"/>
+      <x:c r="C21" s="126"/>
+      <x:c r="D21" s="126"/>
+      <x:c r="E21" s="126"/>
+      <x:c r="F21" s="126"/>
+      <x:c r="G21" s="126"/>
+      <x:c r="H21" s="126"/>
+      <x:c r="I21" s="126"/>
+      <x:c r="J21" s="126"/>
+    </x:row>
+    <x:row r="22" ht="42" customHeight="1">
+      <x:c r="A22" s="126"/>
+      <x:c r="B22" s="132" t="str">
+        <x:v>Surface</x:v>
+      </x:c>
+      <x:c r="C22" s="132" t="str">
+        <x:v>Axle</x:v>
+      </x:c>
+      <x:c r="D22" s="132" t="str">
+        <x:v>Position</x:v>
+      </x:c>
+      <x:c r="E22" s="132" t="str">
+        <x:v>Wheel ΔZ
+(mm)</x:v>
+      </x:c>
+      <x:c r="F22" s="132" t="str">
+        <x:v>arb1 End Y
+(m)</x:v>
+      </x:c>
+      <x:c r="G22" s="132" t="str">
+        <x:v>arb1 End Z
+(m)</x:v>
+      </x:c>
+      <x:c r="H22" s="132" t="str">
+        <x:v>End angle
+(°)</x:v>
+      </x:c>
+      <x:c r="I22" s="132" t="str">
+        <x:v>Radius
+(mm)</x:v>
+      </x:c>
+      <x:c r="J22" s="126"/>
+    </x:row>
+    <x:row r="23" ht="27" customHeight="1">
+      <x:c r="A23" s="126"/>
+      <x:c r="B23" s="134" t="str">
+        <x:v>Tarmac</x:v>
+      </x:c>
+      <x:c r="C23" s="134" t="str">
+        <x:v>Front</x:v>
+      </x:c>
+      <x:c r="D23" s="134" t="str">
+        <x:v>Inner</x:v>
+      </x:c>
+      <x:c r="E23" s="139" t="n">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="D18" s="25"/>
-      <x:c r="E18" s="25"/>
-      <x:c r="F18" s="25"/>
-      <x:c r="G18" s="25"/>
-      <x:c r="H18" s="25"/>
-      <x:c r="I18" s="25"/>
-    </x:row>
-    <x:row r="19" ht="40" customHeight="1">
-      <x:c r="A19" s="25"/>
-      <x:c r="B19" s="32" t="str">
-        <x:v>State</x:v>
-      </x:c>
-      <x:c r="C19" s="32" t="str">
-        <x:v>arb1 Y (m)</x:v>
-      </x:c>
-      <x:c r="D19" s="32" t="str">
-        <x:v>arb1 Z (m)</x:v>
-      </x:c>
-      <x:c r="E19" s="32" t="str">
-        <x:v>arb2 Y (m)</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="str">
-        <x:v>arb2 Z (m)</x:v>
-      </x:c>
-      <x:c r="G19" s="32" t="str">
-        <x:v>Arm angle (°)</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="str">
-        <x:v>Radius (mm)</x:v>
-      </x:c>
-      <x:c r="I19" s="25"/>
-    </x:row>
-    <x:row r="20" ht="26" customHeight="1">
-      <x:c r="A20" s="25"/>
-      <x:c r="B20" s="35" t="str">
-        <x:v>Start</x:v>
-      </x:c>
-      <x:c r="C20" s="49"/>
-      <x:c r="D20" s="49"/>
-      <x:c r="E20" s="49"/>
-      <x:c r="F20" s="49"/>
-      <x:c r="G20" s="50" t="str">
-        <x:f>IF(COUNT(C20:F20)&lt;4,"",IF(H20=0,"无效半径",IF(D20&lt;F20,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E20-C20)*1000/H20))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H20" s="52" t="str">
-        <x:f>IF(COUNT(C20:F20)&lt;4,"",1000*SQRT((C20-E20)^2+(D20-F20)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I20" s="25"/>
-    </x:row>
-    <x:row r="21" ht="26" customHeight="1">
-      <x:c r="A21" s="25"/>
-      <x:c r="B21" s="34" t="str">
-        <x:v>End</x:v>
-      </x:c>
-      <x:c r="C21" s="49"/>
-      <x:c r="D21" s="49"/>
-      <x:c r="E21" s="49"/>
-      <x:c r="F21" s="49"/>
-      <x:c r="G21" s="51" t="str">
-        <x:f>IF(COUNT(C21:F21)&lt;4,"",IF(H21=0,"无效半径",IF(D21&lt;F21,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E21-C21)*1000/H21))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H21" s="53" t="str">
-        <x:f>IF(COUNT(C21:F21)&lt;4,"",1000*SQRT((C21-E21)^2+(D21-F21)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I21" s="25"/>
-    </x:row>
-    <x:row r="22" ht="26" customHeight="1">
-      <x:c r="A22" s="25"/>
-      <x:c r="B22" s="25"/>
-      <x:c r="C22" s="25"/>
-      <x:c r="D22" s="25"/>
-      <x:c r="E22" s="25"/>
-      <x:c r="F22" s="25"/>
-      <x:c r="G22" s="25"/>
-      <x:c r="H22" s="25"/>
-      <x:c r="I22" s="25"/>
-    </x:row>
-    <x:row r="23" ht="26" customHeight="1">
-      <x:c r="A23" s="25"/>
-      <x:c r="B23" s="25"/>
-      <x:c r="C23" s="25"/>
-      <x:c r="D23" s="25"/>
-      <x:c r="E23" s="25"/>
-      <x:c r="F23" s="25"/>
-      <x:c r="G23" s="25"/>
-      <x:c r="H23" s="25"/>
-      <x:c r="I23" s="25"/>
-    </x:row>
-    <x:row r="24" ht="26" customHeight="1">
-      <x:c r="A24" s="25"/>
-      <x:c r="B24" s="44" t="str">
-        <x:v>Tarmac / Front / Middle</x:v>
-      </x:c>
-      <x:c r="C24" s="44" t="str">
-        <x:v>Tarmac / Front / Middle</x:v>
-      </x:c>
-      <x:c r="D24" s="44" t="str">
-        <x:v>Tarmac / Front / Middle</x:v>
-      </x:c>
-      <x:c r="E24" s="44" t="str">
-        <x:v>Tarmac / Front / Middle</x:v>
-      </x:c>
-      <x:c r="F24" s="44" t="str">
-        <x:v>Tarmac / Front / Middle</x:v>
-      </x:c>
-      <x:c r="G24" s="44" t="str">
-        <x:v>Tarmac / Front / Middle</x:v>
-      </x:c>
-      <x:c r="H24" s="44" t="str">
-        <x:v>Tarmac / Front / Middle</x:v>
-      </x:c>
-      <x:c r="I24" s="25"/>
-    </x:row>
-    <x:row r="25" ht="26" customHeight="1">
-      <x:c r="A25" s="25"/>
-      <x:c r="B25" s="25" t="str">
-        <x:v>Wheel ΔZ (mm)</x:v>
-      </x:c>
-      <x:c r="C25" s="48" t="n">
+      <x:c r="F23" s="146"/>
+      <x:c r="G23" s="146"/>
+      <x:c r="H23" s="147" t="str">
+        <x:f>IF(COUNT(F23:G23,E17:F17)&lt;4,"",IF(I23=0,"无效半径",IF(G23&lt;F17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E17-F23)*1000/I23))))))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="I23" s="149" t="str">
+        <x:f>IF(COUNT(F23:G23,E17:F17)&lt;4,"",1000*SQRT((F23-E17)^2+(G23-F17)^2))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="J23" s="126"/>
+    </x:row>
+    <x:row r="24" ht="27" customHeight="1">
+      <x:c r="A24" s="126"/>
+      <x:c r="B24" s="135" t="str">
+        <x:v>Tarmac</x:v>
+      </x:c>
+      <x:c r="C24" s="135" t="str">
+        <x:v>Front</x:v>
+      </x:c>
+      <x:c r="D24" s="135" t="str">
+        <x:v>Middle</x:v>
+      </x:c>
+      <x:c r="E24" s="139" t="n">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="D25" s="25"/>
-      <x:c r="E25" s="25"/>
-      <x:c r="F25" s="25"/>
-      <x:c r="G25" s="25"/>
-      <x:c r="H25" s="25"/>
-      <x:c r="I25" s="25"/>
-    </x:row>
-    <x:row r="26" ht="40" customHeight="1">
-      <x:c r="A26" s="25"/>
-      <x:c r="B26" s="32" t="str">
-        <x:v>State</x:v>
-      </x:c>
-      <x:c r="C26" s="32" t="str">
-        <x:v>arb1 Y (m)</x:v>
-      </x:c>
-      <x:c r="D26" s="32" t="str">
-        <x:v>arb1 Z (m)</x:v>
-      </x:c>
-      <x:c r="E26" s="32" t="str">
-        <x:v>arb2 Y (m)</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="str">
-        <x:v>arb2 Z (m)</x:v>
-      </x:c>
-      <x:c r="G26" s="32" t="str">
-        <x:v>Arm angle (°)</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="str">
-        <x:v>Radius (mm)</x:v>
-      </x:c>
-      <x:c r="I26" s="25"/>
-    </x:row>
-    <x:row r="27" ht="26" customHeight="1">
-      <x:c r="A27" s="25"/>
-      <x:c r="B27" s="34" t="str">
-        <x:v>Start</x:v>
-      </x:c>
-      <x:c r="C27" s="49"/>
-      <x:c r="D27" s="49"/>
-      <x:c r="E27" s="49"/>
-      <x:c r="F27" s="49"/>
-      <x:c r="G27" s="51" t="str">
-        <x:f>IF(COUNT(C27:F27)&lt;4,"",IF(H27=0,"无效半径",IF(D27&lt;F27,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E27-C27)*1000/H27))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H27" s="53" t="str">
-        <x:f>IF(COUNT(C27:F27)&lt;4,"",1000*SQRT((C27-E27)^2+(D27-F27)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I27" s="25"/>
-    </x:row>
-    <x:row r="28" ht="26" customHeight="1">
-      <x:c r="A28" s="25"/>
-      <x:c r="B28" s="35" t="str">
-        <x:v>End</x:v>
-      </x:c>
-      <x:c r="C28" s="49"/>
-      <x:c r="D28" s="49"/>
-      <x:c r="E28" s="49"/>
-      <x:c r="F28" s="49"/>
-      <x:c r="G28" s="50" t="str">
-        <x:f>IF(COUNT(C28:F28)&lt;4,"",IF(H28=0,"无效半径",IF(D28&lt;F28,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E28-C28)*1000/H28))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H28" s="52" t="str">
-        <x:f>IF(COUNT(C28:F28)&lt;4,"",1000*SQRT((C28-E28)^2+(D28-F28)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I28" s="25"/>
-    </x:row>
-    <x:row r="29" ht="26" customHeight="1">
-      <x:c r="A29" s="25"/>
-      <x:c r="B29" s="25"/>
-      <x:c r="C29" s="25"/>
-      <x:c r="D29" s="25"/>
-      <x:c r="E29" s="25"/>
-      <x:c r="F29" s="25"/>
-      <x:c r="G29" s="25"/>
-      <x:c r="H29" s="25"/>
-      <x:c r="I29" s="25"/>
-    </x:row>
-    <x:row r="30" ht="26" customHeight="1">
-      <x:c r="A30" s="25"/>
-      <x:c r="B30" s="25"/>
-      <x:c r="C30" s="25"/>
-      <x:c r="D30" s="25"/>
-      <x:c r="E30" s="25"/>
-      <x:c r="F30" s="25"/>
-      <x:c r="G30" s="25"/>
-      <x:c r="H30" s="25"/>
-      <x:c r="I30" s="25"/>
-    </x:row>
-    <x:row r="31" ht="26" customHeight="1">
-      <x:c r="A31" s="25"/>
-      <x:c r="B31" s="44" t="str">
-        <x:v>Tarmac / Front / Outer</x:v>
-      </x:c>
-      <x:c r="C31" s="44" t="str">
-        <x:v>Tarmac / Front / Outer</x:v>
-      </x:c>
-      <x:c r="D31" s="44" t="str">
-        <x:v>Tarmac / Front / Outer</x:v>
-      </x:c>
-      <x:c r="E31" s="44" t="str">
-        <x:v>Tarmac / Front / Outer</x:v>
-      </x:c>
-      <x:c r="F31" s="44" t="str">
-        <x:v>Tarmac / Front / Outer</x:v>
-      </x:c>
-      <x:c r="G31" s="44" t="str">
-        <x:v>Tarmac / Front / Outer</x:v>
-      </x:c>
-      <x:c r="H31" s="44" t="str">
-        <x:v>Tarmac / Front / Outer</x:v>
-      </x:c>
-      <x:c r="I31" s="25"/>
-    </x:row>
-    <x:row r="32" ht="26" customHeight="1">
-      <x:c r="A32" s="25"/>
-      <x:c r="B32" s="25" t="str">
-        <x:v>Wheel ΔZ (mm)</x:v>
-      </x:c>
-      <x:c r="C32" s="48" t="n">
+      <x:c r="F24" s="146"/>
+      <x:c r="G24" s="146"/>
+      <x:c r="H24" s="148" t="str">
+        <x:f>IF(COUNT(F24:G24,E17:F17)&lt;4,"",IF(I24=0,"无效半径",IF(G24&lt;F17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E17-F24)*1000/I24))))))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="I24" s="150" t="str">
+        <x:f>IF(COUNT(F24:G24,E17:F17)&lt;4,"",1000*SQRT((F24-E17)^2+(G24-F17)^2))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="J24" s="126"/>
+    </x:row>
+    <x:row r="25" ht="27" customHeight="1">
+      <x:c r="A25" s="126"/>
+      <x:c r="B25" s="134" t="str">
+        <x:v>Tarmac</x:v>
+      </x:c>
+      <x:c r="C25" s="134" t="str">
+        <x:v>Front</x:v>
+      </x:c>
+      <x:c r="D25" s="134" t="str">
+        <x:v>Outer</x:v>
+      </x:c>
+      <x:c r="E25" s="139" t="n">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="D32" s="25"/>
-      <x:c r="E32" s="25"/>
-      <x:c r="F32" s="25"/>
-      <x:c r="G32" s="25"/>
-      <x:c r="H32" s="25"/>
-      <x:c r="I32" s="25"/>
-    </x:row>
-    <x:row r="33" ht="40" customHeight="1">
-      <x:c r="A33" s="25"/>
-      <x:c r="B33" s="32" t="str">
-        <x:v>State</x:v>
-      </x:c>
-      <x:c r="C33" s="32" t="str">
-        <x:v>arb1 Y (m)</x:v>
-      </x:c>
-      <x:c r="D33" s="32" t="str">
-        <x:v>arb1 Z (m)</x:v>
-      </x:c>
-      <x:c r="E33" s="32" t="str">
-        <x:v>arb2 Y (m)</x:v>
-      </x:c>
-      <x:c r="F33" s="32" t="str">
-        <x:v>arb2 Z (m)</x:v>
-      </x:c>
-      <x:c r="G33" s="32" t="str">
-        <x:v>Arm angle (°)</x:v>
-      </x:c>
-      <x:c r="H33" s="32" t="str">
-        <x:v>Radius (mm)</x:v>
-      </x:c>
-      <x:c r="I33" s="25"/>
-    </x:row>
-    <x:row r="34" ht="26" customHeight="1">
-      <x:c r="A34" s="25"/>
-      <x:c r="B34" s="35" t="str">
-        <x:v>Start</x:v>
-      </x:c>
-      <x:c r="C34" s="49"/>
-      <x:c r="D34" s="49"/>
-      <x:c r="E34" s="49"/>
-      <x:c r="F34" s="49"/>
-      <x:c r="G34" s="50" t="str">
-        <x:f>IF(COUNT(C34:F34)&lt;4,"",IF(H34=0,"无效半径",IF(D34&lt;F34,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E34-C34)*1000/H34))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H34" s="52" t="str">
-        <x:f>IF(COUNT(C34:F34)&lt;4,"",1000*SQRT((C34-E34)^2+(D34-F34)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I34" s="25"/>
-    </x:row>
-    <x:row r="35" ht="26" customHeight="1">
-      <x:c r="A35" s="25"/>
-      <x:c r="B35" s="34" t="str">
-        <x:v>End</x:v>
-      </x:c>
-      <x:c r="C35" s="49"/>
-      <x:c r="D35" s="49"/>
-      <x:c r="E35" s="49"/>
-      <x:c r="F35" s="49"/>
-      <x:c r="G35" s="51" t="str">
-        <x:f>IF(COUNT(C35:F35)&lt;4,"",IF(H35=0,"无效半径",IF(D35&lt;F35,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E35-C35)*1000/H35))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H35" s="53" t="str">
-        <x:f>IF(COUNT(C35:F35)&lt;4,"",1000*SQRT((C35-E35)^2+(D35-F35)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I35" s="25"/>
-    </x:row>
-    <x:row r="36" ht="26" customHeight="1">
-      <x:c r="A36" s="25"/>
-      <x:c r="B36" s="25"/>
-      <x:c r="C36" s="25"/>
-      <x:c r="D36" s="25"/>
-      <x:c r="E36" s="25"/>
-      <x:c r="F36" s="25"/>
-      <x:c r="G36" s="25"/>
-      <x:c r="H36" s="25"/>
-      <x:c r="I36" s="25"/>
-    </x:row>
-    <x:row r="37" ht="26" customHeight="1">
-      <x:c r="A37" s="25"/>
-      <x:c r="B37" s="25"/>
-      <x:c r="C37" s="25"/>
-      <x:c r="D37" s="25"/>
-      <x:c r="E37" s="25"/>
-      <x:c r="F37" s="25"/>
-      <x:c r="G37" s="25"/>
-      <x:c r="H37" s="25"/>
-      <x:c r="I37" s="25"/>
-    </x:row>
-    <x:row r="38" ht="26" customHeight="1">
-      <x:c r="A38" s="25"/>
-      <x:c r="B38" s="44" t="str">
-        <x:v>Tarmac / Rear / Inner</x:v>
-      </x:c>
-      <x:c r="C38" s="44" t="str">
-        <x:v>Tarmac / Rear / Inner</x:v>
-      </x:c>
-      <x:c r="D38" s="44" t="str">
-        <x:v>Tarmac / Rear / Inner</x:v>
-      </x:c>
-      <x:c r="E38" s="44" t="str">
-        <x:v>Tarmac / Rear / Inner</x:v>
-      </x:c>
-      <x:c r="F38" s="44" t="str">
-        <x:v>Tarmac / Rear / Inner</x:v>
-      </x:c>
-      <x:c r="G38" s="44" t="str">
-        <x:v>Tarmac / Rear / Inner</x:v>
-      </x:c>
-      <x:c r="H38" s="44" t="str">
-        <x:v>Tarmac / Rear / Inner</x:v>
-      </x:c>
-      <x:c r="I38" s="25"/>
-    </x:row>
-    <x:row r="39" ht="26" customHeight="1">
-      <x:c r="A39" s="25"/>
-      <x:c r="B39" s="25" t="str">
-        <x:v>Wheel ΔZ (mm)</x:v>
-      </x:c>
-      <x:c r="C39" s="48" t="n">
+      <x:c r="F25" s="146"/>
+      <x:c r="G25" s="146"/>
+      <x:c r="H25" s="147" t="str">
+        <x:f>IF(COUNT(F25:G25,E17:F17)&lt;4,"",IF(I25=0,"无效半径",IF(G25&lt;F17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E17-F25)*1000/I25))))))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="I25" s="149" t="str">
+        <x:f>IF(COUNT(F25:G25,E17:F17)&lt;4,"",1000*SQRT((F25-E17)^2+(G25-F17)^2))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="J25" s="126"/>
+    </x:row>
+    <x:row r="26" ht="27" customHeight="1">
+      <x:c r="A26" s="126"/>
+      <x:c r="B26" s="135" t="str">
+        <x:v>Tarmac</x:v>
+      </x:c>
+      <x:c r="C26" s="135" t="str">
+        <x:v>Rear</x:v>
+      </x:c>
+      <x:c r="D26" s="135" t="str">
+        <x:v>Inner</x:v>
+      </x:c>
+      <x:c r="E26" s="139" t="n">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="D39" s="25"/>
-      <x:c r="E39" s="25"/>
-      <x:c r="F39" s="25"/>
-      <x:c r="G39" s="25"/>
-      <x:c r="H39" s="25"/>
-      <x:c r="I39" s="25"/>
-    </x:row>
-    <x:row r="40" ht="40" customHeight="1">
-      <x:c r="A40" s="25"/>
-      <x:c r="B40" s="32" t="str">
-        <x:v>State</x:v>
-      </x:c>
-      <x:c r="C40" s="32" t="str">
-        <x:v>arb1 Y (m)</x:v>
-      </x:c>
-      <x:c r="D40" s="32" t="str">
-        <x:v>arb1 Z (m)</x:v>
-      </x:c>
-      <x:c r="E40" s="32" t="str">
-        <x:v>arb2 Y (m)</x:v>
-      </x:c>
-      <x:c r="F40" s="32" t="str">
-        <x:v>arb2 Z (m)</x:v>
-      </x:c>
-      <x:c r="G40" s="32" t="str">
-        <x:v>Arm angle (°)</x:v>
-      </x:c>
-      <x:c r="H40" s="32" t="str">
-        <x:v>Radius (mm)</x:v>
-      </x:c>
-      <x:c r="I40" s="25"/>
-    </x:row>
-    <x:row r="41" ht="26" customHeight="1">
-      <x:c r="A41" s="25"/>
-      <x:c r="B41" s="34" t="str">
-        <x:v>Start</x:v>
-      </x:c>
-      <x:c r="C41" s="49"/>
-      <x:c r="D41" s="49"/>
-      <x:c r="E41" s="49"/>
-      <x:c r="F41" s="49"/>
-      <x:c r="G41" s="51" t="str">
-        <x:f>IF(COUNT(C41:F41)&lt;4,"",IF(H41=0,"无效半径",IF(D41&lt;F41,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E41-C41)*1000/H41))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H41" s="53" t="str">
-        <x:f>IF(COUNT(C41:F41)&lt;4,"",1000*SQRT((C41-E41)^2+(D41-F41)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I41" s="25"/>
-    </x:row>
-    <x:row r="42" ht="26" customHeight="1">
-      <x:c r="A42" s="25"/>
-      <x:c r="B42" s="35" t="str">
-        <x:v>End</x:v>
-      </x:c>
-      <x:c r="C42" s="49"/>
-      <x:c r="D42" s="49"/>
-      <x:c r="E42" s="49"/>
-      <x:c r="F42" s="49"/>
-      <x:c r="G42" s="50" t="str">
-        <x:f>IF(COUNT(C42:F42)&lt;4,"",IF(H42=0,"无效半径",IF(D42&lt;F42,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E42-C42)*1000/H42))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H42" s="52" t="str">
-        <x:f>IF(COUNT(C42:F42)&lt;4,"",1000*SQRT((C42-E42)^2+(D42-F42)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I42" s="25"/>
-    </x:row>
-    <x:row r="43" ht="26" customHeight="1">
-      <x:c r="A43" s="25"/>
-      <x:c r="B43" s="25"/>
-      <x:c r="C43" s="25"/>
-      <x:c r="D43" s="25"/>
-      <x:c r="E43" s="25"/>
-      <x:c r="F43" s="25"/>
-      <x:c r="G43" s="25"/>
-      <x:c r="H43" s="25"/>
-      <x:c r="I43" s="25"/>
-    </x:row>
-    <x:row r="44" ht="26" customHeight="1">
-      <x:c r="A44" s="25"/>
-      <x:c r="B44" s="25"/>
-      <x:c r="C44" s="25"/>
-      <x:c r="D44" s="25"/>
-      <x:c r="E44" s="25"/>
-      <x:c r="F44" s="25"/>
-      <x:c r="G44" s="25"/>
-      <x:c r="H44" s="25"/>
-      <x:c r="I44" s="25"/>
-    </x:row>
-    <x:row r="45" ht="26" customHeight="1">
-      <x:c r="A45" s="25"/>
-      <x:c r="B45" s="44" t="str">
-        <x:v>Tarmac / Rear / Middle</x:v>
-      </x:c>
-      <x:c r="C45" s="44" t="str">
-        <x:v>Tarmac / Rear / Middle</x:v>
-      </x:c>
-      <x:c r="D45" s="44" t="str">
-        <x:v>Tarmac / Rear / Middle</x:v>
-      </x:c>
-      <x:c r="E45" s="44" t="str">
-        <x:v>Tarmac / Rear / Middle</x:v>
-      </x:c>
-      <x:c r="F45" s="44" t="str">
-        <x:v>Tarmac / Rear / Middle</x:v>
-      </x:c>
-      <x:c r="G45" s="44" t="str">
-        <x:v>Tarmac / Rear / Middle</x:v>
-      </x:c>
-      <x:c r="H45" s="44" t="str">
-        <x:v>Tarmac / Rear / Middle</x:v>
-      </x:c>
-      <x:c r="I45" s="25"/>
-    </x:row>
-    <x:row r="46" ht="26" customHeight="1">
-      <x:c r="A46" s="25"/>
-      <x:c r="B46" s="25" t="str">
-        <x:v>Wheel ΔZ (mm)</x:v>
-      </x:c>
-      <x:c r="C46" s="48" t="n">
+      <x:c r="F26" s="146"/>
+      <x:c r="G26" s="146"/>
+      <x:c r="H26" s="148" t="str">
+        <x:f>IF(COUNT(F26:G26,E18:F18)&lt;4,"",IF(I26=0,"无效半径",IF(G26&lt;F18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E18-F26)*1000/I26))))))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="I26" s="150" t="str">
+        <x:f>IF(COUNT(F26:G26,E18:F18)&lt;4,"",1000*SQRT((F26-E18)^2+(G26-F18)^2))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="J26" s="126"/>
+    </x:row>
+    <x:row r="27" ht="27" customHeight="1">
+      <x:c r="A27" s="126"/>
+      <x:c r="B27" s="134" t="str">
+        <x:v>Tarmac</x:v>
+      </x:c>
+      <x:c r="C27" s="134" t="str">
+        <x:v>Rear</x:v>
+      </x:c>
+      <x:c r="D27" s="134" t="str">
+        <x:v>Middle</x:v>
+      </x:c>
+      <x:c r="E27" s="139" t="n">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="D46" s="25"/>
-      <x:c r="E46" s="25"/>
-      <x:c r="F46" s="25"/>
-      <x:c r="G46" s="25"/>
-      <x:c r="H46" s="25"/>
-      <x:c r="I46" s="25"/>
-    </x:row>
-    <x:row r="47" ht="40" customHeight="1">
-      <x:c r="A47" s="25"/>
-      <x:c r="B47" s="32" t="str">
-        <x:v>State</x:v>
-      </x:c>
-      <x:c r="C47" s="32" t="str">
-        <x:v>arb1 Y (m)</x:v>
-      </x:c>
-      <x:c r="D47" s="32" t="str">
-        <x:v>arb1 Z (m)</x:v>
-      </x:c>
-      <x:c r="E47" s="32" t="str">
-        <x:v>arb2 Y (m)</x:v>
-      </x:c>
-      <x:c r="F47" s="32" t="str">
-        <x:v>arb2 Z (m)</x:v>
-      </x:c>
-      <x:c r="G47" s="32" t="str">
-        <x:v>Arm angle (°)</x:v>
-      </x:c>
-      <x:c r="H47" s="32" t="str">
-        <x:v>Radius (mm)</x:v>
-      </x:c>
-      <x:c r="I47" s="25"/>
-    </x:row>
-    <x:row r="48" ht="26" customHeight="1">
-      <x:c r="A48" s="25"/>
-      <x:c r="B48" s="35" t="str">
-        <x:v>Start</x:v>
-      </x:c>
-      <x:c r="C48" s="49"/>
-      <x:c r="D48" s="49"/>
-      <x:c r="E48" s="49"/>
-      <x:c r="F48" s="49"/>
-      <x:c r="G48" s="50" t="str">
-        <x:f>IF(COUNT(C48:F48)&lt;4,"",IF(H48=0,"无效半径",IF(D48&lt;F48,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E48-C48)*1000/H48))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H48" s="52" t="str">
-        <x:f>IF(COUNT(C48:F48)&lt;4,"",1000*SQRT((C48-E48)^2+(D48-F48)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I48" s="25"/>
-    </x:row>
-    <x:row r="49" ht="26" customHeight="1">
-      <x:c r="A49" s="25"/>
-      <x:c r="B49" s="34" t="str">
-        <x:v>End</x:v>
-      </x:c>
-      <x:c r="C49" s="49"/>
-      <x:c r="D49" s="49"/>
-      <x:c r="E49" s="49"/>
-      <x:c r="F49" s="49"/>
-      <x:c r="G49" s="51" t="str">
-        <x:f>IF(COUNT(C49:F49)&lt;4,"",IF(H49=0,"无效半径",IF(D49&lt;F49,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E49-C49)*1000/H49))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H49" s="53" t="str">
-        <x:f>IF(COUNT(C49:F49)&lt;4,"",1000*SQRT((C49-E49)^2+(D49-F49)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I49" s="25"/>
-    </x:row>
-    <x:row r="50" ht="26" customHeight="1">
-      <x:c r="A50" s="25"/>
-      <x:c r="B50" s="25"/>
-      <x:c r="C50" s="25"/>
-      <x:c r="D50" s="25"/>
-      <x:c r="E50" s="25"/>
-      <x:c r="F50" s="25"/>
-      <x:c r="G50" s="25"/>
-      <x:c r="H50" s="25"/>
-      <x:c r="I50" s="25"/>
-    </x:row>
-    <x:row r="51" ht="26" customHeight="1">
-      <x:c r="A51" s="25"/>
-      <x:c r="B51" s="25"/>
-      <x:c r="C51" s="25"/>
-      <x:c r="D51" s="25"/>
-      <x:c r="E51" s="25"/>
-      <x:c r="F51" s="25"/>
-      <x:c r="G51" s="25"/>
-      <x:c r="H51" s="25"/>
-      <x:c r="I51" s="25"/>
-    </x:row>
-    <x:row r="52" ht="26" customHeight="1">
-      <x:c r="A52" s="25"/>
-      <x:c r="B52" s="44" t="str">
-        <x:v>Tarmac / Rear / Outer</x:v>
-      </x:c>
-      <x:c r="C52" s="44" t="str">
-        <x:v>Tarmac / Rear / Outer</x:v>
-      </x:c>
-      <x:c r="D52" s="44" t="str">
-        <x:v>Tarmac / Rear / Outer</x:v>
-      </x:c>
-      <x:c r="E52" s="44" t="str">
-        <x:v>Tarmac / Rear / Outer</x:v>
-      </x:c>
-      <x:c r="F52" s="44" t="str">
-        <x:v>Tarmac / Rear / Outer</x:v>
-      </x:c>
-      <x:c r="G52" s="44" t="str">
-        <x:v>Tarmac / Rear / Outer</x:v>
-      </x:c>
-      <x:c r="H52" s="44" t="str">
-        <x:v>Tarmac / Rear / Outer</x:v>
-      </x:c>
-      <x:c r="I52" s="25"/>
-    </x:row>
-    <x:row r="53" ht="26" customHeight="1">
-      <x:c r="A53" s="25"/>
-      <x:c r="B53" s="25" t="str">
-        <x:v>Wheel ΔZ (mm)</x:v>
-      </x:c>
-      <x:c r="C53" s="48" t="n">
+      <x:c r="F27" s="146"/>
+      <x:c r="G27" s="146"/>
+      <x:c r="H27" s="147" t="str">
+        <x:f>IF(COUNT(F27:G27,E18:F18)&lt;4,"",IF(I27=0,"无效半径",IF(G27&lt;F18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E18-F27)*1000/I27))))))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="I27" s="149" t="str">
+        <x:f>IF(COUNT(F27:G27,E18:F18)&lt;4,"",1000*SQRT((F27-E18)^2+(G27-F18)^2))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="J27" s="126"/>
+    </x:row>
+    <x:row r="28" ht="27" customHeight="1">
+      <x:c r="A28" s="126"/>
+      <x:c r="B28" s="135" t="str">
+        <x:v>Tarmac</x:v>
+      </x:c>
+      <x:c r="C28" s="135" t="str">
+        <x:v>Rear</x:v>
+      </x:c>
+      <x:c r="D28" s="135" t="str">
+        <x:v>Outer</x:v>
+      </x:c>
+      <x:c r="E28" s="139" t="n">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="D53" s="25"/>
-      <x:c r="E53" s="25"/>
-      <x:c r="F53" s="25"/>
-      <x:c r="G53" s="25"/>
-      <x:c r="H53" s="25"/>
-      <x:c r="I53" s="25"/>
-    </x:row>
-    <x:row r="54" ht="40" customHeight="1">
-      <x:c r="A54" s="25"/>
-      <x:c r="B54" s="32" t="str">
-        <x:v>State</x:v>
-      </x:c>
-      <x:c r="C54" s="32" t="str">
-        <x:v>arb1 Y (m)</x:v>
-      </x:c>
-      <x:c r="D54" s="32" t="str">
-        <x:v>arb1 Z (m)</x:v>
-      </x:c>
-      <x:c r="E54" s="32" t="str">
-        <x:v>arb2 Y (m)</x:v>
-      </x:c>
-      <x:c r="F54" s="32" t="str">
-        <x:v>arb2 Z (m)</x:v>
-      </x:c>
-      <x:c r="G54" s="32" t="str">
-        <x:v>Arm angle (°)</x:v>
-      </x:c>
-      <x:c r="H54" s="32" t="str">
-        <x:v>Radius (mm)</x:v>
-      </x:c>
-      <x:c r="I54" s="25"/>
-    </x:row>
-    <x:row r="55" ht="26" customHeight="1">
-      <x:c r="A55" s="25"/>
-      <x:c r="B55" s="34" t="str">
-        <x:v>Start</x:v>
-      </x:c>
-      <x:c r="C55" s="49"/>
-      <x:c r="D55" s="49"/>
-      <x:c r="E55" s="49"/>
-      <x:c r="F55" s="49"/>
-      <x:c r="G55" s="51" t="str">
-        <x:f>IF(COUNT(C55:F55)&lt;4,"",IF(H55=0,"无效半径",IF(D55&lt;F55,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E55-C55)*1000/H55))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H55" s="53" t="str">
-        <x:f>IF(COUNT(C55:F55)&lt;4,"",1000*SQRT((C55-E55)^2+(D55-F55)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I55" s="25"/>
-    </x:row>
-    <x:row r="56" ht="26" customHeight="1">
-      <x:c r="A56" s="25"/>
-      <x:c r="B56" s="35" t="str">
-        <x:v>End</x:v>
-      </x:c>
-      <x:c r="C56" s="49"/>
-      <x:c r="D56" s="49"/>
-      <x:c r="E56" s="49"/>
-      <x:c r="F56" s="49"/>
-      <x:c r="G56" s="50" t="str">
-        <x:f>IF(COUNT(C56:F56)&lt;4,"",IF(H56=0,"无效半径",IF(D56&lt;F56,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E56-C56)*1000/H56))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H56" s="52" t="str">
-        <x:f>IF(COUNT(C56:F56)&lt;4,"",1000*SQRT((C56-E56)^2+(D56-F56)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I56" s="25"/>
-    </x:row>
-    <x:row r="57" ht="26" customHeight="1">
-      <x:c r="A57" s="25"/>
-      <x:c r="B57" s="25"/>
-      <x:c r="C57" s="25"/>
-      <x:c r="D57" s="25"/>
-      <x:c r="E57" s="25"/>
-      <x:c r="F57" s="25"/>
-      <x:c r="G57" s="25"/>
-      <x:c r="H57" s="25"/>
-      <x:c r="I57" s="25"/>
-    </x:row>
-    <x:row r="58" ht="26" customHeight="1">
-      <x:c r="A58" s="25"/>
-      <x:c r="B58" s="25"/>
-      <x:c r="C58" s="25"/>
-      <x:c r="D58" s="25"/>
-      <x:c r="E58" s="25"/>
-      <x:c r="F58" s="25"/>
-      <x:c r="G58" s="25"/>
-      <x:c r="H58" s="25"/>
-      <x:c r="I58" s="25"/>
-    </x:row>
-    <x:row r="59" ht="26" customHeight="1">
-      <x:c r="A59" s="25"/>
-      <x:c r="B59" s="44" t="str">
-        <x:v>Gravel / Front / Inner</x:v>
-      </x:c>
-      <x:c r="C59" s="44" t="str">
-        <x:v>Gravel / Front / Inner</x:v>
-      </x:c>
-      <x:c r="D59" s="44" t="str">
-        <x:v>Gravel / Front / Inner</x:v>
-      </x:c>
-      <x:c r="E59" s="44" t="str">
-        <x:v>Gravel / Front / Inner</x:v>
-      </x:c>
-      <x:c r="F59" s="44" t="str">
-        <x:v>Gravel / Front / Inner</x:v>
-      </x:c>
-      <x:c r="G59" s="44" t="str">
-        <x:v>Gravel / Front / Inner</x:v>
-      </x:c>
-      <x:c r="H59" s="44" t="str">
-        <x:v>Gravel / Front / Inner</x:v>
-      </x:c>
-      <x:c r="I59" s="25"/>
-    </x:row>
-    <x:row r="60" ht="26" customHeight="1">
-      <x:c r="A60" s="25"/>
-      <x:c r="B60" s="25" t="str">
-        <x:v>Wheel ΔZ (mm)</x:v>
-      </x:c>
-      <x:c r="C60" s="48" t="n">
+      <x:c r="F28" s="146"/>
+      <x:c r="G28" s="146"/>
+      <x:c r="H28" s="148" t="str">
+        <x:f>IF(COUNT(F28:G28,E18:F18)&lt;4,"",IF(I28=0,"无效半径",IF(G28&lt;F18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E18-F28)*1000/I28))))))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="I28" s="150" t="str">
+        <x:f>IF(COUNT(F28:G28,E18:F18)&lt;4,"",1000*SQRT((F28-E18)^2+(G28-F18)^2))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="J28" s="126"/>
+    </x:row>
+    <x:row r="29" ht="27" customHeight="1">
+      <x:c r="A29" s="126"/>
+      <x:c r="B29" s="134" t="str">
+        <x:v>Gravel</x:v>
+      </x:c>
+      <x:c r="C29" s="134" t="str">
+        <x:v>Front</x:v>
+      </x:c>
+      <x:c r="D29" s="134" t="str">
+        <x:v>Inner</x:v>
+      </x:c>
+      <x:c r="E29" s="139" t="n">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="D60" s="25"/>
-      <x:c r="E60" s="25"/>
-      <x:c r="F60" s="25"/>
-      <x:c r="G60" s="25"/>
-      <x:c r="H60" s="25"/>
-      <x:c r="I60" s="25"/>
-    </x:row>
-    <x:row r="61" ht="40" customHeight="1">
-      <x:c r="A61" s="25"/>
-      <x:c r="B61" s="32" t="str">
-        <x:v>State</x:v>
-      </x:c>
-      <x:c r="C61" s="32" t="str">
-        <x:v>arb1 Y (m)</x:v>
-      </x:c>
-      <x:c r="D61" s="32" t="str">
-        <x:v>arb1 Z (m)</x:v>
-      </x:c>
-      <x:c r="E61" s="32" t="str">
-        <x:v>arb2 Y (m)</x:v>
-      </x:c>
-      <x:c r="F61" s="32" t="str">
-        <x:v>arb2 Z (m)</x:v>
-      </x:c>
-      <x:c r="G61" s="32" t="str">
-        <x:v>Arm angle (°)</x:v>
-      </x:c>
-      <x:c r="H61" s="32" t="str">
-        <x:v>Radius (mm)</x:v>
-      </x:c>
-      <x:c r="I61" s="25"/>
-    </x:row>
-    <x:row r="62" ht="26" customHeight="1">
-      <x:c r="A62" s="25"/>
-      <x:c r="B62" s="35" t="str">
-        <x:v>Start</x:v>
-      </x:c>
-      <x:c r="C62" s="49"/>
-      <x:c r="D62" s="49"/>
-      <x:c r="E62" s="49"/>
-      <x:c r="F62" s="49"/>
-      <x:c r="G62" s="50" t="str">
-        <x:f>IF(COUNT(C62:F62)&lt;4,"",IF(H62=0,"无效半径",IF(D62&lt;F62,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E62-C62)*1000/H62))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H62" s="52" t="str">
-        <x:f>IF(COUNT(C62:F62)&lt;4,"",1000*SQRT((C62-E62)^2+(D62-F62)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I62" s="25"/>
-    </x:row>
-    <x:row r="63" ht="26" customHeight="1">
-      <x:c r="A63" s="25"/>
-      <x:c r="B63" s="34" t="str">
-        <x:v>End</x:v>
-      </x:c>
-      <x:c r="C63" s="49"/>
-      <x:c r="D63" s="49"/>
-      <x:c r="E63" s="49"/>
-      <x:c r="F63" s="49"/>
-      <x:c r="G63" s="51" t="str">
-        <x:f>IF(COUNT(C63:F63)&lt;4,"",IF(H63=0,"无效半径",IF(D63&lt;F63,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E63-C63)*1000/H63))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H63" s="53" t="str">
-        <x:f>IF(COUNT(C63:F63)&lt;4,"",1000*SQRT((C63-E63)^2+(D63-F63)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I63" s="25"/>
-    </x:row>
-    <x:row r="64" ht="26" customHeight="1">
-      <x:c r="A64" s="25"/>
-      <x:c r="B64" s="25"/>
-      <x:c r="C64" s="25"/>
-      <x:c r="D64" s="25"/>
-      <x:c r="E64" s="25"/>
-      <x:c r="F64" s="25"/>
-      <x:c r="G64" s="25"/>
-      <x:c r="H64" s="25"/>
-      <x:c r="I64" s="25"/>
-    </x:row>
-    <x:row r="65" ht="26" customHeight="1">
-      <x:c r="A65" s="25"/>
-      <x:c r="B65" s="25"/>
-      <x:c r="C65" s="25"/>
-      <x:c r="D65" s="25"/>
-      <x:c r="E65" s="25"/>
-      <x:c r="F65" s="25"/>
-      <x:c r="G65" s="25"/>
-      <x:c r="H65" s="25"/>
-      <x:c r="I65" s="25"/>
+      <x:c r="F29" s="146"/>
+      <x:c r="G29" s="146"/>
+      <x:c r="H29" s="147" t="str">
+        <x:f>IF(COUNT(F29:G29,E17:F17)&lt;4,"",IF(I29=0,"无效半径",IF(G29&lt;F17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E17-F29)*1000/I29))))))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="I29" s="149" t="str">
+        <x:f>IF(COUNT(F29:G29,E17:F17)&lt;4,"",1000*SQRT((F29-E17)^2+(G29-F17)^2))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="J29" s="126"/>
+    </x:row>
+    <x:row r="30" ht="27" customHeight="1">
+      <x:c r="A30" s="126"/>
+      <x:c r="B30" s="135" t="str">
+        <x:v>Gravel</x:v>
+      </x:c>
+      <x:c r="C30" s="135" t="str">
+        <x:v>Front</x:v>
+      </x:c>
+      <x:c r="D30" s="135" t="str">
+        <x:v>Middle</x:v>
+      </x:c>
+      <x:c r="E30" s="139" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="F30" s="146"/>
+      <x:c r="G30" s="146"/>
+      <x:c r="H30" s="148" t="str">
+        <x:f>IF(COUNT(F30:G30,E17:F17)&lt;4,"",IF(I30=0,"无效半径",IF(G30&lt;F17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E17-F30)*1000/I30))))))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="I30" s="150" t="str">
+        <x:f>IF(COUNT(F30:G30,E17:F17)&lt;4,"",1000*SQRT((F30-E17)^2+(G30-F17)^2))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="J30" s="126"/>
+    </x:row>
+    <x:row r="31" ht="27" customHeight="1">
+      <x:c r="A31" s="126"/>
+      <x:c r="B31" s="134" t="str">
+        <x:v>Gravel</x:v>
+      </x:c>
+      <x:c r="C31" s="134" t="str">
+        <x:v>Front</x:v>
+      </x:c>
+      <x:c r="D31" s="134" t="str">
+        <x:v>Outer</x:v>
+      </x:c>
+      <x:c r="E31" s="139" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="F31" s="146"/>
+      <x:c r="G31" s="146"/>
+      <x:c r="H31" s="147" t="str">
+        <x:f>IF(COUNT(F31:G31,E17:F17)&lt;4,"",IF(I31=0,"无效半径",IF(G31&lt;F17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E17-F31)*1000/I31))))))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="I31" s="149" t="str">
+        <x:f>IF(COUNT(F31:G31,E17:F17)&lt;4,"",1000*SQRT((F31-E17)^2+(G31-F17)^2))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="J31" s="126"/>
+    </x:row>
+    <x:row r="32" ht="27" customHeight="1">
+      <x:c r="A32" s="126"/>
+      <x:c r="B32" s="135" t="str">
+        <x:v>Gravel</x:v>
+      </x:c>
+      <x:c r="C32" s="135" t="str">
+        <x:v>Rear</x:v>
+      </x:c>
+      <x:c r="D32" s="135" t="str">
+        <x:v>Inner</x:v>
+      </x:c>
+      <x:c r="E32" s="139" t="n">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="F32" s="146"/>
+      <x:c r="G32" s="146"/>
+      <x:c r="H32" s="148" t="str">
+        <x:f>IF(COUNT(F32:G32,E18:F18)&lt;4,"",IF(I32=0,"无效半径",IF(G32&lt;F18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E18-F32)*1000/I32))))))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="I32" s="150" t="str">
+        <x:f>IF(COUNT(F32:G32,E18:F18)&lt;4,"",1000*SQRT((F32-E18)^2+(G32-F18)^2))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="J32" s="126"/>
+    </x:row>
+    <x:row r="33" ht="27" customHeight="1">
+      <x:c r="A33" s="126"/>
+      <x:c r="B33" s="134" t="str">
+        <x:v>Gravel</x:v>
+      </x:c>
+      <x:c r="C33" s="134" t="str">
+        <x:v>Rear</x:v>
+      </x:c>
+      <x:c r="D33" s="134" t="str">
+        <x:v>Middle</x:v>
+      </x:c>
+      <x:c r="E33" s="139" t="n">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="F33" s="146"/>
+      <x:c r="G33" s="146"/>
+      <x:c r="H33" s="147" t="str">
+        <x:f>IF(COUNT(F33:G33,E18:F18)&lt;4,"",IF(I33=0,"无效半径",IF(G33&lt;F18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E18-F33)*1000/I33))))))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="I33" s="149" t="str">
+        <x:f>IF(COUNT(F33:G33,E18:F18)&lt;4,"",1000*SQRT((F33-E18)^2+(G33-F18)^2))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="J33" s="126"/>
+    </x:row>
+    <x:row r="34" ht="27" customHeight="1">
+      <x:c r="A34" s="126"/>
+      <x:c r="B34" s="135" t="str">
+        <x:v>Gravel</x:v>
+      </x:c>
+      <x:c r="C34" s="135" t="str">
+        <x:v>Rear</x:v>
+      </x:c>
+      <x:c r="D34" s="135" t="str">
+        <x:v>Outer</x:v>
+      </x:c>
+      <x:c r="E34" s="139" t="n">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="F34" s="146"/>
+      <x:c r="G34" s="146"/>
+      <x:c r="H34" s="148" t="str">
+        <x:f>IF(COUNT(F34:G34,E18:F18)&lt;4,"",IF(I34=0,"无效半径",IF(G34&lt;F18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E18-F34)*1000/I34))))))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="I34" s="150" t="str">
+        <x:f>IF(COUNT(F34:G34,E18:F18)&lt;4,"",1000*SQRT((F34-E18)^2+(G34-F18)^2))</x:f>
+        <x:v/>
+      </x:c>
+      <x:c r="J34" s="126"/>
+    </x:row>
+    <x:row r="35" ht="27" customHeight="1">
+      <x:c r="A35" s="126"/>
+      <x:c r="B35" s="126"/>
+      <x:c r="C35" s="126"/>
+      <x:c r="D35" s="126"/>
+      <x:c r="E35" s="126"/>
+      <x:c r="F35" s="126"/>
+      <x:c r="G35" s="126"/>
+      <x:c r="H35" s="126"/>
+      <x:c r="I35" s="126"/>
+      <x:c r="J35" s="126"/>
+    </x:row>
+    <x:row r="36" ht="27" customHeight="1">
+      <x:c r="A36" s="126"/>
+      <x:c r="B36" s="126"/>
+      <x:c r="C36" s="126"/>
+      <x:c r="D36" s="126"/>
+      <x:c r="E36" s="126"/>
+      <x:c r="F36" s="126"/>
+      <x:c r="G36" s="126"/>
+      <x:c r="H36" s="126"/>
+      <x:c r="I36" s="126"/>
+      <x:c r="J36" s="126"/>
+    </x:row>
+    <x:row r="37" ht="27" customHeight="1">
+      <x:c r="A37" s="126"/>
+      <x:c r="B37" s="126"/>
+      <x:c r="C37" s="126"/>
+      <x:c r="D37" s="126"/>
+      <x:c r="E37" s="126"/>
+      <x:c r="F37" s="126"/>
+      <x:c r="G37" s="126"/>
+      <x:c r="H37" s="126"/>
+      <x:c r="I37" s="126"/>
+      <x:c r="J37" s="126"/>
+    </x:row>
+    <x:row r="38" ht="27" customHeight="1">
+      <x:c r="A38" s="126"/>
+      <x:c r="B38" s="144" t="str">
+        <x:v>原 Z 测量记录（不参与刚度计算）</x:v>
+      </x:c>
+      <x:c r="C38" s="144" t="str">
+        <x:v>原 Z 测量记录（不参与刚度计算）</x:v>
+      </x:c>
+      <x:c r="D38" s="144" t="str">
+        <x:v>原 Z 测量记录（不参与刚度计算）</x:v>
+      </x:c>
+      <x:c r="E38" s="144" t="str">
+        <x:v>原 Z 测量记录（不参与刚度计算）</x:v>
+      </x:c>
+      <x:c r="F38" s="144" t="str">
+        <x:v>原 Z 测量记录（不参与刚度计算）</x:v>
+      </x:c>
+      <x:c r="G38" s="144" t="str">
+        <x:v>原 Z 测量记录（不参与刚度计算）</x:v>
+      </x:c>
+      <x:c r="H38" s="144" t="str">
+        <x:v>原 Z 测量记录（不参与刚度计算）</x:v>
+      </x:c>
+      <x:c r="I38" s="144" t="str">
+        <x:v>原 Z 测量记录（不参与刚度计算）</x:v>
+      </x:c>
+      <x:c r="J38" s="126"/>
+    </x:row>
+    <x:row r="39" ht="42" customHeight="1">
+      <x:c r="A39" s="126"/>
+      <x:c r="B39" s="132" t="str">
+        <x:v>Surface</x:v>
+      </x:c>
+      <x:c r="C39" s="132" t="str">
+        <x:v>Axle</x:v>
+      </x:c>
+      <x:c r="D39" s="132" t="str">
+        <x:v>Position</x:v>
+      </x:c>
+      <x:c r="E39" s="132" t="str">
+        <x:v>ARB ΔZ (mm)</x:v>
+      </x:c>
+      <x:c r="F39" s="132" t="str">
+        <x:v>Original arm (mm)</x:v>
+      </x:c>
+      <x:c r="G39" s="126"/>
+      <x:c r="H39" s="126"/>
+      <x:c r="I39" s="126"/>
+      <x:c r="J39" s="126"/>
+    </x:row>
+    <x:row r="40" ht="27" customHeight="1">
+      <x:c r="A40" s="126"/>
+      <x:c r="B40" s="135" t="str">
+        <x:v>Tarmac</x:v>
+      </x:c>
+      <x:c r="C40" s="135" t="str">
+        <x:v>Front</x:v>
+      </x:c>
+      <x:c r="D40" s="135" t="str">
+        <x:v>Inner</x:v>
+      </x:c>
+      <x:c r="E40" s="150" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F40" s="150" t="n">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G40" s="126"/>
+      <x:c r="H40" s="126"/>
+      <x:c r="I40" s="126"/>
+      <x:c r="J40" s="126"/>
+    </x:row>
+    <x:row r="41" ht="27" customHeight="1">
+      <x:c r="A41" s="126"/>
+      <x:c r="B41" s="134" t="str">
+        <x:v>Tarmac</x:v>
+      </x:c>
+      <x:c r="C41" s="134" t="str">
+        <x:v>Front</x:v>
+      </x:c>
+      <x:c r="D41" s="134" t="str">
+        <x:v>Middle</x:v>
+      </x:c>
+      <x:c r="E41" s="149" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F41" s="149" t="n">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G41" s="126"/>
+      <x:c r="H41" s="126"/>
+      <x:c r="I41" s="126"/>
+      <x:c r="J41" s="126"/>
+    </x:row>
+    <x:row r="42" ht="27" customHeight="1">
+      <x:c r="A42" s="126"/>
+      <x:c r="B42" s="135" t="str">
+        <x:v>Tarmac</x:v>
+      </x:c>
+      <x:c r="C42" s="135" t="str">
+        <x:v>Front</x:v>
+      </x:c>
+      <x:c r="D42" s="135" t="str">
+        <x:v>Outer</x:v>
+      </x:c>
+      <x:c r="E42" s="150" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F42" s="150" t="n">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G42" s="126"/>
+      <x:c r="H42" s="126"/>
+      <x:c r="I42" s="126"/>
+      <x:c r="J42" s="126"/>
+    </x:row>
+    <x:row r="43" ht="27" customHeight="1">
+      <x:c r="A43" s="126"/>
+      <x:c r="B43" s="134" t="str">
+        <x:v>Tarmac</x:v>
+      </x:c>
+      <x:c r="C43" s="134" t="str">
+        <x:v>Rear</x:v>
+      </x:c>
+      <x:c r="D43" s="134" t="str">
+        <x:v>Inner</x:v>
+      </x:c>
+      <x:c r="E43" s="149" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F43" s="149" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G43" s="126"/>
+      <x:c r="H43" s="126"/>
+      <x:c r="I43" s="126"/>
+      <x:c r="J43" s="126"/>
+    </x:row>
+    <x:row r="44" ht="27" customHeight="1">
+      <x:c r="A44" s="126"/>
+      <x:c r="B44" s="135" t="str">
+        <x:v>Tarmac</x:v>
+      </x:c>
+      <x:c r="C44" s="135" t="str">
+        <x:v>Rear</x:v>
+      </x:c>
+      <x:c r="D44" s="135" t="str">
+        <x:v>Middle</x:v>
+      </x:c>
+      <x:c r="E44" s="150" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F44" s="150" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G44" s="126"/>
+      <x:c r="H44" s="126"/>
+      <x:c r="I44" s="126"/>
+      <x:c r="J44" s="126"/>
+    </x:row>
+    <x:row r="45" ht="27" customHeight="1">
+      <x:c r="A45" s="126"/>
+      <x:c r="B45" s="134" t="str">
+        <x:v>Tarmac</x:v>
+      </x:c>
+      <x:c r="C45" s="134" t="str">
+        <x:v>Rear</x:v>
+      </x:c>
+      <x:c r="D45" s="134" t="str">
+        <x:v>Outer</x:v>
+      </x:c>
+      <x:c r="E45" s="149" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F45" s="149" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G45" s="126"/>
+      <x:c r="H45" s="126"/>
+      <x:c r="I45" s="126"/>
+      <x:c r="J45" s="126"/>
+    </x:row>
+    <x:row r="46" ht="27" customHeight="1">
+      <x:c r="A46" s="126"/>
+      <x:c r="B46" s="135" t="str">
+        <x:v>Gravel</x:v>
+      </x:c>
+      <x:c r="C46" s="135" t="str">
+        <x:v>Front</x:v>
+      </x:c>
+      <x:c r="D46" s="135" t="str">
+        <x:v>Inner</x:v>
+      </x:c>
+      <x:c r="E46" s="150" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F46" s="150" t="n">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G46" s="126"/>
+      <x:c r="H46" s="126"/>
+      <x:c r="I46" s="126"/>
+      <x:c r="J46" s="126"/>
+    </x:row>
+    <x:row r="47" ht="27" customHeight="1">
+      <x:c r="A47" s="126"/>
+      <x:c r="B47" s="134" t="str">
+        <x:v>Gravel</x:v>
+      </x:c>
+      <x:c r="C47" s="134" t="str">
+        <x:v>Front</x:v>
+      </x:c>
+      <x:c r="D47" s="134" t="str">
+        <x:v>Middle</x:v>
+      </x:c>
+      <x:c r="E47" s="149" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F47" s="149" t="n">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G47" s="126"/>
+      <x:c r="H47" s="126"/>
+      <x:c r="I47" s="126"/>
+      <x:c r="J47" s="126"/>
+    </x:row>
+    <x:row r="48" ht="27" customHeight="1">
+      <x:c r="A48" s="126"/>
+      <x:c r="B48" s="135" t="str">
+        <x:v>Gravel</x:v>
+      </x:c>
+      <x:c r="C48" s="135" t="str">
+        <x:v>Front</x:v>
+      </x:c>
+      <x:c r="D48" s="135" t="str">
+        <x:v>Outer</x:v>
+      </x:c>
+      <x:c r="E48" s="150" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F48" s="150" t="n">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G48" s="126"/>
+      <x:c r="H48" s="126"/>
+      <x:c r="I48" s="126"/>
+      <x:c r="J48" s="126"/>
+    </x:row>
+    <x:row r="49" ht="27" customHeight="1">
+      <x:c r="A49" s="126"/>
+      <x:c r="B49" s="134" t="str">
+        <x:v>Gravel</x:v>
+      </x:c>
+      <x:c r="C49" s="134" t="str">
+        <x:v>Rear</x:v>
+      </x:c>
+      <x:c r="D49" s="134" t="str">
+        <x:v>Inner</x:v>
+      </x:c>
+      <x:c r="E49" s="149" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F49" s="149" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G49" s="126"/>
+      <x:c r="H49" s="126"/>
+      <x:c r="I49" s="126"/>
+      <x:c r="J49" s="126"/>
+    </x:row>
+    <x:row r="50" ht="27" customHeight="1">
+      <x:c r="A50" s="126"/>
+      <x:c r="B50" s="135" t="str">
+        <x:v>Gravel</x:v>
+      </x:c>
+      <x:c r="C50" s="135" t="str">
+        <x:v>Rear</x:v>
+      </x:c>
+      <x:c r="D50" s="135" t="str">
+        <x:v>Middle</x:v>
+      </x:c>
+      <x:c r="E50" s="150" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F50" s="150" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G50" s="126"/>
+      <x:c r="H50" s="126"/>
+      <x:c r="I50" s="126"/>
+      <x:c r="J50" s="126"/>
+    </x:row>
+    <x:row r="51" ht="27" customHeight="1">
+      <x:c r="A51" s="126"/>
+      <x:c r="B51" s="134" t="str">
+        <x:v>Gravel</x:v>
+      </x:c>
+      <x:c r="C51" s="134" t="str">
+        <x:v>Rear</x:v>
+      </x:c>
+      <x:c r="D51" s="134" t="str">
+        <x:v>Outer</x:v>
+      </x:c>
+      <x:c r="E51" s="149" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F51" s="149" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G51" s="126"/>
+      <x:c r="H51" s="126"/>
+      <x:c r="I51" s="126"/>
+      <x:c r="J51" s="126"/>
+    </x:row>
+    <x:row r="52" ht="27" customHeight="1">
+      <x:c r="A52" s="126"/>
+      <x:c r="B52" s="126"/>
+      <x:c r="C52" s="126"/>
+      <x:c r="D52" s="126"/>
+      <x:c r="E52" s="126"/>
+      <x:c r="F52" s="126"/>
+      <x:c r="G52" s="126"/>
+      <x:c r="H52" s="126"/>
+      <x:c r="I52" s="126"/>
+      <x:c r="J52" s="126"/>
+    </x:row>
+    <x:row r="53" ht="27" customHeight="1">
+      <x:c r="A53" s="126"/>
+      <x:c r="B53" s="126"/>
+      <x:c r="C53" s="126"/>
+      <x:c r="D53" s="126"/>
+      <x:c r="E53" s="126"/>
+      <x:c r="F53" s="126"/>
+      <x:c r="G53" s="126"/>
+      <x:c r="H53" s="126"/>
+      <x:c r="I53" s="126"/>
+      <x:c r="J53" s="126"/>
+    </x:row>
+    <x:row r="54" ht="27" customHeight="1">
+      <x:c r="A54" s="126"/>
+      <x:c r="B54" s="126"/>
+      <x:c r="C54" s="126"/>
+      <x:c r="D54" s="126"/>
+      <x:c r="E54" s="126"/>
+      <x:c r="F54" s="126"/>
+      <x:c r="G54" s="126"/>
+      <x:c r="H54" s="126"/>
+      <x:c r="I54" s="126"/>
+      <x:c r="J54" s="126"/>
+    </x:row>
+    <x:row r="55" ht="27" customHeight="1">
+      <x:c r="A55" s="126"/>
+      <x:c r="B55" s="126"/>
+      <x:c r="C55" s="126"/>
+      <x:c r="D55" s="126"/>
+      <x:c r="E55" s="126"/>
+      <x:c r="F55" s="126"/>
+      <x:c r="G55" s="126"/>
+      <x:c r="H55" s="126"/>
+      <x:c r="I55" s="126"/>
+      <x:c r="J55" s="126"/>
+    </x:row>
+    <x:row r="56" ht="27" customHeight="1">
+      <x:c r="A56" s="126"/>
+      <x:c r="B56" s="126"/>
+      <x:c r="C56" s="126"/>
+      <x:c r="D56" s="126"/>
+      <x:c r="E56" s="126"/>
+      <x:c r="F56" s="126"/>
+      <x:c r="G56" s="126"/>
+      <x:c r="H56" s="126"/>
+      <x:c r="I56" s="126"/>
+      <x:c r="J56" s="126"/>
+    </x:row>
+    <x:row r="57" ht="27" customHeight="1">
+      <x:c r="A57" s="126"/>
+      <x:c r="B57" s="126"/>
+      <x:c r="C57" s="126"/>
+      <x:c r="D57" s="126"/>
+      <x:c r="E57" s="126"/>
+      <x:c r="F57" s="126"/>
+      <x:c r="G57" s="126"/>
+      <x:c r="H57" s="126"/>
+      <x:c r="I57" s="126"/>
+      <x:c r="J57" s="126"/>
+    </x:row>
+    <x:row r="58" ht="27" customHeight="1">
+      <x:c r="A58" s="126"/>
+      <x:c r="B58" s="126"/>
+      <x:c r="C58" s="126"/>
+      <x:c r="D58" s="126"/>
+      <x:c r="E58" s="126"/>
+      <x:c r="F58" s="126"/>
+      <x:c r="G58" s="126"/>
+      <x:c r="H58" s="126"/>
+      <x:c r="I58" s="126"/>
+      <x:c r="J58" s="126"/>
+    </x:row>
+    <x:row r="59" ht="27" customHeight="1">
+      <x:c r="A59" s="126"/>
+      <x:c r="B59" s="126"/>
+      <x:c r="C59" s="126"/>
+      <x:c r="D59" s="126"/>
+      <x:c r="E59" s="126"/>
+      <x:c r="F59" s="126"/>
+      <x:c r="G59" s="126"/>
+      <x:c r="H59" s="126"/>
+      <x:c r="I59" s="126"/>
+      <x:c r="J59" s="126"/>
+    </x:row>
+    <x:row r="60" ht="27" customHeight="1">
+      <x:c r="A60" s="126"/>
+      <x:c r="B60" s="126"/>
+      <x:c r="C60" s="126"/>
+      <x:c r="D60" s="126"/>
+      <x:c r="E60" s="126"/>
+      <x:c r="F60" s="126"/>
+      <x:c r="G60" s="126"/>
+      <x:c r="H60" s="126"/>
+      <x:c r="I60" s="126"/>
+      <x:c r="J60" s="126"/>
+    </x:row>
+    <x:row r="61" ht="27" customHeight="1">
+      <x:c r="A61" s="126"/>
+      <x:c r="B61" s="126"/>
+      <x:c r="C61" s="126"/>
+      <x:c r="D61" s="126"/>
+      <x:c r="E61" s="126"/>
+      <x:c r="F61" s="126"/>
+      <x:c r="G61" s="126"/>
+      <x:c r="H61" s="126"/>
+      <x:c r="I61" s="126"/>
+      <x:c r="J61" s="126"/>
+    </x:row>
+    <x:row r="62" ht="27" customHeight="1">
+      <x:c r="A62" s="126"/>
+      <x:c r="B62" s="126"/>
+      <x:c r="C62" s="126"/>
+      <x:c r="D62" s="126"/>
+      <x:c r="E62" s="126"/>
+      <x:c r="F62" s="126"/>
+      <x:c r="G62" s="126"/>
+      <x:c r="H62" s="126"/>
+      <x:c r="I62" s="126"/>
+      <x:c r="J62" s="126"/>
+    </x:row>
+    <x:row r="63" ht="27" customHeight="1">
+      <x:c r="A63" s="126"/>
+      <x:c r="B63" s="126"/>
+      <x:c r="C63" s="126"/>
+      <x:c r="D63" s="126"/>
+      <x:c r="E63" s="126"/>
+      <x:c r="F63" s="126"/>
+      <x:c r="G63" s="126"/>
+      <x:c r="H63" s="126"/>
+      <x:c r="I63" s="126"/>
+      <x:c r="J63" s="126"/>
+    </x:row>
+    <x:row r="64" ht="27" customHeight="1">
+      <x:c r="A64" s="126"/>
+      <x:c r="B64" s="126"/>
+      <x:c r="C64" s="126"/>
+      <x:c r="D64" s="126"/>
+      <x:c r="E64" s="126"/>
+      <x:c r="F64" s="126"/>
+      <x:c r="G64" s="126"/>
+      <x:c r="H64" s="126"/>
+      <x:c r="I64" s="126"/>
+      <x:c r="J64" s="126"/>
+    </x:row>
+    <x:row r="65" ht="27" customHeight="1">
+      <x:c r="A65" s="126"/>
+      <x:c r="B65" s="126"/>
+      <x:c r="C65" s="126"/>
+      <x:c r="D65" s="126"/>
+      <x:c r="E65" s="126"/>
+      <x:c r="F65" s="126"/>
+      <x:c r="G65" s="126"/>
+      <x:c r="H65" s="126"/>
+      <x:c r="I65" s="126"/>
+      <x:c r="J65" s="126"/>
     </x:row>
     <x:row r="66" ht="26" customHeight="1">
-      <x:c r="A66" s="25"/>
-      <x:c r="B66" s="44" t="str">
-        <x:v>Gravel / Front / Middle</x:v>
-      </x:c>
-      <x:c r="C66" s="44" t="str">
-        <x:v>Gravel / Front / Middle</x:v>
-      </x:c>
-      <x:c r="D66" s="44" t="str">
-        <x:v>Gravel / Front / Middle</x:v>
-      </x:c>
-      <x:c r="E66" s="44" t="str">
-        <x:v>Gravel / Front / Middle</x:v>
-      </x:c>
-      <x:c r="F66" s="44" t="str">
-        <x:v>Gravel / Front / Middle</x:v>
-      </x:c>
-      <x:c r="G66" s="44" t="str">
-        <x:v>Gravel / Front / Middle</x:v>
-      </x:c>
-      <x:c r="H66" s="44" t="str">
-        <x:v>Gravel / Front / Middle</x:v>
-      </x:c>
-      <x:c r="I66" s="25"/>
+      <x:c r="A66"/>
+      <x:c r="B66"/>
+      <x:c r="C66"/>
+      <x:c r="D66"/>
+      <x:c r="E66"/>
+      <x:c r="F66"/>
+      <x:c r="G66"/>
+      <x:c r="H66"/>
+      <x:c r="I66"/>
     </x:row>
     <x:row r="67" ht="26" customHeight="1">
-      <x:c r="A67" s="25"/>
-      <x:c r="B67" s="25" t="str">
-        <x:v>Wheel ΔZ (mm)</x:v>
-      </x:c>
-      <x:c r="C67" s="48" t="n">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="D67" s="25"/>
-      <x:c r="E67" s="25"/>
-      <x:c r="F67" s="25"/>
-      <x:c r="G67" s="25"/>
-      <x:c r="H67" s="25"/>
-      <x:c r="I67" s="25"/>
+      <x:c r="A67"/>
+      <x:c r="B67"/>
+      <x:c r="C67"/>
+      <x:c r="D67"/>
+      <x:c r="E67"/>
+      <x:c r="F67"/>
+      <x:c r="G67"/>
+      <x:c r="H67"/>
+      <x:c r="I67"/>
     </x:row>
     <x:row r="68" ht="40" customHeight="1">
-      <x:c r="A68" s="25"/>
-      <x:c r="B68" s="32" t="str">
-        <x:v>State</x:v>
-      </x:c>
-      <x:c r="C68" s="32" t="str">
-        <x:v>arb1 Y (m)</x:v>
-      </x:c>
-      <x:c r="D68" s="32" t="str">
-        <x:v>arb1 Z (m)</x:v>
-      </x:c>
-      <x:c r="E68" s="32" t="str">
-        <x:v>arb2 Y (m)</x:v>
-      </x:c>
-      <x:c r="F68" s="32" t="str">
-        <x:v>arb2 Z (m)</x:v>
-      </x:c>
-      <x:c r="G68" s="32" t="str">
-        <x:v>Arm angle (°)</x:v>
-      </x:c>
-      <x:c r="H68" s="32" t="str">
-        <x:v>Radius (mm)</x:v>
-      </x:c>
-      <x:c r="I68" s="25"/>
+      <x:c r="A68"/>
+      <x:c r="B68"/>
+      <x:c r="C68"/>
+      <x:c r="D68"/>
+      <x:c r="E68"/>
+      <x:c r="F68"/>
+      <x:c r="G68"/>
+      <x:c r="H68"/>
+      <x:c r="I68"/>
     </x:row>
     <x:row r="69" ht="26" customHeight="1">
-      <x:c r="A69" s="25"/>
-      <x:c r="B69" s="34" t="str">
-        <x:v>Start</x:v>
-      </x:c>
-      <x:c r="C69" s="49"/>
-      <x:c r="D69" s="49"/>
-      <x:c r="E69" s="49"/>
-      <x:c r="F69" s="49"/>
-      <x:c r="G69" s="51" t="str">
-        <x:f>IF(COUNT(C69:F69)&lt;4,"",IF(H69=0,"无效半径",IF(D69&lt;F69,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E69-C69)*1000/H69))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H69" s="53" t="str">
-        <x:f>IF(COUNT(C69:F69)&lt;4,"",1000*SQRT((C69-E69)^2+(D69-F69)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I69" s="25"/>
+      <x:c r="A69"/>
+      <x:c r="B69"/>
+      <x:c r="C69"/>
+      <x:c r="D69"/>
+      <x:c r="E69"/>
+      <x:c r="F69"/>
+      <x:c r="G69"/>
+      <x:c r="H69"/>
+      <x:c r="I69"/>
     </x:row>
     <x:row r="70" ht="26" customHeight="1">
-      <x:c r="A70" s="25"/>
-      <x:c r="B70" s="35" t="str">
-        <x:v>End</x:v>
-      </x:c>
-      <x:c r="C70" s="49"/>
-      <x:c r="D70" s="49"/>
-      <x:c r="E70" s="49"/>
-      <x:c r="F70" s="49"/>
-      <x:c r="G70" s="50" t="str">
-        <x:f>IF(COUNT(C70:F70)&lt;4,"",IF(H70=0,"无效半径",IF(D70&lt;F70,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E70-C70)*1000/H70))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H70" s="52" t="str">
-        <x:f>IF(COUNT(C70:F70)&lt;4,"",1000*SQRT((C70-E70)^2+(D70-F70)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I70" s="25"/>
+      <x:c r="A70"/>
+      <x:c r="B70"/>
+      <x:c r="C70"/>
+      <x:c r="D70"/>
+      <x:c r="E70"/>
+      <x:c r="F70"/>
+      <x:c r="G70"/>
+      <x:c r="H70"/>
+      <x:c r="I70"/>
     </x:row>
     <x:row r="71" ht="26" customHeight="1">
-      <x:c r="A71" s="25"/>
-      <x:c r="B71" s="25"/>
-      <x:c r="C71" s="25"/>
-      <x:c r="D71" s="25"/>
-      <x:c r="E71" s="25"/>
-      <x:c r="F71" s="25"/>
-      <x:c r="G71" s="25"/>
-      <x:c r="H71" s="25"/>
-      <x:c r="I71" s="25"/>
+      <x:c r="A71"/>
+      <x:c r="B71"/>
+      <x:c r="C71"/>
+      <x:c r="D71"/>
+      <x:c r="E71"/>
+      <x:c r="F71"/>
+      <x:c r="G71"/>
+      <x:c r="H71"/>
+      <x:c r="I71"/>
     </x:row>
     <x:row r="72" ht="26" customHeight="1">
-      <x:c r="A72" s="25"/>
-      <x:c r="B72" s="25"/>
-      <x:c r="C72" s="25"/>
-      <x:c r="D72" s="25"/>
-      <x:c r="E72" s="25"/>
-      <x:c r="F72" s="25"/>
-      <x:c r="G72" s="25"/>
-      <x:c r="H72" s="25"/>
-      <x:c r="I72" s="25"/>
+      <x:c r="A72"/>
+      <x:c r="B72"/>
+      <x:c r="C72"/>
+      <x:c r="D72"/>
+      <x:c r="E72"/>
+      <x:c r="F72"/>
+      <x:c r="G72"/>
+      <x:c r="H72"/>
+      <x:c r="I72"/>
     </x:row>
     <x:row r="73" ht="26" customHeight="1">
-      <x:c r="A73" s="25"/>
-      <x:c r="B73" s="44" t="str">
-        <x:v>Gravel / Front / Outer</x:v>
-      </x:c>
-      <x:c r="C73" s="44" t="str">
-        <x:v>Gravel / Front / Outer</x:v>
-      </x:c>
-      <x:c r="D73" s="44" t="str">
-        <x:v>Gravel / Front / Outer</x:v>
-      </x:c>
-      <x:c r="E73" s="44" t="str">
-        <x:v>Gravel / Front / Outer</x:v>
-      </x:c>
-      <x:c r="F73" s="44" t="str">
-        <x:v>Gravel / Front / Outer</x:v>
-      </x:c>
-      <x:c r="G73" s="44" t="str">
-        <x:v>Gravel / Front / Outer</x:v>
-      </x:c>
-      <x:c r="H73" s="44" t="str">
-        <x:v>Gravel / Front / Outer</x:v>
-      </x:c>
-      <x:c r="I73" s="25"/>
+      <x:c r="A73"/>
+      <x:c r="B73"/>
+      <x:c r="C73"/>
+      <x:c r="D73"/>
+      <x:c r="E73"/>
+      <x:c r="F73"/>
+      <x:c r="G73"/>
+      <x:c r="H73"/>
+      <x:c r="I73"/>
     </x:row>
     <x:row r="74" ht="26" customHeight="1">
-      <x:c r="A74" s="25"/>
-      <x:c r="B74" s="25" t="str">
-        <x:v>Wheel ΔZ (mm)</x:v>
-      </x:c>
-      <x:c r="C74" s="48" t="n">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="D74" s="25"/>
-      <x:c r="E74" s="25"/>
-      <x:c r="F74" s="25"/>
-      <x:c r="G74" s="25"/>
-      <x:c r="H74" s="25"/>
-      <x:c r="I74" s="25"/>
+      <x:c r="A74"/>
+      <x:c r="B74"/>
+      <x:c r="C74"/>
+      <x:c r="D74"/>
+      <x:c r="E74"/>
+      <x:c r="F74"/>
+      <x:c r="G74"/>
+      <x:c r="H74"/>
+      <x:c r="I74"/>
     </x:row>
     <x:row r="75" ht="40" customHeight="1">
-      <x:c r="A75" s="25"/>
-      <x:c r="B75" s="32" t="str">
-        <x:v>State</x:v>
-      </x:c>
-      <x:c r="C75" s="32" t="str">
-        <x:v>arb1 Y (m)</x:v>
-      </x:c>
-      <x:c r="D75" s="32" t="str">
-        <x:v>arb1 Z (m)</x:v>
-      </x:c>
-      <x:c r="E75" s="32" t="str">
-        <x:v>arb2 Y (m)</x:v>
-      </x:c>
-      <x:c r="F75" s="32" t="str">
-        <x:v>arb2 Z (m)</x:v>
-      </x:c>
-      <x:c r="G75" s="32" t="str">
-        <x:v>Arm angle (°)</x:v>
-      </x:c>
-      <x:c r="H75" s="32" t="str">
-        <x:v>Radius (mm)</x:v>
-      </x:c>
-      <x:c r="I75" s="25"/>
+      <x:c r="A75"/>
+      <x:c r="B75"/>
+      <x:c r="C75"/>
+      <x:c r="D75"/>
+      <x:c r="E75"/>
+      <x:c r="F75"/>
+      <x:c r="G75"/>
+      <x:c r="H75"/>
+      <x:c r="I75"/>
     </x:row>
     <x:row r="76" ht="26" customHeight="1">
-      <x:c r="A76" s="25"/>
-      <x:c r="B76" s="35" t="str">
-        <x:v>Start</x:v>
-      </x:c>
-      <x:c r="C76" s="49"/>
-      <x:c r="D76" s="49"/>
-      <x:c r="E76" s="49"/>
-      <x:c r="F76" s="49"/>
-      <x:c r="G76" s="50" t="str">
-        <x:f>IF(COUNT(C76:F76)&lt;4,"",IF(H76=0,"无效半径",IF(D76&lt;F76,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E76-C76)*1000/H76))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H76" s="52" t="str">
-        <x:f>IF(COUNT(C76:F76)&lt;4,"",1000*SQRT((C76-E76)^2+(D76-F76)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I76" s="25"/>
+      <x:c r="A76"/>
+      <x:c r="B76"/>
+      <x:c r="C76"/>
+      <x:c r="D76"/>
+      <x:c r="E76"/>
+      <x:c r="F76"/>
+      <x:c r="G76"/>
+      <x:c r="H76"/>
+      <x:c r="I76"/>
     </x:row>
     <x:row r="77" ht="26" customHeight="1">
-      <x:c r="A77" s="25"/>
-      <x:c r="B77" s="34" t="str">
-        <x:v>End</x:v>
-      </x:c>
-      <x:c r="C77" s="49"/>
-      <x:c r="D77" s="49"/>
-      <x:c r="E77" s="49"/>
-      <x:c r="F77" s="49"/>
-      <x:c r="G77" s="51" t="str">
-        <x:f>IF(COUNT(C77:F77)&lt;4,"",IF(H77=0,"无效半径",IF(D77&lt;F77,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E77-C77)*1000/H77))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H77" s="53" t="str">
-        <x:f>IF(COUNT(C77:F77)&lt;4,"",1000*SQRT((C77-E77)^2+(D77-F77)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I77" s="25"/>
+      <x:c r="A77"/>
+      <x:c r="B77"/>
+      <x:c r="C77"/>
+      <x:c r="D77"/>
+      <x:c r="E77"/>
+      <x:c r="F77"/>
+      <x:c r="G77"/>
+      <x:c r="H77"/>
+      <x:c r="I77"/>
     </x:row>
     <x:row r="78" ht="26" customHeight="1">
-      <x:c r="A78" s="25"/>
-      <x:c r="B78" s="25"/>
-      <x:c r="C78" s="25"/>
-      <x:c r="D78" s="25"/>
-      <x:c r="E78" s="25"/>
-      <x:c r="F78" s="25"/>
-      <x:c r="G78" s="25"/>
-      <x:c r="H78" s="25"/>
-      <x:c r="I78" s="25"/>
+      <x:c r="A78"/>
+      <x:c r="B78"/>
+      <x:c r="C78"/>
+      <x:c r="D78"/>
+      <x:c r="E78"/>
+      <x:c r="F78"/>
+      <x:c r="G78"/>
+      <x:c r="H78"/>
+      <x:c r="I78"/>
     </x:row>
     <x:row r="79" ht="26" customHeight="1">
-      <x:c r="A79" s="25"/>
-      <x:c r="B79" s="25"/>
-      <x:c r="C79" s="25"/>
-      <x:c r="D79" s="25"/>
-      <x:c r="E79" s="25"/>
-      <x:c r="F79" s="25"/>
-      <x:c r="G79" s="25"/>
-      <x:c r="H79" s="25"/>
-      <x:c r="I79" s="25"/>
+      <x:c r="A79"/>
+      <x:c r="B79"/>
+      <x:c r="C79"/>
+      <x:c r="D79"/>
+      <x:c r="E79"/>
+      <x:c r="F79"/>
+      <x:c r="G79"/>
+      <x:c r="H79"/>
+      <x:c r="I79"/>
     </x:row>
     <x:row r="80" ht="26" customHeight="1">
-      <x:c r="A80" s="25"/>
-      <x:c r="B80" s="44" t="str">
-        <x:v>Gravel / Rear / Inner</x:v>
-      </x:c>
-      <x:c r="C80" s="44" t="str">
-        <x:v>Gravel / Rear / Inner</x:v>
-      </x:c>
-      <x:c r="D80" s="44" t="str">
-        <x:v>Gravel / Rear / Inner</x:v>
-      </x:c>
-      <x:c r="E80" s="44" t="str">
-        <x:v>Gravel / Rear / Inner</x:v>
-      </x:c>
-      <x:c r="F80" s="44" t="str">
-        <x:v>Gravel / Rear / Inner</x:v>
-      </x:c>
-      <x:c r="G80" s="44" t="str">
-        <x:v>Gravel / Rear / Inner</x:v>
-      </x:c>
-      <x:c r="H80" s="44" t="str">
-        <x:v>Gravel / Rear / Inner</x:v>
-      </x:c>
-      <x:c r="I80" s="25"/>
+      <x:c r="A80"/>
+      <x:c r="B80"/>
+      <x:c r="C80"/>
+      <x:c r="D80"/>
+      <x:c r="E80"/>
+      <x:c r="F80"/>
+      <x:c r="G80"/>
+      <x:c r="H80"/>
+      <x:c r="I80"/>
     </x:row>
     <x:row r="81" ht="26" customHeight="1">
-      <x:c r="A81" s="25"/>
-      <x:c r="B81" s="25" t="str">
-        <x:v>Wheel ΔZ (mm)</x:v>
-      </x:c>
-      <x:c r="C81" s="48" t="n">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="D81" s="25"/>
-      <x:c r="E81" s="25"/>
-      <x:c r="F81" s="25"/>
-      <x:c r="G81" s="25"/>
-      <x:c r="H81" s="25"/>
-      <x:c r="I81" s="25"/>
+      <x:c r="A81"/>
+      <x:c r="B81"/>
+      <x:c r="C81"/>
+      <x:c r="D81"/>
+      <x:c r="E81"/>
+      <x:c r="F81"/>
+      <x:c r="G81"/>
+      <x:c r="H81"/>
+      <x:c r="I81"/>
     </x:row>
     <x:row r="82" ht="40" customHeight="1">
-      <x:c r="A82" s="25"/>
-      <x:c r="B82" s="32" t="str">
-        <x:v>State</x:v>
-      </x:c>
-      <x:c r="C82" s="32" t="str">
-        <x:v>arb1 Y (m)</x:v>
-      </x:c>
-      <x:c r="D82" s="32" t="str">
-        <x:v>arb1 Z (m)</x:v>
-      </x:c>
-      <x:c r="E82" s="32" t="str">
-        <x:v>arb2 Y (m)</x:v>
-      </x:c>
-      <x:c r="F82" s="32" t="str">
-        <x:v>arb2 Z (m)</x:v>
-      </x:c>
-      <x:c r="G82" s="32" t="str">
-        <x:v>Arm angle (°)</x:v>
-      </x:c>
-      <x:c r="H82" s="32" t="str">
-        <x:v>Radius (mm)</x:v>
-      </x:c>
-      <x:c r="I82" s="25"/>
+      <x:c r="A82"/>
+      <x:c r="B82"/>
+      <x:c r="C82"/>
+      <x:c r="D82"/>
+      <x:c r="E82"/>
+      <x:c r="F82"/>
+      <x:c r="G82"/>
+      <x:c r="H82"/>
+      <x:c r="I82"/>
     </x:row>
     <x:row r="83" ht="26" customHeight="1">
-      <x:c r="A83" s="25"/>
-      <x:c r="B83" s="34" t="str">
-        <x:v>Start</x:v>
-      </x:c>
-      <x:c r="C83" s="49"/>
-      <x:c r="D83" s="49"/>
-      <x:c r="E83" s="49"/>
-      <x:c r="F83" s="49"/>
-      <x:c r="G83" s="51" t="str">
-        <x:f>IF(COUNT(C83:F83)&lt;4,"",IF(H83=0,"无效半径",IF(D83&lt;F83,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E83-C83)*1000/H83))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H83" s="53" t="str">
-        <x:f>IF(COUNT(C83:F83)&lt;4,"",1000*SQRT((C83-E83)^2+(D83-F83)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I83" s="25"/>
+      <x:c r="A83"/>
+      <x:c r="B83"/>
+      <x:c r="C83"/>
+      <x:c r="D83"/>
+      <x:c r="E83"/>
+      <x:c r="F83"/>
+      <x:c r="G83"/>
+      <x:c r="H83"/>
+      <x:c r="I83"/>
     </x:row>
     <x:row r="84" ht="26" customHeight="1">
-      <x:c r="A84" s="25"/>
-      <x:c r="B84" s="35" t="str">
-        <x:v>End</x:v>
-      </x:c>
-      <x:c r="C84" s="49"/>
-      <x:c r="D84" s="49"/>
-      <x:c r="E84" s="49"/>
-      <x:c r="F84" s="49"/>
-      <x:c r="G84" s="50" t="str">
-        <x:f>IF(COUNT(C84:F84)&lt;4,"",IF(H84=0,"无效半径",IF(D84&lt;F84,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E84-C84)*1000/H84))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H84" s="52" t="str">
-        <x:f>IF(COUNT(C84:F84)&lt;4,"",1000*SQRT((C84-E84)^2+(D84-F84)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I84" s="25"/>
+      <x:c r="A84"/>
+      <x:c r="B84"/>
+      <x:c r="C84"/>
+      <x:c r="D84"/>
+      <x:c r="E84"/>
+      <x:c r="F84"/>
+      <x:c r="G84"/>
+      <x:c r="H84"/>
+      <x:c r="I84"/>
     </x:row>
     <x:row r="85" ht="26" customHeight="1">
-      <x:c r="A85" s="25"/>
-      <x:c r="B85" s="25"/>
-      <x:c r="C85" s="25"/>
-      <x:c r="D85" s="25"/>
-      <x:c r="E85" s="25"/>
-      <x:c r="F85" s="25"/>
-      <x:c r="G85" s="25"/>
-      <x:c r="H85" s="25"/>
-      <x:c r="I85" s="25"/>
+      <x:c r="A85"/>
+      <x:c r="B85"/>
+      <x:c r="C85"/>
+      <x:c r="D85"/>
+      <x:c r="E85"/>
+      <x:c r="F85"/>
+      <x:c r="G85"/>
+      <x:c r="H85"/>
+      <x:c r="I85"/>
     </x:row>
     <x:row r="86" ht="26" customHeight="1">
-      <x:c r="A86" s="25"/>
-      <x:c r="B86" s="25"/>
-      <x:c r="C86" s="25"/>
-      <x:c r="D86" s="25"/>
-      <x:c r="E86" s="25"/>
-      <x:c r="F86" s="25"/>
-      <x:c r="G86" s="25"/>
-      <x:c r="H86" s="25"/>
-      <x:c r="I86" s="25"/>
+      <x:c r="A86"/>
+      <x:c r="B86"/>
+      <x:c r="C86"/>
+      <x:c r="D86"/>
+      <x:c r="E86"/>
+      <x:c r="F86"/>
+      <x:c r="G86"/>
+      <x:c r="H86"/>
+      <x:c r="I86"/>
     </x:row>
     <x:row r="87" ht="26" customHeight="1">
-      <x:c r="A87" s="25"/>
-      <x:c r="B87" s="44" t="str">
-        <x:v>Gravel / Rear / Middle</x:v>
-      </x:c>
-      <x:c r="C87" s="44" t="str">
-        <x:v>Gravel / Rear / Middle</x:v>
-      </x:c>
-      <x:c r="D87" s="44" t="str">
-        <x:v>Gravel / Rear / Middle</x:v>
-      </x:c>
-      <x:c r="E87" s="44" t="str">
-        <x:v>Gravel / Rear / Middle</x:v>
-      </x:c>
-      <x:c r="F87" s="44" t="str">
-        <x:v>Gravel / Rear / Middle</x:v>
-      </x:c>
-      <x:c r="G87" s="44" t="str">
-        <x:v>Gravel / Rear / Middle</x:v>
-      </x:c>
-      <x:c r="H87" s="44" t="str">
-        <x:v>Gravel / Rear / Middle</x:v>
-      </x:c>
-      <x:c r="I87" s="25"/>
+      <x:c r="A87"/>
+      <x:c r="B87"/>
+      <x:c r="C87"/>
+      <x:c r="D87"/>
+      <x:c r="E87"/>
+      <x:c r="F87"/>
+      <x:c r="G87"/>
+      <x:c r="H87"/>
+      <x:c r="I87"/>
     </x:row>
     <x:row r="88" ht="26" customHeight="1">
-      <x:c r="A88" s="25"/>
-      <x:c r="B88" s="25" t="str">
-        <x:v>Wheel ΔZ (mm)</x:v>
-      </x:c>
-      <x:c r="C88" s="48" t="n">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="D88" s="25"/>
-      <x:c r="E88" s="25"/>
-      <x:c r="F88" s="25"/>
-      <x:c r="G88" s="25"/>
-      <x:c r="H88" s="25"/>
-      <x:c r="I88" s="25"/>
+      <x:c r="A88"/>
+      <x:c r="B88"/>
+      <x:c r="C88"/>
+      <x:c r="D88"/>
+      <x:c r="E88"/>
+      <x:c r="F88"/>
+      <x:c r="G88"/>
+      <x:c r="H88"/>
+      <x:c r="I88"/>
     </x:row>
     <x:row r="89" ht="40" customHeight="1">
-      <x:c r="A89" s="25"/>
-      <x:c r="B89" s="32" t="str">
-        <x:v>State</x:v>
-      </x:c>
-      <x:c r="C89" s="32" t="str">
-        <x:v>arb1 Y (m)</x:v>
-      </x:c>
-      <x:c r="D89" s="32" t="str">
-        <x:v>arb1 Z (m)</x:v>
-      </x:c>
-      <x:c r="E89" s="32" t="str">
-        <x:v>arb2 Y (m)</x:v>
-      </x:c>
-      <x:c r="F89" s="32" t="str">
-        <x:v>arb2 Z (m)</x:v>
-      </x:c>
-      <x:c r="G89" s="32" t="str">
-        <x:v>Arm angle (°)</x:v>
-      </x:c>
-      <x:c r="H89" s="32" t="str">
-        <x:v>Radius (mm)</x:v>
-      </x:c>
-      <x:c r="I89" s="25"/>
+      <x:c r="A89"/>
+      <x:c r="B89"/>
+      <x:c r="C89"/>
+      <x:c r="D89"/>
+      <x:c r="E89"/>
+      <x:c r="F89"/>
+      <x:c r="G89"/>
+      <x:c r="H89"/>
+      <x:c r="I89"/>
     </x:row>
     <x:row r="90" ht="26" customHeight="1">
-      <x:c r="A90" s="25"/>
-      <x:c r="B90" s="35" t="str">
-        <x:v>Start</x:v>
-      </x:c>
-      <x:c r="C90" s="49"/>
-      <x:c r="D90" s="49"/>
-      <x:c r="E90" s="49"/>
-      <x:c r="F90" s="49"/>
-      <x:c r="G90" s="50" t="str">
-        <x:f>IF(COUNT(C90:F90)&lt;4,"",IF(H90=0,"无效半径",IF(D90&lt;F90,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E90-C90)*1000/H90))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H90" s="52" t="str">
-        <x:f>IF(COUNT(C90:F90)&lt;4,"",1000*SQRT((C90-E90)^2+(D90-F90)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I90" s="25"/>
+      <x:c r="A90"/>
+      <x:c r="B90"/>
+      <x:c r="C90"/>
+      <x:c r="D90"/>
+      <x:c r="E90"/>
+      <x:c r="F90"/>
+      <x:c r="G90"/>
+      <x:c r="H90"/>
+      <x:c r="I90"/>
     </x:row>
     <x:row r="91" ht="26" customHeight="1">
-      <x:c r="A91" s="25"/>
-      <x:c r="B91" s="34" t="str">
-        <x:v>End</x:v>
-      </x:c>
-      <x:c r="C91" s="49"/>
-      <x:c r="D91" s="49"/>
-      <x:c r="E91" s="49"/>
-      <x:c r="F91" s="49"/>
-      <x:c r="G91" s="51" t="str">
-        <x:f>IF(COUNT(C91:F91)&lt;4,"",IF(H91=0,"无效半径",IF(D91&lt;F91,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E91-C91)*1000/H91))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H91" s="53" t="str">
-        <x:f>IF(COUNT(C91:F91)&lt;4,"",1000*SQRT((C91-E91)^2+(D91-F91)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I91" s="25"/>
+      <x:c r="A91"/>
+      <x:c r="B91"/>
+      <x:c r="C91"/>
+      <x:c r="D91"/>
+      <x:c r="E91"/>
+      <x:c r="F91"/>
+      <x:c r="G91"/>
+      <x:c r="H91"/>
+      <x:c r="I91"/>
     </x:row>
     <x:row r="92" ht="26" customHeight="1">
-      <x:c r="A92" s="25"/>
-      <x:c r="B92" s="25"/>
-      <x:c r="C92" s="25"/>
-      <x:c r="D92" s="25"/>
-      <x:c r="E92" s="25"/>
-      <x:c r="F92" s="25"/>
-      <x:c r="G92" s="25"/>
-      <x:c r="H92" s="25"/>
-      <x:c r="I92" s="25"/>
+      <x:c r="A92"/>
+      <x:c r="B92"/>
+      <x:c r="C92"/>
+      <x:c r="D92"/>
+      <x:c r="E92"/>
+      <x:c r="F92"/>
+      <x:c r="G92"/>
+      <x:c r="H92"/>
+      <x:c r="I92"/>
     </x:row>
     <x:row r="93" ht="26" customHeight="1">
-      <x:c r="A93" s="25"/>
-      <x:c r="B93" s="25"/>
-      <x:c r="C93" s="25"/>
-      <x:c r="D93" s="25"/>
-      <x:c r="E93" s="25"/>
-      <x:c r="F93" s="25"/>
-      <x:c r="G93" s="25"/>
-      <x:c r="H93" s="25"/>
-      <x:c r="I93" s="25"/>
+      <x:c r="A93"/>
+      <x:c r="B93"/>
+      <x:c r="C93"/>
+      <x:c r="D93"/>
+      <x:c r="E93"/>
+      <x:c r="F93"/>
+      <x:c r="G93"/>
+      <x:c r="H93"/>
+      <x:c r="I93"/>
     </x:row>
     <x:row r="94" ht="26" customHeight="1">
-      <x:c r="A94" s="25"/>
-      <x:c r="B94" s="44" t="str">
-        <x:v>Gravel / Rear / Outer</x:v>
-      </x:c>
-      <x:c r="C94" s="44" t="str">
-        <x:v>Gravel / Rear / Outer</x:v>
-      </x:c>
-      <x:c r="D94" s="44" t="str">
-        <x:v>Gravel / Rear / Outer</x:v>
-      </x:c>
-      <x:c r="E94" s="44" t="str">
-        <x:v>Gravel / Rear / Outer</x:v>
-      </x:c>
-      <x:c r="F94" s="44" t="str">
-        <x:v>Gravel / Rear / Outer</x:v>
-      </x:c>
-      <x:c r="G94" s="44" t="str">
-        <x:v>Gravel / Rear / Outer</x:v>
-      </x:c>
-      <x:c r="H94" s="44" t="str">
-        <x:v>Gravel / Rear / Outer</x:v>
-      </x:c>
-      <x:c r="I94" s="25"/>
+      <x:c r="A94"/>
+      <x:c r="B94"/>
+      <x:c r="C94"/>
+      <x:c r="D94"/>
+      <x:c r="E94"/>
+      <x:c r="F94"/>
+      <x:c r="G94"/>
+      <x:c r="H94"/>
+      <x:c r="I94"/>
     </x:row>
     <x:row r="95" ht="26" customHeight="1">
-      <x:c r="A95" s="25"/>
-      <x:c r="B95" s="25" t="str">
-        <x:v>Wheel ΔZ (mm)</x:v>
-      </x:c>
-      <x:c r="C95" s="48" t="n">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="D95" s="25"/>
-      <x:c r="E95" s="25"/>
-      <x:c r="F95" s="25"/>
-      <x:c r="G95" s="25"/>
-      <x:c r="H95" s="25"/>
-      <x:c r="I95" s="25"/>
+      <x:c r="A95"/>
+      <x:c r="B95"/>
+      <x:c r="C95"/>
+      <x:c r="D95"/>
+      <x:c r="E95"/>
+      <x:c r="F95"/>
+      <x:c r="G95"/>
+      <x:c r="H95"/>
+      <x:c r="I95"/>
     </x:row>
     <x:row r="96" ht="40" customHeight="1">
-      <x:c r="A96" s="25"/>
-      <x:c r="B96" s="32" t="str">
-        <x:v>State</x:v>
-      </x:c>
-      <x:c r="C96" s="32" t="str">
-        <x:v>arb1 Y (m)</x:v>
-      </x:c>
-      <x:c r="D96" s="32" t="str">
-        <x:v>arb1 Z (m)</x:v>
-      </x:c>
-      <x:c r="E96" s="32" t="str">
-        <x:v>arb2 Y (m)</x:v>
-      </x:c>
-      <x:c r="F96" s="32" t="str">
-        <x:v>arb2 Z (m)</x:v>
-      </x:c>
-      <x:c r="G96" s="32" t="str">
-        <x:v>Arm angle (°)</x:v>
-      </x:c>
-      <x:c r="H96" s="32" t="str">
-        <x:v>Radius (mm)</x:v>
-      </x:c>
-      <x:c r="I96" s="25"/>
+      <x:c r="A96"/>
+      <x:c r="B96"/>
+      <x:c r="C96"/>
+      <x:c r="D96"/>
+      <x:c r="E96"/>
+      <x:c r="F96"/>
+      <x:c r="G96"/>
+      <x:c r="H96"/>
+      <x:c r="I96"/>
     </x:row>
     <x:row r="97" ht="26" customHeight="1">
-      <x:c r="A97" s="25"/>
-      <x:c r="B97" s="34" t="str">
-        <x:v>Start</x:v>
-      </x:c>
-      <x:c r="C97" s="49"/>
-      <x:c r="D97" s="49"/>
-      <x:c r="E97" s="49"/>
-      <x:c r="F97" s="49"/>
-      <x:c r="G97" s="51" t="str">
-        <x:f>IF(COUNT(C97:F97)&lt;4,"",IF(H97=0,"无效半径",IF(D97&lt;F97,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E97-C97)*1000/H97))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H97" s="53" t="str">
-        <x:f>IF(COUNT(C97:F97)&lt;4,"",1000*SQRT((C97-E97)^2+(D97-F97)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I97" s="25"/>
+      <x:c r="A97"/>
+      <x:c r="B97"/>
+      <x:c r="C97"/>
+      <x:c r="D97"/>
+      <x:c r="E97"/>
+      <x:c r="F97"/>
+      <x:c r="G97"/>
+      <x:c r="H97"/>
+      <x:c r="I97"/>
     </x:row>
     <x:row r="98" ht="26" customHeight="1">
-      <x:c r="A98" s="25"/>
-      <x:c r="B98" s="35" t="str">
-        <x:v>End</x:v>
-      </x:c>
-      <x:c r="C98" s="49"/>
-      <x:c r="D98" s="49"/>
-      <x:c r="E98" s="49"/>
-      <x:c r="F98" s="49"/>
-      <x:c r="G98" s="50" t="str">
-        <x:f>IF(COUNT(C98:F98)&lt;4,"",IF(H98=0,"无效半径",IF(D98&lt;F98,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E98-C98)*1000/H98))))))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="H98" s="52" t="str">
-        <x:f>IF(COUNT(C98:F98)&lt;4,"",1000*SQRT((C98-E98)^2+(D98-F98)^2))</x:f>
-        <x:v/>
-      </x:c>
-      <x:c r="I98" s="25"/>
+      <x:c r="A98"/>
+      <x:c r="B98"/>
+      <x:c r="C98"/>
+      <x:c r="D98"/>
+      <x:c r="E98"/>
+      <x:c r="F98"/>
+      <x:c r="G98"/>
+      <x:c r="H98"/>
+      <x:c r="I98"/>
     </x:row>
     <x:row r="99" ht="26" customHeight="1">
-      <x:c r="A99" s="25"/>
-      <x:c r="B99" s="25"/>
-      <x:c r="C99" s="25"/>
-      <x:c r="D99" s="25"/>
-      <x:c r="E99" s="25"/>
-      <x:c r="F99" s="25"/>
-      <x:c r="G99" s="25"/>
-      <x:c r="H99" s="25"/>
-      <x:c r="I99" s="25"/>
+      <x:c r="A99"/>
+      <x:c r="B99"/>
+      <x:c r="C99"/>
+      <x:c r="D99"/>
+      <x:c r="E99"/>
+      <x:c r="F99"/>
+      <x:c r="G99"/>
+      <x:c r="H99"/>
+      <x:c r="I99"/>
     </x:row>
     <x:row r="100" ht="26" customHeight="1">
-      <x:c r="A100" s="25"/>
-      <x:c r="B100" s="25"/>
-      <x:c r="C100" s="25"/>
-      <x:c r="D100" s="25"/>
-      <x:c r="E100" s="25"/>
-      <x:c r="F100" s="25"/>
-      <x:c r="G100" s="25"/>
-      <x:c r="H100" s="25"/>
-      <x:c r="I100" s="25"/>
+      <x:c r="A100"/>
+      <x:c r="B100"/>
+      <x:c r="C100"/>
+      <x:c r="D100"/>
+      <x:c r="E100"/>
+      <x:c r="F100"/>
+      <x:c r="G100"/>
+      <x:c r="H100"/>
+      <x:c r="I100"/>
     </x:row>
     <x:row r="101" ht="26" customHeight="1">
-      <x:c r="A101" s="25"/>
-      <x:c r="B101" s="25"/>
-      <x:c r="C101" s="25"/>
-      <x:c r="D101" s="25"/>
-      <x:c r="E101" s="25"/>
-      <x:c r="F101" s="25"/>
-      <x:c r="G101" s="25"/>
-      <x:c r="H101" s="25"/>
-      <x:c r="I101" s="25"/>
+      <x:c r="A101"/>
+      <x:c r="B101"/>
+      <x:c r="C101"/>
+      <x:c r="D101"/>
+      <x:c r="E101"/>
+      <x:c r="F101"/>
+      <x:c r="G101"/>
+      <x:c r="H101"/>
+      <x:c r="I101"/>
     </x:row>
     <x:row r="102" ht="26" customHeight="1">
-      <x:c r="A102" s="25"/>
-      <x:c r="B102" s="55" t="str">
-        <x:v>原 Z 测量记录（不参与刚度计算）</x:v>
-      </x:c>
-      <x:c r="C102" s="55" t="str">
-        <x:v>原 Z 测量记录（不参与刚度计算）</x:v>
-      </x:c>
-      <x:c r="D102" s="55" t="str">
-        <x:v>原 Z 测量记录（不参与刚度计算）</x:v>
-      </x:c>
-      <x:c r="E102" s="55" t="str">
-        <x:v>原 Z 测量记录（不参与刚度计算）</x:v>
-      </x:c>
-      <x:c r="F102" s="55" t="str">
-        <x:v>原 Z 测量记录（不参与刚度计算）</x:v>
-      </x:c>
-      <x:c r="G102" s="55" t="str">
-        <x:v>原 Z 测量记录（不参与刚度计算）</x:v>
-      </x:c>
-      <x:c r="H102" s="55" t="str">
-        <x:v>原 Z 测量记录（不参与刚度计算）</x:v>
-      </x:c>
-      <x:c r="I102" s="25"/>
+      <x:c r="A102"/>
+      <x:c r="B102"/>
+      <x:c r="C102"/>
+      <x:c r="D102"/>
+      <x:c r="E102"/>
+      <x:c r="F102"/>
+      <x:c r="G102"/>
+      <x:c r="H102"/>
+      <x:c r="I102"/>
     </x:row>
     <x:row r="103" ht="40" customHeight="1">
-      <x:c r="A103" s="25"/>
-      <x:c r="B103" s="32" t="str">
-        <x:v>Surface</x:v>
-      </x:c>
-      <x:c r="C103" s="32" t="str">
-        <x:v>Axle</x:v>
-      </x:c>
-      <x:c r="D103" s="32" t="str">
-        <x:v>Position</x:v>
-      </x:c>
-      <x:c r="E103" s="32" t="str">
-        <x:v>ARB ΔZ (mm)</x:v>
-      </x:c>
-      <x:c r="F103" s="32" t="str">
-        <x:v>Original arm (mm)</x:v>
-      </x:c>
-      <x:c r="G103" s="25"/>
-      <x:c r="H103" s="25"/>
-      <x:c r="I103" s="25"/>
+      <x:c r="A103"/>
+      <x:c r="B103"/>
+      <x:c r="C103"/>
+      <x:c r="D103"/>
+      <x:c r="E103"/>
+      <x:c r="F103"/>
+      <x:c r="G103"/>
+      <x:c r="H103"/>
+      <x:c r="I103"/>
     </x:row>
     <x:row r="104" ht="26" customHeight="1">
-      <x:c r="A104" s="25"/>
-      <x:c r="B104" s="35" t="str">
-        <x:v>Tarmac</x:v>
-      </x:c>
-      <x:c r="C104" s="35" t="str">
-        <x:v>Front</x:v>
-      </x:c>
-      <x:c r="D104" s="35" t="str">
-        <x:v>Inner</x:v>
-      </x:c>
-      <x:c r="E104" s="52" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F104" s="52" t="n">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="G104" s="25"/>
-      <x:c r="H104" s="25"/>
-      <x:c r="I104" s="25"/>
+      <x:c r="A104"/>
+      <x:c r="B104"/>
+      <x:c r="C104"/>
+      <x:c r="D104"/>
+      <x:c r="E104"/>
+      <x:c r="F104"/>
+      <x:c r="G104"/>
+      <x:c r="H104"/>
+      <x:c r="I104"/>
     </x:row>
     <x:row r="105" ht="26" customHeight="1">
-      <x:c r="A105" s="25"/>
-      <x:c r="B105" s="34" t="str">
-        <x:v>Tarmac</x:v>
-      </x:c>
-      <x:c r="C105" s="34" t="str">
-        <x:v>Front</x:v>
-      </x:c>
-      <x:c r="D105" s="34" t="str">
-        <x:v>Middle</x:v>
-      </x:c>
-      <x:c r="E105" s="53" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F105" s="53" t="n">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="G105" s="25"/>
-      <x:c r="H105" s="25"/>
-      <x:c r="I105" s="25"/>
+      <x:c r="A105"/>
+      <x:c r="B105"/>
+      <x:c r="C105"/>
+      <x:c r="D105"/>
+      <x:c r="E105"/>
+      <x:c r="F105"/>
+      <x:c r="G105"/>
+      <x:c r="H105"/>
+      <x:c r="I105"/>
     </x:row>
     <x:row r="106" ht="26" customHeight="1">
-      <x:c r="A106" s="25"/>
-      <x:c r="B106" s="35" t="str">
-        <x:v>Tarmac</x:v>
-      </x:c>
-      <x:c r="C106" s="35" t="str">
-        <x:v>Front</x:v>
-      </x:c>
-      <x:c r="D106" s="35" t="str">
-        <x:v>Outer</x:v>
-      </x:c>
-      <x:c r="E106" s="52" t="n">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F106" s="52" t="n">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="G106" s="25"/>
-      <x:c r="H106" s="25"/>
-      <x:c r="I106" s="25"/>
+      <x:c r="A106"/>
+      <x:c r="B106"/>
+      <x:c r="C106"/>
+      <x:c r="D106"/>
+      <x:c r="E106"/>
+      <x:c r="F106"/>
+      <x:c r="G106"/>
+      <x:c r="H106"/>
+      <x:c r="I106"/>
     </x:row>
     <x:row r="107" ht="26" customHeight="1">
-      <x:c r="A107" s="25"/>
-      <x:c r="B107" s="34" t="str">
-        <x:v>Tarmac</x:v>
-      </x:c>
-      <x:c r="C107" s="34" t="str">
-        <x:v>Rear</x:v>
-      </x:c>
-      <x:c r="D107" s="34" t="str">
-        <x:v>Inner</x:v>
-      </x:c>
-      <x:c r="E107" s="53" t="n">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F107" s="53" t="n">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="G107" s="25"/>
-      <x:c r="H107" s="25"/>
-      <x:c r="I107" s="25"/>
+      <x:c r="A107"/>
+      <x:c r="B107"/>
+      <x:c r="C107"/>
+      <x:c r="D107"/>
+      <x:c r="E107"/>
+      <x:c r="F107"/>
+      <x:c r="G107"/>
+      <x:c r="H107"/>
+      <x:c r="I107"/>
     </x:row>
     <x:row r="108" ht="26" customHeight="1">
-      <x:c r="A108" s="25"/>
-      <x:c r="B108" s="35" t="str">
-        <x:v>Tarmac</x:v>
-      </x:c>
-      <x:c r="C108" s="35" t="str">
-        <x:v>Rear</x:v>
-      </x:c>
-      <x:c r="D108" s="35" t="str">
-        <x:v>Middle</x:v>
-      </x:c>
-      <x:c r="E108" s="52" t="n">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F108" s="52" t="n">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="G108" s="25"/>
-      <x:c r="H108" s="25"/>
-      <x:c r="I108" s="25"/>
+      <x:c r="A108"/>
+      <x:c r="B108"/>
+      <x:c r="C108"/>
+      <x:c r="D108"/>
+      <x:c r="E108"/>
+      <x:c r="F108"/>
+      <x:c r="G108"/>
+      <x:c r="H108"/>
+      <x:c r="I108"/>
     </x:row>
     <x:row r="109" ht="26" customHeight="1">
-      <x:c r="A109" s="25"/>
-      <x:c r="B109" s="34" t="str">
-        <x:v>Tarmac</x:v>
-      </x:c>
-      <x:c r="C109" s="34" t="str">
-        <x:v>Rear</x:v>
-      </x:c>
-      <x:c r="D109" s="34" t="str">
-        <x:v>Outer</x:v>
-      </x:c>
-      <x:c r="E109" s="53" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F109" s="53" t="n">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="G109" s="25"/>
-      <x:c r="H109" s="25"/>
-      <x:c r="I109" s="25"/>
+      <x:c r="A109"/>
+      <x:c r="B109"/>
+      <x:c r="C109"/>
+      <x:c r="D109"/>
+      <x:c r="E109"/>
+      <x:c r="F109"/>
+      <x:c r="G109"/>
+      <x:c r="H109"/>
+      <x:c r="I109"/>
     </x:row>
     <x:row r="110" ht="26" customHeight="1">
-      <x:c r="A110" s="25"/>
-      <x:c r="B110" s="35" t="str">
-        <x:v>Gravel</x:v>
-      </x:c>
-      <x:c r="C110" s="35" t="str">
-        <x:v>Front</x:v>
-      </x:c>
-      <x:c r="D110" s="35" t="str">
-        <x:v>Inner</x:v>
-      </x:c>
-      <x:c r="E110" s="52" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F110" s="52" t="n">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="G110" s="25"/>
-      <x:c r="H110" s="25"/>
-      <x:c r="I110" s="25"/>
+      <x:c r="A110"/>
+      <x:c r="B110"/>
+      <x:c r="C110"/>
+      <x:c r="D110"/>
+      <x:c r="E110"/>
+      <x:c r="F110"/>
+      <x:c r="G110"/>
+      <x:c r="H110"/>
+      <x:c r="I110"/>
     </x:row>
     <x:row r="111" ht="26" customHeight="1">
-      <x:c r="A111" s="25"/>
-      <x:c r="B111" s="34" t="str">
-        <x:v>Gravel</x:v>
-      </x:c>
-      <x:c r="C111" s="34" t="str">
-        <x:v>Front</x:v>
-      </x:c>
-      <x:c r="D111" s="34" t="str">
-        <x:v>Middle</x:v>
-      </x:c>
-      <x:c r="E111" s="53" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F111" s="53" t="n">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="G111" s="25"/>
-      <x:c r="H111" s="25"/>
-      <x:c r="I111" s="25"/>
+      <x:c r="A111"/>
+      <x:c r="B111"/>
+      <x:c r="C111"/>
+      <x:c r="D111"/>
+      <x:c r="E111"/>
+      <x:c r="F111"/>
+      <x:c r="G111"/>
+      <x:c r="H111"/>
+      <x:c r="I111"/>
     </x:row>
     <x:row r="112" ht="26" customHeight="1">
-      <x:c r="A112" s="25"/>
-      <x:c r="B112" s="35" t="str">
-        <x:v>Gravel</x:v>
-      </x:c>
-      <x:c r="C112" s="35" t="str">
-        <x:v>Front</x:v>
-      </x:c>
-      <x:c r="D112" s="35" t="str">
-        <x:v>Outer</x:v>
-      </x:c>
-      <x:c r="E112" s="52" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F112" s="52" t="n">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="G112" s="25"/>
-      <x:c r="H112" s="25"/>
-      <x:c r="I112" s="25"/>
+      <x:c r="A112"/>
+      <x:c r="B112"/>
+      <x:c r="C112"/>
+      <x:c r="D112"/>
+      <x:c r="E112"/>
+      <x:c r="F112"/>
+      <x:c r="G112"/>
+      <x:c r="H112"/>
+      <x:c r="I112"/>
     </x:row>
     <x:row r="113" ht="26" customHeight="1">
-      <x:c r="A113" s="25"/>
-      <x:c r="B113" s="34" t="str">
-        <x:v>Gravel</x:v>
-      </x:c>
-      <x:c r="C113" s="34" t="str">
-        <x:v>Rear</x:v>
-      </x:c>
-      <x:c r="D113" s="34" t="str">
-        <x:v>Inner</x:v>
-      </x:c>
-      <x:c r="E113" s="53" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F113" s="53" t="n">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="G113" s="25"/>
-      <x:c r="H113" s="25"/>
-      <x:c r="I113" s="25"/>
+      <x:c r="A113"/>
+      <x:c r="B113"/>
+      <x:c r="C113"/>
+      <x:c r="D113"/>
+      <x:c r="E113"/>
+      <x:c r="F113"/>
+      <x:c r="G113"/>
+      <x:c r="H113"/>
+      <x:c r="I113"/>
     </x:row>
     <x:row r="114" ht="26" customHeight="1">
-      <x:c r="A114" s="25"/>
-      <x:c r="B114" s="35" t="str">
-        <x:v>Gravel</x:v>
-      </x:c>
-      <x:c r="C114" s="35" t="str">
-        <x:v>Rear</x:v>
-      </x:c>
-      <x:c r="D114" s="35" t="str">
-        <x:v>Middle</x:v>
-      </x:c>
-      <x:c r="E114" s="52" t="n">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F114" s="52" t="n">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="G114" s="25"/>
-      <x:c r="H114" s="25"/>
-      <x:c r="I114" s="25"/>
+      <x:c r="A114"/>
+      <x:c r="B114"/>
+      <x:c r="C114"/>
+      <x:c r="D114"/>
+      <x:c r="E114"/>
+      <x:c r="F114"/>
+      <x:c r="G114"/>
+      <x:c r="H114"/>
+      <x:c r="I114"/>
     </x:row>
     <x:row r="115" ht="26" customHeight="1">
-      <x:c r="A115" s="25"/>
-      <x:c r="B115" s="34" t="str">
-        <x:v>Gravel</x:v>
-      </x:c>
-      <x:c r="C115" s="34" t="str">
-        <x:v>Rear</x:v>
-      </x:c>
-      <x:c r="D115" s="34" t="str">
-        <x:v>Outer</x:v>
-      </x:c>
-      <x:c r="E115" s="53" t="n">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F115" s="53" t="n">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="G115" s="25"/>
-      <x:c r="H115" s="25"/>
-      <x:c r="I115" s="25"/>
+      <x:c r="A115"/>
+      <x:c r="B115"/>
+      <x:c r="C115"/>
+      <x:c r="D115"/>
+      <x:c r="E115"/>
+      <x:c r="F115"/>
+      <x:c r="G115"/>
+      <x:c r="H115"/>
+      <x:c r="I115"/>
     </x:row>
     <x:row r="116" ht="26" customHeight="1">
-      <x:c r="A116" s="25"/>
-      <x:c r="B116" s="25"/>
-      <x:c r="C116" s="25"/>
-      <x:c r="D116" s="25"/>
-      <x:c r="E116" s="25"/>
-      <x:c r="F116" s="25"/>
-      <x:c r="G116" s="25"/>
-      <x:c r="H116" s="25"/>
-      <x:c r="I116" s="25"/>
+      <x:c r="A116"/>
+      <x:c r="B116"/>
+      <x:c r="C116"/>
+      <x:c r="D116"/>
+      <x:c r="E116"/>
+      <x:c r="F116"/>
+      <x:c r="G116"/>
+      <x:c r="H116"/>
+      <x:c r="I116"/>
     </x:row>
     <x:row r="117" ht="26" customHeight="1">
-      <x:c r="A117" s="25"/>
-      <x:c r="B117" s="25"/>
-      <x:c r="C117" s="25"/>
-      <x:c r="D117" s="25"/>
-      <x:c r="E117" s="25"/>
-      <x:c r="F117" s="25"/>
-      <x:c r="G117" s="25"/>
-      <x:c r="H117" s="25"/>
-      <x:c r="I117" s="25"/>
+      <x:c r="A117"/>
+      <x:c r="B117"/>
+      <x:c r="C117"/>
+      <x:c r="D117"/>
+      <x:c r="E117"/>
+      <x:c r="F117"/>
+      <x:c r="G117"/>
+      <x:c r="H117"/>
+      <x:c r="I117"/>
     </x:row>
     <x:row r="118" ht="26" customHeight="1">
-      <x:c r="A118" s="25"/>
-      <x:c r="B118" s="25"/>
-      <x:c r="C118" s="25"/>
-      <x:c r="D118" s="25"/>
-      <x:c r="E118" s="25"/>
-      <x:c r="F118" s="25"/>
-      <x:c r="G118" s="25"/>
-      <x:c r="H118" s="25"/>
-      <x:c r="I118" s="25"/>
+      <x:c r="A118"/>
+      <x:c r="B118"/>
+      <x:c r="C118"/>
+      <x:c r="D118"/>
+      <x:c r="E118"/>
+      <x:c r="F118"/>
+      <x:c r="G118"/>
+      <x:c r="H118"/>
+      <x:c r="I118"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B2:H3"/>
-    <x:mergeCell ref="B4:H4"/>
-    <x:mergeCell ref="B14:H14"/>
-    <x:mergeCell ref="B15:H15"/>
-    <x:mergeCell ref="B17:H17"/>
-    <x:mergeCell ref="B24:H24"/>
-    <x:mergeCell ref="B31:H31"/>
-    <x:mergeCell ref="B38:H38"/>
-    <x:mergeCell ref="B45:H45"/>
-    <x:mergeCell ref="B52:H52"/>
-    <x:mergeCell ref="B59:H59"/>
-    <x:mergeCell ref="B66:H66"/>
-    <x:mergeCell ref="B73:H73"/>
-    <x:mergeCell ref="B80:H80"/>
-    <x:mergeCell ref="B87:H87"/>
-    <x:mergeCell ref="B94:H94"/>
-    <x:mergeCell ref="B102:H102"/>
+    <x:mergeCell ref="B2:I3"/>
+    <x:mergeCell ref="B4:I4"/>
+    <x:mergeCell ref="B14:I14"/>
+    <x:mergeCell ref="B15:I15"/>
+    <x:mergeCell ref="B20:I20"/>
+    <x:mergeCell ref="B38:I38"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -4469,11 +4719,11 @@
         <x:v>Inner</x:v>
       </x:c>
       <x:c r="E6" s="52">
-        <x:f>IF(ISNUMBER(Parameters!C18),Parameters!C18,"")</x:f>
+        <x:f>IF(ISNUMBER(Parameters!E23),Parameters!E23,"")</x:f>
         <x:v>127</x:v>
       </x:c>
       <x:c r="F6" s="56" t="str">
-        <x:f>IF(COUNT(Parameters!G20:G21)&lt;2,"",MOD(Parameters!G21-Parameters!G20+180,360)-180)</x:f>
+        <x:f>IF(COUNT(Parameters!G17,Parameters!H23)&lt;2,"",MOD(Parameters!H23-Parameters!G17+180,360)-180)</x:f>
         <x:v/>
       </x:c>
       <x:c r="G6" s="58" t="str">
@@ -4493,7 +4743,7 @@
         <x:v/>
       </x:c>
       <x:c r="K6" s="60" t="str">
-        <x:f>IF(COUNT(Parameters!C20:F21)&lt;8,"待补坐标",IF(NOT(ISNUMBER(E6)),"待填轮行程",IF(E6&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G20:G21)&lt;2,"无效半径",""))))</x:f>
+        <x:f>IF(COUNT(Parameters!C17:F17,Parameters!F23:G23)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E6)),"待填轮行程",IF(E6&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G17,Parameters!H23)&lt;2,"无效半径",""))))</x:f>
         <x:v>待补坐标</x:v>
       </x:c>
       <x:c r="L6" s="25"/>
@@ -4514,11 +4764,11 @@
         <x:v>Middle</x:v>
       </x:c>
       <x:c r="E7" s="53">
-        <x:f>IF(ISNUMBER(Parameters!C25),Parameters!C25,"")</x:f>
+        <x:f>IF(ISNUMBER(Parameters!E24),Parameters!E24,"")</x:f>
         <x:v>127</x:v>
       </x:c>
       <x:c r="F7" s="57" t="str">
-        <x:f>IF(COUNT(Parameters!G27:G28)&lt;2,"",MOD(Parameters!G28-Parameters!G27+180,360)-180)</x:f>
+        <x:f>IF(COUNT(Parameters!G17,Parameters!H24)&lt;2,"",MOD(Parameters!H24-Parameters!G17+180,360)-180)</x:f>
         <x:v/>
       </x:c>
       <x:c r="G7" s="59" t="str">
@@ -4538,7 +4788,7 @@
         <x:v/>
       </x:c>
       <x:c r="K7" s="61" t="str">
-        <x:f>IF(COUNT(Parameters!C27:F28)&lt;8,"待补坐标",IF(NOT(ISNUMBER(E7)),"待填轮行程",IF(E7&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G27:G28)&lt;2,"无效半径",""))))</x:f>
+        <x:f>IF(COUNT(Parameters!C17:F17,Parameters!F24:G24)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E7)),"待填轮行程",IF(E7&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G17,Parameters!H24)&lt;2,"无效半径",""))))</x:f>
         <x:v>待补坐标</x:v>
       </x:c>
       <x:c r="L7" s="25"/>
@@ -4559,11 +4809,11 @@
         <x:v>Outer</x:v>
       </x:c>
       <x:c r="E8" s="52">
-        <x:f>IF(ISNUMBER(Parameters!C32),Parameters!C32,"")</x:f>
+        <x:f>IF(ISNUMBER(Parameters!E25),Parameters!E25,"")</x:f>
         <x:v>127</x:v>
       </x:c>
       <x:c r="F8" s="56" t="str">
-        <x:f>IF(COUNT(Parameters!G34:G35)&lt;2,"",MOD(Parameters!G35-Parameters!G34+180,360)-180)</x:f>
+        <x:f>IF(COUNT(Parameters!G17,Parameters!H25)&lt;2,"",MOD(Parameters!H25-Parameters!G17+180,360)-180)</x:f>
         <x:v/>
       </x:c>
       <x:c r="G8" s="58" t="str">
@@ -4583,7 +4833,7 @@
         <x:v/>
       </x:c>
       <x:c r="K8" s="60" t="str">
-        <x:f>IF(COUNT(Parameters!C34:F35)&lt;8,"待补坐标",IF(NOT(ISNUMBER(E8)),"待填轮行程",IF(E8&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G34:G35)&lt;2,"无效半径",""))))</x:f>
+        <x:f>IF(COUNT(Parameters!C17:F17,Parameters!F25:G25)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E8)),"待填轮行程",IF(E8&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G17,Parameters!H25)&lt;2,"无效半径",""))))</x:f>
         <x:v>待补坐标</x:v>
       </x:c>
       <x:c r="L8" s="25"/>
@@ -4604,11 +4854,11 @@
         <x:v>Inner</x:v>
       </x:c>
       <x:c r="E9" s="53">
-        <x:f>IF(ISNUMBER(Parameters!C39),Parameters!C39,"")</x:f>
+        <x:f>IF(ISNUMBER(Parameters!E26),Parameters!E26,"")</x:f>
         <x:v>136</x:v>
       </x:c>
       <x:c r="F9" s="57" t="str">
-        <x:f>IF(COUNT(Parameters!G41:G42)&lt;2,"",MOD(Parameters!G42-Parameters!G41+180,360)-180)</x:f>
+        <x:f>IF(COUNT(Parameters!G18,Parameters!H26)&lt;2,"",MOD(Parameters!H26-Parameters!G18+180,360)-180)</x:f>
         <x:v/>
       </x:c>
       <x:c r="G9" s="59" t="str">
@@ -4628,7 +4878,7 @@
         <x:v/>
       </x:c>
       <x:c r="K9" s="61" t="str">
-        <x:f>IF(COUNT(Parameters!C41:F42)&lt;8,"待补坐标",IF(NOT(ISNUMBER(E9)),"待填轮行程",IF(E9&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G41:G42)&lt;2,"无效半径",""))))</x:f>
+        <x:f>IF(COUNT(Parameters!C18:F18,Parameters!F26:G26)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E9)),"待填轮行程",IF(E9&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G18,Parameters!H26)&lt;2,"无效半径",""))))</x:f>
         <x:v>待补坐标</x:v>
       </x:c>
       <x:c r="L9" s="25"/>
@@ -4649,11 +4899,11 @@
         <x:v>Middle</x:v>
       </x:c>
       <x:c r="E10" s="52">
-        <x:f>IF(ISNUMBER(Parameters!C46),Parameters!C46,"")</x:f>
+        <x:f>IF(ISNUMBER(Parameters!E27),Parameters!E27,"")</x:f>
         <x:v>136</x:v>
       </x:c>
       <x:c r="F10" s="56" t="str">
-        <x:f>IF(COUNT(Parameters!G48:G49)&lt;2,"",MOD(Parameters!G49-Parameters!G48+180,360)-180)</x:f>
+        <x:f>IF(COUNT(Parameters!G18,Parameters!H27)&lt;2,"",MOD(Parameters!H27-Parameters!G18+180,360)-180)</x:f>
         <x:v/>
       </x:c>
       <x:c r="G10" s="58" t="str">
@@ -4673,7 +4923,7 @@
         <x:v/>
       </x:c>
       <x:c r="K10" s="60" t="str">
-        <x:f>IF(COUNT(Parameters!C48:F49)&lt;8,"待补坐标",IF(NOT(ISNUMBER(E10)),"待填轮行程",IF(E10&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G48:G49)&lt;2,"无效半径",""))))</x:f>
+        <x:f>IF(COUNT(Parameters!C18:F18,Parameters!F27:G27)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E10)),"待填轮行程",IF(E10&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G18,Parameters!H27)&lt;2,"无效半径",""))))</x:f>
         <x:v>待补坐标</x:v>
       </x:c>
       <x:c r="L10" s="25"/>
@@ -4694,11 +4944,11 @@
         <x:v>Outer</x:v>
       </x:c>
       <x:c r="E11" s="53">
-        <x:f>IF(ISNUMBER(Parameters!C53),Parameters!C53,"")</x:f>
+        <x:f>IF(ISNUMBER(Parameters!E28),Parameters!E28,"")</x:f>
         <x:v>136</x:v>
       </x:c>
       <x:c r="F11" s="57" t="str">
-        <x:f>IF(COUNT(Parameters!G55:G56)&lt;2,"",MOD(Parameters!G56-Parameters!G55+180,360)-180)</x:f>
+        <x:f>IF(COUNT(Parameters!G18,Parameters!H28)&lt;2,"",MOD(Parameters!H28-Parameters!G18+180,360)-180)</x:f>
         <x:v/>
       </x:c>
       <x:c r="G11" s="59" t="str">
@@ -4718,7 +4968,7 @@
         <x:v/>
       </x:c>
       <x:c r="K11" s="61" t="str">
-        <x:f>IF(COUNT(Parameters!C55:F56)&lt;8,"待补坐标",IF(NOT(ISNUMBER(E11)),"待填轮行程",IF(E11&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G55:G56)&lt;2,"无效半径",""))))</x:f>
+        <x:f>IF(COUNT(Parameters!C18:F18,Parameters!F28:G28)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E11)),"待填轮行程",IF(E11&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G18,Parameters!H28)&lt;2,"无效半径",""))))</x:f>
         <x:v>待补坐标</x:v>
       </x:c>
       <x:c r="L11" s="25"/>
@@ -4739,11 +4989,11 @@
         <x:v>Inner</x:v>
       </x:c>
       <x:c r="E12" s="52">
-        <x:f>IF(ISNUMBER(Parameters!C60),Parameters!C60,"")</x:f>
+        <x:f>IF(ISNUMBER(Parameters!E29),Parameters!E29,"")</x:f>
         <x:v>126</x:v>
       </x:c>
       <x:c r="F12" s="56" t="str">
-        <x:f>IF(COUNT(Parameters!G62:G63)&lt;2,"",MOD(Parameters!G63-Parameters!G62+180,360)-180)</x:f>
+        <x:f>IF(COUNT(Parameters!G17,Parameters!H29)&lt;2,"",MOD(Parameters!H29-Parameters!G17+180,360)-180)</x:f>
         <x:v/>
       </x:c>
       <x:c r="G12" s="58" t="str">
@@ -4763,7 +5013,7 @@
         <x:v/>
       </x:c>
       <x:c r="K12" s="60" t="str">
-        <x:f>IF(COUNT(Parameters!C62:F63)&lt;8,"待补坐标",IF(NOT(ISNUMBER(E12)),"待填轮行程",IF(E12&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G62:G63)&lt;2,"无效半径",""))))</x:f>
+        <x:f>IF(COUNT(Parameters!C17:F17,Parameters!F29:G29)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E12)),"待填轮行程",IF(E12&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G17,Parameters!H29)&lt;2,"无效半径",""))))</x:f>
         <x:v>待补坐标</x:v>
       </x:c>
       <x:c r="L12" s="25"/>
@@ -4784,11 +5034,11 @@
         <x:v>Middle</x:v>
       </x:c>
       <x:c r="E13" s="53">
-        <x:f>IF(ISNUMBER(Parameters!C67),Parameters!C67,"")</x:f>
+        <x:f>IF(ISNUMBER(Parameters!E30),Parameters!E30,"")</x:f>
         <x:v>126</x:v>
       </x:c>
       <x:c r="F13" s="57" t="str">
-        <x:f>IF(COUNT(Parameters!G69:G70)&lt;2,"",MOD(Parameters!G70-Parameters!G69+180,360)-180)</x:f>
+        <x:f>IF(COUNT(Parameters!G17,Parameters!H30)&lt;2,"",MOD(Parameters!H30-Parameters!G17+180,360)-180)</x:f>
         <x:v/>
       </x:c>
       <x:c r="G13" s="59" t="str">
@@ -4808,7 +5058,7 @@
         <x:v/>
       </x:c>
       <x:c r="K13" s="61" t="str">
-        <x:f>IF(COUNT(Parameters!C69:F70)&lt;8,"待补坐标",IF(NOT(ISNUMBER(E13)),"待填轮行程",IF(E13&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G69:G70)&lt;2,"无效半径",""))))</x:f>
+        <x:f>IF(COUNT(Parameters!C17:F17,Parameters!F30:G30)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E13)),"待填轮行程",IF(E13&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G17,Parameters!H30)&lt;2,"无效半径",""))))</x:f>
         <x:v>待补坐标</x:v>
       </x:c>
       <x:c r="L13" s="25"/>
@@ -4829,11 +5079,11 @@
         <x:v>Outer</x:v>
       </x:c>
       <x:c r="E14" s="52">
-        <x:f>IF(ISNUMBER(Parameters!C74),Parameters!C74,"")</x:f>
+        <x:f>IF(ISNUMBER(Parameters!E31),Parameters!E31,"")</x:f>
         <x:v>126</x:v>
       </x:c>
       <x:c r="F14" s="56" t="str">
-        <x:f>IF(COUNT(Parameters!G76:G77)&lt;2,"",MOD(Parameters!G77-Parameters!G76+180,360)-180)</x:f>
+        <x:f>IF(COUNT(Parameters!G17,Parameters!H31)&lt;2,"",MOD(Parameters!H31-Parameters!G17+180,360)-180)</x:f>
         <x:v/>
       </x:c>
       <x:c r="G14" s="58" t="str">
@@ -4853,7 +5103,7 @@
         <x:v/>
       </x:c>
       <x:c r="K14" s="60" t="str">
-        <x:f>IF(COUNT(Parameters!C76:F77)&lt;8,"待补坐标",IF(NOT(ISNUMBER(E14)),"待填轮行程",IF(E14&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G76:G77)&lt;2,"无效半径",""))))</x:f>
+        <x:f>IF(COUNT(Parameters!C17:F17,Parameters!F31:G31)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E14)),"待填轮行程",IF(E14&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G17,Parameters!H31)&lt;2,"无效半径",""))))</x:f>
         <x:v>待补坐标</x:v>
       </x:c>
       <x:c r="L14" s="25"/>
@@ -4872,11 +5122,11 @@
         <x:v>Inner</x:v>
       </x:c>
       <x:c r="E15" s="53">
-        <x:f>IF(ISNUMBER(Parameters!C81),Parameters!C81,"")</x:f>
+        <x:f>IF(ISNUMBER(Parameters!E32),Parameters!E32,"")</x:f>
         <x:v>127</x:v>
       </x:c>
       <x:c r="F15" s="57" t="str">
-        <x:f>IF(COUNT(Parameters!G83:G84)&lt;2,"",MOD(Parameters!G84-Parameters!G83+180,360)-180)</x:f>
+        <x:f>IF(COUNT(Parameters!G18,Parameters!H32)&lt;2,"",MOD(Parameters!H32-Parameters!G18+180,360)-180)</x:f>
         <x:v/>
       </x:c>
       <x:c r="G15" s="59" t="str">
@@ -4896,7 +5146,7 @@
         <x:v/>
       </x:c>
       <x:c r="K15" s="61" t="str">
-        <x:f>IF(COUNT(Parameters!C83:F84)&lt;8,"待补坐标",IF(NOT(ISNUMBER(E15)),"待填轮行程",IF(E15&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G83:G84)&lt;2,"无效半径",""))))</x:f>
+        <x:f>IF(COUNT(Parameters!C18:F18,Parameters!F32:G32)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E15)),"待填轮行程",IF(E15&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G18,Parameters!H32)&lt;2,"无效半径",""))))</x:f>
         <x:v>待补坐标</x:v>
       </x:c>
       <x:c r="L15" s="25"/>
@@ -4915,11 +5165,11 @@
         <x:v>Middle</x:v>
       </x:c>
       <x:c r="E16" s="52">
-        <x:f>IF(ISNUMBER(Parameters!C88),Parameters!C88,"")</x:f>
+        <x:f>IF(ISNUMBER(Parameters!E33),Parameters!E33,"")</x:f>
         <x:v>127</x:v>
       </x:c>
       <x:c r="F16" s="56" t="str">
-        <x:f>IF(COUNT(Parameters!G90:G91)&lt;2,"",MOD(Parameters!G91-Parameters!G90+180,360)-180)</x:f>
+        <x:f>IF(COUNT(Parameters!G18,Parameters!H33)&lt;2,"",MOD(Parameters!H33-Parameters!G18+180,360)-180)</x:f>
         <x:v/>
       </x:c>
       <x:c r="G16" s="58" t="str">
@@ -4939,7 +5189,7 @@
         <x:v/>
       </x:c>
       <x:c r="K16" s="60" t="str">
-        <x:f>IF(COUNT(Parameters!C90:F91)&lt;8,"待补坐标",IF(NOT(ISNUMBER(E16)),"待填轮行程",IF(E16&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G90:G91)&lt;2,"无效半径",""))))</x:f>
+        <x:f>IF(COUNT(Parameters!C18:F18,Parameters!F33:G33)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E16)),"待填轮行程",IF(E16&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G18,Parameters!H33)&lt;2,"无效半径",""))))</x:f>
         <x:v>待补坐标</x:v>
       </x:c>
       <x:c r="L16" s="25"/>
@@ -4958,11 +5208,11 @@
         <x:v>Outer</x:v>
       </x:c>
       <x:c r="E17" s="53">
-        <x:f>IF(ISNUMBER(Parameters!C95),Parameters!C95,"")</x:f>
+        <x:f>IF(ISNUMBER(Parameters!E34),Parameters!E34,"")</x:f>
         <x:v>127</x:v>
       </x:c>
       <x:c r="F17" s="57" t="str">
-        <x:f>IF(COUNT(Parameters!G97:G98)&lt;2,"",MOD(Parameters!G98-Parameters!G97+180,360)-180)</x:f>
+        <x:f>IF(COUNT(Parameters!G18,Parameters!H34)&lt;2,"",MOD(Parameters!H34-Parameters!G18+180,360)-180)</x:f>
         <x:v/>
       </x:c>
       <x:c r="G17" s="59" t="str">
@@ -4982,7 +5232,7 @@
         <x:v/>
       </x:c>
       <x:c r="K17" s="61" t="str">
-        <x:f>IF(COUNT(Parameters!C97:F98)&lt;8,"待补坐标",IF(NOT(ISNUMBER(E17)),"待填轮行程",IF(E17&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G97:G98)&lt;2,"无效半径",""))))</x:f>
+        <x:f>IF(COUNT(Parameters!C18:F18,Parameters!F34:G34)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E17)),"待填轮行程",IF(E17&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G18,Parameters!H34)&lt;2,"无效半径",""))))</x:f>
         <x:v>待补坐标</x:v>
       </x:c>
       <x:c r="L17" s="25"/>

--- a/docs/arb_stiffness.xlsx
+++ b/docs/arb_stiffness.xlsx
@@ -17,7 +17,7 @@
     <sheet name="Parameters" sheetId="5" r:id="rId2"/>
     <sheet name="Samples" sheetId="7" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" forceFullCalc="1"/>
+  <calcPr calcId="191029" forceFullCalc="1" calcMode="auto" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -247,13 +247,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="9">
     <numFmt numFmtId="176" formatCode="0.0"/>
     <numFmt numFmtId="177" formatCode="0.0000"/>
     <numFmt numFmtId="178" formatCode="0.000"/>
     <numFmt numFmtId="179" formatCode="0.000000"/>
+    <numFmt numFmtId="180" formatCode="0.0"/>
+    <numFmt numFmtId="181" formatCode="0.0000"/>
+    <numFmt numFmtId="182" formatCode="0.000"/>
+    <numFmt numFmtId="183" formatCode="0.000000"/>
+    <numFmt numFmtId="184" formatCode="0.00"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -354,8 +359,116 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF667B91"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF667B91"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF667B91"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF667B91"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF195DB1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF667B91"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF667B91"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF667B91"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF195DB1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -407,8 +520,111 @@
         <fgColor rgb="FFEDF2F7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF2F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF2F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -442,13 +658,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="4"/>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -551,6 +771,204 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="4" xfId="2"/>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="4" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="13" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="13" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="16" fillId="13" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="16" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="16" fillId="13" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="16" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="25" fillId="20" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="25" fillId="20" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="19" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="17" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="25" fillId="20" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="19" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="17" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="22" fillId="19" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="22" fillId="17" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="4" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="32" fillId="24" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="32" fillId="24" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="16" fillId="25" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="16" fillId="23" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="31" fillId="25" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="31" fillId="23" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -620,31 +1038,31 @@
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>Soft Inner</c:v>
+                  <c:v>#1 L</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Soft Middle</c:v>
+                  <c:v>#1 M</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Soft Outer</c:v>
+                  <c:v>#1 H</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Medium Inner</c:v>
+                  <c:v>#2 L</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Medium Middle</c:v>
+                  <c:v>#2 M</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Medium Outer</c:v>
+                  <c:v>#2 H</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Hard Inner</c:v>
+                  <c:v>#3 L</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Hard Middle</c:v>
+                  <c:v>#3 M</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Hard Outer</c:v>
+                  <c:v>#3 H</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -653,35 +1071,8 @@
             <c:numRef>
               <c:f>Samples!$C$23:$C$31</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
-                <c:pt idx="0">
-                  <c:v>4.871853581135178</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.979056864038502</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5.1101670255576179</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>10.288059697803645</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>10.514444533871099</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10.791314342504192</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>18.936436183123369</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>19.353125250541339</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>19.862738104297762</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -709,31 +1100,31 @@
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>Soft Inner</c:v>
+                  <c:v>#1 L</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Soft Middle</c:v>
+                  <c:v>#1 M</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Soft Outer</c:v>
+                  <c:v>#1 H</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Medium Inner</c:v>
+                  <c:v>#2 L</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Medium Middle</c:v>
+                  <c:v>#2 M</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Medium Outer</c:v>
+                  <c:v>#2 H</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Hard Inner</c:v>
+                  <c:v>#3 L</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Hard Middle</c:v>
+                  <c:v>#3 M</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Hard Outer</c:v>
+                  <c:v>#3 H</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -742,35 +1133,8 @@
             <c:numRef>
               <c:f>Samples!$D$23:$D$31</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
-                <c:pt idx="0">
-                  <c:v>10.130884546881639</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>11.463956873691107</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>12.876541493683991</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>20.835034678470446</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>23.576612477472587</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>26.481714140375743</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>35.087821313012348</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>39.704851877713608</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>44.597269366675718</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -969,31 +1333,31 @@
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>Soft Inner</c:v>
+                  <c:v>#1 L</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Soft Middle</c:v>
+                  <c:v>#1 M</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Soft Outer</c:v>
+                  <c:v>#1 H</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Medium Inner</c:v>
+                  <c:v>#2 L</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Medium Middle</c:v>
+                  <c:v>#2 M</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Medium Outer</c:v>
+                  <c:v>#2 H</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Hard Inner</c:v>
+                  <c:v>#3 L</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Hard Middle</c:v>
+                  <c:v>#3 M</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Hard Outer</c:v>
+                  <c:v>#3 H</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1002,35 +1366,8 @@
             <c:numRef>
               <c:f>Samples!$C$36:$C$44</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
-                <c:pt idx="0">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>#N/A</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1058,31 +1395,31 @@
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>Soft Inner</c:v>
+                  <c:v>#1 L</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Soft Middle</c:v>
+                  <c:v>#1 M</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Soft Outer</c:v>
+                  <c:v>#1 H</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Medium Inner</c:v>
+                  <c:v>#2 L</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Medium Middle</c:v>
+                  <c:v>#2 M</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Medium Outer</c:v>
+                  <c:v>#2 H</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Hard Inner</c:v>
+                  <c:v>#3 L</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Hard Middle</c:v>
+                  <c:v>#3 M</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Hard Outer</c:v>
+                  <c:v>#3 H</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1091,35 +1428,8 @@
             <c:numRef>
               <c:f>Samples!$D$36:$D$44</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
-                <c:pt idx="0">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>#N/A</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1700,7 +2010,7 @@
       <c r="A5" s="1"/>
       <c r="B5" s="30" t="str">
         <f>IF(COUNT(Samples!H6:J17)=0,"待补节点坐标；暂无刚度结果。","")</f>
-        <v/>
+        <v>待补节点坐标；暂无刚度结果。</v>
       </c>
       <c r="C5" s="30"/>
       <c r="D5" s="30"/>
@@ -2656,15 +2966,17 @@
       <c r="B7" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>10</v>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
       </c>
       <c r="D7" s="19">
         <v>14.6</v>
       </c>
       <c r="E7" s="21">
         <f>$E$8*(D7/$D$8)^4</f>
-        <v>941.40636852684645</v>
+        <v>941.4063685268464</v>
       </c>
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
@@ -2677,8 +2989,10 @@
       <c r="B8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>11</v>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
       </c>
       <c r="D8" s="19">
         <v>17.600000000000001</v>
@@ -2697,15 +3011,17 @@
       <c r="B9" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="17" t="s">
-        <v>12</v>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
       </c>
       <c r="D9" s="19">
         <v>20.5</v>
       </c>
       <c r="E9" s="21">
         <f>$E$8*(D9/$D$8)^4</f>
-        <v>3659.1579207191098</v>
+        <v>3659.1579207191103</v>
       </c>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
@@ -2718,15 +3034,17 @@
       <c r="B10" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>10</v>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
       </c>
       <c r="D10" s="19">
         <v>16.2</v>
       </c>
       <c r="E10" s="22">
-        <f>$E$11*(D10/$D$11)^4</f>
-        <v>1429.0674406245323</v>
+        <f>$E$8*(D10/$D$8)^4</f>
+        <v>1427.0058942593776</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
@@ -2739,14 +3057,17 @@
       <c r="B11" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="17" t="s">
-        <v>11</v>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
       </c>
       <c r="D11" s="19">
         <v>19.399999999999999</v>
       </c>
-      <c r="E11" s="20">
-        <v>2939</v>
+      <c r="E11" s="21">
+        <f>$E$8*(D11/$D$8)^4</f>
+        <v>2934.760252738988</v>
       </c>
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
@@ -2759,15 +3080,17 @@
       <c r="B12" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="18" t="s">
-        <v>12</v>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
       </c>
       <c r="D12" s="19">
         <v>22.1</v>
       </c>
       <c r="E12" s="22">
-        <f>$E$11*(D12/$D$11)^4</f>
-        <v>4949.5049290944507</v>
+        <f>$E$8*(D12/$D$8)^4</f>
+        <v>4942.364864458013</v>
       </c>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
@@ -2789,409 +3112,390 @@
     </row>
     <row r="14" spans="1:10" ht="27" customHeight="1">
       <c r="A14" s="15"/>
-      <c r="B14" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14" s="31" t="s">
-        <v>14</v>
+      <c r="B14" s="66" t="str">
+        <v>固定转轴</v>
+      </c>
+      <c r="C14" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">固定几何 · 生成位置 / 转轴</t>
+        </is>
+      </c>
+      <c r="D14" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">固定几何 · 生成位置 / 转轴</t>
+        </is>
+      </c>
+      <c r="E14" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">固定几何 · 生成位置 / 转轴</t>
+        </is>
+      </c>
+      <c r="F14" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">固定几何 · 生成位置 / 转轴</t>
+        </is>
+      </c>
+      <c r="G14" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">固定几何 · 生成位置 / 转轴</t>
+        </is>
+      </c>
+      <c r="H14" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">固定几何 · 生成位置 / 转轴</t>
+        </is>
+      </c>
+      <c r="I14" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">固定几何 · 生成位置 / 转轴</t>
+        </is>
       </c>
       <c r="J14" s="15"/>
     </row>
     <row r="15" spans="1:10" ht="27" customHeight="1">
       <c r="A15" s="15"/>
-      <c r="B15" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="34" t="s">
-        <v>15</v>
+      <c r="B15" s="69" t="str">
+        <v>节点使用车身相对坐标（m）。</v>
+      </c>
+      <c r="C15" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</t>
+        </is>
+      </c>
+      <c r="D15" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</t>
+        </is>
+      </c>
+      <c r="E15" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</t>
+        </is>
+      </c>
+      <c r="F15" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</t>
+        </is>
+      </c>
+      <c r="G15" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</t>
+        </is>
+      </c>
+      <c r="H15" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</t>
+        </is>
+      </c>
+      <c r="I15" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</t>
+        </is>
       </c>
       <c r="J15" s="15"/>
     </row>
     <row r="16" spans="1:10" ht="42" customHeight="1">
       <c r="A16" s="15"/>
-      <c r="B16" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" s="15"/>
+      <c r="B16" s="74" t="str">
+        <v>Axle</v>
+      </c>
+      <c r="C16" s="74" t="str">
+        <v>arb2 Y
+(m)</v>
+      </c>
+      <c r="D16" s="74" t="str">
+        <v>arb2 Z
+(m)</v>
+      </c>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
       <c r="J16" s="15"/>
     </row>
     <row r="17" spans="1:14" ht="27" customHeight="1">
       <c r="A17" s="15"/>
-      <c r="B17" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="23">
-        <v>-1.083</v>
-      </c>
-      <c r="D17" s="23">
-        <v>0.16400000000000001</v>
-      </c>
-      <c r="E17" s="23">
-        <v>-0.91500000000000004</v>
-      </c>
-      <c r="F17" s="23">
+      <c r="B17" s="78" t="str">
+        <v>Front</v>
+      </c>
+      <c r="C17" s="82" t="n">
+        <v>-0.915</v>
+      </c>
+      <c r="D17" s="82" t="n">
         <v>0.127</v>
       </c>
-      <c r="G17" s="24">
-        <f>IF(COUNT(C17:F17)&lt;4,"",IF(H17=0,"无效半径",IF(D17&lt;F17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E17-C17)*1000/H17))))))</f>
-        <v>12.420429945256622</v>
-      </c>
-      <c r="H17" s="26">
-        <f>IF(COUNT(C17:F17)&lt;4,"",1000*SQRT((C17-E17)^2+(D17-F17)^2))</f>
-        <v>172.02616080119901</v>
-      </c>
-      <c r="I17" s="15"/>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
       <c r="J17" s="15"/>
     </row>
     <row r="18" spans="1:14" ht="27" customHeight="1">
       <c r="A18" s="15"/>
-      <c r="B18" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="23">
-        <v>1.3049999999999999</v>
-      </c>
-      <c r="D18" s="23">
-        <v>0.21299999999999999</v>
-      </c>
-      <c r="E18" s="23">
-        <v>1.4590000000000001</v>
-      </c>
-      <c r="F18" s="23">
+      <c r="B18" s="86" t="str">
+        <v>Rear</v>
+      </c>
+      <c r="C18" s="82" t="n">
+        <v>1.459</v>
+      </c>
+      <c r="D18" s="82" t="n">
         <v>0.26</v>
       </c>
-      <c r="G18" s="25">
-        <f>IF(COUNT(C18:F18)&lt;4,"",IF(H18=0,"无效半径",IF(D18&lt;F18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E18-C18)*1000/H18))))))</f>
-        <v>-16.971916914347634</v>
-      </c>
-      <c r="H18" s="27">
-        <f>IF(COUNT(C18:F18)&lt;4,"",1000*SQRT((C18-E18)^2+(D18-F18)^2))</f>
-        <v>161.01242188104632</v>
-      </c>
-      <c r="I18" s="15"/>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
       <c r="J18" s="15"/>
     </row>
     <row r="19" spans="1:14" ht="27" customHeight="1">
       <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
+      <c r="B19" s="50"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="50"/>
       <c r="J19" s="15"/>
     </row>
     <row r="20" spans="1:14" ht="27" customHeight="1">
       <c r="A20" s="15"/>
-      <c r="B20" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="H20" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" s="31" t="s">
-        <v>22</v>
+      <c r="B20" s="66" t="str">
+        <v>测量 · 各档起点 / 终点</v>
+      </c>
+      <c r="C20" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">测量 · 每组填写轮行程和 arb1 终点</t>
+        </is>
+      </c>
+      <c r="D20" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">测量 · 每组填写轮行程和 arb1 终点</t>
+        </is>
+      </c>
+      <c r="E20" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">测量 · 每组填写轮行程和 arb1 终点</t>
+        </is>
+      </c>
+      <c r="F20" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">测量 · 每组填写轮行程和 arb1 终点</t>
+        </is>
+      </c>
+      <c r="G20" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">测量 · 每组填写轮行程和 arb1 终点</t>
+        </is>
+      </c>
+      <c r="H20" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">测量 · 每组填写轮行程和 arb1 终点</t>
+        </is>
+      </c>
+      <c r="I20" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">测量 · 每组填写轮行程和 arb1 终点</t>
+        </is>
       </c>
       <c r="J20" s="15"/>
     </row>
     <row r="21" spans="1:14" ht="27" customHeight="1">
       <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
+      <c r="B21" s="87" t="str">
+        <v>起点为 wheeljack 架起、全伸展稳定后的位置；轮行程从同一起点计算。</v>
+      </c>
+      <c r="C21" s="87"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="87"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="87"/>
+      <c r="H21" s="87"/>
+      <c r="I21" s="87"/>
       <c r="J21" s="15"/>
     </row>
     <row r="22" spans="1:14" ht="42" customHeight="1">
       <c r="A22" s="15"/>
-      <c r="B22" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="H22" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="I22" s="16" t="s">
-        <v>21</v>
+      <c r="B22" s="74" t="str">
+        <v>Surface</v>
+      </c>
+      <c r="C22" s="74" t="str">
+        <v>Axle</v>
+      </c>
+      <c r="D22" s="74" t="str">
+        <v>Position</v>
+      </c>
+      <c r="E22" s="74" t="str">
+        <v>Wheel ΔZ
+(mm)</v>
+      </c>
+      <c r="F22" s="74" t="str">
+        <v>arb1 Start Y
+(m)</v>
+      </c>
+      <c r="G22" s="74" t="str">
+        <v>arb1 Start Z
+(m)</v>
+      </c>
+      <c r="H22" s="74" t="str">
+        <v>arb1 End Y
+(m)</v>
+      </c>
+      <c r="I22" s="74" t="str">
+        <v>arb1 End Z
+(m)</v>
       </c>
       <c r="J22" s="15"/>
     </row>
     <row r="23" spans="1:14" ht="27" customHeight="1">
       <c r="A23" s="15"/>
-      <c r="B23" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" s="19">
+      <c r="B23" s="78" t="str">
+        <v>Tarmac</v>
+      </c>
+      <c r="C23" s="78" t="str">
+        <v>Front</v>
+      </c>
+      <c r="D23" s="78" t="str">
+        <v>L</v>
+      </c>
+      <c r="E23" s="92" t="n">
         <v>167</v>
       </c>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="24" t="str">
-        <f>IF(COUNT(F23:G23,E17:F17)&lt;4,"",IF(I23=0,"无效半径",IF(G23&lt;F17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E17-F23)*1000/I23))))))</f>
-        <v/>
-      </c>
-      <c r="I23" s="26" t="str">
-        <f>IF(COUNT(F23:G23,E17:F17)&lt;4,"",1000*SQRT((F23-E17)^2+(G23-F17)^2))</f>
-        <v/>
-      </c>
+      <c r="F23" s="82"/>
+      <c r="G23" s="82"/>
+      <c r="H23" s="82"/>
+      <c r="I23" s="82"/>
       <c r="J23" s="15"/>
     </row>
     <row r="24" spans="1:14" ht="27" customHeight="1">
       <c r="A24" s="15"/>
-      <c r="B24" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" s="19">
+      <c r="B24" s="86" t="str">
+        <v>Tarmac</v>
+      </c>
+      <c r="C24" s="86" t="str">
+        <v>Front</v>
+      </c>
+      <c r="D24" s="86" t="str">
+        <v>M</v>
+      </c>
+      <c r="E24" s="92" t="n">
         <v>167</v>
       </c>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="25" t="str">
-        <f>IF(COUNT(F24:G24,E17:F17)&lt;4,"",IF(I24=0,"无效半径",IF(G24&lt;F17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E17-F24)*1000/I24))))))</f>
-        <v/>
-      </c>
-      <c r="I24" s="27" t="str">
-        <f>IF(COUNT(F24:G24,E17:F17)&lt;4,"",1000*SQRT((F24-E17)^2+(G24-F17)^2))</f>
-        <v/>
-      </c>
+      <c r="F24" s="82"/>
+      <c r="G24" s="82"/>
+      <c r="H24" s="82"/>
+      <c r="I24" s="82"/>
       <c r="J24" s="15"/>
       <c r="M24" s="23"/>
       <c r="N24" s="23"/>
     </row>
     <row r="25" spans="1:14" ht="27" customHeight="1">
       <c r="A25" s="15"/>
-      <c r="B25" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="19">
+      <c r="B25" s="78" t="str">
+        <v>Tarmac</v>
+      </c>
+      <c r="C25" s="78" t="str">
+        <v>Front</v>
+      </c>
+      <c r="D25" s="78" t="str">
+        <v>H</v>
+      </c>
+      <c r="E25" s="92" t="n">
         <v>167</v>
       </c>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="24" t="str">
-        <f>IF(COUNT(F25:G25,E17:F17)&lt;4,"",IF(I25=0,"无效半径",IF(G25&lt;F17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E17-F25)*1000/I25))))))</f>
-        <v/>
-      </c>
-      <c r="I25" s="26" t="str">
-        <f>IF(COUNT(F25:G25,E17:F17)&lt;4,"",1000*SQRT((F25-E17)^2+(G25-F17)^2))</f>
-        <v/>
-      </c>
+      <c r="F25" s="82"/>
+      <c r="G25" s="82"/>
+      <c r="H25" s="82"/>
+      <c r="I25" s="82"/>
       <c r="J25" s="15"/>
     </row>
     <row r="26" spans="1:14" ht="27" customHeight="1">
       <c r="A26" s="15"/>
-      <c r="B26" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="E26" s="19">
+      <c r="B26" s="86" t="str">
+        <v>Tarmac</v>
+      </c>
+      <c r="C26" s="86" t="str">
+        <v>Rear</v>
+      </c>
+      <c r="D26" s="86" t="str">
+        <v>L</v>
+      </c>
+      <c r="E26" s="92" t="n">
         <v>166</v>
       </c>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="25" t="str">
-        <f>IF(COUNT(F26:G26,E18:F18)&lt;4,"",IF(I26=0,"无效半径",IF(G26&lt;F18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E18-F26)*1000/I26))))))</f>
-        <v/>
-      </c>
-      <c r="I26" s="27" t="str">
-        <f>IF(COUNT(F26:G26,E18:F18)&lt;4,"",1000*SQRT((F26-E18)^2+(G26-F18)^2))</f>
-        <v/>
-      </c>
+      <c r="F26" s="82"/>
+      <c r="G26" s="82"/>
+      <c r="H26" s="82"/>
+      <c r="I26" s="82"/>
       <c r="J26" s="15"/>
     </row>
     <row r="27" spans="1:14" ht="27" customHeight="1">
       <c r="A27" s="15"/>
-      <c r="B27" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27" s="19">
+      <c r="B27" s="78" t="str">
+        <v>Tarmac</v>
+      </c>
+      <c r="C27" s="78" t="str">
+        <v>Rear</v>
+      </c>
+      <c r="D27" s="78" t="str">
+        <v>M</v>
+      </c>
+      <c r="E27" s="92" t="n">
         <v>166</v>
       </c>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="24" t="str">
-        <f>IF(COUNT(F27:G27,E18:F18)&lt;4,"",IF(I27=0,"无效半径",IF(G27&lt;F18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E18-F27)*1000/I27))))))</f>
-        <v/>
-      </c>
-      <c r="I27" s="26" t="str">
-        <f>IF(COUNT(F27:G27,E18:F18)&lt;4,"",1000*SQRT((F27-E18)^2+(G27-F18)^2))</f>
-        <v/>
-      </c>
+      <c r="F27" s="82"/>
+      <c r="G27" s="82"/>
+      <c r="H27" s="82"/>
+      <c r="I27" s="82"/>
       <c r="J27" s="15"/>
       <c r="M27" s="23"/>
       <c r="N27" s="23"/>
     </row>
     <row r="28" spans="1:14" ht="27" customHeight="1">
       <c r="A28" s="15"/>
-      <c r="B28" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E28" s="19">
+      <c r="B28" s="86" t="str">
+        <v>Tarmac</v>
+      </c>
+      <c r="C28" s="86" t="str">
+        <v>Rear</v>
+      </c>
+      <c r="D28" s="86" t="str">
+        <v>H</v>
+      </c>
+      <c r="E28" s="92" t="n">
         <v>166</v>
       </c>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="25" t="str">
-        <f>IF(COUNT(F28:G28,E18:F18)&lt;4,"",IF(I28=0,"无效半径",IF(G28&lt;F18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E18-F28)*1000/I28))))))</f>
-        <v/>
-      </c>
-      <c r="I28" s="27" t="str">
-        <f>IF(COUNT(F28:G28,E18:F18)&lt;4,"",1000*SQRT((F28-E18)^2+(G28-F18)^2))</f>
-        <v/>
-      </c>
+      <c r="F28" s="82"/>
+      <c r="G28" s="82"/>
+      <c r="H28" s="82"/>
+      <c r="I28" s="82"/>
       <c r="J28" s="15"/>
     </row>
     <row r="29" spans="1:14" ht="27" customHeight="1">
       <c r="A29" s="15"/>
-      <c r="B29" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E29" s="19">
+      <c r="B29" s="78" t="str">
+        <v>Gravel</v>
+      </c>
+      <c r="C29" s="78" t="str">
+        <v>Front</v>
+      </c>
+      <c r="D29" s="78" t="str">
+        <v>L</v>
+      </c>
+      <c r="E29" s="92" t="n">
         <v>259</v>
       </c>
-      <c r="F29" s="23">
+      <c r="F29" s="82"/>
+      <c r="G29" s="82"/>
+      <c r="H29" s="82" t="n">
         <v>-1.034</v>
       </c>
-      <c r="G29" s="23">
+      <c r="I29" s="82" t="n">
         <v>0.251</v>
-      </c>
-      <c r="H29" s="24">
-        <f>IF(COUNT(F29:G29,E17:F17)&lt;4,"",IF(I29=0,"无效半径",IF(G29&lt;F17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E17-F29)*1000/I29))))))</f>
-        <v>46.178759169911231</v>
-      </c>
-      <c r="I29" s="26">
-        <f>IF(COUNT(F29:G29,E17:F17)&lt;4,"",1000*SQRT((F29-E17)^2+(G29-F17)^2))</f>
-        <v>171.86331778480246</v>
       </c>
       <c r="J29" s="15"/>
       <c r="M29" s="23"/>
@@ -3199,121 +3503,97 @@
     </row>
     <row r="30" spans="1:14" ht="27" customHeight="1">
       <c r="A30" s="15"/>
-      <c r="B30" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="E30" s="19">
+      <c r="B30" s="86" t="str">
+        <v>Gravel</v>
+      </c>
+      <c r="C30" s="86" t="str">
+        <v>Front</v>
+      </c>
+      <c r="D30" s="86" t="str">
+        <v>M</v>
+      </c>
+      <c r="E30" s="92" t="n">
         <v>259</v>
       </c>
-      <c r="F30" s="23">
-        <v>-1.0229999999999999</v>
-      </c>
-      <c r="G30" s="23">
-        <v>0.24099999999999999</v>
-      </c>
-      <c r="H30" s="25">
-        <f>IF(COUNT(F30:G30,E17:F17)&lt;4,"",IF(I30=0,"无效半径",IF(G30&lt;F17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E17-F30)*1000/I30))))))</f>
-        <v>46.548157698977988</v>
-      </c>
-      <c r="I30" s="27">
-        <f>IF(COUNT(F30:G30,E17:F17)&lt;4,"",1000*SQRT((F30-E17)^2+(G30-F17)^2))</f>
-        <v>157.03502793962869</v>
+      <c r="F30" s="82"/>
+      <c r="G30" s="82"/>
+      <c r="H30" s="82" t="n">
+        <v>-1.023</v>
+      </c>
+      <c r="I30" s="82" t="n">
+        <v>0.241</v>
       </c>
       <c r="J30" s="15"/>
     </row>
     <row r="31" spans="1:14" ht="27" customHeight="1">
       <c r="A31" s="15"/>
-      <c r="B31" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E31" s="19">
+      <c r="B31" s="78" t="str">
+        <v>Gravel</v>
+      </c>
+      <c r="C31" s="78" t="str">
+        <v>Front</v>
+      </c>
+      <c r="D31" s="78" t="str">
+        <v>H</v>
+      </c>
+      <c r="E31" s="92" t="n">
         <v>259</v>
       </c>
-      <c r="F31" s="23">
+      <c r="F31" s="82"/>
+      <c r="G31" s="82"/>
+      <c r="H31" s="82" t="n">
         <v>-1.012</v>
       </c>
-      <c r="G31" s="23">
-        <v>0.23100000000000001</v>
-      </c>
-      <c r="H31" s="24">
-        <f>IF(COUNT(F31:G31,E17:F17)&lt;4,"",IF(I31=0,"无效半径",IF(G31&lt;F17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E17-F31)*1000/I31))))))</f>
-        <v>46.994569301241839</v>
-      </c>
-      <c r="I31" s="26">
-        <f>IF(COUNT(F31:G31,E17:F17)&lt;4,"",1000*SQRT((F31-E17)^2+(G31-F17)^2))</f>
-        <v>142.2146265332789</v>
+      <c r="I31" s="82" t="n">
+        <v>0.231</v>
       </c>
       <c r="J31" s="15"/>
     </row>
     <row r="32" spans="1:14" ht="27" customHeight="1">
       <c r="A32" s="15"/>
-      <c r="B32" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32" s="19">
+      <c r="B32" s="86" t="str">
+        <v>Gravel</v>
+      </c>
+      <c r="C32" s="86" t="str">
+        <v>Rear</v>
+      </c>
+      <c r="D32" s="86" t="str">
+        <v>L</v>
+      </c>
+      <c r="E32" s="92" t="n">
         <v>252</v>
       </c>
-      <c r="F32" s="23">
-        <v>1.3089999999999999</v>
-      </c>
-      <c r="G32" s="23">
-        <v>0.31900000000000001</v>
-      </c>
-      <c r="H32" s="25">
-        <f>IF(COUNT(F32:G32,E18:F18)&lt;4,"",IF(I32=0,"无效半径",IF(G32&lt;F18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E18-F32)*1000/I32))))))</f>
-        <v>21.471368323914561</v>
-      </c>
-      <c r="I32" s="27">
-        <f>IF(COUNT(F32:G32,E18:F18)&lt;4,"",1000*SQRT((F32-E18)^2+(G32-F18)^2))</f>
-        <v>161.18622769951543</v>
+      <c r="F32" s="82"/>
+      <c r="G32" s="82"/>
+      <c r="H32" s="82" t="n">
+        <v>1.309</v>
+      </c>
+      <c r="I32" s="82" t="n">
+        <v>0.319</v>
       </c>
       <c r="J32" s="15"/>
     </row>
     <row r="33" spans="1:14" ht="27" customHeight="1">
       <c r="A33" s="15"/>
-      <c r="B33" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E33" s="19">
+      <c r="B33" s="78" t="str">
+        <v>Gravel</v>
+      </c>
+      <c r="C33" s="78" t="str">
+        <v>Rear</v>
+      </c>
+      <c r="D33" s="78" t="str">
+        <v>M</v>
+      </c>
+      <c r="E33" s="92" t="n">
         <v>252</v>
       </c>
-      <c r="F33" s="23">
-        <v>1.3260000000000001</v>
-      </c>
-      <c r="G33" s="23">
-        <v>0.31900000000000001</v>
-      </c>
-      <c r="H33" s="24">
-        <f>IF(COUNT(F33:G33,E18:F18)&lt;4,"",IF(I33=0,"无效半径",IF(G33&lt;F18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E18-F33)*1000/I33))))))</f>
-        <v>23.922505883013255</v>
-      </c>
-      <c r="I33" s="26">
-        <f>IF(COUNT(F33:G33,E18:F18)&lt;4,"",1000*SQRT((F33-E18)^2+(G33-F18)^2))</f>
-        <v>145.49914089093446</v>
+      <c r="F33" s="82"/>
+      <c r="G33" s="82"/>
+      <c r="H33" s="82" t="n">
+        <v>1.326</v>
+      </c>
+      <c r="I33" s="82" t="n">
+        <v>0.319</v>
       </c>
       <c r="J33" s="15"/>
       <c r="M33" s="23"/>
@@ -3321,31 +3601,25 @@
     </row>
     <row r="34" spans="1:14" ht="27" customHeight="1">
       <c r="A34" s="15"/>
-      <c r="B34" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E34" s="19">
+      <c r="B34" s="86" t="str">
+        <v>Gravel</v>
+      </c>
+      <c r="C34" s="86" t="str">
+        <v>Rear</v>
+      </c>
+      <c r="D34" s="86" t="str">
+        <v>H</v>
+      </c>
+      <c r="E34" s="92" t="n">
         <v>252</v>
       </c>
-      <c r="F34" s="23">
-        <v>1.3420000000000001</v>
-      </c>
-      <c r="G34" s="23">
+      <c r="F34" s="82"/>
+      <c r="G34" s="82"/>
+      <c r="H34" s="82" t="n">
+        <v>1.342</v>
+      </c>
+      <c r="I34" s="82" t="n">
         <v>0.318</v>
-      </c>
-      <c r="H34" s="25">
-        <f>IF(COUNT(F34:G34,E18:F18)&lt;4,"",IF(I34=0,"无效半径",IF(G34&lt;F18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(E18-F34)*1000/I34))))))</f>
-        <v>26.368833521184065</v>
-      </c>
-      <c r="I34" s="27">
-        <f>IF(COUNT(F34:G34,E18:F18)&lt;4,"",1000*SQRT((F34-E18)^2+(G34-F18)^2))</f>
-        <v>130.58713566044705</v>
       </c>
       <c r="J34" s="15"/>
       <c r="L34" s="23"/>
@@ -3445,8 +3719,10 @@
       <c r="C40" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D40" s="18" t="s">
-        <v>30</v>
+      <c r="D40" s="18" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
       </c>
       <c r="E40" s="27">
         <v>35</v>
@@ -3467,8 +3743,10 @@
       <c r="C41" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D41" s="17" t="s">
-        <v>31</v>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="E41" s="26">
         <v>42</v>
@@ -3489,8 +3767,10 @@
       <c r="C42" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D42" s="18" t="s">
-        <v>32</v>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
       <c r="E42" s="27">
         <v>46</v>
@@ -3511,8 +3791,10 @@
       <c r="C43" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D43" s="17" t="s">
-        <v>30</v>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
       </c>
       <c r="E43" s="26">
         <v>41</v>
@@ -3533,8 +3815,10 @@
       <c r="C44" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D44" s="18" t="s">
-        <v>31</v>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="E44" s="27">
         <v>49</v>
@@ -3555,8 +3839,10 @@
       <c r="C45" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D45" s="17" t="s">
-        <v>32</v>
+      <c r="D45" s="17" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
       <c r="E45" s="26">
         <v>54</v>
@@ -3577,8 +3863,10 @@
       <c r="C46" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D46" s="18" t="s">
-        <v>30</v>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
       </c>
       <c r="E46" s="27">
         <v>32</v>
@@ -3599,8 +3887,10 @@
       <c r="C47" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D47" s="17" t="s">
-        <v>31</v>
+      <c r="D47" s="17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="E47" s="26">
         <v>40</v>
@@ -3621,8 +3911,10 @@
       <c r="C48" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D48" s="18" t="s">
-        <v>32</v>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
       <c r="E48" s="27">
         <v>45</v>
@@ -3643,8 +3935,10 @@
       <c r="C49" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D49" s="17" t="s">
-        <v>30</v>
+      <c r="D49" s="17" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
       </c>
       <c r="E49" s="26">
         <v>39</v>
@@ -3665,8 +3959,10 @@
       <c r="C50" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D50" s="18" t="s">
-        <v>31</v>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="E50" s="27">
         <v>47</v>
@@ -3687,8 +3983,10 @@
       <c r="C51" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D51" s="17" t="s">
-        <v>32</v>
+      <c r="D51" s="17" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
       <c r="E51" s="26">
         <v>51</v>
@@ -3923,13 +4221,14 @@
     <row r="117" ht="26.1" customHeight="1"/>
     <row r="118" ht="26.1" customHeight="1"/>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B38:I38"/>
     <mergeCell ref="B2:I3"/>
     <mergeCell ref="B4:I4"/>
     <mergeCell ref="B14:I14"/>
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B21:I21"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3941,7 +4240,7 @@
   <sheetPr>
     <tabColor rgb="FF31475E"/>
   </sheetPr>
-  <dimension ref="A1:M157"/>
+  <dimension ref="A1:O90"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.75" customWidth="1"/>
@@ -3954,7 +4253,11 @@
     <col min="8" max="10" width="12.5" customWidth="1"/>
     <col min="11" max="11" width="18.125" customWidth="1"/>
     <col min="12" max="13" width="2.75" customWidth="1"/>
+    <col min="12" max="12" width="16" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="16" hidden="0" customWidth="1"/>
     <col min="14" max="15" width="13" customWidth="1"/>
+    <col min="14" max="14" width="16" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="16" hidden="0" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
     <col min="17" max="17" width="12" customWidth="1"/>
     <col min="18" max="22" width="13" customWidth="1"/>
@@ -4080,20 +4383,43 @@
       <c r="G5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>42</v>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>#1
+(N/mm)</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>#2
+(N/mm)</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>#3
+(N/mm)</t>
+        </is>
       </c>
       <c r="K5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
+      <c r="L5" s="91" t="str">
+        <v>Start angle
+(°)</v>
+      </c>
+      <c r="M5" s="91" t="str">
+        <v>End angle
+(°)</v>
+      </c>
+      <c r="N5" s="74" t="str">
+        <v>Start radius
+(mm)</v>
+      </c>
+      <c r="O5" s="74" t="str">
+        <v>End radius
+(mm)</v>
+      </c>
     </row>
     <row r="6" spans="1:13" ht="26.1" customHeight="1">
       <c r="A6" s="1"/>
@@ -4103,19 +4429,21 @@
       <c r="C6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>30</v>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
       </c>
       <c r="E6" s="7">
         <f>IF(ISNUMBER(Parameters!E23),Parameters!E23,"")</f>
         <v>167</v>
       </c>
       <c r="F6" s="9" t="str">
-        <f>IF(COUNT(Parameters!G17,Parameters!H23)&lt;2,"",MOD(Parameters!H23-Parameters!G17+180,360)-180)</f>
+        <f>IF(COUNT(L6:M6)&lt;2,"",MOD(M6-L6+180,360)-180)</f>
         <v/>
       </c>
       <c r="G6" s="11" t="str">
-        <f t="shared" ref="G6:G17" si="0">IF(COUNT(E6:F6)&lt;2,"",IF(E6&lt;=0,"",RADIANS(F6)/E6))</f>
+        <f>IF(COUNT(E6:F6)&lt;2,"",IF(E6&lt;=0,"",RADIANS(F6)/E6))</f>
         <v/>
       </c>
       <c r="H6" s="5" t="str">
@@ -4131,11 +4459,25 @@
         <v/>
       </c>
       <c r="K6" s="13" t="str">
-        <f>IF(COUNT(Parameters!C17:F17,Parameters!F23:G23)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E6)),"待填轮行程",IF(E6&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G17,Parameters!H23)&lt;2,"无效半径",""))))</f>
+        <f>IF(COUNT(Parameters!C17:D17,Parameters!F23:I23)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E6)),"待填轮行程",IF(E6&lt;=0,"轮行程须大于0",IF(COUNT(L6:M6)&lt;2,"无效半径",""))))</f>
         <v>待补坐标</v>
       </c>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
+      <c r="L6" s="103" t="str">
+        <f>IF(COUNT(Parameters!F23,Parameters!G23,Parameters!C17,Parameters!D17)&lt;4,"",IF(N6=0,"",IF(Parameters!G23&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!F23)*1000/N6))))))</f>
+        <v/>
+      </c>
+      <c r="M6" s="103" t="str">
+        <f>IF(COUNT(Parameters!H23,Parameters!I23,Parameters!C17,Parameters!D17)&lt;4,"",IF(O6=0,"",IF(Parameters!I23&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!H23)*1000/O6))))))</f>
+        <v/>
+      </c>
+      <c r="N6" s="105" t="str">
+        <f>IF(COUNT(Parameters!F23,Parameters!G23,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!F23-Parameters!C17)^2+(Parameters!G23-Parameters!D17)^2))</f>
+        <v/>
+      </c>
+      <c r="O6" s="105" t="str">
+        <f>IF(COUNT(Parameters!H23,Parameters!I23,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!H23-Parameters!C17)^2+(Parameters!I23-Parameters!D17)^2))</f>
+        <v/>
+      </c>
     </row>
     <row r="7" spans="1:13" ht="26.1" customHeight="1">
       <c r="A7" s="1"/>
@@ -4145,19 +4487,21 @@
       <c r="C7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>31</v>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="E7" s="8">
         <f>IF(ISNUMBER(Parameters!E24),Parameters!E24,"")</f>
         <v>167</v>
       </c>
       <c r="F7" s="10" t="str">
-        <f>IF(COUNT(Parameters!G17,Parameters!H24)&lt;2,"",MOD(Parameters!H24-Parameters!G17+180,360)-180)</f>
+        <f>IF(COUNT(L7:M7)&lt;2,"",MOD(M7-L7+180,360)-180)</f>
         <v/>
       </c>
       <c r="G7" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E7:F7)&lt;2,"",IF(E7&lt;=0,"",RADIANS(F7)/E7))</f>
         <v/>
       </c>
       <c r="H7" s="6" t="str">
@@ -4173,11 +4517,25 @@
         <v/>
       </c>
       <c r="K7" s="14" t="str">
-        <f>IF(COUNT(Parameters!C17:F17,Parameters!F24:G24)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E7)),"待填轮行程",IF(E7&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G17,Parameters!H24)&lt;2,"无效半径",""))))</f>
+        <f>IF(COUNT(Parameters!C17:D17,Parameters!F24:I24)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E7)),"待填轮行程",IF(E7&lt;=0,"轮行程须大于0",IF(COUNT(L7:M7)&lt;2,"无效半径",""))))</f>
         <v>待补坐标</v>
       </c>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
+      <c r="L7" s="104" t="str">
+        <f>IF(COUNT(Parameters!F24,Parameters!G24,Parameters!C17,Parameters!D17)&lt;4,"",IF(N7=0,"",IF(Parameters!G24&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!F24)*1000/N7))))))</f>
+        <v/>
+      </c>
+      <c r="M7" s="104" t="str">
+        <f>IF(COUNT(Parameters!H24,Parameters!I24,Parameters!C17,Parameters!D17)&lt;4,"",IF(O7=0,"",IF(Parameters!I24&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!H24)*1000/O7))))))</f>
+        <v/>
+      </c>
+      <c r="N7" s="106" t="str">
+        <f>IF(COUNT(Parameters!F24,Parameters!G24,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!F24-Parameters!C17)^2+(Parameters!G24-Parameters!D17)^2))</f>
+        <v/>
+      </c>
+      <c r="O7" s="106" t="str">
+        <f>IF(COUNT(Parameters!H24,Parameters!I24,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!H24-Parameters!C17)^2+(Parameters!I24-Parameters!D17)^2))</f>
+        <v/>
+      </c>
     </row>
     <row r="8" spans="1:13" ht="26.1" customHeight="1">
       <c r="A8" s="1"/>
@@ -4187,19 +4545,21 @@
       <c r="C8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>32</v>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
       <c r="E8" s="7">
         <f>IF(ISNUMBER(Parameters!E25),Parameters!E25,"")</f>
         <v>167</v>
       </c>
       <c r="F8" s="9" t="str">
-        <f>IF(COUNT(Parameters!G17,Parameters!H25)&lt;2,"",MOD(Parameters!H25-Parameters!G17+180,360)-180)</f>
+        <f>IF(COUNT(L8:M8)&lt;2,"",MOD(M8-L8+180,360)-180)</f>
         <v/>
       </c>
       <c r="G8" s="11" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E8:F8)&lt;2,"",IF(E8&lt;=0,"",RADIANS(F8)/E8))</f>
         <v/>
       </c>
       <c r="H8" s="5" t="str">
@@ -4215,11 +4575,25 @@
         <v/>
       </c>
       <c r="K8" s="13" t="str">
-        <f>IF(COUNT(Parameters!C17:F17,Parameters!F25:G25)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E8)),"待填轮行程",IF(E8&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G17,Parameters!H25)&lt;2,"无效半径",""))))</f>
+        <f>IF(COUNT(Parameters!C17:D17,Parameters!F25:I25)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E8)),"待填轮行程",IF(E8&lt;=0,"轮行程须大于0",IF(COUNT(L8:M8)&lt;2,"无效半径",""))))</f>
         <v>待补坐标</v>
       </c>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
+      <c r="L8" s="103" t="str">
+        <f>IF(COUNT(Parameters!F25,Parameters!G25,Parameters!C17,Parameters!D17)&lt;4,"",IF(N8=0,"",IF(Parameters!G25&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!F25)*1000/N8))))))</f>
+        <v/>
+      </c>
+      <c r="M8" s="103" t="str">
+        <f>IF(COUNT(Parameters!H25,Parameters!I25,Parameters!C17,Parameters!D17)&lt;4,"",IF(O8=0,"",IF(Parameters!I25&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!H25)*1000/O8))))))</f>
+        <v/>
+      </c>
+      <c r="N8" s="105" t="str">
+        <f>IF(COUNT(Parameters!F25,Parameters!G25,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!F25-Parameters!C17)^2+(Parameters!G25-Parameters!D17)^2))</f>
+        <v/>
+      </c>
+      <c r="O8" s="105" t="str">
+        <f>IF(COUNT(Parameters!H25,Parameters!I25,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!H25-Parameters!C17)^2+(Parameters!I25-Parameters!D17)^2))</f>
+        <v/>
+      </c>
     </row>
     <row r="9" spans="1:13" ht="26.1" customHeight="1">
       <c r="A9" s="1"/>
@@ -4229,19 +4603,21 @@
       <c r="C9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>30</v>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
       </c>
       <c r="E9" s="8">
         <f>IF(ISNUMBER(Parameters!E26),Parameters!E26,"")</f>
         <v>166</v>
       </c>
       <c r="F9" s="10" t="str">
-        <f>IF(COUNT(Parameters!G18,Parameters!H26)&lt;2,"",MOD(Parameters!H26-Parameters!G18+180,360)-180)</f>
+        <f>IF(COUNT(L9:M9)&lt;2,"",MOD(M9-L9+180,360)-180)</f>
         <v/>
       </c>
       <c r="G9" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E9:F9)&lt;2,"",IF(E9&lt;=0,"",RADIANS(F9)/E9))</f>
         <v/>
       </c>
       <c r="H9" s="6" t="str">
@@ -4257,11 +4633,25 @@
         <v/>
       </c>
       <c r="K9" s="14" t="str">
-        <f>IF(COUNT(Parameters!C18:F18,Parameters!F26:G26)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E9)),"待填轮行程",IF(E9&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G18,Parameters!H26)&lt;2,"无效半径",""))))</f>
+        <f>IF(COUNT(Parameters!C18:D18,Parameters!F26:I26)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E9)),"待填轮行程",IF(E9&lt;=0,"轮行程须大于0",IF(COUNT(L9:M9)&lt;2,"无效半径",""))))</f>
         <v>待补坐标</v>
       </c>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
+      <c r="L9" s="104" t="str">
+        <f>IF(COUNT(Parameters!F26,Parameters!G26,Parameters!C18,Parameters!D18)&lt;4,"",IF(N9=0,"",IF(Parameters!G26&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!F26)*1000/N9))))))</f>
+        <v/>
+      </c>
+      <c r="M9" s="104" t="str">
+        <f>IF(COUNT(Parameters!H26,Parameters!I26,Parameters!C18,Parameters!D18)&lt;4,"",IF(O9=0,"",IF(Parameters!I26&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!H26)*1000/O9))))))</f>
+        <v/>
+      </c>
+      <c r="N9" s="106" t="str">
+        <f>IF(COUNT(Parameters!F26,Parameters!G26,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!F26-Parameters!C18)^2+(Parameters!G26-Parameters!D18)^2))</f>
+        <v/>
+      </c>
+      <c r="O9" s="106" t="str">
+        <f>IF(COUNT(Parameters!H26,Parameters!I26,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!H26-Parameters!C18)^2+(Parameters!I26-Parameters!D18)^2))</f>
+        <v/>
+      </c>
     </row>
     <row r="10" spans="1:13" ht="26.1" customHeight="1">
       <c r="A10" s="1"/>
@@ -4271,19 +4661,21 @@
       <c r="C10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>31</v>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="E10" s="7">
         <f>IF(ISNUMBER(Parameters!E27),Parameters!E27,"")</f>
         <v>166</v>
       </c>
       <c r="F10" s="9" t="str">
-        <f>IF(COUNT(Parameters!G18,Parameters!H27)&lt;2,"",MOD(Parameters!H27-Parameters!G18+180,360)-180)</f>
+        <f>IF(COUNT(L10:M10)&lt;2,"",MOD(M10-L10+180,360)-180)</f>
         <v/>
       </c>
       <c r="G10" s="11" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E10:F10)&lt;2,"",IF(E10&lt;=0,"",RADIANS(F10)/E10))</f>
         <v/>
       </c>
       <c r="H10" s="5" t="str">
@@ -4299,11 +4691,25 @@
         <v/>
       </c>
       <c r="K10" s="13" t="str">
-        <f>IF(COUNT(Parameters!C18:F18,Parameters!F27:G27)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E10)),"待填轮行程",IF(E10&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G18,Parameters!H27)&lt;2,"无效半径",""))))</f>
+        <f>IF(COUNT(Parameters!C18:D18,Parameters!F27:I27)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E10)),"待填轮行程",IF(E10&lt;=0,"轮行程须大于0",IF(COUNT(L10:M10)&lt;2,"无效半径",""))))</f>
         <v>待补坐标</v>
       </c>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
+      <c r="L10" s="103" t="str">
+        <f>IF(COUNT(Parameters!F27,Parameters!G27,Parameters!C18,Parameters!D18)&lt;4,"",IF(N10=0,"",IF(Parameters!G27&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!F27)*1000/N10))))))</f>
+        <v/>
+      </c>
+      <c r="M10" s="103" t="str">
+        <f>IF(COUNT(Parameters!H27,Parameters!I27,Parameters!C18,Parameters!D18)&lt;4,"",IF(O10=0,"",IF(Parameters!I27&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!H27)*1000/O10))))))</f>
+        <v/>
+      </c>
+      <c r="N10" s="105" t="str">
+        <f>IF(COUNT(Parameters!F27,Parameters!G27,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!F27-Parameters!C18)^2+(Parameters!G27-Parameters!D18)^2))</f>
+        <v/>
+      </c>
+      <c r="O10" s="105" t="str">
+        <f>IF(COUNT(Parameters!H27,Parameters!I27,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!H27-Parameters!C18)^2+(Parameters!I27-Parameters!D18)^2))</f>
+        <v/>
+      </c>
     </row>
     <row r="11" spans="1:13" ht="26.1" customHeight="1">
       <c r="A11" s="1"/>
@@ -4313,19 +4719,21 @@
       <c r="C11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>32</v>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
       <c r="E11" s="8">
         <f>IF(ISNUMBER(Parameters!E28),Parameters!E28,"")</f>
         <v>166</v>
       </c>
       <c r="F11" s="10" t="str">
-        <f>IF(COUNT(Parameters!G18,Parameters!H28)&lt;2,"",MOD(Parameters!H28-Parameters!G18+180,360)-180)</f>
+        <f>IF(COUNT(L11:M11)&lt;2,"",MOD(M11-L11+180,360)-180)</f>
         <v/>
       </c>
       <c r="G11" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E11:F11)&lt;2,"",IF(E11&lt;=0,"",RADIANS(F11)/E11))</f>
         <v/>
       </c>
       <c r="H11" s="6" t="str">
@@ -4341,11 +4749,25 @@
         <v/>
       </c>
       <c r="K11" s="14" t="str">
-        <f>IF(COUNT(Parameters!C18:F18,Parameters!F28:G28)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E11)),"待填轮行程",IF(E11&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G18,Parameters!H28)&lt;2,"无效半径",""))))</f>
+        <f>IF(COUNT(Parameters!C18:D18,Parameters!F28:I28)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E11)),"待填轮行程",IF(E11&lt;=0,"轮行程须大于0",IF(COUNT(L11:M11)&lt;2,"无效半径",""))))</f>
         <v>待补坐标</v>
       </c>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
+      <c r="L11" s="104" t="str">
+        <f>IF(COUNT(Parameters!F28,Parameters!G28,Parameters!C18,Parameters!D18)&lt;4,"",IF(N11=0,"",IF(Parameters!G28&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!F28)*1000/N11))))))</f>
+        <v/>
+      </c>
+      <c r="M11" s="104" t="str">
+        <f>IF(COUNT(Parameters!H28,Parameters!I28,Parameters!C18,Parameters!D18)&lt;4,"",IF(O11=0,"",IF(Parameters!I28&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!H28)*1000/O11))))))</f>
+        <v/>
+      </c>
+      <c r="N11" s="106" t="str">
+        <f>IF(COUNT(Parameters!F28,Parameters!G28,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!F28-Parameters!C18)^2+(Parameters!G28-Parameters!D18)^2))</f>
+        <v/>
+      </c>
+      <c r="O11" s="106" t="str">
+        <f>IF(COUNT(Parameters!H28,Parameters!I28,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!H28-Parameters!C18)^2+(Parameters!I28-Parameters!D18)^2))</f>
+        <v/>
+      </c>
     </row>
     <row r="12" spans="1:13" ht="26.1" customHeight="1">
       <c r="A12" s="1"/>
@@ -4355,39 +4777,55 @@
       <c r="C12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>30</v>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
       </c>
       <c r="E12" s="7">
         <f>IF(ISNUMBER(Parameters!E29),Parameters!E29,"")</f>
         <v>259</v>
       </c>
-      <c r="F12" s="9">
-        <f>IF(COUNT(Parameters!G17,Parameters!H29)&lt;2,"",MOD(Parameters!H29-Parameters!G17+180,360)-180)</f>
-        <v>33.758329224654602</v>
-      </c>
-      <c r="G12" s="11">
-        <f t="shared" si="0"/>
-        <v>2.2748802893530783E-3</v>
-      </c>
-      <c r="H12" s="5">
+      <c r="F12" s="9" t="str">
+        <f>IF(COUNT(L12:M12)&lt;2,"",MOD(M12-L12+180,360)-180)</f>
+        <v/>
+      </c>
+      <c r="G12" s="11" t="str">
+        <f>IF(COUNT(E12:F12)&lt;2,"",IF(E12&lt;=0,"",RADIANS(F12)/E12))</f>
+        <v/>
+      </c>
+      <c r="H12" s="5" t="str">
         <f>IF(ISNUMBER(G12),1000*Parameters!E7*G12^2,"")</f>
-        <v>4.871853581135178</v>
-      </c>
-      <c r="I12" s="5">
+        <v/>
+      </c>
+      <c r="I12" s="5" t="str">
         <f>IF(ISNUMBER(G12),1000*Parameters!E8*G12^2,"")</f>
-        <v>10.288059697803645</v>
-      </c>
-      <c r="J12" s="5">
+        <v/>
+      </c>
+      <c r="J12" s="5" t="str">
         <f>IF(ISNUMBER(G12),1000*Parameters!E9*G12^2,"")</f>
-        <v>18.936436183123369</v>
+        <v/>
       </c>
       <c r="K12" s="13" t="str">
-        <f>IF(COUNT(Parameters!C17:F17,Parameters!F29:G29)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E12)),"待填轮行程",IF(E12&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G17,Parameters!H29)&lt;2,"无效半径",""))))</f>
-        <v/>
-      </c>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
+        <f>IF(COUNT(Parameters!C17:D17,Parameters!F29:I29)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E12)),"待填轮行程",IF(E12&lt;=0,"轮行程须大于0",IF(COUNT(L12:M12)&lt;2,"无效半径",""))))</f>
+        <v>待补坐标</v>
+      </c>
+      <c r="L12" s="103" t="str">
+        <f>IF(COUNT(Parameters!F29,Parameters!G29,Parameters!C17,Parameters!D17)&lt;4,"",IF(N12=0,"",IF(Parameters!G29&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!F29)*1000/N12))))))</f>
+        <v/>
+      </c>
+      <c r="M12" s="103">
+        <f>IF(COUNT(Parameters!H29,Parameters!I29,Parameters!C17,Parameters!D17)&lt;4,"",IF(O12=0,"",IF(Parameters!I29&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!H29)*1000/O12))))))</f>
+        <v>46.178759169911224</v>
+      </c>
+      <c r="N12" s="105" t="str">
+        <f>IF(COUNT(Parameters!F29,Parameters!G29,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!F29-Parameters!C17)^2+(Parameters!G29-Parameters!D17)^2))</f>
+        <v/>
+      </c>
+      <c r="O12" s="105">
+        <f>IF(COUNT(Parameters!H29,Parameters!I29,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!H29-Parameters!C17)^2+(Parameters!I29-Parameters!D17)^2))</f>
+        <v>171.86331778480246</v>
+      </c>
     </row>
     <row r="13" spans="1:13" ht="26.1" customHeight="1">
       <c r="A13" s="1"/>
@@ -4397,39 +4835,55 @@
       <c r="C13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>31</v>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="E13" s="8">
         <f>IF(ISNUMBER(Parameters!E30),Parameters!E30,"")</f>
         <v>259</v>
       </c>
-      <c r="F13" s="10">
-        <f>IF(COUNT(Parameters!G17,Parameters!H30)&lt;2,"",MOD(Parameters!H30-Parameters!G17+180,360)-180)</f>
-        <v>34.127727753721359</v>
-      </c>
-      <c r="G13" s="12">
-        <f t="shared" si="0"/>
-        <v>2.2997730329215684E-3</v>
-      </c>
-      <c r="H13" s="6">
+      <c r="F13" s="10" t="str">
+        <f>IF(COUNT(L13:M13)&lt;2,"",MOD(M13-L13+180,360)-180)</f>
+        <v/>
+      </c>
+      <c r="G13" s="12" t="str">
+        <f>IF(COUNT(E13:F13)&lt;2,"",IF(E13&lt;=0,"",RADIANS(F13)/E13))</f>
+        <v/>
+      </c>
+      <c r="H13" s="6" t="str">
         <f>IF(ISNUMBER(G13),1000*Parameters!E7*G13^2,"")</f>
-        <v>4.979056864038502</v>
-      </c>
-      <c r="I13" s="6">
+        <v/>
+      </c>
+      <c r="I13" s="6" t="str">
         <f>IF(ISNUMBER(G13),1000*Parameters!E8*G13^2,"")</f>
-        <v>10.514444533871099</v>
-      </c>
-      <c r="J13" s="6">
+        <v/>
+      </c>
+      <c r="J13" s="6" t="str">
         <f>IF(ISNUMBER(G13),1000*Parameters!E9*G13^2,"")</f>
-        <v>19.353125250541339</v>
+        <v/>
       </c>
       <c r="K13" s="14" t="str">
-        <f>IF(COUNT(Parameters!C17:F17,Parameters!F30:G30)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E13)),"待填轮行程",IF(E13&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G17,Parameters!H30)&lt;2,"无效半径",""))))</f>
-        <v/>
-      </c>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
+        <f>IF(COUNT(Parameters!C17:D17,Parameters!F30:I30)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E13)),"待填轮行程",IF(E13&lt;=0,"轮行程须大于0",IF(COUNT(L13:M13)&lt;2,"无效半径",""))))</f>
+        <v>待补坐标</v>
+      </c>
+      <c r="L13" s="104" t="str">
+        <f>IF(COUNT(Parameters!F30,Parameters!G30,Parameters!C17,Parameters!D17)&lt;4,"",IF(N13=0,"",IF(Parameters!G30&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!F30)*1000/N13))))))</f>
+        <v/>
+      </c>
+      <c r="M13" s="104">
+        <f>IF(COUNT(Parameters!H30,Parameters!I30,Parameters!C17,Parameters!D17)&lt;4,"",IF(O13=0,"",IF(Parameters!I30&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!H30)*1000/O13))))))</f>
+        <v>46.548157698977995</v>
+      </c>
+      <c r="N13" s="106" t="str">
+        <f>IF(COUNT(Parameters!F30,Parameters!G30,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!F30-Parameters!C17)^2+(Parameters!G30-Parameters!D17)^2))</f>
+        <v/>
+      </c>
+      <c r="O13" s="106">
+        <f>IF(COUNT(Parameters!H30,Parameters!I30,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!H30-Parameters!C17)^2+(Parameters!I30-Parameters!D17)^2))</f>
+        <v>157.0350279396287</v>
+      </c>
     </row>
     <row r="14" spans="1:13" ht="26.1" customHeight="1">
       <c r="A14" s="1"/>
@@ -4439,39 +4893,55 @@
       <c r="C14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>32</v>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
       <c r="E14" s="7">
         <f>IF(ISNUMBER(Parameters!E31),Parameters!E31,"")</f>
         <v>259</v>
       </c>
-      <c r="F14" s="9">
-        <f>IF(COUNT(Parameters!G17,Parameters!H31)&lt;2,"",MOD(Parameters!H31-Parameters!G17+180,360)-180)</f>
-        <v>34.57413935598521</v>
-      </c>
-      <c r="G14" s="11">
-        <f t="shared" si="0"/>
-        <v>2.3298554741517132E-3</v>
-      </c>
-      <c r="H14" s="5">
+      <c r="F14" s="9" t="str">
+        <f>IF(COUNT(L14:M14)&lt;2,"",MOD(M14-L14+180,360)-180)</f>
+        <v/>
+      </c>
+      <c r="G14" s="11" t="str">
+        <f>IF(COUNT(E14:F14)&lt;2,"",IF(E14&lt;=0,"",RADIANS(F14)/E14))</f>
+        <v/>
+      </c>
+      <c r="H14" s="5" t="str">
         <f>IF(ISNUMBER(G14),1000*Parameters!E7*G14^2,"")</f>
-        <v>5.1101670255576179</v>
-      </c>
-      <c r="I14" s="5">
+        <v/>
+      </c>
+      <c r="I14" s="5" t="str">
         <f>IF(ISNUMBER(G14),1000*Parameters!E8*G14^2,"")</f>
-        <v>10.791314342504192</v>
-      </c>
-      <c r="J14" s="5">
+        <v/>
+      </c>
+      <c r="J14" s="5" t="str">
         <f>IF(ISNUMBER(G14),1000*Parameters!E9*G14^2,"")</f>
-        <v>19.862738104297762</v>
+        <v/>
       </c>
       <c r="K14" s="13" t="str">
-        <f>IF(COUNT(Parameters!C17:F17,Parameters!F31:G31)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E14)),"待填轮行程",IF(E14&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G17,Parameters!H31)&lt;2,"无效半径",""))))</f>
-        <v/>
-      </c>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
+        <f>IF(COUNT(Parameters!C17:D17,Parameters!F31:I31)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E14)),"待填轮行程",IF(E14&lt;=0,"轮行程须大于0",IF(COUNT(L14:M14)&lt;2,"无效半径",""))))</f>
+        <v>待补坐标</v>
+      </c>
+      <c r="L14" s="103" t="str">
+        <f>IF(COUNT(Parameters!F31,Parameters!G31,Parameters!C17,Parameters!D17)&lt;4,"",IF(N14=0,"",IF(Parameters!G31&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!F31)*1000/N14))))))</f>
+        <v/>
+      </c>
+      <c r="M14" s="103">
+        <f>IF(COUNT(Parameters!H31,Parameters!I31,Parameters!C17,Parameters!D17)&lt;4,"",IF(O14=0,"",IF(Parameters!I31&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!H31)*1000/O14))))))</f>
+        <v>46.994569301241846</v>
+      </c>
+      <c r="N14" s="105" t="str">
+        <f>IF(COUNT(Parameters!F31,Parameters!G31,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!F31-Parameters!C17)^2+(Parameters!G31-Parameters!D17)^2))</f>
+        <v/>
+      </c>
+      <c r="O14" s="105">
+        <f>IF(COUNT(Parameters!H31,Parameters!I31,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!H31-Parameters!C17)^2+(Parameters!I31-Parameters!D17)^2))</f>
+        <v>142.2146265332789</v>
+      </c>
     </row>
     <row r="15" spans="1:13" ht="26.1" customHeight="1">
       <c r="A15" s="1"/>
@@ -4481,39 +4951,55 @@
       <c r="C15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>30</v>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
       </c>
       <c r="E15" s="8">
         <f>IF(ISNUMBER(Parameters!E32),Parameters!E32,"")</f>
         <v>252</v>
       </c>
-      <c r="F15" s="10">
-        <f>IF(COUNT(Parameters!G18,Parameters!H32)&lt;2,"",MOD(Parameters!H32-Parameters!G18+180,360)-180)</f>
-        <v>38.443285238262206</v>
-      </c>
-      <c r="G15" s="12">
-        <f t="shared" si="0"/>
-        <v>2.6625472329008266E-3</v>
-      </c>
-      <c r="H15" s="6">
+      <c r="F15" s="10" t="str">
+        <f>IF(COUNT(L15:M15)&lt;2,"",MOD(M15-L15+180,360)-180)</f>
+        <v/>
+      </c>
+      <c r="G15" s="12" t="str">
+        <f>IF(COUNT(E15:F15)&lt;2,"",IF(E15&lt;=0,"",RADIANS(F15)/E15))</f>
+        <v/>
+      </c>
+      <c r="H15" s="6" t="str">
         <f>IF(ISNUMBER(G15),1000*Parameters!E10*G15^2,"")</f>
-        <v>10.130884546881639</v>
-      </c>
-      <c r="I15" s="6">
+        <v/>
+      </c>
+      <c r="I15" s="6" t="str">
         <f>IF(ISNUMBER(G15),1000*Parameters!E11*G15^2,"")</f>
-        <v>20.835034678470446</v>
-      </c>
-      <c r="J15" s="6">
+        <v/>
+      </c>
+      <c r="J15" s="6" t="str">
         <f>IF(ISNUMBER(G15),1000*Parameters!E12*G15^2,"")</f>
-        <v>35.087821313012348</v>
+        <v/>
       </c>
       <c r="K15" s="14" t="str">
-        <f>IF(COUNT(Parameters!C18:F18,Parameters!F32:G32)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E15)),"待填轮行程",IF(E15&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G18,Parameters!H32)&lt;2,"无效半径",""))))</f>
-        <v/>
-      </c>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
+        <f>IF(COUNT(Parameters!C18:D18,Parameters!F32:I32)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E15)),"待填轮行程",IF(E15&lt;=0,"轮行程须大于0",IF(COUNT(L15:M15)&lt;2,"无效半径",""))))</f>
+        <v>待补坐标</v>
+      </c>
+      <c r="L15" s="104" t="str">
+        <f>IF(COUNT(Parameters!F32,Parameters!G32,Parameters!C18,Parameters!D18)&lt;4,"",IF(N15=0,"",IF(Parameters!G32&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!F32)*1000/N15))))))</f>
+        <v/>
+      </c>
+      <c r="M15" s="104">
+        <f>IF(COUNT(Parameters!H32,Parameters!I32,Parameters!C18,Parameters!D18)&lt;4,"",IF(O15=0,"",IF(Parameters!I32&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!H32)*1000/O15))))))</f>
+        <v>21.471368323914565</v>
+      </c>
+      <c r="N15" s="106" t="str">
+        <f>IF(COUNT(Parameters!F32,Parameters!G32,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!F32-Parameters!C18)^2+(Parameters!G32-Parameters!D18)^2))</f>
+        <v/>
+      </c>
+      <c r="O15" s="106">
+        <f>IF(COUNT(Parameters!H32,Parameters!I32,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!H32-Parameters!C18)^2+(Parameters!I32-Parameters!D18)^2))</f>
+        <v>161.18622769951543</v>
+      </c>
     </row>
     <row r="16" spans="1:13" ht="26.1" customHeight="1">
       <c r="A16" s="1"/>
@@ -4523,39 +5009,55 @@
       <c r="C16" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>31</v>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="E16" s="7">
         <f>IF(ISNUMBER(Parameters!E33),Parameters!E33,"")</f>
         <v>252</v>
       </c>
-      <c r="F16" s="9">
-        <f>IF(COUNT(Parameters!G18,Parameters!H33)&lt;2,"",MOD(Parameters!H33-Parameters!G18+180,360)-180)</f>
-        <v>40.894422797360903</v>
-      </c>
-      <c r="G16" s="11">
-        <f t="shared" si="0"/>
-        <v>2.8323108076054667E-3</v>
-      </c>
-      <c r="H16" s="5">
+      <c r="F16" s="9" t="str">
+        <f>IF(COUNT(L16:M16)&lt;2,"",MOD(M16-L16+180,360)-180)</f>
+        <v/>
+      </c>
+      <c r="G16" s="11" t="str">
+        <f>IF(COUNT(E16:F16)&lt;2,"",IF(E16&lt;=0,"",RADIANS(F16)/E16))</f>
+        <v/>
+      </c>
+      <c r="H16" s="5" t="str">
         <f>IF(ISNUMBER(G16),1000*Parameters!E10*G16^2,"")</f>
-        <v>11.463956873691107</v>
-      </c>
-      <c r="I16" s="5">
+        <v/>
+      </c>
+      <c r="I16" s="5" t="str">
         <f>IF(ISNUMBER(G16),1000*Parameters!E11*G16^2,"")</f>
-        <v>23.576612477472587</v>
-      </c>
-      <c r="J16" s="5">
+        <v/>
+      </c>
+      <c r="J16" s="5" t="str">
         <f>IF(ISNUMBER(G16),1000*Parameters!E12*G16^2,"")</f>
-        <v>39.704851877713608</v>
+        <v/>
       </c>
       <c r="K16" s="13" t="str">
-        <f>IF(COUNT(Parameters!C18:F18,Parameters!F33:G33)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E16)),"待填轮行程",IF(E16&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G18,Parameters!H33)&lt;2,"无效半径",""))))</f>
-        <v/>
-      </c>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
+        <f>IF(COUNT(Parameters!C18:D18,Parameters!F33:I33)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E16)),"待填轮行程",IF(E16&lt;=0,"轮行程须大于0",IF(COUNT(L16:M16)&lt;2,"无效半径",""))))</f>
+        <v>待补坐标</v>
+      </c>
+      <c r="L16" s="103" t="str">
+        <f>IF(COUNT(Parameters!F33,Parameters!G33,Parameters!C18,Parameters!D18)&lt;4,"",IF(N16=0,"",IF(Parameters!G33&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!F33)*1000/N16))))))</f>
+        <v/>
+      </c>
+      <c r="M16" s="103">
+        <f>IF(COUNT(Parameters!H33,Parameters!I33,Parameters!C18,Parameters!D18)&lt;4,"",IF(O16=0,"",IF(Parameters!I33&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!H33)*1000/O16))))))</f>
+        <v>23.922505883013255</v>
+      </c>
+      <c r="N16" s="105" t="str">
+        <f>IF(COUNT(Parameters!F33,Parameters!G33,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!F33-Parameters!C18)^2+(Parameters!G33-Parameters!D18)^2))</f>
+        <v/>
+      </c>
+      <c r="O16" s="105">
+        <f>IF(COUNT(Parameters!H33,Parameters!I33,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!H33-Parameters!C18)^2+(Parameters!I33-Parameters!D18)^2))</f>
+        <v>145.49914089093446</v>
+      </c>
     </row>
     <row r="17" spans="1:13" ht="26.1" customHeight="1">
       <c r="A17" s="1"/>
@@ -4565,39 +5067,55 @@
       <c r="C17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>32</v>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
       <c r="E17" s="8">
         <f>IF(ISNUMBER(Parameters!E34),Parameters!E34,"")</f>
         <v>252</v>
       </c>
-      <c r="F17" s="10">
-        <f>IF(COUNT(Parameters!G18,Parameters!H34)&lt;2,"",MOD(Parameters!H34-Parameters!G18+180,360)-180)</f>
-        <v>43.340750435531703</v>
-      </c>
-      <c r="G17" s="12">
-        <f t="shared" si="0"/>
-        <v>3.0017412515285502E-3</v>
-      </c>
-      <c r="H17" s="6">
+      <c r="F17" s="10" t="str">
+        <f>IF(COUNT(L17:M17)&lt;2,"",MOD(M17-L17+180,360)-180)</f>
+        <v/>
+      </c>
+      <c r="G17" s="12" t="str">
+        <f>IF(COUNT(E17:F17)&lt;2,"",IF(E17&lt;=0,"",RADIANS(F17)/E17))</f>
+        <v/>
+      </c>
+      <c r="H17" s="6" t="str">
         <f>IF(ISNUMBER(G17),1000*Parameters!E10*G17^2,"")</f>
-        <v>12.876541493683991</v>
-      </c>
-      <c r="I17" s="6">
+        <v/>
+      </c>
+      <c r="I17" s="6" t="str">
         <f>IF(ISNUMBER(G17),1000*Parameters!E11*G17^2,"")</f>
-        <v>26.481714140375743</v>
-      </c>
-      <c r="J17" s="6">
+        <v/>
+      </c>
+      <c r="J17" s="6" t="str">
         <f>IF(ISNUMBER(G17),1000*Parameters!E12*G17^2,"")</f>
-        <v>44.597269366675718</v>
+        <v/>
       </c>
       <c r="K17" s="14" t="str">
-        <f>IF(COUNT(Parameters!C18:F18,Parameters!F34:G34)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E17)),"待填轮行程",IF(E17&lt;=0,"轮行程须大于0",IF(COUNT(Parameters!G18,Parameters!H34)&lt;2,"无效半径",""))))</f>
-        <v/>
-      </c>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
+        <f>IF(COUNT(Parameters!C18:D18,Parameters!F34:I34)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E17)),"待填轮行程",IF(E17&lt;=0,"轮行程须大于0",IF(COUNT(L17:M17)&lt;2,"无效半径",""))))</f>
+        <v>待补坐标</v>
+      </c>
+      <c r="L17" s="104" t="str">
+        <f>IF(COUNT(Parameters!F34,Parameters!G34,Parameters!C18,Parameters!D18)&lt;4,"",IF(N17=0,"",IF(Parameters!G34&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!F34)*1000/N17))))))</f>
+        <v/>
+      </c>
+      <c r="M17" s="104">
+        <f>IF(COUNT(Parameters!H34,Parameters!I34,Parameters!C18,Parameters!D18)&lt;4,"",IF(O17=0,"",IF(Parameters!I34&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!H34)*1000/O17))))))</f>
+        <v>26.368833521184072</v>
+      </c>
+      <c r="N17" s="106" t="str">
+        <f>IF(COUNT(Parameters!F34,Parameters!G34,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!F34-Parameters!C18)^2+(Parameters!G34-Parameters!D18)^2))</f>
+        <v/>
+      </c>
+      <c r="O17" s="106">
+        <f>IF(COUNT(Parameters!H34,Parameters!I34,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!H34-Parameters!C18)^2+(Parameters!I34-Parameters!D18)^2))</f>
+        <v>130.58713566044705</v>
+      </c>
     </row>
     <row r="18" spans="1:13" ht="26.1" customHeight="1">
       <c r="A18" s="1"/>
@@ -4682,16 +5200,18 @@
     </row>
     <row r="23" spans="1:13" ht="26.1" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="6">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>#1 L</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="e">
         <f>IF(ISNUMBER(H12),H12,NA())</f>
-        <v>4.871853581135178</v>
-      </c>
-      <c r="D23" s="6">
+        <v>#N/A</v>
+      </c>
+      <c r="D23" s="6" t="e">
         <f>IF(ISNUMBER(H15),H15,NA())</f>
-        <v>10.130884546881639</v>
+        <v>#N/A</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -4705,16 +5225,18 @@
     </row>
     <row r="24" spans="1:13" ht="26.1" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="5">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>#1 M</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="e">
         <f>IF(ISNUMBER(H13),H13,NA())</f>
-        <v>4.979056864038502</v>
-      </c>
-      <c r="D24" s="5">
+        <v>#N/A</v>
+      </c>
+      <c r="D24" s="5" t="e">
         <f>IF(ISNUMBER(H16),H16,NA())</f>
-        <v>11.463956873691107</v>
+        <v>#N/A</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
@@ -4728,16 +5250,18 @@
     </row>
     <row r="25" spans="1:13" ht="26.1" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="6">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>#1 H</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="e">
         <f>IF(ISNUMBER(H14),H14,NA())</f>
-        <v>5.1101670255576179</v>
-      </c>
-      <c r="D25" s="6">
+        <v>#N/A</v>
+      </c>
+      <c r="D25" s="6" t="e">
         <f>IF(ISNUMBER(H17),H17,NA())</f>
-        <v>12.876541493683991</v>
+        <v>#N/A</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -4751,16 +5275,18 @@
     </row>
     <row r="26" spans="1:13" ht="26.1" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" s="5">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>#2 L</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="e">
         <f>IF(ISNUMBER(I12),I12,NA())</f>
-        <v>10.288059697803645</v>
-      </c>
-      <c r="D26" s="5">
+        <v>#N/A</v>
+      </c>
+      <c r="D26" s="5" t="e">
         <f>IF(ISNUMBER(I15),I15,NA())</f>
-        <v>20.835034678470446</v>
+        <v>#N/A</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
@@ -4774,16 +5300,18 @@
     </row>
     <row r="27" spans="1:13" ht="26.1" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C27" s="6">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>#2 M</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="e">
         <f>IF(ISNUMBER(I13),I13,NA())</f>
-        <v>10.514444533871099</v>
-      </c>
-      <c r="D27" s="6">
+        <v>#N/A</v>
+      </c>
+      <c r="D27" s="6" t="e">
         <f>IF(ISNUMBER(I16),I16,NA())</f>
-        <v>23.576612477472587</v>
+        <v>#N/A</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -4797,16 +5325,18 @@
     </row>
     <row r="28" spans="1:13" ht="26.1" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="5">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>#2 H</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="e">
         <f>IF(ISNUMBER(I14),I14,NA())</f>
-        <v>10.791314342504192</v>
-      </c>
-      <c r="D28" s="5">
+        <v>#N/A</v>
+      </c>
+      <c r="D28" s="5" t="e">
         <f>IF(ISNUMBER(I17),I17,NA())</f>
-        <v>26.481714140375743</v>
+        <v>#N/A</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
@@ -4820,16 +5350,18 @@
     </row>
     <row r="29" spans="1:13" ht="26.1" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" s="6">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>#3 L</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="e">
         <f>IF(ISNUMBER(J12),J12,NA())</f>
-        <v>18.936436183123369</v>
-      </c>
-      <c r="D29" s="6">
+        <v>#N/A</v>
+      </c>
+      <c r="D29" s="6" t="e">
         <f>IF(ISNUMBER(J15),J15,NA())</f>
-        <v>35.087821313012348</v>
+        <v>#N/A</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
@@ -4843,16 +5375,18 @@
     </row>
     <row r="30" spans="1:13" ht="26.1" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C30" s="5">
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>#3 M</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="e">
         <f>IF(ISNUMBER(J13),J13,NA())</f>
-        <v>19.353125250541339</v>
-      </c>
-      <c r="D30" s="5">
+        <v>#N/A</v>
+      </c>
+      <c r="D30" s="5" t="e">
         <f>IF(ISNUMBER(J16),J16,NA())</f>
-        <v>39.704851877713608</v>
+        <v>#N/A</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -4866,16 +5400,18 @@
     </row>
     <row r="31" spans="1:13" ht="26.1" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C31" s="6">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>#3 H</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="e">
         <f>IF(ISNUMBER(J14),J14,NA())</f>
-        <v>19.862738104297762</v>
-      </c>
-      <c r="D31" s="6">
+        <v>#N/A</v>
+      </c>
+      <c r="D31" s="6" t="e">
         <f>IF(ISNUMBER(J17),J17,NA())</f>
-        <v>44.597269366675718</v>
+        <v>#N/A</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -4955,8 +5491,10 @@
     </row>
     <row r="36" spans="1:13" ht="26.1" customHeight="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="4" t="s">
-        <v>45</v>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>#1 L</t>
+        </is>
       </c>
       <c r="C36" s="5" t="e">
         <f>IF(ISNUMBER(H6),H6,NA())</f>
@@ -4978,8 +5516,10 @@
     </row>
     <row r="37" spans="1:13" ht="26.1" customHeight="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="3" t="s">
-        <v>46</v>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>#1 M</t>
+        </is>
       </c>
       <c r="C37" s="6" t="e">
         <f>IF(ISNUMBER(H7),H7,NA())</f>
@@ -5001,8 +5541,10 @@
     </row>
     <row r="38" spans="1:13" ht="26.1" customHeight="1">
       <c r="A38" s="1"/>
-      <c r="B38" s="4" t="s">
-        <v>47</v>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>#1 H</t>
+        </is>
       </c>
       <c r="C38" s="5" t="e">
         <f>IF(ISNUMBER(H8),H8,NA())</f>
@@ -5024,8 +5566,10 @@
     </row>
     <row r="39" spans="1:13" ht="26.1" customHeight="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="3" t="s">
-        <v>48</v>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>#2 L</t>
+        </is>
       </c>
       <c r="C39" s="6" t="e">
         <f>IF(ISNUMBER(I6),I6,NA())</f>
@@ -5047,8 +5591,10 @@
     </row>
     <row r="40" spans="1:13" ht="26.1" customHeight="1">
       <c r="A40" s="1"/>
-      <c r="B40" s="4" t="s">
-        <v>49</v>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>#2 M</t>
+        </is>
       </c>
       <c r="C40" s="5" t="e">
         <f>IF(ISNUMBER(I7),I7,NA())</f>
@@ -5070,8 +5616,10 @@
     </row>
     <row r="41" spans="1:13" ht="26.1" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="3" t="s">
-        <v>50</v>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>#2 H</t>
+        </is>
       </c>
       <c r="C41" s="6" t="e">
         <f>IF(ISNUMBER(I8),I8,NA())</f>
@@ -5093,8 +5641,10 @@
     </row>
     <row r="42" spans="1:13" ht="26.1" customHeight="1">
       <c r="A42" s="1"/>
-      <c r="B42" s="4" t="s">
-        <v>51</v>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>#3 L</t>
+        </is>
       </c>
       <c r="C42" s="5" t="e">
         <f>IF(ISNUMBER(J6),J6,NA())</f>
@@ -5116,8 +5666,10 @@
     </row>
     <row r="43" spans="1:13" ht="26.1" customHeight="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="3" t="s">
-        <v>52</v>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>#3 M</t>
+        </is>
       </c>
       <c r="C43" s="6" t="e">
         <f>IF(ISNUMBER(J7),J7,NA())</f>
@@ -5139,8 +5691,10 @@
     </row>
     <row r="44" spans="1:13" ht="26.1" customHeight="1">
       <c r="A44" s="1"/>
-      <c r="B44" s="4" t="s">
-        <v>53</v>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>#3 H</t>
+        </is>
       </c>
       <c r="C44" s="5" t="e">
         <f>IF(ISNUMBER(J8),J8,NA())</f>

--- a/docs/arb_stiffness.xlsx
+++ b/docs/arb_stiffness.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\UserSpace\Games\Steam_Library\common\BeamNG_Userdata\current\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BD550C-4EB9-4305-944E-259FF8944632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A3CF3C-168E-43FE-9070-7AEC032FD9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comparison" sheetId="1" r:id="rId1"/>
     <sheet name="Parameters" sheetId="5" r:id="rId2"/>
     <sheet name="Samples" sheetId="7" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" forceFullCalc="1" calcMode="auto" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="68">
   <si>
     <t>Astral · Anti-Roll Bar Stiffness</t>
   </si>
@@ -69,15 +69,6 @@
     <t>Front</t>
   </si>
   <si>
-    <t>Soft</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Hard</t>
-  </si>
-  <si>
     <t>Rear</t>
   </si>
   <si>
@@ -107,10 +98,6 @@
 (°)</t>
   </si>
   <si>
-    <t>Radius
-(mm)</t>
-  </si>
-  <si>
     <t>测量 · 每组填写轮行程和 arb1 终点</t>
   </si>
   <si>
@@ -139,15 +126,6 @@
     <t>Tarmac</t>
   </si>
   <si>
-    <t>Inner</t>
-  </si>
-  <si>
-    <t>Middle</t>
-  </si>
-  <si>
-    <t>Outer</t>
-  </si>
-  <si>
     <t>Gravel</t>
   </si>
   <si>
@@ -171,94 +149,127 @@
 (rad/mm)</t>
   </si>
   <si>
-    <t>Soft
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>旧表原值</t>
+  </si>
+  <si>
+    <t>Tarmac!I19</t>
+  </si>
+  <si>
+    <t>Tarmac!J19</t>
+  </si>
+  <si>
+    <t>Tarmac!K19</t>
+  </si>
+  <si>
+    <t>Tarmac!I20</t>
+  </si>
+  <si>
+    <t>Tarmac!J20</t>
+  </si>
+  <si>
+    <t>Gravel!K6</t>
+  </si>
+  <si>
+    <t>Gravel!K7</t>
+  </si>
+  <si>
+    <t>Gravel!K8</t>
+  </si>
+  <si>
+    <t>#1</t>
+  </si>
+  <si>
+    <t>#2</t>
+  </si>
+  <si>
+    <t>#3</t>
+  </si>
+  <si>
+    <t>固定转轴</t>
+  </si>
+  <si>
+    <t>节点使用车身相对坐标（m）。</t>
+  </si>
+  <si>
+    <t>测量 · 各档起点 / 终点</t>
+  </si>
+  <si>
+    <t>起点为 wheeljack 架起、全伸展稳定后的位置；轮行程从同一起点计算。</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>#1
 (N/mm)</t>
   </si>
   <si>
-    <t>Medium
+    <t>#2
 (N/mm)</t>
   </si>
   <si>
-    <t>Hard
+    <t>#3
 (N/mm)</t>
   </si>
   <si>
-    <t>Input</t>
-  </si>
-  <si>
-    <t>Setting</t>
-  </si>
-  <si>
-    <t>Soft Inner</t>
-  </si>
-  <si>
-    <t>Soft Middle</t>
-  </si>
-  <si>
-    <t>Soft Outer</t>
-  </si>
-  <si>
-    <t>Medium Inner</t>
-  </si>
-  <si>
-    <t>Medium Middle</t>
-  </si>
-  <si>
-    <t>Medium Outer</t>
-  </si>
-  <si>
-    <t>Hard Inner</t>
-  </si>
-  <si>
-    <t>Hard Middle</t>
-  </si>
-  <si>
-    <t>Hard Outer</t>
-  </si>
-  <si>
-    <t>旧表原值</t>
-  </si>
-  <si>
-    <t>Tarmac!I19</t>
-  </si>
-  <si>
-    <t>Tarmac!J19</t>
-  </si>
-  <si>
-    <t>Tarmac!K19</t>
-  </si>
-  <si>
-    <t>Tarmac!I20</t>
-  </si>
-  <si>
-    <t>Tarmac!J20</t>
-  </si>
-  <si>
-    <t>Gravel!K6</t>
-  </si>
-  <si>
-    <t>Gravel!K7</t>
-  </si>
-  <si>
-    <t>Gravel!K8</t>
+    <t>Start radius
+(mm)</t>
+  </si>
+  <si>
+    <t>End radius
+(mm)</t>
+  </si>
+  <si>
+    <t>#1 L</t>
+  </si>
+  <si>
+    <t>#1 M</t>
+  </si>
+  <si>
+    <t>#1 H</t>
+  </si>
+  <si>
+    <t>#2 L</t>
+  </si>
+  <si>
+    <t>#2 M</t>
+  </si>
+  <si>
+    <t>#2 H</t>
+  </si>
+  <si>
+    <t>#3 L</t>
+  </si>
+  <si>
+    <t>#3 M</t>
+  </si>
+  <si>
+    <t>#3 H</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="9">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="0.0"/>
     <numFmt numFmtId="177" formatCode="0.0000"/>
     <numFmt numFmtId="178" formatCode="0.000"/>
     <numFmt numFmtId="179" formatCode="0.000000"/>
-    <numFmt numFmtId="180" formatCode="0.0"/>
-    <numFmt numFmtId="181" formatCode="0.0000"/>
-    <numFmt numFmtId="182" formatCode="0.000"/>
-    <numFmt numFmtId="183" formatCode="0.000000"/>
-    <numFmt numFmtId="184" formatCode="0.00"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -347,21 +358,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF667B91"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Carlito"/>
     </font>
     <font>
       <sz val="11"/>
@@ -370,7 +370,27 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF667B91"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color rgb="FF667B91"/>
       <name val="Microsoft YaHei"/>
       <family val="2"/>
@@ -389,35 +409,8 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF667B91"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF667B91"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF283C50"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FF283C50"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -427,99 +420,8 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF667B91"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF667B91"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF667B91"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF283C50"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF195DB1"/>
-      <name val="Arial"/>
-    </font>
   </fonts>
-  <fills count="26">
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31475E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5F7FA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDF2F7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31475E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5F7FA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDF2F7"/>
-      </patternFill>
-    </fill>
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -573,6 +475,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF2F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF31475E"/>
       </patternFill>
     </fill>
@@ -592,7 +509,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -648,27 +565,20 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFDCE4EB"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="4"/>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -739,19 +649,58 @@
     <xf numFmtId="177" fontId="10" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="7" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="4" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="22" fillId="16" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="4" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="16" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="17" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="17" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -760,215 +709,8 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="4" xfId="2"/>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="4" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="13" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="13" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="16" fillId="13" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="16" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="16" fillId="13" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="16" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="25" fillId="20" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="25" fillId="20" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="22" fillId="19" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="22" fillId="17" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="25" fillId="20" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="22" fillId="19" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="22" fillId="17" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="22" fillId="19" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="22" fillId="17" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="4" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="24" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="24" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="32" fillId="24" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="32" fillId="24" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="16" fillId="25" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="16" fillId="23" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="31" fillId="25" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="31" fillId="23" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1071,8 +813,35 @@
             <c:numRef>
               <c:f>Samples!$C$23:$C$31</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>5.2468630107600935</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.504576622925577</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.0098659998526269</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.07997992589914</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11.624202567803193</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12.691239412798074</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20.394062528804113</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>21.395771075463013</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>23.359783310403735</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1133,8 +902,35 @@
             <c:numRef>
               <c:f>Samples!$D$23:$D$31</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>11.08545128513005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13.681622555635043</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.523535202834569</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22.798183207336258</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>28.137432529733275</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>36.038656047347558</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>38.393916352197742</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>47.385628104109358</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>60.691903961989226</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1366,8 +1162,35 @@
             <c:numRef>
               <c:f>Samples!$C$36:$C$44</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>#N/A</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1428,8 +1251,35 @@
             <c:numRef>
               <c:f>Samples!$D$36:$D$44</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>#N/A</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1879,151 +1729,151 @@
     </row>
     <row r="2" spans="1:15" ht="26.1" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="41" t="s">
         <v>0</v>
       </c>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:15" ht="26.1" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="41" t="s">
         <v>0</v>
       </c>
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" ht="26.1" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="29" t="s">
+      <c r="G4" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="I4" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="J4" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="L4" s="29" t="s">
+      <c r="L4" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="N4" s="29" t="s">
+      <c r="N4" s="42" t="s">
         <v>1</v>
       </c>
       <c r="O4" s="1"/>
     </row>
     <row r="5" spans="1:15" ht="26.1" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="30" t="str">
+      <c r="B5" s="43" t="str">
         <f>IF(COUNT(Samples!H6:J17)=0,"待补节点坐标；暂无刚度结果。","")</f>
-        <v>待补节点坐标；暂无刚度结果。</v>
-      </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="30"/>
-      <c r="N5" s="30"/>
+        <v/>
+      </c>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="26.1" customHeight="1">
@@ -2759,43 +2609,43 @@
     </row>
     <row r="49" spans="1:15" ht="26.1" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="30" t="s">
+      <c r="B49" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="C49" s="30" t="s">
+      <c r="C49" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="D49" s="30" t="s">
+      <c r="D49" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="E49" s="30" t="s">
+      <c r="E49" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="F49" s="30" t="s">
+      <c r="F49" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="G49" s="30" t="s">
+      <c r="G49" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="H49" s="30" t="s">
+      <c r="H49" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="I49" s="30" t="s">
+      <c r="I49" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="J49" s="30" t="s">
+      <c r="J49" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="K49" s="30" t="s">
+      <c r="K49" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="L49" s="30" t="s">
+      <c r="L49" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="M49" s="30" t="s">
+      <c r="M49" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="N49" s="30" t="s">
+      <c r="N49" s="43" t="s">
         <v>2</v>
       </c>
       <c r="O49" s="1"/>
@@ -2807,7 +2657,7 @@
     <mergeCell ref="B5:N5"/>
     <mergeCell ref="B49:N49"/>
   </mergeCells>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2847,84 +2697,84 @@
     </row>
     <row r="2" spans="1:10" ht="27" customHeight="1">
       <c r="A2" s="15"/>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="G2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="32" t="s">
+      <c r="I2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10" ht="27" customHeight="1">
       <c r="A3" s="15"/>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="F3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="I3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="J3" s="15"/>
     </row>
     <row r="4" spans="1:10" ht="27" customHeight="1">
       <c r="A4" s="15"/>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="F4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="G4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="H4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="33" t="s">
+      <c r="I4" s="37" t="s">
         <v>4</v>
       </c>
       <c r="J4" s="15"/>
@@ -2966,17 +2816,15 @@
       <c r="B7" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
+      <c r="C7" s="17" t="s">
+        <v>44</v>
       </c>
       <c r="D7" s="19">
         <v>14.6</v>
       </c>
       <c r="E7" s="21">
         <f>$E$8*(D7/$D$8)^4</f>
-        <v>941.4063685268464</v>
+        <v>941.40636852684645</v>
       </c>
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
@@ -2989,10 +2837,8 @@
       <c r="B8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
+      <c r="C8" s="18" t="s">
+        <v>45</v>
       </c>
       <c r="D8" s="19">
         <v>17.600000000000001</v>
@@ -3011,17 +2857,15 @@
       <c r="B9" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
+      <c r="C9" s="17" t="s">
+        <v>46</v>
       </c>
       <c r="D9" s="19">
         <v>20.5</v>
       </c>
       <c r="E9" s="21">
         <f>$E$8*(D9/$D$8)^4</f>
-        <v>3659.1579207191103</v>
+        <v>3659.1579207191098</v>
       </c>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
@@ -3032,19 +2876,17 @@
     <row r="10" spans="1:10" ht="27" customHeight="1">
       <c r="A10" s="15"/>
       <c r="B10" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>44</v>
       </c>
       <c r="D10" s="19">
         <v>16.2</v>
       </c>
       <c r="E10" s="22">
         <f>$E$8*(D10/$D$8)^4</f>
-        <v>1427.0058942593776</v>
+        <v>1427.0058942593778</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
@@ -3055,19 +2897,17 @@
     <row r="11" spans="1:10" ht="27" customHeight="1">
       <c r="A11" s="15"/>
       <c r="B11" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>45</v>
       </c>
       <c r="D11" s="19">
         <v>19.399999999999999</v>
       </c>
       <c r="E11" s="21">
         <f>$E$8*(D11/$D$8)^4</f>
-        <v>2934.760252738988</v>
+        <v>2934.7602527389881</v>
       </c>
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
@@ -3078,19 +2918,17 @@
     <row r="12" spans="1:10" ht="27" customHeight="1">
       <c r="A12" s="15"/>
       <c r="B12" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>46</v>
       </c>
       <c r="D12" s="19">
         <v>22.1</v>
       </c>
       <c r="E12" s="22">
         <f>$E$8*(D12/$D$8)^4</f>
-        <v>4942.364864458013</v>
+        <v>4942.3648644580135</v>
       </c>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
@@ -3112,390 +2950,330 @@
     </row>
     <row r="14" spans="1:10" ht="27" customHeight="1">
       <c r="A14" s="15"/>
-      <c r="B14" s="66" t="str">
-        <v>固定转轴</v>
-      </c>
-      <c r="C14" s="66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">固定几何 · 生成位置 / 转轴</t>
-        </is>
-      </c>
-      <c r="D14" s="66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">固定几何 · 生成位置 / 转轴</t>
-        </is>
-      </c>
-      <c r="E14" s="66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">固定几何 · 生成位置 / 转轴</t>
-        </is>
-      </c>
-      <c r="F14" s="66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">固定几何 · 生成位置 / 转轴</t>
-        </is>
-      </c>
-      <c r="G14" s="66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">固定几何 · 生成位置 / 转轴</t>
-        </is>
-      </c>
-      <c r="H14" s="66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">固定几何 · 生成位置 / 转轴</t>
-        </is>
-      </c>
-      <c r="I14" s="66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">固定几何 · 生成位置 / 转轴</t>
-        </is>
+      <c r="B14" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="38" t="s">
+        <v>11</v>
       </c>
       <c r="J14" s="15"/>
     </row>
     <row r="15" spans="1:10" ht="27" customHeight="1">
       <c r="A15" s="15"/>
-      <c r="B15" s="69" t="str">
-        <v>节点使用车身相对坐标（m）。</v>
-      </c>
-      <c r="C15" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</t>
-        </is>
-      </c>
-      <c r="D15" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</t>
-        </is>
-      </c>
-      <c r="E15" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</t>
-        </is>
-      </c>
-      <c r="F15" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</t>
-        </is>
-      </c>
-      <c r="G15" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</t>
-        </is>
-      </c>
-      <c r="H15" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</t>
-        </is>
-      </c>
-      <c r="I15" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</t>
-        </is>
+      <c r="B15" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="39" t="s">
+        <v>12</v>
       </c>
       <c r="J15" s="15"/>
     </row>
     <row r="16" spans="1:10" ht="42" customHeight="1">
       <c r="A16" s="15"/>
-      <c r="B16" s="74" t="str">
-        <v>Axle</v>
-      </c>
-      <c r="C16" s="74" t="str">
-        <v>arb2 Y
-(m)</v>
-      </c>
-      <c r="D16" s="74" t="str">
-        <v>arb2 Z
-(m)</v>
-      </c>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
+      <c r="B16" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>16</v>
+      </c>
       <c r="J16" s="15"/>
     </row>
     <row r="17" spans="1:14" ht="27" customHeight="1">
       <c r="A17" s="15"/>
-      <c r="B17" s="78" t="str">
-        <v>Front</v>
-      </c>
-      <c r="C17" s="82" t="n">
-        <v>-0.915</v>
-      </c>
-      <c r="D17" s="82" t="n">
+      <c r="B17" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="29">
+        <v>-0.91500000000000004</v>
+      </c>
+      <c r="D17" s="29">
         <v>0.127</v>
       </c>
-      <c r="E17"/>
-      <c r="F17"/>
-      <c r="G17"/>
-      <c r="H17"/>
-      <c r="I17"/>
       <c r="J17" s="15"/>
     </row>
     <row r="18" spans="1:14" ht="27" customHeight="1">
       <c r="A18" s="15"/>
-      <c r="B18" s="86" t="str">
-        <v>Rear</v>
-      </c>
-      <c r="C18" s="82" t="n">
-        <v>1.459</v>
-      </c>
-      <c r="D18" s="82" t="n">
+      <c r="B18" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="29">
+        <v>1.4590000000000001</v>
+      </c>
+      <c r="D18" s="29">
         <v>0.26</v>
       </c>
-      <c r="E18"/>
-      <c r="F18"/>
-      <c r="G18"/>
-      <c r="H18"/>
-      <c r="I18"/>
       <c r="J18" s="15"/>
     </row>
     <row r="19" spans="1:14" ht="27" customHeight="1">
       <c r="A19" s="15"/>
-      <c r="B19" s="50"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="50"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
       <c r="J19" s="15"/>
     </row>
     <row r="20" spans="1:14" ht="27" customHeight="1">
       <c r="A20" s="15"/>
-      <c r="B20" s="66" t="str">
-        <v>测量 · 各档起点 / 终点</v>
-      </c>
-      <c r="C20" s="66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">测量 · 每组填写轮行程和 arb1 终点</t>
-        </is>
-      </c>
-      <c r="D20" s="66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">测量 · 每组填写轮行程和 arb1 终点</t>
-        </is>
-      </c>
-      <c r="E20" s="66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">测量 · 每组填写轮行程和 arb1 终点</t>
-        </is>
-      </c>
-      <c r="F20" s="66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">测量 · 每组填写轮行程和 arb1 终点</t>
-        </is>
-      </c>
-      <c r="G20" s="66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">测量 · 每组填写轮行程和 arb1 终点</t>
-        </is>
-      </c>
-      <c r="H20" s="66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">测量 · 每组填写轮行程和 arb1 终点</t>
-        </is>
-      </c>
-      <c r="I20" s="66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">测量 · 每组填写轮行程和 arb1 终点</t>
-        </is>
+      <c r="B20" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="38" t="s">
+        <v>18</v>
       </c>
       <c r="J20" s="15"/>
     </row>
     <row r="21" spans="1:14" ht="27" customHeight="1">
       <c r="A21" s="15"/>
-      <c r="B21" s="87" t="str">
-        <v>起点为 wheeljack 架起、全伸展稳定后的位置；轮行程从同一起点计算。</v>
-      </c>
-      <c r="C21" s="87"/>
-      <c r="D21" s="87"/>
-      <c r="E21" s="87"/>
-      <c r="F21" s="87"/>
-      <c r="G21" s="87"/>
-      <c r="H21" s="87"/>
-      <c r="I21" s="87"/>
+      <c r="B21" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
       <c r="J21" s="15"/>
     </row>
     <row r="22" spans="1:14" ht="42" customHeight="1">
       <c r="A22" s="15"/>
-      <c r="B22" s="74" t="str">
-        <v>Surface</v>
-      </c>
-      <c r="C22" s="74" t="str">
-        <v>Axle</v>
-      </c>
-      <c r="D22" s="74" t="str">
-        <v>Position</v>
-      </c>
-      <c r="E22" s="74" t="str">
-        <v>Wheel ΔZ
-(mm)</v>
-      </c>
-      <c r="F22" s="74" t="str">
-        <v>arb1 Start Y
-(m)</v>
-      </c>
-      <c r="G22" s="74" t="str">
-        <v>arb1 Start Z
-(m)</v>
-      </c>
-      <c r="H22" s="74" t="str">
-        <v>arb1 End Y
-(m)</v>
-      </c>
-      <c r="I22" s="74" t="str">
-        <v>arb1 End Z
-(m)</v>
+      <c r="B22" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" s="27" t="s">
+        <v>23</v>
       </c>
       <c r="J22" s="15"/>
     </row>
     <row r="23" spans="1:14" ht="27" customHeight="1">
       <c r="A23" s="15"/>
-      <c r="B23" s="78" t="str">
-        <v>Tarmac</v>
-      </c>
-      <c r="C23" s="78" t="str">
-        <v>Front</v>
-      </c>
-      <c r="D23" s="78" t="str">
-        <v>L</v>
-      </c>
-      <c r="E23" s="92" t="n">
+      <c r="B23" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="32">
         <v>167</v>
       </c>
-      <c r="F23" s="82"/>
-      <c r="G23" s="82"/>
-      <c r="H23" s="82"/>
-      <c r="I23" s="82"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
       <c r="J23" s="15"/>
     </row>
     <row r="24" spans="1:14" ht="27" customHeight="1">
       <c r="A24" s="15"/>
-      <c r="B24" s="86" t="str">
-        <v>Tarmac</v>
-      </c>
-      <c r="C24" s="86" t="str">
-        <v>Front</v>
-      </c>
-      <c r="D24" s="86" t="str">
-        <v>M</v>
-      </c>
-      <c r="E24" s="92" t="n">
+      <c r="B24" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="32">
         <v>167</v>
       </c>
-      <c r="F24" s="82"/>
-      <c r="G24" s="82"/>
-      <c r="H24" s="82"/>
-      <c r="I24" s="82"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
       <c r="J24" s="15"/>
       <c r="M24" s="23"/>
       <c r="N24" s="23"/>
     </row>
     <row r="25" spans="1:14" ht="27" customHeight="1">
       <c r="A25" s="15"/>
-      <c r="B25" s="78" t="str">
-        <v>Tarmac</v>
-      </c>
-      <c r="C25" s="78" t="str">
-        <v>Front</v>
-      </c>
-      <c r="D25" s="78" t="str">
-        <v>H</v>
-      </c>
-      <c r="E25" s="92" t="n">
+      <c r="B25" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25" s="32">
         <v>167</v>
       </c>
-      <c r="F25" s="82"/>
-      <c r="G25" s="82"/>
-      <c r="H25" s="82"/>
-      <c r="I25" s="82"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
       <c r="J25" s="15"/>
     </row>
     <row r="26" spans="1:14" ht="27" customHeight="1">
       <c r="A26" s="15"/>
-      <c r="B26" s="86" t="str">
-        <v>Tarmac</v>
-      </c>
-      <c r="C26" s="86" t="str">
-        <v>Rear</v>
-      </c>
-      <c r="D26" s="86" t="str">
-        <v>L</v>
-      </c>
-      <c r="E26" s="92" t="n">
+      <c r="B26" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" s="32">
         <v>166</v>
       </c>
-      <c r="F26" s="82"/>
-      <c r="G26" s="82"/>
-      <c r="H26" s="82"/>
-      <c r="I26" s="82"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
       <c r="J26" s="15"/>
     </row>
     <row r="27" spans="1:14" ht="27" customHeight="1">
       <c r="A27" s="15"/>
-      <c r="B27" s="78" t="str">
-        <v>Tarmac</v>
-      </c>
-      <c r="C27" s="78" t="str">
-        <v>Rear</v>
-      </c>
-      <c r="D27" s="78" t="str">
-        <v>M</v>
-      </c>
-      <c r="E27" s="92" t="n">
+      <c r="B27" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" s="32">
         <v>166</v>
       </c>
-      <c r="F27" s="82"/>
-      <c r="G27" s="82"/>
-      <c r="H27" s="82"/>
-      <c r="I27" s="82"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
       <c r="J27" s="15"/>
       <c r="M27" s="23"/>
       <c r="N27" s="23"/>
     </row>
     <row r="28" spans="1:14" ht="27" customHeight="1">
       <c r="A28" s="15"/>
-      <c r="B28" s="86" t="str">
-        <v>Tarmac</v>
-      </c>
-      <c r="C28" s="86" t="str">
-        <v>Rear</v>
-      </c>
-      <c r="D28" s="86" t="str">
-        <v>H</v>
-      </c>
-      <c r="E28" s="92" t="n">
+      <c r="B28" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" s="32">
         <v>166</v>
       </c>
-      <c r="F28" s="82"/>
-      <c r="G28" s="82"/>
-      <c r="H28" s="82"/>
-      <c r="I28" s="82"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
       <c r="J28" s="15"/>
     </row>
     <row r="29" spans="1:14" ht="27" customHeight="1">
       <c r="A29" s="15"/>
-      <c r="B29" s="78" t="str">
-        <v>Gravel</v>
-      </c>
-      <c r="C29" s="78" t="str">
-        <v>Front</v>
-      </c>
-      <c r="D29" s="78" t="str">
-        <v>L</v>
-      </c>
-      <c r="E29" s="92" t="n">
+      <c r="B29" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" s="32">
         <v>259</v>
       </c>
-      <c r="F29" s="82"/>
-      <c r="G29" s="82"/>
-      <c r="H29" s="82" t="n">
+      <c r="F29" s="29">
+        <v>-1.0840000000000001</v>
+      </c>
+      <c r="G29" s="29">
+        <v>0.161</v>
+      </c>
+      <c r="H29" s="29">
         <v>-1.034</v>
       </c>
-      <c r="I29" s="82" t="n">
-        <v>0.251</v>
+      <c r="I29" s="29">
+        <v>0.252</v>
       </c>
       <c r="J29" s="15"/>
       <c r="M29" s="23"/>
@@ -3503,97 +3281,113 @@
     </row>
     <row r="30" spans="1:14" ht="27" customHeight="1">
       <c r="A30" s="15"/>
-      <c r="B30" s="86" t="str">
-        <v>Gravel</v>
-      </c>
-      <c r="C30" s="86" t="str">
-        <v>Front</v>
-      </c>
-      <c r="D30" s="86" t="str">
-        <v>M</v>
-      </c>
-      <c r="E30" s="92" t="n">
+      <c r="B30" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="E30" s="32">
         <v>259</v>
       </c>
-      <c r="F30" s="82"/>
-      <c r="G30" s="82"/>
-      <c r="H30" s="82" t="n">
-        <v>-1.023</v>
-      </c>
-      <c r="I30" s="82" t="n">
-        <v>0.241</v>
+      <c r="F30" s="29">
+        <v>-1.069</v>
+      </c>
+      <c r="G30" s="29">
+        <v>0.156</v>
+      </c>
+      <c r="H30" s="29">
+        <v>-1.0229999999999999</v>
+      </c>
+      <c r="I30" s="29">
+        <v>0.24099999999999999</v>
       </c>
       <c r="J30" s="15"/>
     </row>
     <row r="31" spans="1:14" ht="27" customHeight="1">
       <c r="A31" s="15"/>
-      <c r="B31" s="78" t="str">
-        <v>Gravel</v>
-      </c>
-      <c r="C31" s="78" t="str">
-        <v>Front</v>
-      </c>
-      <c r="D31" s="78" t="str">
-        <v>H</v>
-      </c>
-      <c r="E31" s="92" t="n">
+      <c r="B31" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="E31" s="32">
         <v>259</v>
       </c>
-      <c r="F31" s="82"/>
-      <c r="G31" s="82"/>
-      <c r="H31" s="82" t="n">
-        <v>-1.012</v>
-      </c>
-      <c r="I31" s="82" t="n">
-        <v>0.231</v>
+      <c r="F31" s="29">
+        <v>-1.0549999999999999</v>
+      </c>
+      <c r="G31" s="29">
+        <v>0.14899999999999999</v>
+      </c>
+      <c r="H31" s="29">
+        <v>-1.0129999999999999</v>
+      </c>
+      <c r="I31" s="29">
+        <v>0.23</v>
       </c>
       <c r="J31" s="15"/>
     </row>
     <row r="32" spans="1:14" ht="27" customHeight="1">
       <c r="A32" s="15"/>
-      <c r="B32" s="86" t="str">
-        <v>Gravel</v>
-      </c>
-      <c r="C32" s="86" t="str">
-        <v>Rear</v>
-      </c>
-      <c r="D32" s="86" t="str">
-        <v>L</v>
-      </c>
-      <c r="E32" s="92" t="n">
+      <c r="B32" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" s="32">
         <v>252</v>
       </c>
-      <c r="F32" s="82"/>
-      <c r="G32" s="82"/>
-      <c r="H32" s="82" t="n">
-        <v>1.309</v>
-      </c>
-      <c r="I32" s="82" t="n">
-        <v>0.319</v>
+      <c r="F32" s="29">
+        <v>1.306</v>
+      </c>
+      <c r="G32" s="29">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="H32" s="29">
+        <v>1.3089999999999999</v>
+      </c>
+      <c r="I32" s="29">
+        <v>0.31900000000000001</v>
       </c>
       <c r="J32" s="15"/>
     </row>
     <row r="33" spans="1:14" ht="27" customHeight="1">
       <c r="A33" s="15"/>
-      <c r="B33" s="78" t="str">
-        <v>Gravel</v>
-      </c>
-      <c r="C33" s="78" t="str">
-        <v>Rear</v>
-      </c>
-      <c r="D33" s="78" t="str">
-        <v>M</v>
-      </c>
-      <c r="E33" s="92" t="n">
+      <c r="B33" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="E33" s="32">
         <v>252</v>
       </c>
-      <c r="F33" s="82"/>
-      <c r="G33" s="82"/>
-      <c r="H33" s="82" t="n">
-        <v>1.326</v>
-      </c>
-      <c r="I33" s="82" t="n">
-        <v>0.319</v>
+      <c r="F33" s="29">
+        <v>1.3220000000000001</v>
+      </c>
+      <c r="G33" s="29">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="H33" s="29">
+        <v>1.3260000000000001</v>
+      </c>
+      <c r="I33" s="29">
+        <v>0.31900000000000001</v>
       </c>
       <c r="J33" s="15"/>
       <c r="M33" s="23"/>
@@ -3601,24 +3395,28 @@
     </row>
     <row r="34" spans="1:14" ht="27" customHeight="1">
       <c r="A34" s="15"/>
-      <c r="B34" s="86" t="str">
-        <v>Gravel</v>
-      </c>
-      <c r="C34" s="86" t="str">
-        <v>Rear</v>
-      </c>
-      <c r="D34" s="86" t="str">
-        <v>H</v>
-      </c>
-      <c r="E34" s="92" t="n">
+      <c r="B34" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="E34" s="32">
         <v>252</v>
       </c>
-      <c r="F34" s="82"/>
-      <c r="G34" s="82"/>
-      <c r="H34" s="82" t="n">
-        <v>1.342</v>
-      </c>
-      <c r="I34" s="82" t="n">
+      <c r="F34" s="29">
+        <v>1.339</v>
+      </c>
+      <c r="G34" s="29">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="H34" s="29">
+        <v>1.3420000000000001</v>
+      </c>
+      <c r="I34" s="29">
         <v>0.318</v>
       </c>
       <c r="J34" s="15"/>
@@ -3663,48 +3461,48 @@
     </row>
     <row r="38" spans="1:14" ht="27" customHeight="1">
       <c r="A38" s="15"/>
-      <c r="B38" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="C38" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="D38" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="E38" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="F38" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="G38" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="H38" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I38" s="31" t="s">
-        <v>34</v>
+      <c r="B38" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="J38" s="15"/>
     </row>
     <row r="39" spans="1:14" ht="42" customHeight="1">
       <c r="A39" s="15"/>
       <c r="B39" s="16" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C39" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G39" s="15"/>
       <c r="H39" s="15"/>
@@ -3714,20 +3512,18 @@
     <row r="40" spans="1:14" ht="27" customHeight="1">
       <c r="A40" s="15"/>
       <c r="B40" s="18" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C40" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D40" s="18" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E40" s="27">
+      <c r="D40" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E40" s="25">
         <v>35</v>
       </c>
-      <c r="F40" s="27">
+      <c r="F40" s="25">
         <v>163</v>
       </c>
       <c r="G40" s="15"/>
@@ -3738,20 +3534,18 @@
     <row r="41" spans="1:14" ht="27" customHeight="1">
       <c r="A41" s="15"/>
       <c r="B41" s="17" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C41" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D41" s="17" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E41" s="26">
+      <c r="D41" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E41" s="24">
         <v>42</v>
       </c>
-      <c r="F41" s="26">
+      <c r="F41" s="24">
         <v>163</v>
       </c>
       <c r="G41" s="15"/>
@@ -3762,20 +3556,18 @@
     <row r="42" spans="1:14" ht="27" customHeight="1">
       <c r="A42" s="15"/>
       <c r="B42" s="18" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C42" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D42" s="18" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="E42" s="27">
+      <c r="D42" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E42" s="25">
         <v>46</v>
       </c>
-      <c r="F42" s="27">
+      <c r="F42" s="25">
         <v>163</v>
       </c>
       <c r="G42" s="15"/>
@@ -3786,20 +3578,18 @@
     <row r="43" spans="1:14" ht="27" customHeight="1">
       <c r="A43" s="15"/>
       <c r="B43" s="17" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D43" s="17" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E43" s="26">
+        <v>10</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E43" s="24">
         <v>41</v>
       </c>
-      <c r="F43" s="26">
+      <c r="F43" s="24">
         <v>154</v>
       </c>
       <c r="G43" s="15"/>
@@ -3810,20 +3600,18 @@
     <row r="44" spans="1:14" ht="27" customHeight="1">
       <c r="A44" s="15"/>
       <c r="B44" s="18" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" s="18" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E44" s="27">
+        <v>10</v>
+      </c>
+      <c r="D44" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="E44" s="25">
         <v>49</v>
       </c>
-      <c r="F44" s="27">
+      <c r="F44" s="25">
         <v>154</v>
       </c>
       <c r="G44" s="15"/>
@@ -3834,20 +3622,18 @@
     <row r="45" spans="1:14" ht="27" customHeight="1">
       <c r="A45" s="15"/>
       <c r="B45" s="17" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D45" s="17" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="E45" s="26">
+        <v>10</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E45" s="24">
         <v>54</v>
       </c>
-      <c r="F45" s="26">
+      <c r="F45" s="24">
         <v>154</v>
       </c>
       <c r="G45" s="15"/>
@@ -3858,20 +3644,18 @@
     <row r="46" spans="1:14" ht="27" customHeight="1">
       <c r="A46" s="15"/>
       <c r="B46" s="18" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C46" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D46" s="18" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E46" s="27">
+      <c r="D46" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E46" s="25">
         <v>32</v>
       </c>
-      <c r="F46" s="27">
+      <c r="F46" s="25">
         <v>163</v>
       </c>
       <c r="G46" s="15"/>
@@ -3882,20 +3666,18 @@
     <row r="47" spans="1:14" ht="27" customHeight="1">
       <c r="A47" s="15"/>
       <c r="B47" s="17" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D47" s="17" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E47" s="26">
+      <c r="D47" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E47" s="24">
         <v>40</v>
       </c>
-      <c r="F47" s="26">
+      <c r="F47" s="24">
         <v>163</v>
       </c>
       <c r="G47" s="15"/>
@@ -3906,20 +3688,18 @@
     <row r="48" spans="1:14" ht="27" customHeight="1">
       <c r="A48" s="15"/>
       <c r="B48" s="18" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C48" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D48" s="18" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="E48" s="27">
+      <c r="D48" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E48" s="25">
         <v>45</v>
       </c>
-      <c r="F48" s="27">
+      <c r="F48" s="25">
         <v>163</v>
       </c>
       <c r="G48" s="15"/>
@@ -3930,20 +3710,18 @@
     <row r="49" spans="1:10" ht="27" customHeight="1">
       <c r="A49" s="15"/>
       <c r="B49" s="17" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D49" s="17" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E49" s="26">
+        <v>10</v>
+      </c>
+      <c r="D49" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E49" s="24">
         <v>39</v>
       </c>
-      <c r="F49" s="26">
+      <c r="F49" s="24">
         <v>154</v>
       </c>
       <c r="G49" s="15"/>
@@ -3954,20 +3732,18 @@
     <row r="50" spans="1:10" ht="27" customHeight="1">
       <c r="A50" s="15"/>
       <c r="B50" s="18" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="18" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E50" s="27">
+        <v>10</v>
+      </c>
+      <c r="D50" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="E50" s="25">
         <v>47</v>
       </c>
-      <c r="F50" s="27">
+      <c r="F50" s="25">
         <v>154</v>
       </c>
       <c r="G50" s="15"/>
@@ -3978,20 +3754,18 @@
     <row r="51" spans="1:10" ht="27" customHeight="1">
       <c r="A51" s="15"/>
       <c r="B51" s="17" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D51" s="17" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="E51" s="26">
+        <v>10</v>
+      </c>
+      <c r="D51" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E51" s="24">
         <v>51</v>
       </c>
-      <c r="F51" s="26">
+      <c r="F51" s="24">
         <v>154</v>
       </c>
       <c r="G51" s="15"/>
@@ -4230,7 +4004,7 @@
     <mergeCell ref="B20:I20"/>
     <mergeCell ref="B21:I21"/>
   </mergeCells>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4240,7 +4014,7 @@
   <sheetPr>
     <tabColor rgb="FF31475E"/>
   </sheetPr>
-  <dimension ref="A1:O90"/>
+  <dimension ref="A1:O157"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.75" customWidth="1"/>
@@ -4252,18 +4026,13 @@
     <col min="7" max="7" width="15.625" customWidth="1"/>
     <col min="8" max="10" width="12.5" customWidth="1"/>
     <col min="11" max="11" width="18.125" customWidth="1"/>
-    <col min="12" max="13" width="2.75" customWidth="1"/>
-    <col min="12" max="12" width="16" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="16" hidden="0" customWidth="1"/>
-    <col min="14" max="15" width="13" customWidth="1"/>
-    <col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="16" hidden="0" customWidth="1"/>
+    <col min="12" max="15" width="16" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
     <col min="17" max="17" width="12" customWidth="1"/>
     <col min="18" max="22" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="26.1" customHeight="1">
+    <row r="1" spans="1:15" ht="26.1" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4278,77 +4047,77 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:13" ht="26.1" customHeight="1">
+    <row r="2" spans="1:15" ht="26.1" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>37</v>
+      <c r="B2" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="41" t="s">
+        <v>30</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:13" ht="26.1" customHeight="1">
+    <row r="3" spans="1:15" ht="26.1" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>37</v>
+      <c r="B3" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="41" t="s">
+        <v>30</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" ht="26.1" customHeight="1">
+    <row r="4" spans="1:15" ht="26.1" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -4363,87 +4132,72 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="1:13" ht="39.950000000000003" customHeight="1">
+    <row r="5" spans="1:15" ht="39.950000000000003" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>#1
-(N/mm)</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>#2
-(N/mm)</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>#3
-(N/mm)</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L5" s="91" t="str">
-        <v>Start angle
-(°)</v>
-      </c>
-      <c r="M5" s="91" t="str">
-        <v>End angle
-(°)</v>
-      </c>
-      <c r="N5" s="74" t="str">
-        <v>Start radius
-(mm)</v>
-      </c>
-      <c r="O5" s="74" t="str">
-        <v>End radius
-(mm)</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="26.1" customHeight="1">
+      <c r="N5" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="O5" s="27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="26.1" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="D6" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="E6" s="7">
         <f>IF(ISNUMBER(Parameters!E23),Parameters!E23,"")</f>
         <v>167</v>
       </c>
       <c r="F6" s="9" t="str">
-        <f>IF(COUNT(L6:M6)&lt;2,"",MOD(M6-L6+180,360)-180)</f>
+        <f t="shared" ref="F6:F17" si="0">IF(COUNT(L6:M6)&lt;2,"",MOD(M6-L6+180,360)-180)</f>
         <v/>
       </c>
       <c r="G6" s="11" t="str">
-        <f>IF(COUNT(E6:F6)&lt;2,"",IF(E6&lt;=0,"",RADIANS(F6)/E6))</f>
+        <f t="shared" ref="G6:G17" si="1">IF(COUNT(E6:F6)&lt;2,"",IF(E6&lt;=0,"",RADIANS(F6)/E6))</f>
         <v/>
       </c>
       <c r="H6" s="5" t="str">
@@ -4462,46 +4216,44 @@
         <f>IF(COUNT(Parameters!C17:D17,Parameters!F23:I23)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E6)),"待填轮行程",IF(E6&lt;=0,"轮行程须大于0",IF(COUNT(L6:M6)&lt;2,"无效半径",""))))</f>
         <v>待补坐标</v>
       </c>
-      <c r="L6" s="103" t="str">
+      <c r="L6" s="33" t="str">
         <f>IF(COUNT(Parameters!F23,Parameters!G23,Parameters!C17,Parameters!D17)&lt;4,"",IF(N6=0,"",IF(Parameters!G23&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!F23)*1000/N6))))))</f>
         <v/>
       </c>
-      <c r="M6" s="103" t="str">
+      <c r="M6" s="33" t="str">
         <f>IF(COUNT(Parameters!H23,Parameters!I23,Parameters!C17,Parameters!D17)&lt;4,"",IF(O6=0,"",IF(Parameters!I23&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!H23)*1000/O6))))))</f>
         <v/>
       </c>
-      <c r="N6" s="105" t="str">
+      <c r="N6" s="35" t="str">
         <f>IF(COUNT(Parameters!F23,Parameters!G23,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!F23-Parameters!C17)^2+(Parameters!G23-Parameters!D17)^2))</f>
         <v/>
       </c>
-      <c r="O6" s="105" t="str">
+      <c r="O6" s="35" t="str">
         <f>IF(COUNT(Parameters!H23,Parameters!I23,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!H23-Parameters!C17)^2+(Parameters!I23-Parameters!D17)^2))</f>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="26.1" customHeight="1">
+    <row r="7" spans="1:15" ht="26.1" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
+      <c r="D7" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="E7" s="8">
         <f>IF(ISNUMBER(Parameters!E24),Parameters!E24,"")</f>
         <v>167</v>
       </c>
       <c r="F7" s="10" t="str">
-        <f>IF(COUNT(L7:M7)&lt;2,"",MOD(M7-L7+180,360)-180)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="G7" s="12" t="str">
-        <f>IF(COUNT(E7:F7)&lt;2,"",IF(E7&lt;=0,"",RADIANS(F7)/E7))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="H7" s="6" t="str">
@@ -4520,46 +4272,44 @@
         <f>IF(COUNT(Parameters!C17:D17,Parameters!F24:I24)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E7)),"待填轮行程",IF(E7&lt;=0,"轮行程须大于0",IF(COUNT(L7:M7)&lt;2,"无效半径",""))))</f>
         <v>待补坐标</v>
       </c>
-      <c r="L7" s="104" t="str">
+      <c r="L7" s="34" t="str">
         <f>IF(COUNT(Parameters!F24,Parameters!G24,Parameters!C17,Parameters!D17)&lt;4,"",IF(N7=0,"",IF(Parameters!G24&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!F24)*1000/N7))))))</f>
         <v/>
       </c>
-      <c r="M7" s="104" t="str">
+      <c r="M7" s="34" t="str">
         <f>IF(COUNT(Parameters!H24,Parameters!I24,Parameters!C17,Parameters!D17)&lt;4,"",IF(O7=0,"",IF(Parameters!I24&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!H24)*1000/O7))))))</f>
         <v/>
       </c>
-      <c r="N7" s="106" t="str">
+      <c r="N7" s="36" t="str">
         <f>IF(COUNT(Parameters!F24,Parameters!G24,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!F24-Parameters!C17)^2+(Parameters!G24-Parameters!D17)^2))</f>
         <v/>
       </c>
-      <c r="O7" s="106" t="str">
+      <c r="O7" s="36" t="str">
         <f>IF(COUNT(Parameters!H24,Parameters!I24,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!H24-Parameters!C17)^2+(Parameters!I24-Parameters!D17)^2))</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="26.1" customHeight="1">
+    <row r="8" spans="1:15" ht="26.1" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+      <c r="D8" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="E8" s="7">
         <f>IF(ISNUMBER(Parameters!E25),Parameters!E25,"")</f>
         <v>167</v>
       </c>
       <c r="F8" s="9" t="str">
-        <f>IF(COUNT(L8:M8)&lt;2,"",MOD(M8-L8+180,360)-180)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="G8" s="11" t="str">
-        <f>IF(COUNT(E8:F8)&lt;2,"",IF(E8&lt;=0,"",RADIANS(F8)/E8))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="H8" s="5" t="str">
@@ -4578,46 +4328,44 @@
         <f>IF(COUNT(Parameters!C17:D17,Parameters!F25:I25)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E8)),"待填轮行程",IF(E8&lt;=0,"轮行程须大于0",IF(COUNT(L8:M8)&lt;2,"无效半径",""))))</f>
         <v>待补坐标</v>
       </c>
-      <c r="L8" s="103" t="str">
+      <c r="L8" s="33" t="str">
         <f>IF(COUNT(Parameters!F25,Parameters!G25,Parameters!C17,Parameters!D17)&lt;4,"",IF(N8=0,"",IF(Parameters!G25&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!F25)*1000/N8))))))</f>
         <v/>
       </c>
-      <c r="M8" s="103" t="str">
+      <c r="M8" s="33" t="str">
         <f>IF(COUNT(Parameters!H25,Parameters!I25,Parameters!C17,Parameters!D17)&lt;4,"",IF(O8=0,"",IF(Parameters!I25&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!H25)*1000/O8))))))</f>
         <v/>
       </c>
-      <c r="N8" s="105" t="str">
+      <c r="N8" s="35" t="str">
         <f>IF(COUNT(Parameters!F25,Parameters!G25,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!F25-Parameters!C17)^2+(Parameters!G25-Parameters!D17)^2))</f>
         <v/>
       </c>
-      <c r="O8" s="105" t="str">
+      <c r="O8" s="35" t="str">
         <f>IF(COUNT(Parameters!H25,Parameters!I25,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!H25-Parameters!C17)^2+(Parameters!I25-Parameters!D17)^2))</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="26.1" customHeight="1">
+    <row r="9" spans="1:15" ht="26.1" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="E9" s="8">
         <f>IF(ISNUMBER(Parameters!E26),Parameters!E26,"")</f>
         <v>166</v>
       </c>
       <c r="F9" s="10" t="str">
-        <f>IF(COUNT(L9:M9)&lt;2,"",MOD(M9-L9+180,360)-180)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="G9" s="12" t="str">
-        <f>IF(COUNT(E9:F9)&lt;2,"",IF(E9&lt;=0,"",RADIANS(F9)/E9))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="H9" s="6" t="str">
@@ -4636,46 +4384,44 @@
         <f>IF(COUNT(Parameters!C18:D18,Parameters!F26:I26)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E9)),"待填轮行程",IF(E9&lt;=0,"轮行程须大于0",IF(COUNT(L9:M9)&lt;2,"无效半径",""))))</f>
         <v>待补坐标</v>
       </c>
-      <c r="L9" s="104" t="str">
+      <c r="L9" s="34" t="str">
         <f>IF(COUNT(Parameters!F26,Parameters!G26,Parameters!C18,Parameters!D18)&lt;4,"",IF(N9=0,"",IF(Parameters!G26&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!F26)*1000/N9))))))</f>
         <v/>
       </c>
-      <c r="M9" s="104" t="str">
+      <c r="M9" s="34" t="str">
         <f>IF(COUNT(Parameters!H26,Parameters!I26,Parameters!C18,Parameters!D18)&lt;4,"",IF(O9=0,"",IF(Parameters!I26&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!H26)*1000/O9))))))</f>
         <v/>
       </c>
-      <c r="N9" s="106" t="str">
+      <c r="N9" s="36" t="str">
         <f>IF(COUNT(Parameters!F26,Parameters!G26,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!F26-Parameters!C18)^2+(Parameters!G26-Parameters!D18)^2))</f>
         <v/>
       </c>
-      <c r="O9" s="106" t="str">
+      <c r="O9" s="36" t="str">
         <f>IF(COUNT(Parameters!H26,Parameters!I26,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!H26-Parameters!C18)^2+(Parameters!I26-Parameters!D18)^2))</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="26.1" customHeight="1">
+    <row r="10" spans="1:15" ht="26.1" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="E10" s="7">
         <f>IF(ISNUMBER(Parameters!E27),Parameters!E27,"")</f>
         <v>166</v>
       </c>
       <c r="F10" s="9" t="str">
-        <f>IF(COUNT(L10:M10)&lt;2,"",MOD(M10-L10+180,360)-180)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="G10" s="11" t="str">
-        <f>IF(COUNT(E10:F10)&lt;2,"",IF(E10&lt;=0,"",RADIANS(F10)/E10))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="H10" s="5" t="str">
@@ -4694,46 +4440,44 @@
         <f>IF(COUNT(Parameters!C18:D18,Parameters!F27:I27)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E10)),"待填轮行程",IF(E10&lt;=0,"轮行程须大于0",IF(COUNT(L10:M10)&lt;2,"无效半径",""))))</f>
         <v>待补坐标</v>
       </c>
-      <c r="L10" s="103" t="str">
+      <c r="L10" s="33" t="str">
         <f>IF(COUNT(Parameters!F27,Parameters!G27,Parameters!C18,Parameters!D18)&lt;4,"",IF(N10=0,"",IF(Parameters!G27&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!F27)*1000/N10))))))</f>
         <v/>
       </c>
-      <c r="M10" s="103" t="str">
+      <c r="M10" s="33" t="str">
         <f>IF(COUNT(Parameters!H27,Parameters!I27,Parameters!C18,Parameters!D18)&lt;4,"",IF(O10=0,"",IF(Parameters!I27&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!H27)*1000/O10))))))</f>
         <v/>
       </c>
-      <c r="N10" s="105" t="str">
+      <c r="N10" s="35" t="str">
         <f>IF(COUNT(Parameters!F27,Parameters!G27,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!F27-Parameters!C18)^2+(Parameters!G27-Parameters!D18)^2))</f>
         <v/>
       </c>
-      <c r="O10" s="105" t="str">
+      <c r="O10" s="35" t="str">
         <f>IF(COUNT(Parameters!H27,Parameters!I27,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!H27-Parameters!C18)^2+(Parameters!I27-Parameters!D18)^2))</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="26.1" customHeight="1">
+    <row r="11" spans="1:15" ht="26.1" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="E11" s="8">
         <f>IF(ISNUMBER(Parameters!E28),Parameters!E28,"")</f>
         <v>166</v>
       </c>
       <c r="F11" s="10" t="str">
-        <f>IF(COUNT(L11:M11)&lt;2,"",MOD(M11-L11+180,360)-180)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="G11" s="12" t="str">
-        <f>IF(COUNT(E11:F11)&lt;2,"",IF(E11&lt;=0,"",RADIANS(F11)/E11))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="H11" s="6" t="str">
@@ -4752,372 +4496,360 @@
         <f>IF(COUNT(Parameters!C18:D18,Parameters!F28:I28)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E11)),"待填轮行程",IF(E11&lt;=0,"轮行程须大于0",IF(COUNT(L11:M11)&lt;2,"无效半径",""))))</f>
         <v>待补坐标</v>
       </c>
-      <c r="L11" s="104" t="str">
+      <c r="L11" s="34" t="str">
         <f>IF(COUNT(Parameters!F28,Parameters!G28,Parameters!C18,Parameters!D18)&lt;4,"",IF(N11=0,"",IF(Parameters!G28&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!F28)*1000/N11))))))</f>
         <v/>
       </c>
-      <c r="M11" s="104" t="str">
+      <c r="M11" s="34" t="str">
         <f>IF(COUNT(Parameters!H28,Parameters!I28,Parameters!C18,Parameters!D18)&lt;4,"",IF(O11=0,"",IF(Parameters!I28&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!H28)*1000/O11))))))</f>
         <v/>
       </c>
-      <c r="N11" s="106" t="str">
+      <c r="N11" s="36" t="str">
         <f>IF(COUNT(Parameters!F28,Parameters!G28,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!F28-Parameters!C18)^2+(Parameters!G28-Parameters!D18)^2))</f>
         <v/>
       </c>
-      <c r="O11" s="106" t="str">
+      <c r="O11" s="36" t="str">
         <f>IF(COUNT(Parameters!H28,Parameters!I28,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!H28-Parameters!C18)^2+(Parameters!I28-Parameters!D18)^2))</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="26.1" customHeight="1">
+    <row r="12" spans="1:15" ht="26.1" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="D12" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="E12" s="7">
         <f>IF(ISNUMBER(Parameters!E29),Parameters!E29,"")</f>
         <v>259</v>
       </c>
-      <c r="F12" s="9" t="str">
-        <f>IF(COUNT(L12:M12)&lt;2,"",MOD(M12-L12+180,360)-180)</f>
-        <v/>
-      </c>
-      <c r="G12" s="11" t="str">
-        <f>IF(COUNT(E12:F12)&lt;2,"",IF(E12&lt;=0,"",RADIANS(F12)/E12))</f>
-        <v/>
-      </c>
-      <c r="H12" s="5" t="str">
+      <c r="F12" s="9">
+        <f t="shared" si="0"/>
+        <v>35.033513377592925</v>
+      </c>
+      <c r="G12" s="11">
+        <f t="shared" si="1"/>
+        <v>2.3608114169130349E-3</v>
+      </c>
+      <c r="H12" s="5">
         <f>IF(ISNUMBER(G12),1000*Parameters!E7*G12^2,"")</f>
-        <v/>
-      </c>
-      <c r="I12" s="5" t="str">
+        <v>5.2468630107600935</v>
+      </c>
+      <c r="I12" s="5">
         <f>IF(ISNUMBER(G12),1000*Parameters!E8*G12^2,"")</f>
-        <v/>
-      </c>
-      <c r="J12" s="5" t="str">
+        <v>11.07997992589914</v>
+      </c>
+      <c r="J12" s="5">
         <f>IF(ISNUMBER(G12),1000*Parameters!E9*G12^2,"")</f>
-        <v/>
+        <v>20.394062528804113</v>
       </c>
       <c r="K12" s="13" t="str">
         <f>IF(COUNT(Parameters!C17:D17,Parameters!F29:I29)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E12)),"待填轮行程",IF(E12&lt;=0,"轮行程须大于0",IF(COUNT(L12:M12)&lt;2,"无效半径",""))))</f>
-        <v>待补坐标</v>
-      </c>
-      <c r="L12" s="103" t="str">
+        <v/>
+      </c>
+      <c r="L12" s="33">
         <f>IF(COUNT(Parameters!F29,Parameters!G29,Parameters!C17,Parameters!D17)&lt;4,"",IF(N12=0,"",IF(Parameters!G29&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!F29)*1000/N12))))))</f>
-        <v/>
-      </c>
-      <c r="M12" s="103">
+        <v>11.375115357745536</v>
+      </c>
+      <c r="M12" s="33">
         <f>IF(COUNT(Parameters!H29,Parameters!I29,Parameters!C17,Parameters!D17)&lt;4,"",IF(O12=0,"",IF(Parameters!I29&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!H29)*1000/O12))))))</f>
-        <v>46.178759169911224</v>
-      </c>
-      <c r="N12" s="105" t="str">
+        <v>46.408628735338468</v>
+      </c>
+      <c r="N12" s="35">
         <f>IF(COUNT(Parameters!F29,Parameters!G29,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!F29-Parameters!C17)^2+(Parameters!G29-Parameters!D17)^2))</f>
-        <v/>
-      </c>
-      <c r="O12" s="105">
+        <v>172.38619434281858</v>
+      </c>
+      <c r="O12" s="35">
         <f>IF(COUNT(Parameters!H29,Parameters!I29,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!H29-Parameters!C17)^2+(Parameters!I29-Parameters!D17)^2))</f>
-        <v>171.86331778480246</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="26.1" customHeight="1">
+        <v>172.58621034138272</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="26.1" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
+      <c r="D13" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="E13" s="8">
         <f>IF(ISNUMBER(Parameters!E30),Parameters!E30,"")</f>
         <v>259</v>
       </c>
-      <c r="F13" s="10" t="str">
-        <f>IF(COUNT(L13:M13)&lt;2,"",MOD(M13-L13+180,360)-180)</f>
-        <v/>
-      </c>
-      <c r="G13" s="12" t="str">
-        <f>IF(COUNT(E13:F13)&lt;2,"",IF(E13&lt;=0,"",RADIANS(F13)/E13))</f>
-        <v/>
-      </c>
-      <c r="H13" s="6" t="str">
+      <c r="F13" s="10">
+        <f t="shared" si="0"/>
+        <v>35.883582181526236</v>
+      </c>
+      <c r="G13" s="12">
+        <f t="shared" si="1"/>
+        <v>2.4180951987552218E-3</v>
+      </c>
+      <c r="H13" s="6">
         <f>IF(ISNUMBER(G13),1000*Parameters!E7*G13^2,"")</f>
-        <v/>
-      </c>
-      <c r="I13" s="6" t="str">
+        <v>5.504576622925577</v>
+      </c>
+      <c r="I13" s="6">
         <f>IF(ISNUMBER(G13),1000*Parameters!E8*G13^2,"")</f>
-        <v/>
-      </c>
-      <c r="J13" s="6" t="str">
+        <v>11.624202567803193</v>
+      </c>
+      <c r="J13" s="6">
         <f>IF(ISNUMBER(G13),1000*Parameters!E9*G13^2,"")</f>
-        <v/>
+        <v>21.395771075463013</v>
       </c>
       <c r="K13" s="14" t="str">
         <f>IF(COUNT(Parameters!C17:D17,Parameters!F30:I30)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E13)),"待填轮行程",IF(E13&lt;=0,"轮行程须大于0",IF(COUNT(L13:M13)&lt;2,"无效半径",""))))</f>
-        <v>待补坐标</v>
-      </c>
-      <c r="L13" s="104" t="str">
+        <v/>
+      </c>
+      <c r="L13" s="34">
         <f>IF(COUNT(Parameters!F30,Parameters!G30,Parameters!C17,Parameters!D17)&lt;4,"",IF(N13=0,"",IF(Parameters!G30&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!F30)*1000/N13))))))</f>
-        <v/>
-      </c>
-      <c r="M13" s="104">
+        <v>10.664575517451754</v>
+      </c>
+      <c r="M13" s="34">
         <f>IF(COUNT(Parameters!H30,Parameters!I30,Parameters!C17,Parameters!D17)&lt;4,"",IF(O13=0,"",IF(Parameters!I30&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!H30)*1000/O13))))))</f>
-        <v>46.548157698977995</v>
-      </c>
-      <c r="N13" s="106" t="str">
+        <v>46.548157698977988</v>
+      </c>
+      <c r="N13" s="36">
         <f>IF(COUNT(Parameters!F30,Parameters!G30,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!F30-Parameters!C17)^2+(Parameters!G30-Parameters!D17)^2))</f>
-        <v/>
-      </c>
-      <c r="O13" s="106">
+        <v>156.7067324654559</v>
+      </c>
+      <c r="O13" s="36">
         <f>IF(COUNT(Parameters!H30,Parameters!I30,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!H30-Parameters!C17)^2+(Parameters!I30-Parameters!D17)^2))</f>
-        <v>157.0350279396287</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="26.1" customHeight="1">
+        <v>157.03502793962869</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="26.1" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+      <c r="D14" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="E14" s="7">
         <f>IF(ISNUMBER(Parameters!E31),Parameters!E31,"")</f>
         <v>259</v>
       </c>
-      <c r="F14" s="9" t="str">
-        <f>IF(COUNT(L14:M14)&lt;2,"",MOD(M14-L14+180,360)-180)</f>
-        <v/>
-      </c>
-      <c r="G14" s="11" t="str">
-        <f>IF(COUNT(E14:F14)&lt;2,"",IF(E14&lt;=0,"",RADIANS(F14)/E14))</f>
-        <v/>
-      </c>
-      <c r="H14" s="5" t="str">
+      <c r="F14" s="9">
+        <f t="shared" si="0"/>
+        <v>37.494384172096488</v>
+      </c>
+      <c r="G14" s="11">
+        <f t="shared" si="1"/>
+        <v>2.5266426826669186E-3</v>
+      </c>
+      <c r="H14" s="5">
         <f>IF(ISNUMBER(G14),1000*Parameters!E7*G14^2,"")</f>
-        <v/>
-      </c>
-      <c r="I14" s="5" t="str">
+        <v>6.0098659998526269</v>
+      </c>
+      <c r="I14" s="5">
         <f>IF(ISNUMBER(G14),1000*Parameters!E8*G14^2,"")</f>
-        <v/>
-      </c>
-      <c r="J14" s="5" t="str">
+        <v>12.691239412798074</v>
+      </c>
+      <c r="J14" s="5">
         <f>IF(ISNUMBER(G14),1000*Parameters!E9*G14^2,"")</f>
-        <v/>
+        <v>23.359783310403735</v>
       </c>
       <c r="K14" s="13" t="str">
         <f>IF(COUNT(Parameters!C17:D17,Parameters!F31:I31)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E14)),"待填轮行程",IF(E14&lt;=0,"轮行程须大于0",IF(COUNT(L14:M14)&lt;2,"无效半径",""))))</f>
-        <v>待补坐标</v>
-      </c>
-      <c r="L14" s="103" t="str">
+        <v/>
+      </c>
+      <c r="L14" s="33">
         <f>IF(COUNT(Parameters!F31,Parameters!G31,Parameters!C17,Parameters!D17)&lt;4,"",IF(N14=0,"",IF(Parameters!G31&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!F31)*1000/N14))))))</f>
-        <v/>
-      </c>
-      <c r="M14" s="103">
+        <v>8.9305901004189874</v>
+      </c>
+      <c r="M14" s="33">
         <f>IF(COUNT(Parameters!H31,Parameters!I31,Parameters!C17,Parameters!D17)&lt;4,"",IF(O14=0,"",IF(Parameters!I31&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!H31)*1000/O14))))))</f>
-        <v>46.994569301241846</v>
-      </c>
-      <c r="N14" s="105" t="str">
+        <v>46.42497427251547</v>
+      </c>
+      <c r="N14" s="35">
         <f>IF(COUNT(Parameters!F31,Parameters!G31,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!F31-Parameters!C17)^2+(Parameters!G31-Parameters!D17)^2))</f>
-        <v/>
-      </c>
-      <c r="O14" s="105">
+        <v>141.71802990445491</v>
+      </c>
+      <c r="O14" s="35">
         <f>IF(COUNT(Parameters!H31,Parameters!I31,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!H31-Parameters!C17)^2+(Parameters!I31-Parameters!D17)^2))</f>
-        <v>142.2146265332789</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="26.1" customHeight="1">
+        <v>142.17243052012572</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="26.1" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="E15" s="8">
         <f>IF(ISNUMBER(Parameters!E32),Parameters!E32,"")</f>
         <v>252</v>
       </c>
-      <c r="F15" s="10" t="str">
-        <f>IF(COUNT(L15:M15)&lt;2,"",MOD(M15-L15+180,360)-180)</f>
-        <v/>
-      </c>
-      <c r="G15" s="12" t="str">
-        <f>IF(COUNT(E15:F15)&lt;2,"",IF(E15&lt;=0,"",RADIANS(F15)/E15))</f>
-        <v/>
-      </c>
-      <c r="H15" s="6" t="str">
+      <c r="F15" s="10">
+        <f t="shared" si="0"/>
+        <v>40.242687721746677</v>
+      </c>
+      <c r="G15" s="12">
+        <f t="shared" si="1"/>
+        <v>2.7871722245887904E-3</v>
+      </c>
+      <c r="H15" s="6">
         <f>IF(ISNUMBER(G15),1000*Parameters!E10*G15^2,"")</f>
-        <v/>
-      </c>
-      <c r="I15" s="6" t="str">
+        <v>11.08545128513005</v>
+      </c>
+      <c r="I15" s="6">
         <f>IF(ISNUMBER(G15),1000*Parameters!E11*G15^2,"")</f>
-        <v/>
-      </c>
-      <c r="J15" s="6" t="str">
+        <v>22.798183207336258</v>
+      </c>
+      <c r="J15" s="6">
         <f>IF(ISNUMBER(G15),1000*Parameters!E12*G15^2,"")</f>
-        <v/>
+        <v>38.393916352197742</v>
       </c>
       <c r="K15" s="14" t="str">
         <f>IF(COUNT(Parameters!C18:D18,Parameters!F32:I32)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E15)),"待填轮行程",IF(E15&lt;=0,"轮行程须大于0",IF(COUNT(L15:M15)&lt;2,"无效半径",""))))</f>
-        <v>待补坐标</v>
-      </c>
-      <c r="L15" s="104" t="str">
+        <v/>
+      </c>
+      <c r="L15" s="34">
         <f>IF(COUNT(Parameters!F32,Parameters!G32,Parameters!C18,Parameters!D18)&lt;4,"",IF(N15=0,"",IF(Parameters!G32&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!F32)*1000/N15))))))</f>
-        <v/>
-      </c>
-      <c r="M15" s="104">
+        <v>-18.771319397832116</v>
+      </c>
+      <c r="M15" s="34">
         <f>IF(COUNT(Parameters!H32,Parameters!I32,Parameters!C18,Parameters!D18)&lt;4,"",IF(O15=0,"",IF(Parameters!I32&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!H32)*1000/O15))))))</f>
-        <v>21.471368323914565</v>
-      </c>
-      <c r="N15" s="106" t="str">
+        <v>21.471368323914561</v>
+      </c>
+      <c r="N15" s="36">
         <f>IF(COUNT(Parameters!F32,Parameters!G32,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!F32-Parameters!C18)^2+(Parameters!G32-Parameters!D18)^2))</f>
-        <v/>
-      </c>
-      <c r="O15" s="106">
+        <v>161.59517319524122</v>
+      </c>
+      <c r="O15" s="36">
         <f>IF(COUNT(Parameters!H32,Parameters!I32,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!H32-Parameters!C18)^2+(Parameters!I32-Parameters!D18)^2))</f>
         <v>161.18622769951543</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="26.1" customHeight="1">
+    <row r="16" spans="1:15" ht="26.1" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="E16" s="7">
         <f>IF(ISNUMBER(Parameters!E33),Parameters!E33,"")</f>
         <v>252</v>
       </c>
-      <c r="F16" s="9" t="str">
-        <f>IF(COUNT(L16:M16)&lt;2,"",MOD(M16-L16+180,360)-180)</f>
-        <v/>
-      </c>
-      <c r="G16" s="11" t="str">
-        <f>IF(COUNT(E16:F16)&lt;2,"",IF(E16&lt;=0,"",RADIANS(F16)/E16))</f>
-        <v/>
-      </c>
-      <c r="H16" s="5" t="str">
+      <c r="F16" s="9">
+        <f t="shared" si="0"/>
+        <v>44.707366896981739</v>
+      </c>
+      <c r="G16" s="11">
+        <f t="shared" si="1"/>
+        <v>3.0963918740057614E-3</v>
+      </c>
+      <c r="H16" s="5">
         <f>IF(ISNUMBER(G16),1000*Parameters!E10*G16^2,"")</f>
-        <v/>
-      </c>
-      <c r="I16" s="5" t="str">
+        <v>13.681622555635043</v>
+      </c>
+      <c r="I16" s="5">
         <f>IF(ISNUMBER(G16),1000*Parameters!E11*G16^2,"")</f>
-        <v/>
-      </c>
-      <c r="J16" s="5" t="str">
+        <v>28.137432529733275</v>
+      </c>
+      <c r="J16" s="5">
         <f>IF(ISNUMBER(G16),1000*Parameters!E12*G16^2,"")</f>
-        <v/>
+        <v>47.385628104109358</v>
       </c>
       <c r="K16" s="13" t="str">
         <f>IF(COUNT(Parameters!C18:D18,Parameters!F33:I33)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E16)),"待填轮行程",IF(E16&lt;=0,"轮行程须大于0",IF(COUNT(L16:M16)&lt;2,"无效半径",""))))</f>
-        <v>待补坐标</v>
-      </c>
-      <c r="L16" s="103" t="str">
+        <v/>
+      </c>
+      <c r="L16" s="33">
         <f>IF(COUNT(Parameters!F33,Parameters!G33,Parameters!C18,Parameters!D18)&lt;4,"",IF(N16=0,"",IF(Parameters!G33&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!F33)*1000/N16))))))</f>
-        <v/>
-      </c>
-      <c r="M16" s="103">
+        <v>-20.784861013968488</v>
+      </c>
+      <c r="M16" s="33">
         <f>IF(COUNT(Parameters!H33,Parameters!I33,Parameters!C18,Parameters!D18)&lt;4,"",IF(O16=0,"",IF(Parameters!I33&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!H33)*1000/O16))))))</f>
         <v>23.922505883013255</v>
       </c>
-      <c r="N16" s="105" t="str">
+      <c r="N16" s="35">
         <f>IF(COUNT(Parameters!F33,Parameters!G33,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!F33-Parameters!C18)^2+(Parameters!G33-Parameters!D18)^2))</f>
-        <v/>
-      </c>
-      <c r="O16" s="105">
+        <v>146.53668482670133</v>
+      </c>
+      <c r="O16" s="35">
         <f>IF(COUNT(Parameters!H33,Parameters!I33,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!H33-Parameters!C18)^2+(Parameters!I33-Parameters!D18)^2))</f>
         <v>145.49914089093446</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="26.1" customHeight="1">
+    <row r="17" spans="1:15" ht="26.1" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="E17" s="8">
         <f>IF(ISNUMBER(Parameters!E34),Parameters!E34,"")</f>
         <v>252</v>
       </c>
-      <c r="F17" s="10" t="str">
-        <f>IF(COUNT(L17:M17)&lt;2,"",MOD(M17-L17+180,360)-180)</f>
-        <v/>
-      </c>
-      <c r="G17" s="12" t="str">
-        <f>IF(COUNT(E17:F17)&lt;2,"",IF(E17&lt;=0,"",RADIANS(F17)/E17))</f>
-        <v/>
-      </c>
-      <c r="H17" s="6" t="str">
+      <c r="F17" s="10">
+        <f t="shared" si="0"/>
+        <v>50.596578839138232</v>
+      </c>
+      <c r="G17" s="12">
+        <f t="shared" si="1"/>
+        <v>3.504273376935923E-3</v>
+      </c>
+      <c r="H17" s="6">
         <f>IF(ISNUMBER(G17),1000*Parameters!E10*G17^2,"")</f>
-        <v/>
-      </c>
-      <c r="I17" s="6" t="str">
+        <v>17.523535202834569</v>
+      </c>
+      <c r="I17" s="6">
         <f>IF(ISNUMBER(G17),1000*Parameters!E11*G17^2,"")</f>
-        <v/>
-      </c>
-      <c r="J17" s="6" t="str">
+        <v>36.038656047347558</v>
+      </c>
+      <c r="J17" s="6">
         <f>IF(ISNUMBER(G17),1000*Parameters!E12*G17^2,"")</f>
-        <v/>
+        <v>60.691903961989226</v>
       </c>
       <c r="K17" s="14" t="str">
         <f>IF(COUNT(Parameters!C18:D18,Parameters!F34:I34)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E17)),"待填轮行程",IF(E17&lt;=0,"轮行程须大于0",IF(COUNT(L17:M17)&lt;2,"无效半径",""))))</f>
-        <v>待补坐标</v>
-      </c>
-      <c r="L17" s="104" t="str">
+        <v/>
+      </c>
+      <c r="L17" s="34">
         <f>IF(COUNT(Parameters!F34,Parameters!G34,Parameters!C18,Parameters!D18)&lt;4,"",IF(N17=0,"",IF(Parameters!G34&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!F34)*1000/N17))))))</f>
-        <v/>
-      </c>
-      <c r="M17" s="104">
+        <v>-24.22774531795417</v>
+      </c>
+      <c r="M17" s="34">
         <f>IF(COUNT(Parameters!H34,Parameters!I34,Parameters!C18,Parameters!D18)&lt;4,"",IF(O17=0,"",IF(Parameters!I34&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!H34)*1000/O17))))))</f>
-        <v>26.368833521184072</v>
-      </c>
-      <c r="N17" s="106" t="str">
+        <v>26.368833521184065</v>
+      </c>
+      <c r="N17" s="36">
         <f>IF(COUNT(Parameters!F34,Parameters!G34,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!F34-Parameters!C18)^2+(Parameters!G34-Parameters!D18)^2))</f>
-        <v/>
-      </c>
-      <c r="O17" s="106">
+        <v>131.59027319676798</v>
+      </c>
+      <c r="O17" s="36">
         <f>IF(COUNT(Parameters!H34,Parameters!I34,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!H34-Parameters!C18)^2+(Parameters!I34-Parameters!D18)^2))</f>
         <v>130.58713566044705</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="26.1" customHeight="1">
+    <row r="18" spans="1:15" ht="26.1" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -5132,7 +4864,7 @@
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
     </row>
-    <row r="19" spans="1:13" ht="26.1" customHeight="1">
+    <row r="19" spans="1:15" ht="26.1" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -5147,7 +4879,7 @@
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
     </row>
-    <row r="20" spans="1:13" ht="26.1" customHeight="1">
+    <row r="20" spans="1:15" ht="26.1" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -5162,7 +4894,7 @@
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
     </row>
-    <row r="21" spans="1:13" ht="26.1" customHeight="1">
+    <row r="21" spans="1:15" ht="26.1" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -5177,16 +4909,16 @@
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
     </row>
-    <row r="22" spans="1:13" ht="39.950000000000003" customHeight="1">
+    <row r="22" spans="1:15" ht="39.950000000000003" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -5198,20 +4930,18 @@
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
     </row>
-    <row r="23" spans="1:13" ht="26.1" customHeight="1">
+    <row r="23" spans="1:15" ht="26.1" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>#1 L</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="e">
+      <c r="B23" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="6">
         <f>IF(ISNUMBER(H12),H12,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D23" s="6" t="e">
+        <v>5.2468630107600935</v>
+      </c>
+      <c r="D23" s="6">
         <f>IF(ISNUMBER(H15),H15,NA())</f>
-        <v>#N/A</v>
+        <v>11.08545128513005</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -5223,20 +4953,18 @@
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
     </row>
-    <row r="24" spans="1:13" ht="26.1" customHeight="1">
+    <row r="24" spans="1:15" ht="26.1" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>#1 M</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="e">
+      <c r="B24" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="5">
         <f>IF(ISNUMBER(H13),H13,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D24" s="5" t="e">
+        <v>5.504576622925577</v>
+      </c>
+      <c r="D24" s="5">
         <f>IF(ISNUMBER(H16),H16,NA())</f>
-        <v>#N/A</v>
+        <v>13.681622555635043</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
@@ -5248,20 +4976,18 @@
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
     </row>
-    <row r="25" spans="1:13" ht="26.1" customHeight="1">
+    <row r="25" spans="1:15" ht="26.1" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>#1 H</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="e">
+      <c r="B25" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="6">
         <f>IF(ISNUMBER(H14),H14,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D25" s="6" t="e">
+        <v>6.0098659998526269</v>
+      </c>
+      <c r="D25" s="6">
         <f>IF(ISNUMBER(H17),H17,NA())</f>
-        <v>#N/A</v>
+        <v>17.523535202834569</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -5273,20 +4999,18 @@
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
     </row>
-    <row r="26" spans="1:13" ht="26.1" customHeight="1">
+    <row r="26" spans="1:15" ht="26.1" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>#2 L</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="e">
+      <c r="B26" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="5">
         <f>IF(ISNUMBER(I12),I12,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D26" s="5" t="e">
+        <v>11.07997992589914</v>
+      </c>
+      <c r="D26" s="5">
         <f>IF(ISNUMBER(I15),I15,NA())</f>
-        <v>#N/A</v>
+        <v>22.798183207336258</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
@@ -5298,20 +5022,18 @@
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
     </row>
-    <row r="27" spans="1:13" ht="26.1" customHeight="1">
+    <row r="27" spans="1:15" ht="26.1" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>#2 M</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="e">
+      <c r="B27" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="6">
         <f>IF(ISNUMBER(I13),I13,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D27" s="6" t="e">
+        <v>11.624202567803193</v>
+      </c>
+      <c r="D27" s="6">
         <f>IF(ISNUMBER(I16),I16,NA())</f>
-        <v>#N/A</v>
+        <v>28.137432529733275</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -5323,20 +5045,18 @@
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
     </row>
-    <row r="28" spans="1:13" ht="26.1" customHeight="1">
+    <row r="28" spans="1:15" ht="26.1" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>#2 H</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="e">
+      <c r="B28" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="5">
         <f>IF(ISNUMBER(I14),I14,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D28" s="5" t="e">
+        <v>12.691239412798074</v>
+      </c>
+      <c r="D28" s="5">
         <f>IF(ISNUMBER(I17),I17,NA())</f>
-        <v>#N/A</v>
+        <v>36.038656047347558</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
@@ -5348,20 +5068,18 @@
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
     </row>
-    <row r="29" spans="1:13" ht="26.1" customHeight="1">
+    <row r="29" spans="1:15" ht="26.1" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>#3 L</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="e">
+      <c r="B29" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="6">
         <f>IF(ISNUMBER(J12),J12,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D29" s="6" t="e">
+        <v>20.394062528804113</v>
+      </c>
+      <c r="D29" s="6">
         <f>IF(ISNUMBER(J15),J15,NA())</f>
-        <v>#N/A</v>
+        <v>38.393916352197742</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
@@ -5373,20 +5091,18 @@
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
     </row>
-    <row r="30" spans="1:13" ht="26.1" customHeight="1">
+    <row r="30" spans="1:15" ht="26.1" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>#3 M</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="e">
+      <c r="B30" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="5">
         <f>IF(ISNUMBER(J13),J13,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D30" s="5" t="e">
+        <v>21.395771075463013</v>
+      </c>
+      <c r="D30" s="5">
         <f>IF(ISNUMBER(J16),J16,NA())</f>
-        <v>#N/A</v>
+        <v>47.385628104109358</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -5398,20 +5114,18 @@
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
     </row>
-    <row r="31" spans="1:13" ht="26.1" customHeight="1">
+    <row r="31" spans="1:15" ht="26.1" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>#3 H</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="e">
+      <c r="B31" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="6">
         <f>IF(ISNUMBER(J14),J14,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D31" s="6" t="e">
+        <v>23.359783310403735</v>
+      </c>
+      <c r="D31" s="6">
         <f>IF(ISNUMBER(J17),J17,NA())</f>
-        <v>#N/A</v>
+        <v>60.691903961989226</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -5423,7 +5137,7 @@
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
     </row>
-    <row r="32" spans="1:13" ht="26.1" customHeight="1">
+    <row r="32" spans="1:15" ht="26.1" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -5471,13 +5185,13 @@
     <row r="35" spans="1:13" ht="39.950000000000003" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
@@ -5491,10 +5205,8 @@
     </row>
     <row r="36" spans="1:13" ht="26.1" customHeight="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>#1 L</t>
-        </is>
+      <c r="B36" s="4" t="s">
+        <v>59</v>
       </c>
       <c r="C36" s="5" t="e">
         <f>IF(ISNUMBER(H6),H6,NA())</f>
@@ -5516,10 +5228,8 @@
     </row>
     <row r="37" spans="1:13" ht="26.1" customHeight="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>#1 M</t>
-        </is>
+      <c r="B37" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="C37" s="6" t="e">
         <f>IF(ISNUMBER(H7),H7,NA())</f>
@@ -5541,10 +5251,8 @@
     </row>
     <row r="38" spans="1:13" ht="26.1" customHeight="1">
       <c r="A38" s="1"/>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>#1 H</t>
-        </is>
+      <c r="B38" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="C38" s="5" t="e">
         <f>IF(ISNUMBER(H8),H8,NA())</f>
@@ -5566,10 +5274,8 @@
     </row>
     <row r="39" spans="1:13" ht="26.1" customHeight="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>#2 L</t>
-        </is>
+      <c r="B39" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C39" s="6" t="e">
         <f>IF(ISNUMBER(I6),I6,NA())</f>
@@ -5591,10 +5297,8 @@
     </row>
     <row r="40" spans="1:13" ht="26.1" customHeight="1">
       <c r="A40" s="1"/>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>#2 M</t>
-        </is>
+      <c r="B40" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="C40" s="5" t="e">
         <f>IF(ISNUMBER(I7),I7,NA())</f>
@@ -5616,10 +5320,8 @@
     </row>
     <row r="41" spans="1:13" ht="26.1" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>#2 H</t>
-        </is>
+      <c r="B41" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="C41" s="6" t="e">
         <f>IF(ISNUMBER(I8),I8,NA())</f>
@@ -5641,10 +5343,8 @@
     </row>
     <row r="42" spans="1:13" ht="26.1" customHeight="1">
       <c r="A42" s="1"/>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>#3 L</t>
-        </is>
+      <c r="B42" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="C42" s="5" t="e">
         <f>IF(ISNUMBER(J6),J6,NA())</f>
@@ -5666,10 +5366,8 @@
     </row>
     <row r="43" spans="1:13" ht="26.1" customHeight="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>#3 M</t>
-        </is>
+      <c r="B43" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="C43" s="6" t="e">
         <f>IF(ISNUMBER(J7),J7,NA())</f>
@@ -5691,10 +5389,8 @@
     </row>
     <row r="44" spans="1:13" ht="26.1" customHeight="1">
       <c r="A44" s="1"/>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>#3 H</t>
-        </is>
+      <c r="B44" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="C44" s="5" t="e">
         <f>IF(ISNUMBER(J8),J8,NA())</f>
@@ -5776,14 +5472,14 @@
     </row>
     <row r="49" spans="1:13" ht="26.1" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="C49" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="D49" s="28" t="s">
-        <v>54</v>
+      <c r="B49" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="D49" s="44" t="s">
+        <v>35</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -5798,7 +5494,7 @@
     <row r="50" spans="1:13" ht="26.1" customHeight="1">
       <c r="A50" s="1"/>
       <c r="B50" s="1" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="C50" s="1">
         <v>223</v>
@@ -5817,7 +5513,7 @@
     <row r="51" spans="1:13" ht="26.1" customHeight="1">
       <c r="A51" s="1"/>
       <c r="B51" s="1" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="C51" s="1">
         <v>267</v>
@@ -5836,7 +5532,7 @@
     <row r="52" spans="1:13" ht="26.1" customHeight="1">
       <c r="A52" s="1"/>
       <c r="B52" s="1" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="C52" s="1">
         <v>236</v>
@@ -5855,7 +5551,7 @@
     <row r="53" spans="1:13" ht="26.1" customHeight="1">
       <c r="A53" s="1"/>
       <c r="B53" s="1" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="C53" s="1">
         <v>238</v>
@@ -5874,7 +5570,7 @@
     <row r="54" spans="1:13" ht="26.1" customHeight="1">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C54" s="1">
         <v>279</v>
@@ -5893,7 +5589,7 @@
     <row r="55" spans="1:13" ht="26.1" customHeight="1">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="C55" s="1">
         <v>16</v>
@@ -5912,7 +5608,7 @@
     <row r="56" spans="1:13" ht="26.1" customHeight="1">
       <c r="A56" s="1"/>
       <c r="B56" s="1" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C56" s="1">
         <v>23</v>
@@ -5931,7 +5627,7 @@
     <row r="57" spans="1:13" ht="26.1" customHeight="1">
       <c r="A57" s="1"/>
       <c r="B57" s="1" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="C57" s="1">
         <v>24</v>
@@ -6514,7 +6210,7 @@
     <mergeCell ref="B2:K3"/>
     <mergeCell ref="B49:D49"/>
   </mergeCells>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/arb_stiffness.xlsx
+++ b/docs/arb_stiffness.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\UserSpace\Games\Steam_Library\common\BeamNG_Userdata\current\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A3CF3C-168E-43FE-9070-7AEC032FD9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B39674A-0F99-4379-9495-B7ACE30517CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="70">
   <si>
     <t>Astral · Anti-Roll Bar Stiffness</t>
   </si>
@@ -257,6 +257,14 @@
   </si>
   <si>
     <t>#3 H</t>
+  </si>
+  <si>
+    <t>Front</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>M</t>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -269,7 +277,7 @@
     <numFmt numFmtId="178" formatCode="0.000"/>
     <numFmt numFmtId="179" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -324,13 +332,6 @@
     </font>
     <font>
       <b/>
-      <sz val="20"/>
-      <color rgb="FF283C50"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
@@ -341,14 +342,6 @@
       <color rgb="FF195DB1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF667B91"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -421,7 +414,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -466,11 +459,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDF2F7"/>
       </patternFill>
     </fill>
     <fill>
@@ -568,17 +556,17 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -622,91 +610,88 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="1" fontId="7" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="9" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="7" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="4" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="22" fillId="16" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="20" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="4" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="16" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="20" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="17" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="12" fillId="16" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="12" fillId="14" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="21" fillId="17" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="19" fillId="16" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="21" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="19" fillId="14" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -816,31 +801,31 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>5.2468630107600935</c:v>
+                  <c:v>9.0145383497721205</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.504576622925577</c:v>
+                  <c:v>10.603232186754845</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.0098659998526269</c:v>
+                  <c:v>12.572445303571339</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.07997992589914</c:v>
+                  <c:v>16.700545198921954</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11.624202567803193</c:v>
+                  <c:v>19.643796666974055</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>12.691239412798074</c:v>
+                  <c:v>23.292007078607082</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20.394062528804113</c:v>
+                  <c:v>31.330224796635314</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>21.395771075463013</c:v>
+                  <c:v>36.85176490378413</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>23.359783310403735</c:v>
+                  <c:v>43.695808073660181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -905,31 +890,31 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>11.08545128513005</c:v>
+                  <c:v>13.838466461259268</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.681622555635043</c:v>
+                  <c:v>16.853552276273707</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>17.523535202834569</c:v>
+                  <c:v>21.242835430841463</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>22.798183207336258</c:v>
+                  <c:v>26.445946096343832</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>28.137432529733275</c:v>
+                  <c:v>32.207913808802836</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>36.038656047347558</c:v>
+                  <c:v>40.596035862084598</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38.393916352197742</c:v>
+                  <c:v>49.574188917265118</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>47.385628104109358</c:v>
+                  <c:v>60.375272564339298</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>60.691903961989226</c:v>
+                  <c:v>76.0992079386142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1165,31 +1150,31 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>8.3256960949803513</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>#N/A</c:v>
+                  <c:v>10.192545394173928</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>#N/A</c:v>
+                  <c:v>13.650114740317481</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>#N/A</c:v>
+                  <c:v>15.424379879666526</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>#N/A</c:v>
+                  <c:v>18.882948681644748</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>#N/A</c:v>
+                  <c:v>25.28852275578878</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>#N/A</c:v>
+                  <c:v>28.936138504618729</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>#N/A</c:v>
+                  <c:v>35.424413992032278</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>#N/A</c:v>
+                  <c:v>47.441271723562288</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1254,31 +1239,31 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>14.102664166988719</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>#N/A</c:v>
+                  <c:v>17.536246316263107</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>#N/A</c:v>
+                  <c:v>22.987373184334313</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>#N/A</c:v>
+                  <c:v>26.950840067367189</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>#N/A</c:v>
+                  <c:v>33.512573529039784</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>#N/A</c:v>
+                  <c:v>43.929927772800724</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>#N/A</c:v>
+                  <c:v>50.520636777799808</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>#N/A</c:v>
+                  <c:v>62.820919515601688</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>#N/A</c:v>
+                  <c:v>82.348747539484549</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1729,151 +1714,151 @@
     </row>
     <row r="2" spans="1:15" ht="26.1" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="C2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="41" t="s">
+      <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="41" t="s">
+      <c r="E2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="41" t="s">
+      <c r="F2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="41" t="s">
+      <c r="G2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="41" t="s">
+      <c r="H2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="41" t="s">
+      <c r="I2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="41" t="s">
+      <c r="J2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="41" t="s">
+      <c r="K2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="41" t="s">
+      <c r="L2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="M2" s="41" t="s">
+      <c r="M2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="N2" s="41" t="s">
+      <c r="N2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:15" ht="26.1" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="41" t="s">
+      <c r="H3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="I3" s="41" t="s">
+      <c r="I3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="41" t="s">
+      <c r="J3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="41" t="s">
+      <c r="K3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="41" t="s">
+      <c r="L3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="M3" s="41" t="s">
+      <c r="M3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="N3" s="41" t="s">
+      <c r="N3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" ht="26.1" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="C4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="42" t="s">
+      <c r="D4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="E4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="42" t="s">
+      <c r="F4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="42" t="s">
+      <c r="G4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="42" t="s">
+      <c r="H4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="42" t="s">
+      <c r="I4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J4" s="42" t="s">
+      <c r="J4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="K4" s="42" t="s">
+      <c r="K4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L4" s="42" t="s">
+      <c r="L4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="42" t="s">
+      <c r="M4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="N4" s="42" t="s">
+      <c r="N4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="O4" s="1"/>
     </row>
     <row r="5" spans="1:15" ht="26.1" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="43" t="str">
+      <c r="B5" s="1" t="str">
         <f>IF(COUNT(Samples!H6:J17)=0,"待补节点坐标；暂无刚度结果。","")</f>
         <v/>
       </c>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="26.1" customHeight="1">
@@ -2609,43 +2594,43 @@
     </row>
     <row r="49" spans="1:15" ht="26.1" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="43" t="s">
+      <c r="B49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C49" s="43" t="s">
+      <c r="C49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D49" s="43" t="s">
+      <c r="D49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E49" s="43" t="s">
+      <c r="E49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F49" s="43" t="s">
+      <c r="F49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G49" s="43" t="s">
+      <c r="G49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H49" s="43" t="s">
+      <c r="H49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I49" s="43" t="s">
+      <c r="I49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J49" s="43" t="s">
+      <c r="J49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K49" s="43" t="s">
+      <c r="K49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L49" s="43" t="s">
+      <c r="L49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M49" s="43" t="s">
+      <c r="M49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="N49" s="43" t="s">
+      <c r="N49" s="1" t="s">
         <v>2</v>
       </c>
       <c r="O49" s="1"/>
@@ -2657,7 +2642,7 @@
     <mergeCell ref="B5:N5"/>
     <mergeCell ref="B49:N49"/>
   </mergeCells>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2697,84 +2682,84 @@
     </row>
     <row r="2" spans="1:10" ht="27" customHeight="1">
       <c r="A2" s="15"/>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="38" t="s">
         <v>3</v>
       </c>
       <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10" ht="27" customHeight="1">
       <c r="A3" s="15"/>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="38" t="s">
         <v>3</v>
       </c>
       <c r="J3" s="15"/>
     </row>
     <row r="4" spans="1:10" ht="27" customHeight="1">
       <c r="A4" s="15"/>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="37" t="s">
+      <c r="E4" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="37" t="s">
+      <c r="F4" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="37" t="s">
+      <c r="G4" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="37" t="s">
+      <c r="H4" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="37" t="s">
+      <c r="I4" s="39" t="s">
         <v>4</v>
       </c>
       <c r="J4" s="15"/>
@@ -2820,11 +2805,11 @@
         <v>44</v>
       </c>
       <c r="D7" s="19">
-        <v>14.6</v>
+        <v>15.6</v>
       </c>
       <c r="E7" s="21">
         <f>$E$8*(D7/$D$8)^4</f>
-        <v>941.40636852684645</v>
+        <v>1423.3869221157856</v>
       </c>
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
@@ -2841,10 +2826,10 @@
         <v>45</v>
       </c>
       <c r="D8" s="19">
-        <v>17.600000000000001</v>
+        <v>18.2</v>
       </c>
       <c r="E8" s="20">
-        <v>1988</v>
+        <v>2637</v>
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
@@ -2861,11 +2846,11 @@
         <v>46</v>
       </c>
       <c r="D9" s="19">
-        <v>20.5</v>
+        <v>21.3</v>
       </c>
       <c r="E9" s="21">
         <f>$E$8*(D9/$D$8)^4</f>
-        <v>3659.1579207191098</v>
+        <v>4947.0123163440448</v>
       </c>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
@@ -2882,11 +2867,11 @@
         <v>44</v>
       </c>
       <c r="D10" s="19">
-        <v>16.2</v>
+        <v>16.5</v>
       </c>
       <c r="E10" s="22">
         <f>$E$8*(D10/$D$8)^4</f>
-        <v>1427.0058942593778</v>
+        <v>1781.3955155995275</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
@@ -2907,7 +2892,7 @@
       </c>
       <c r="E11" s="21">
         <f>$E$8*(D11/$D$8)^4</f>
-        <v>2934.7602527389881</v>
+        <v>3404.3287898771091</v>
       </c>
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
@@ -2924,11 +2909,11 @@
         <v>46</v>
       </c>
       <c r="D12" s="19">
-        <v>22.1</v>
+        <v>22.7</v>
       </c>
       <c r="E12" s="22">
         <f>$E$8*(D12/$D$8)^4</f>
-        <v>4942.3648644580135</v>
+        <v>6381.5768946600283</v>
       </c>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
@@ -2950,56 +2935,56 @@
     </row>
     <row r="14" spans="1:10" ht="27" customHeight="1">
       <c r="A14" s="15"/>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="38" t="s">
+      <c r="E14" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="38" t="s">
+      <c r="F14" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="38" t="s">
+      <c r="G14" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="38" t="s">
+      <c r="H14" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="I14" s="38" t="s">
+      <c r="I14" s="40" t="s">
         <v>11</v>
       </c>
       <c r="J14" s="15"/>
     </row>
     <row r="15" spans="1:10" ht="27" customHeight="1">
       <c r="A15" s="15"/>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="39" t="s">
+      <c r="E15" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="39" t="s">
+      <c r="F15" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="39" t="s">
+      <c r="G15" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="H15" s="39" t="s">
+      <c r="H15" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="39" t="s">
+      <c r="I15" s="41" t="s">
         <v>12</v>
       </c>
       <c r="J15" s="15"/>
@@ -3026,7 +3011,7 @@
         <v>-0.91500000000000004</v>
       </c>
       <c r="D17" s="29">
-        <v>0.127</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="J17" s="15"/>
     </row>
@@ -3057,44 +3042,44 @@
     </row>
     <row r="20" spans="1:14" ht="27" customHeight="1">
       <c r="A20" s="15"/>
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="D20" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="38" t="s">
+      <c r="E20" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="38" t="s">
+      <c r="F20" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="G20" s="38" t="s">
+      <c r="G20" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="H20" s="38" t="s">
+      <c r="H20" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="I20" s="38" t="s">
+      <c r="I20" s="40" t="s">
         <v>18</v>
       </c>
       <c r="J20" s="15"/>
     </row>
     <row r="21" spans="1:14" ht="27" customHeight="1">
       <c r="A21" s="15"/>
-      <c r="B21" s="40" t="s">
+      <c r="B21" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="40"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
       <c r="J21" s="15"/>
     </row>
     <row r="22" spans="1:14" ht="42" customHeight="1">
@@ -3137,12 +3122,20 @@
         <v>51</v>
       </c>
       <c r="E23" s="32">
-        <v>167</v>
-      </c>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
+        <v>153</v>
+      </c>
+      <c r="F23" s="29">
+        <v>-1.083</v>
+      </c>
+      <c r="G23" s="29">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="H23" s="29">
+        <v>-1.073</v>
+      </c>
+      <c r="I23" s="29">
+        <v>0.224</v>
+      </c>
       <c r="J23" s="15"/>
     </row>
     <row r="24" spans="1:14" ht="27" customHeight="1">
@@ -3157,12 +3150,20 @@
         <v>52</v>
       </c>
       <c r="E24" s="32">
-        <v>167</v>
-      </c>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
+        <v>153</v>
+      </c>
+      <c r="F24" s="29">
+        <v>-1.0660000000000001</v>
+      </c>
+      <c r="G24" s="29">
+        <v>0.155</v>
+      </c>
+      <c r="H24" s="29">
+        <v>-1.0580000000000001</v>
+      </c>
+      <c r="I24" s="29">
+        <v>0.216</v>
+      </c>
       <c r="J24" s="15"/>
       <c r="M24" s="23"/>
       <c r="N24" s="23"/>
@@ -3179,12 +3180,20 @@
         <v>53</v>
       </c>
       <c r="E25" s="32">
-        <v>167</v>
-      </c>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="29"/>
+        <v>153</v>
+      </c>
+      <c r="F25" s="29">
+        <v>-1.0469999999999999</v>
+      </c>
+      <c r="G25" s="29">
+        <v>0.14099999999999999</v>
+      </c>
+      <c r="H25" s="29">
+        <v>-1.044</v>
+      </c>
+      <c r="I25" s="29">
+        <v>0.20399999999999999</v>
+      </c>
       <c r="J25" s="15"/>
     </row>
     <row r="26" spans="1:14" ht="27" customHeight="1">
@@ -3199,12 +3208,20 @@
         <v>51</v>
       </c>
       <c r="E26" s="32">
-        <v>166</v>
-      </c>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
+        <v>147</v>
+      </c>
+      <c r="F26" s="29">
+        <v>1.3049999999999999</v>
+      </c>
+      <c r="G26" s="29">
+        <v>0.21</v>
+      </c>
+      <c r="H26" s="29">
+        <v>1.2989999999999999</v>
+      </c>
+      <c r="I26" s="29">
+        <v>0.27600000000000002</v>
+      </c>
       <c r="J26" s="15"/>
     </row>
     <row r="27" spans="1:14" ht="27" customHeight="1">
@@ -3219,12 +3236,20 @@
         <v>52</v>
       </c>
       <c r="E27" s="32">
-        <v>166</v>
-      </c>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="29"/>
+        <v>147</v>
+      </c>
+      <c r="F27" s="29">
+        <v>1.32</v>
+      </c>
+      <c r="G27" s="29">
+        <v>0.21</v>
+      </c>
+      <c r="H27" s="29">
+        <v>1.3129999999999999</v>
+      </c>
+      <c r="I27" s="29">
+        <v>0.27700000000000002</v>
+      </c>
       <c r="J27" s="15"/>
       <c r="M27" s="23"/>
       <c r="N27" s="23"/>
@@ -3241,12 +3266,20 @@
         <v>53</v>
       </c>
       <c r="E28" s="32">
-        <v>166</v>
-      </c>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
+        <v>147</v>
+      </c>
+      <c r="F28" s="29">
+        <v>1.3360000000000001</v>
+      </c>
+      <c r="G28" s="29">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="H28" s="29">
+        <v>1.327</v>
+      </c>
+      <c r="I28" s="29">
+        <v>0.27700000000000002</v>
+      </c>
       <c r="J28" s="15"/>
     </row>
     <row r="29" spans="1:14" ht="27" customHeight="1">
@@ -3264,16 +3297,16 @@
         <v>259</v>
       </c>
       <c r="F29" s="29">
-        <v>-1.0840000000000001</v>
+        <v>-1.083</v>
       </c>
       <c r="G29" s="29">
         <v>0.161</v>
       </c>
       <c r="H29" s="29">
-        <v>-1.034</v>
+        <v>-1.052</v>
       </c>
       <c r="I29" s="29">
-        <v>0.252</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="J29" s="15"/>
       <c r="M29" s="23"/>
@@ -3294,16 +3327,16 @@
         <v>259</v>
       </c>
       <c r="F30" s="29">
-        <v>-1.069</v>
+        <v>-1.0660000000000001</v>
       </c>
       <c r="G30" s="29">
-        <v>0.156</v>
+        <v>0.154</v>
       </c>
       <c r="H30" s="29">
-        <v>-1.0229999999999999</v>
+        <v>-1.038</v>
       </c>
       <c r="I30" s="29">
-        <v>0.24099999999999999</v>
+        <v>0.255</v>
       </c>
       <c r="J30" s="15"/>
     </row>
@@ -3322,16 +3355,16 @@
         <v>259</v>
       </c>
       <c r="F31" s="29">
-        <v>-1.0549999999999999</v>
+        <v>-1.0469999999999999</v>
       </c>
       <c r="G31" s="29">
-        <v>0.14899999999999999</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="H31" s="29">
-        <v>-1.0129999999999999</v>
+        <v>-1.0249999999999999</v>
       </c>
       <c r="I31" s="29">
-        <v>0.23</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="J31" s="15"/>
     </row>
@@ -3378,13 +3411,13 @@
         <v>252</v>
       </c>
       <c r="F33" s="29">
-        <v>1.3220000000000001</v>
+        <v>1.321</v>
       </c>
       <c r="G33" s="29">
         <v>0.20799999999999999</v>
       </c>
       <c r="H33" s="29">
-        <v>1.3260000000000001</v>
+        <v>1.325</v>
       </c>
       <c r="I33" s="29">
         <v>0.31900000000000001</v>
@@ -3408,13 +3441,13 @@
         <v>252</v>
       </c>
       <c r="F34" s="29">
-        <v>1.339</v>
+        <v>1.337</v>
       </c>
       <c r="G34" s="29">
         <v>0.20599999999999999</v>
       </c>
       <c r="H34" s="29">
-        <v>1.3420000000000001</v>
+        <v>1.34</v>
       </c>
       <c r="I34" s="29">
         <v>0.318</v>
@@ -3461,28 +3494,28 @@
     </row>
     <row r="38" spans="1:14" ht="27" customHeight="1">
       <c r="A38" s="15"/>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="F38" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G38" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="H38" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="I38" s="3" t="s">
+      <c r="I38" s="37" t="s">
         <v>27</v>
       </c>
       <c r="J38" s="15"/>
@@ -4004,7 +4037,7 @@
     <mergeCell ref="B20:I20"/>
     <mergeCell ref="B21:I21"/>
   </mergeCells>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4049,34 +4082,34 @@
     </row>
     <row r="2" spans="1:15" ht="26.1" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="C2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="41" t="s">
+      <c r="D2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="41" t="s">
+      <c r="E2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="41" t="s">
+      <c r="F2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="41" t="s">
+      <c r="G2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="41" t="s">
+      <c r="H2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="41" t="s">
+      <c r="I2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="41" t="s">
+      <c r="J2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="K2" s="41" t="s">
+      <c r="K2" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L2" s="1"/>
@@ -4084,34 +4117,34 @@
     </row>
     <row r="3" spans="1:15" ht="26.1" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="C3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="D3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="41" t="s">
+      <c r="H3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="41" t="s">
+      <c r="I3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="41" t="s">
+      <c r="J3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="41" t="s">
+      <c r="K3" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L3" s="1"/>
@@ -4190,47 +4223,47 @@
       </c>
       <c r="E6" s="7">
         <f>IF(ISNUMBER(Parameters!E23),Parameters!E23,"")</f>
-        <v>167</v>
-      </c>
-      <c r="F6" s="9" t="str">
+        <v>153</v>
+      </c>
+      <c r="F6" s="9">
         <f t="shared" ref="F6:F17" si="0">IF(COUNT(L6:M6)&lt;2,"",MOD(M6-L6+180,360)-180)</f>
-        <v/>
-      </c>
-      <c r="G6" s="11" t="str">
+        <v>21.201317736150372</v>
+      </c>
+      <c r="G6" s="11">
         <f t="shared" ref="G6:G17" si="1">IF(COUNT(E6:F6)&lt;2,"",IF(E6&lt;=0,"",RADIANS(F6)/E6))</f>
-        <v/>
-      </c>
-      <c r="H6" s="5" t="str">
+        <v>2.4185150343614013E-3</v>
+      </c>
+      <c r="H6" s="5">
         <f>IF(ISNUMBER(G6),1000*Parameters!E7*G6^2,"")</f>
-        <v/>
-      </c>
-      <c r="I6" s="5" t="str">
+        <v>8.3256960949803513</v>
+      </c>
+      <c r="I6" s="5">
         <f>IF(ISNUMBER(G6),1000*Parameters!E8*G6^2,"")</f>
-        <v/>
-      </c>
-      <c r="J6" s="5" t="str">
+        <v>15.424379879666526</v>
+      </c>
+      <c r="J6" s="5">
         <f>IF(ISNUMBER(G6),1000*Parameters!E9*G6^2,"")</f>
-        <v/>
+        <v>28.936138504618729</v>
       </c>
       <c r="K6" s="13" t="str">
         <f>IF(COUNT(Parameters!C17:D17,Parameters!F23:I23)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E6)),"待填轮行程",IF(E6&lt;=0,"轮行程须大于0",IF(COUNT(L6:M6)&lt;2,"无效半径",""))))</f>
-        <v>待补坐标</v>
-      </c>
-      <c r="L6" s="33" t="str">
+        <v/>
+      </c>
+      <c r="L6" s="33">
         <f>IF(COUNT(Parameters!F23,Parameters!G23,Parameters!C17,Parameters!D17)&lt;4,"",IF(N6=0,"",IF(Parameters!G23&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!F23)*1000/N6))))))</f>
-        <v/>
-      </c>
-      <c r="M6" s="33" t="str">
+        <v>-1.36392753160292</v>
+      </c>
+      <c r="M6" s="33">
         <f>IF(COUNT(Parameters!H23,Parameters!I23,Parameters!C17,Parameters!D17)&lt;4,"",IF(O6=0,"",IF(Parameters!I23&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!H23)*1000/O6))))))</f>
-        <v/>
-      </c>
-      <c r="N6" s="35" t="str">
+        <v>19.837390204547461</v>
+      </c>
+      <c r="N6" s="35">
         <f>IF(COUNT(Parameters!F23,Parameters!G23,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!F23-Parameters!C17)^2+(Parameters!G23-Parameters!D17)^2))</f>
-        <v/>
-      </c>
-      <c r="O6" s="35" t="str">
+        <v>168.04761230079995</v>
+      </c>
+      <c r="O6" s="35">
         <f>IF(COUNT(Parameters!H23,Parameters!I23,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!H23-Parameters!C17)^2+(Parameters!I23-Parameters!D17)^2))</f>
-        <v/>
+        <v>167.96725871431008</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="26.1" customHeight="1">
@@ -4246,47 +4279,47 @@
       </c>
       <c r="E7" s="8">
         <f>IF(ISNUMBER(Parameters!E24),Parameters!E24,"")</f>
-        <v>167</v>
-      </c>
-      <c r="F7" s="10" t="str">
+        <v>153</v>
+      </c>
+      <c r="F7" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G7" s="12" t="str">
+        <v>23.458157873185627</v>
+      </c>
+      <c r="G7" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H7" s="6" t="str">
+        <v>2.6759613813053572E-3</v>
+      </c>
+      <c r="H7" s="6">
         <f>IF(ISNUMBER(G7),1000*Parameters!E7*G7^2,"")</f>
-        <v/>
-      </c>
-      <c r="I7" s="6" t="str">
+        <v>10.192545394173928</v>
+      </c>
+      <c r="I7" s="6">
         <f>IF(ISNUMBER(G7),1000*Parameters!E8*G7^2,"")</f>
-        <v/>
-      </c>
-      <c r="J7" s="6" t="str">
+        <v>18.882948681644748</v>
+      </c>
+      <c r="J7" s="6">
         <f>IF(ISNUMBER(G7),1000*Parameters!E9*G7^2,"")</f>
-        <v/>
+        <v>35.424413992032278</v>
       </c>
       <c r="K7" s="14" t="str">
         <f>IF(COUNT(Parameters!C17:D17,Parameters!F24:I24)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E7)),"待填轮行程",IF(E7&lt;=0,"轮行程须大于0",IF(COUNT(L7:M7)&lt;2,"无效半径",""))))</f>
-        <v>待补坐标</v>
-      </c>
-      <c r="L7" s="34" t="str">
+        <v/>
+      </c>
+      <c r="L7" s="34">
         <f>IF(COUNT(Parameters!F24,Parameters!G24,Parameters!C17,Parameters!D17)&lt;4,"",IF(N7=0,"",IF(Parameters!G24&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!F24)*1000/N7))))))</f>
-        <v/>
-      </c>
-      <c r="M7" s="34" t="str">
+        <v>-4.5437576514670672</v>
+      </c>
+      <c r="M7" s="34">
         <f>IF(COUNT(Parameters!H24,Parameters!I24,Parameters!C17,Parameters!D17)&lt;4,"",IF(O7=0,"",IF(Parameters!I24&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!H24)*1000/O7))))))</f>
-        <v/>
-      </c>
-      <c r="N7" s="36" t="str">
+        <v>18.914400221718555</v>
+      </c>
+      <c r="N7" s="36">
         <f>IF(COUNT(Parameters!F24,Parameters!G24,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!F24-Parameters!C17)^2+(Parameters!G24-Parameters!D17)^2))</f>
-        <v/>
-      </c>
-      <c r="O7" s="36" t="str">
+        <v>151.47607071745691</v>
+      </c>
+      <c r="O7" s="36">
         <f>IF(COUNT(Parameters!H24,Parameters!I24,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!H24-Parameters!C17)^2+(Parameters!I24-Parameters!D17)^2))</f>
-        <v/>
+        <v>151.16216457830976</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="26.1" customHeight="1">
@@ -4302,47 +4335,47 @@
       </c>
       <c r="E8" s="7">
         <f>IF(ISNUMBER(Parameters!E25),Parameters!E25,"")</f>
-        <v>167</v>
-      </c>
-      <c r="F8" s="9" t="str">
+        <v>153</v>
+      </c>
+      <c r="F8" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G8" s="11" t="str">
+        <v>27.14693034422092</v>
+      </c>
+      <c r="G8" s="11">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H8" s="5" t="str">
+        <v>3.0967537014131544E-3</v>
+      </c>
+      <c r="H8" s="5">
         <f>IF(ISNUMBER(G8),1000*Parameters!E7*G8^2,"")</f>
-        <v/>
-      </c>
-      <c r="I8" s="5" t="str">
+        <v>13.650114740317481</v>
+      </c>
+      <c r="I8" s="5">
         <f>IF(ISNUMBER(G8),1000*Parameters!E8*G8^2,"")</f>
-        <v/>
-      </c>
-      <c r="J8" s="5" t="str">
+        <v>25.28852275578878</v>
+      </c>
+      <c r="J8" s="5">
         <f>IF(ISNUMBER(G8),1000*Parameters!E9*G8^2,"")</f>
-        <v/>
+        <v>47.441271723562288</v>
       </c>
       <c r="K8" s="13" t="str">
         <f>IF(COUNT(Parameters!C17:D17,Parameters!F25:I25)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E8)),"待填轮行程",IF(E8&lt;=0,"轮行程须大于0",IF(COUNT(L8:M8)&lt;2,"无效半径",""))))</f>
-        <v>待补坐标</v>
-      </c>
-      <c r="L8" s="33" t="str">
+        <v/>
+      </c>
+      <c r="L8" s="33">
         <f>IF(COUNT(Parameters!F25,Parameters!G25,Parameters!C17,Parameters!D17)&lt;4,"",IF(N8=0,"",IF(Parameters!G25&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!F25)*1000/N8))))))</f>
-        <v/>
-      </c>
-      <c r="M8" s="33" t="str">
+        <v>-11.14288985833935</v>
+      </c>
+      <c r="M8" s="33">
         <f>IF(COUNT(Parameters!H25,Parameters!I25,Parameters!C17,Parameters!D17)&lt;4,"",IF(O8=0,"",IF(Parameters!I25&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!H25)*1000/O8))))))</f>
-        <v/>
-      </c>
-      <c r="N8" s="35" t="str">
+        <v>16.004040485881575</v>
+      </c>
+      <c r="N8" s="35">
         <f>IF(COUNT(Parameters!F25,Parameters!G25,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!F25-Parameters!C17)^2+(Parameters!G25-Parameters!D17)^2))</f>
-        <v/>
-      </c>
-      <c r="O8" s="35" t="str">
+        <v>134.536240470737</v>
+      </c>
+      <c r="O8" s="35">
         <f>IF(COUNT(Parameters!H25,Parameters!I25,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!H25-Parameters!C17)^2+(Parameters!I25-Parameters!D17)^2))</f>
-        <v/>
+        <v>134.20134127496638</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="26.1" customHeight="1">
@@ -4358,47 +4391,47 @@
       </c>
       <c r="E9" s="8">
         <f>IF(ISNUMBER(Parameters!E26),Parameters!E26,"")</f>
-        <v>166</v>
-      </c>
-      <c r="F9" s="10" t="str">
+        <v>147</v>
+      </c>
+      <c r="F9" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G9" s="12" t="str">
+        <v>23.697927789561106</v>
+      </c>
+      <c r="G9" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H9" s="6" t="str">
+        <v>2.813652148487777E-3</v>
+      </c>
+      <c r="H9" s="6">
         <f>IF(ISNUMBER(G9),1000*Parameters!E10*G9^2,"")</f>
-        <v/>
-      </c>
-      <c r="I9" s="6" t="str">
+        <v>14.102664166988719</v>
+      </c>
+      <c r="I9" s="6">
         <f>IF(ISNUMBER(G9),1000*Parameters!E11*G9^2,"")</f>
-        <v/>
-      </c>
-      <c r="J9" s="6" t="str">
+        <v>26.950840067367189</v>
+      </c>
+      <c r="J9" s="6">
         <f>IF(ISNUMBER(G9),1000*Parameters!E12*G9^2,"")</f>
-        <v/>
+        <v>50.520636777799808</v>
       </c>
       <c r="K9" s="14" t="str">
         <f>IF(COUNT(Parameters!C18:D18,Parameters!F26:I26)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E9)),"待填轮行程",IF(E9&lt;=0,"轮行程须大于0",IF(COUNT(L9:M9)&lt;2,"无效半径",""))))</f>
-        <v>待补坐标</v>
-      </c>
-      <c r="L9" s="34" t="str">
+        <v/>
+      </c>
+      <c r="L9" s="34">
         <f>IF(COUNT(Parameters!F26,Parameters!G26,Parameters!C18,Parameters!D18)&lt;4,"",IF(N9=0,"",IF(Parameters!G26&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!F26)*1000/N9))))))</f>
-        <v/>
-      </c>
-      <c r="M9" s="34" t="str">
+        <v>-17.987334652061463</v>
+      </c>
+      <c r="M9" s="34">
         <f>IF(COUNT(Parameters!H26,Parameters!I26,Parameters!C18,Parameters!D18)&lt;4,"",IF(O9=0,"",IF(Parameters!I26&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!H26)*1000/O9))))))</f>
-        <v/>
-      </c>
-      <c r="N9" s="36" t="str">
+        <v>5.7105931374996333</v>
+      </c>
+      <c r="N9" s="36">
         <f>IF(COUNT(Parameters!F26,Parameters!G26,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!F26-Parameters!C18)^2+(Parameters!G26-Parameters!D18)^2))</f>
-        <v/>
-      </c>
-      <c r="O9" s="36" t="str">
+        <v>161.91355718407291</v>
+      </c>
+      <c r="O9" s="36">
         <f>IF(COUNT(Parameters!H26,Parameters!I26,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!H26-Parameters!C18)^2+(Parameters!I26-Parameters!D18)^2))</f>
-        <v/>
+        <v>160.79800993793438</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="26.1" customHeight="1">
@@ -4414,47 +4447,47 @@
       </c>
       <c r="E10" s="7">
         <f>IF(ISNUMBER(Parameters!E27),Parameters!E27,"")</f>
-        <v>166</v>
-      </c>
-      <c r="F10" s="9" t="str">
+        <v>147</v>
+      </c>
+      <c r="F10" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G10" s="11" t="str">
+        <v>26.425797842021012</v>
+      </c>
+      <c r="G10" s="11">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H10" s="5" t="str">
+        <v>3.1375318354399935E-3</v>
+      </c>
+      <c r="H10" s="5">
         <f>IF(ISNUMBER(G10),1000*Parameters!E10*G10^2,"")</f>
-        <v/>
-      </c>
-      <c r="I10" s="5" t="str">
+        <v>17.536246316263107</v>
+      </c>
+      <c r="I10" s="5">
         <f>IF(ISNUMBER(G10),1000*Parameters!E11*G10^2,"")</f>
-        <v/>
-      </c>
-      <c r="J10" s="5" t="str">
+        <v>33.512573529039784</v>
+      </c>
+      <c r="J10" s="5">
         <f>IF(ISNUMBER(G10),1000*Parameters!E12*G10^2,"")</f>
-        <v/>
+        <v>62.820919515601688</v>
       </c>
       <c r="K10" s="13" t="str">
         <f>IF(COUNT(Parameters!C18:D18,Parameters!F27:I27)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E10)),"待填轮行程",IF(E10&lt;=0,"轮行程须大于0",IF(COUNT(L10:M10)&lt;2,"无效半径",""))))</f>
-        <v>待补坐标</v>
-      </c>
-      <c r="L10" s="33" t="str">
+        <v/>
+      </c>
+      <c r="L10" s="33">
         <f>IF(COUNT(Parameters!F27,Parameters!G27,Parameters!C18,Parameters!D18)&lt;4,"",IF(N10=0,"",IF(Parameters!G27&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!F27)*1000/N10))))))</f>
-        <v/>
-      </c>
-      <c r="M10" s="33" t="str">
+        <v>-19.784278704009441</v>
+      </c>
+      <c r="M10" s="33">
         <f>IF(COUNT(Parameters!H27,Parameters!I27,Parameters!C18,Parameters!D18)&lt;4,"",IF(O10=0,"",IF(Parameters!I27&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!H27)*1000/O10))))))</f>
-        <v/>
-      </c>
-      <c r="N10" s="35" t="str">
+        <v>6.6415191380115655</v>
+      </c>
+      <c r="N10" s="35">
         <f>IF(COUNT(Parameters!F27,Parameters!G27,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!F27-Parameters!C18)^2+(Parameters!G27-Parameters!D18)^2))</f>
-        <v/>
-      </c>
-      <c r="O10" s="35" t="str">
+        <v>147.71932845772082</v>
+      </c>
+      <c r="O10" s="35">
         <f>IF(COUNT(Parameters!H27,Parameters!I27,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!H27-Parameters!C18)^2+(Parameters!I27-Parameters!D18)^2))</f>
-        <v/>
+        <v>146.98639392814576</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="26.1" customHeight="1">
@@ -4470,47 +4503,47 @@
       </c>
       <c r="E11" s="8">
         <f>IF(ISNUMBER(Parameters!E28),Parameters!E28,"")</f>
-        <v>166</v>
-      </c>
-      <c r="F11" s="10" t="str">
+        <v>147</v>
+      </c>
+      <c r="F11" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="12" t="str">
+        <v>30.255508954682995</v>
+      </c>
+      <c r="G11" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H11" s="6" t="str">
+        <v>3.5922329804479328E-3</v>
+      </c>
+      <c r="H11" s="6">
         <f>IF(ISNUMBER(G11),1000*Parameters!E10*G11^2,"")</f>
-        <v/>
-      </c>
-      <c r="I11" s="6" t="str">
+        <v>22.987373184334313</v>
+      </c>
+      <c r="I11" s="6">
         <f>IF(ISNUMBER(G11),1000*Parameters!E11*G11^2,"")</f>
-        <v/>
-      </c>
-      <c r="J11" s="6" t="str">
+        <v>43.929927772800724</v>
+      </c>
+      <c r="J11" s="6">
         <f>IF(ISNUMBER(G11),1000*Parameters!E12*G11^2,"")</f>
-        <v/>
+        <v>82.348747539484549</v>
       </c>
       <c r="K11" s="14" t="str">
         <f>IF(COUNT(Parameters!C18:D18,Parameters!F28:I28)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E11)),"待填轮行程",IF(E11&lt;=0,"轮行程须大于0",IF(COUNT(L11:M11)&lt;2,"无效半径",""))))</f>
-        <v>待补坐标</v>
-      </c>
-      <c r="L11" s="34" t="str">
+        <v/>
+      </c>
+      <c r="L11" s="34">
         <f>IF(COUNT(Parameters!F28,Parameters!G28,Parameters!C18,Parameters!D18)&lt;4,"",IF(N11=0,"",IF(Parameters!G28&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!F28)*1000/N11))))))</f>
-        <v/>
-      </c>
-      <c r="M11" s="34" t="str">
+        <v>-22.916902618446723</v>
+      </c>
+      <c r="M11" s="34">
         <f>IF(COUNT(Parameters!H28,Parameters!I28,Parameters!C18,Parameters!D18)&lt;4,"",IF(O11=0,"",IF(Parameters!I28&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!H28)*1000/O11))))))</f>
-        <v/>
-      </c>
-      <c r="N11" s="36" t="str">
+        <v>7.3386063362362677</v>
+      </c>
+      <c r="N11" s="36">
         <f>IF(COUNT(Parameters!F28,Parameters!G28,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!F28-Parameters!C18)^2+(Parameters!G28-Parameters!D18)^2))</f>
-        <v/>
-      </c>
-      <c r="O11" s="36" t="str">
+        <v>133.5402561027947</v>
+      </c>
+      <c r="O11" s="36">
         <f>IF(COUNT(Parameters!H28,Parameters!I28,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!H28-Parameters!C18)^2+(Parameters!I28-Parameters!D18)^2))</f>
-        <v/>
+        <v>133.09019498069733</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="26.1" customHeight="1">
@@ -4519,7 +4552,7 @@
         <v>26</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>51</v>
@@ -4530,23 +4563,23 @@
       </c>
       <c r="F12" s="9">
         <f t="shared" si="0"/>
-        <v>35.033513377592925</v>
+        <v>37.345016544941558</v>
       </c>
       <c r="G12" s="11">
         <f t="shared" si="1"/>
-        <v>2.3608114169130349E-3</v>
+        <v>2.5165772120501429E-3</v>
       </c>
       <c r="H12" s="5">
         <f>IF(ISNUMBER(G12),1000*Parameters!E7*G12^2,"")</f>
-        <v>5.2468630107600935</v>
+        <v>9.0145383497721205</v>
       </c>
       <c r="I12" s="5">
         <f>IF(ISNUMBER(G12),1000*Parameters!E8*G12^2,"")</f>
-        <v>11.07997992589914</v>
+        <v>16.700545198921954</v>
       </c>
       <c r="J12" s="5">
         <f>IF(ISNUMBER(G12),1000*Parameters!E9*G12^2,"")</f>
-        <v>20.394062528804113</v>
+        <v>31.330224796635314</v>
       </c>
       <c r="K12" s="13" t="str">
         <f>IF(COUNT(Parameters!C17:D17,Parameters!F29:I29)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E12)),"待填轮行程",IF(E12&lt;=0,"轮行程须大于0",IF(COUNT(L12:M12)&lt;2,"无效半径",""))))</f>
@@ -4554,19 +4587,19 @@
       </c>
       <c r="L12" s="33">
         <f>IF(COUNT(Parameters!F29,Parameters!G29,Parameters!C17,Parameters!D17)&lt;4,"",IF(N12=0,"",IF(Parameters!G29&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!F29)*1000/N12))))))</f>
-        <v>11.375115357745536</v>
+        <v>-2.0454084888873703</v>
       </c>
       <c r="M12" s="33">
         <f>IF(COUNT(Parameters!H29,Parameters!I29,Parameters!C17,Parameters!D17)&lt;4,"",IF(O12=0,"",IF(Parameters!I29&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!H29)*1000/O12))))))</f>
-        <v>46.408628735338468</v>
+        <v>35.299608056054197</v>
       </c>
       <c r="N12" s="35">
         <f>IF(COUNT(Parameters!F29,Parameters!G29,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!F29-Parameters!C17)^2+(Parameters!G29-Parameters!D17)^2))</f>
-        <v>172.38619434281858</v>
+        <v>168.10710871346274</v>
       </c>
       <c r="O12" s="35">
         <f>IF(COUNT(Parameters!H29,Parameters!I29,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!H29-Parameters!C17)^2+(Parameters!I29-Parameters!D17)^2))</f>
-        <v>172.58621034138272</v>
+        <v>167.86303941010956</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="26.1" customHeight="1">
@@ -4578,7 +4611,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="E13" s="8">
         <f>IF(ISNUMBER(Parameters!E30),Parameters!E30,"")</f>
@@ -4586,23 +4619,23 @@
       </c>
       <c r="F13" s="10">
         <f t="shared" si="0"/>
-        <v>35.883582181526236</v>
+        <v>40.502333619444755</v>
       </c>
       <c r="G13" s="12">
         <f t="shared" si="1"/>
-        <v>2.4180951987552218E-3</v>
+        <v>2.7293400633224053E-3</v>
       </c>
       <c r="H13" s="6">
         <f>IF(ISNUMBER(G13),1000*Parameters!E7*G13^2,"")</f>
-        <v>5.504576622925577</v>
+        <v>10.603232186754845</v>
       </c>
       <c r="I13" s="6">
         <f>IF(ISNUMBER(G13),1000*Parameters!E8*G13^2,"")</f>
-        <v>11.624202567803193</v>
+        <v>19.643796666974055</v>
       </c>
       <c r="J13" s="6">
         <f>IF(ISNUMBER(G13),1000*Parameters!E9*G13^2,"")</f>
-        <v>21.395771075463013</v>
+        <v>36.85176490378413</v>
       </c>
       <c r="K13" s="14" t="str">
         <f>IF(COUNT(Parameters!C17:D17,Parameters!F30:I30)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E13)),"待填轮行程",IF(E13&lt;=0,"轮行程须大于0",IF(COUNT(L13:M13)&lt;2,"无效半径",""))))</f>
@@ -4610,19 +4643,19 @@
       </c>
       <c r="L13" s="34">
         <f>IF(COUNT(Parameters!F30,Parameters!G30,Parameters!C17,Parameters!D17)&lt;4,"",IF(N13=0,"",IF(Parameters!G30&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!F30)*1000/N13))))))</f>
-        <v>10.664575517451754</v>
+        <v>-4.92061603636391</v>
       </c>
       <c r="M13" s="34">
         <f>IF(COUNT(Parameters!H30,Parameters!I30,Parameters!C17,Parameters!D17)&lt;4,"",IF(O13=0,"",IF(Parameters!I30&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!H30)*1000/O13))))))</f>
-        <v>46.548157698977988</v>
+        <v>35.581717583080852</v>
       </c>
       <c r="N13" s="36">
         <f>IF(COUNT(Parameters!F30,Parameters!G30,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!F30-Parameters!C17)^2+(Parameters!G30-Parameters!D17)^2))</f>
-        <v>156.7067324654559</v>
+        <v>151.55856953666461</v>
       </c>
       <c r="O13" s="36">
         <f>IF(COUNT(Parameters!H30,Parameters!I30,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!H30-Parameters!C17)^2+(Parameters!I30-Parameters!D17)^2))</f>
-        <v>157.03502793962869</v>
+        <v>151.23822268196622</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="26.1" customHeight="1">
@@ -4642,23 +4675,23 @@
       </c>
       <c r="F14" s="9">
         <f t="shared" si="0"/>
-        <v>37.494384172096488</v>
+        <v>44.103269719941949</v>
       </c>
       <c r="G14" s="11">
         <f t="shared" si="1"/>
-        <v>2.5266426826669186E-3</v>
+        <v>2.9719971718459629E-3</v>
       </c>
       <c r="H14" s="5">
         <f>IF(ISNUMBER(G14),1000*Parameters!E7*G14^2,"")</f>
-        <v>6.0098659998526269</v>
+        <v>12.572445303571339</v>
       </c>
       <c r="I14" s="5">
         <f>IF(ISNUMBER(G14),1000*Parameters!E8*G14^2,"")</f>
-        <v>12.691239412798074</v>
+        <v>23.292007078607082</v>
       </c>
       <c r="J14" s="5">
         <f>IF(ISNUMBER(G14),1000*Parameters!E9*G14^2,"")</f>
-        <v>23.359783310403735</v>
+        <v>43.695808073660181</v>
       </c>
       <c r="K14" s="13" t="str">
         <f>IF(COUNT(Parameters!C17:D17,Parameters!F31:I31)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E14)),"待填轮行程",IF(E14&lt;=0,"轮行程须大于0",IF(COUNT(L14:M14)&lt;2,"无效半径",""))))</f>
@@ -4666,19 +4699,19 @@
       </c>
       <c r="L14" s="33">
         <f>IF(COUNT(Parameters!F31,Parameters!G31,Parameters!C17,Parameters!D17)&lt;4,"",IF(N14=0,"",IF(Parameters!G31&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!F31)*1000/N14))))))</f>
-        <v>8.9305901004189874</v>
+        <v>-9.4623222080256468</v>
       </c>
       <c r="M14" s="33">
         <f>IF(COUNT(Parameters!H31,Parameters!I31,Parameters!C17,Parameters!D17)&lt;4,"",IF(O14=0,"",IF(Parameters!I31&lt;Parameters!D17,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C17-Parameters!H31)*1000/O14))))))</f>
-        <v>46.42497427251547</v>
+        <v>34.640947511916309</v>
       </c>
       <c r="N14" s="35">
         <f>IF(COUNT(Parameters!F31,Parameters!G31,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!F31-Parameters!C17)^2+(Parameters!G31-Parameters!D17)^2))</f>
-        <v>141.71802990445491</v>
+        <v>133.82077566656073</v>
       </c>
       <c r="O14" s="35">
         <f>IF(COUNT(Parameters!H31,Parameters!I31,Parameters!C17,Parameters!D17)&lt;4,"",1000*SQRT((Parameters!H31-Parameters!C17)^2+(Parameters!I31-Parameters!D17)^2))</f>
-        <v>142.17243052012572</v>
+        <v>133.70115930686603</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="26.1" customHeight="1">
@@ -4706,15 +4739,15 @@
       </c>
       <c r="H15" s="6">
         <f>IF(ISNUMBER(G15),1000*Parameters!E10*G15^2,"")</f>
-        <v>11.08545128513005</v>
+        <v>13.838466461259268</v>
       </c>
       <c r="I15" s="6">
         <f>IF(ISNUMBER(G15),1000*Parameters!E11*G15^2,"")</f>
-        <v>22.798183207336258</v>
+        <v>26.445946096343832</v>
       </c>
       <c r="J15" s="6">
         <f>IF(ISNUMBER(G15),1000*Parameters!E12*G15^2,"")</f>
-        <v>38.393916352197742</v>
+        <v>49.574188917265118</v>
       </c>
       <c r="K15" s="14" t="str">
         <f>IF(COUNT(Parameters!C18:D18,Parameters!F32:I32)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E15)),"待填轮行程",IF(E15&lt;=0,"轮行程须大于0",IF(COUNT(L15:M15)&lt;2,"无效半径",""))))</f>
@@ -4754,23 +4787,23 @@
       </c>
       <c r="F16" s="9">
         <f t="shared" si="0"/>
-        <v>44.707366896981739</v>
+        <v>44.410812844298391</v>
       </c>
       <c r="G16" s="11">
         <f t="shared" si="1"/>
-        <v>3.0963918740057614E-3</v>
+        <v>3.0758528080158517E-3</v>
       </c>
       <c r="H16" s="5">
         <f>IF(ISNUMBER(G16),1000*Parameters!E10*G16^2,"")</f>
-        <v>13.681622555635043</v>
+        <v>16.853552276273707</v>
       </c>
       <c r="I16" s="5">
         <f>IF(ISNUMBER(G16),1000*Parameters!E11*G16^2,"")</f>
-        <v>28.137432529733275</v>
+        <v>32.207913808802836</v>
       </c>
       <c r="J16" s="5">
         <f>IF(ISNUMBER(G16),1000*Parameters!E12*G16^2,"")</f>
-        <v>47.385628104109358</v>
+        <v>60.375272564339298</v>
       </c>
       <c r="K16" s="13" t="str">
         <f>IF(COUNT(Parameters!C18:D18,Parameters!F33:I33)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E16)),"待填轮行程",IF(E16&lt;=0,"轮行程须大于0",IF(COUNT(L16:M16)&lt;2,"无效半径",""))))</f>
@@ -4778,19 +4811,19 @@
       </c>
       <c r="L16" s="33">
         <f>IF(COUNT(Parameters!F33,Parameters!G33,Parameters!C18,Parameters!D18)&lt;4,"",IF(N16=0,"",IF(Parameters!G33&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!F33)*1000/N16))))))</f>
-        <v>-20.784861013968488</v>
+        <v>-20.646990824970345</v>
       </c>
       <c r="M16" s="33">
         <f>IF(COUNT(Parameters!H33,Parameters!I33,Parameters!C18,Parameters!D18)&lt;4,"",IF(O16=0,"",IF(Parameters!I33&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!H33)*1000/O16))))))</f>
-        <v>23.922505883013255</v>
+        <v>23.76382201932806</v>
       </c>
       <c r="N16" s="35">
         <f>IF(COUNT(Parameters!F33,Parameters!G33,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!F33-Parameters!C18)^2+(Parameters!G33-Parameters!D18)^2))</f>
-        <v>146.53668482670133</v>
+        <v>147.47203124660632</v>
       </c>
       <c r="O16" s="35">
         <f>IF(COUNT(Parameters!H33,Parameters!I33,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!H33-Parameters!C18)^2+(Parameters!I33-Parameters!D18)^2))</f>
-        <v>145.49914089093446</v>
+        <v>146.41379716406522</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="26.1" customHeight="1">
@@ -4810,23 +4843,23 @@
       </c>
       <c r="F17" s="10">
         <f t="shared" si="0"/>
-        <v>50.596578839138232</v>
+        <v>49.859651445112775</v>
       </c>
       <c r="G17" s="12">
         <f t="shared" si="1"/>
-        <v>3.504273376935923E-3</v>
+        <v>3.4532344508490741E-3</v>
       </c>
       <c r="H17" s="6">
         <f>IF(ISNUMBER(G17),1000*Parameters!E10*G17^2,"")</f>
-        <v>17.523535202834569</v>
+        <v>21.242835430841463</v>
       </c>
       <c r="I17" s="6">
         <f>IF(ISNUMBER(G17),1000*Parameters!E11*G17^2,"")</f>
-        <v>36.038656047347558</v>
+        <v>40.596035862084598</v>
       </c>
       <c r="J17" s="6">
         <f>IF(ISNUMBER(G17),1000*Parameters!E12*G17^2,"")</f>
-        <v>60.691903961989226</v>
+        <v>76.0992079386142</v>
       </c>
       <c r="K17" s="14" t="str">
         <f>IF(COUNT(Parameters!C18:D18,Parameters!F34:I34)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E17)),"待填轮行程",IF(E17&lt;=0,"轮行程须大于0",IF(COUNT(L17:M17)&lt;2,"无效半径",""))))</f>
@@ -4834,19 +4867,19 @@
       </c>
       <c r="L17" s="34">
         <f>IF(COUNT(Parameters!F34,Parameters!G34,Parameters!C18,Parameters!D18)&lt;4,"",IF(N17=0,"",IF(Parameters!G34&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!F34)*1000/N17))))))</f>
-        <v>-24.22774531795417</v>
+        <v>-23.875280853927489</v>
       </c>
       <c r="M17" s="34">
         <f>IF(COUNT(Parameters!H34,Parameters!I34,Parameters!C18,Parameters!D18)&lt;4,"",IF(O17=0,"",IF(Parameters!I34&lt;Parameters!D18,-1,1)*DEGREES(ACOS(MAX(-1,MIN(1,(Parameters!C18-Parameters!H34)*1000/O17))))))</f>
-        <v>26.368833521184065</v>
+        <v>25.984370591185296</v>
       </c>
       <c r="N17" s="36">
         <f>IF(COUNT(Parameters!F34,Parameters!G34,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!F34-Parameters!C18)^2+(Parameters!G34-Parameters!D18)^2))</f>
-        <v>131.59027319676798</v>
+        <v>133.41664064126343</v>
       </c>
       <c r="O17" s="36">
         <f>IF(COUNT(Parameters!H34,Parameters!I34,Parameters!C18,Parameters!D18)&lt;4,"",1000*SQRT((Parameters!H34-Parameters!C18)^2+(Parameters!I34-Parameters!D18)^2))</f>
-        <v>130.58713566044705</v>
+        <v>132.38202294873727</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="26.1" customHeight="1">
@@ -4937,11 +4970,11 @@
       </c>
       <c r="C23" s="6">
         <f>IF(ISNUMBER(H12),H12,NA())</f>
-        <v>5.2468630107600935</v>
+        <v>9.0145383497721205</v>
       </c>
       <c r="D23" s="6">
         <f>IF(ISNUMBER(H15),H15,NA())</f>
-        <v>11.08545128513005</v>
+        <v>13.838466461259268</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -4960,11 +4993,11 @@
       </c>
       <c r="C24" s="5">
         <f>IF(ISNUMBER(H13),H13,NA())</f>
-        <v>5.504576622925577</v>
+        <v>10.603232186754845</v>
       </c>
       <c r="D24" s="5">
         <f>IF(ISNUMBER(H16),H16,NA())</f>
-        <v>13.681622555635043</v>
+        <v>16.853552276273707</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
@@ -4983,11 +5016,11 @@
       </c>
       <c r="C25" s="6">
         <f>IF(ISNUMBER(H14),H14,NA())</f>
-        <v>6.0098659998526269</v>
+        <v>12.572445303571339</v>
       </c>
       <c r="D25" s="6">
         <f>IF(ISNUMBER(H17),H17,NA())</f>
-        <v>17.523535202834569</v>
+        <v>21.242835430841463</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -5006,11 +5039,11 @@
       </c>
       <c r="C26" s="5">
         <f>IF(ISNUMBER(I12),I12,NA())</f>
-        <v>11.07997992589914</v>
+        <v>16.700545198921954</v>
       </c>
       <c r="D26" s="5">
         <f>IF(ISNUMBER(I15),I15,NA())</f>
-        <v>22.798183207336258</v>
+        <v>26.445946096343832</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
@@ -5029,11 +5062,11 @@
       </c>
       <c r="C27" s="6">
         <f>IF(ISNUMBER(I13),I13,NA())</f>
-        <v>11.624202567803193</v>
+        <v>19.643796666974055</v>
       </c>
       <c r="D27" s="6">
         <f>IF(ISNUMBER(I16),I16,NA())</f>
-        <v>28.137432529733275</v>
+        <v>32.207913808802836</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -5052,11 +5085,11 @@
       </c>
       <c r="C28" s="5">
         <f>IF(ISNUMBER(I14),I14,NA())</f>
-        <v>12.691239412798074</v>
+        <v>23.292007078607082</v>
       </c>
       <c r="D28" s="5">
         <f>IF(ISNUMBER(I17),I17,NA())</f>
-        <v>36.038656047347558</v>
+        <v>40.596035862084598</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
@@ -5075,11 +5108,11 @@
       </c>
       <c r="C29" s="6">
         <f>IF(ISNUMBER(J12),J12,NA())</f>
-        <v>20.394062528804113</v>
+        <v>31.330224796635314</v>
       </c>
       <c r="D29" s="6">
         <f>IF(ISNUMBER(J15),J15,NA())</f>
-        <v>38.393916352197742</v>
+        <v>49.574188917265118</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
@@ -5098,11 +5131,11 @@
       </c>
       <c r="C30" s="5">
         <f>IF(ISNUMBER(J13),J13,NA())</f>
-        <v>21.395771075463013</v>
+        <v>36.85176490378413</v>
       </c>
       <c r="D30" s="5">
         <f>IF(ISNUMBER(J16),J16,NA())</f>
-        <v>47.385628104109358</v>
+        <v>60.375272564339298</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -5121,11 +5154,11 @@
       </c>
       <c r="C31" s="6">
         <f>IF(ISNUMBER(J14),J14,NA())</f>
-        <v>23.359783310403735</v>
+        <v>43.695808073660181</v>
       </c>
       <c r="D31" s="6">
         <f>IF(ISNUMBER(J17),J17,NA())</f>
-        <v>60.691903961989226</v>
+        <v>76.0992079386142</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -5208,13 +5241,13 @@
       <c r="B36" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C36" s="5" t="e">
+      <c r="C36" s="5">
         <f>IF(ISNUMBER(H6),H6,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D36" s="5" t="e">
+        <v>8.3256960949803513</v>
+      </c>
+      <c r="D36" s="5">
         <f>IF(ISNUMBER(H9),H9,NA())</f>
-        <v>#N/A</v>
+        <v>14.102664166988719</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
@@ -5231,13 +5264,13 @@
       <c r="B37" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C37" s="6" t="e">
+      <c r="C37" s="6">
         <f>IF(ISNUMBER(H7),H7,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D37" s="6" t="e">
+        <v>10.192545394173928</v>
+      </c>
+      <c r="D37" s="6">
         <f>IF(ISNUMBER(H10),H10,NA())</f>
-        <v>#N/A</v>
+        <v>17.536246316263107</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
@@ -5254,13 +5287,13 @@
       <c r="B38" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C38" s="5" t="e">
+      <c r="C38" s="5">
         <f>IF(ISNUMBER(H8),H8,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D38" s="5" t="e">
+        <v>13.650114740317481</v>
+      </c>
+      <c r="D38" s="5">
         <f>IF(ISNUMBER(H11),H11,NA())</f>
-        <v>#N/A</v>
+        <v>22.987373184334313</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
@@ -5277,13 +5310,13 @@
       <c r="B39" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C39" s="6" t="e">
+      <c r="C39" s="6">
         <f>IF(ISNUMBER(I6),I6,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D39" s="6" t="e">
+        <v>15.424379879666526</v>
+      </c>
+      <c r="D39" s="6">
         <f>IF(ISNUMBER(I9),I9,NA())</f>
-        <v>#N/A</v>
+        <v>26.950840067367189</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
@@ -5300,13 +5333,13 @@
       <c r="B40" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="5" t="e">
+      <c r="C40" s="5">
         <f>IF(ISNUMBER(I7),I7,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D40" s="5" t="e">
+        <v>18.882948681644748</v>
+      </c>
+      <c r="D40" s="5">
         <f>IF(ISNUMBER(I10),I10,NA())</f>
-        <v>#N/A</v>
+        <v>33.512573529039784</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
@@ -5323,13 +5356,13 @@
       <c r="B41" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="6" t="e">
+      <c r="C41" s="6">
         <f>IF(ISNUMBER(I8),I8,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D41" s="6" t="e">
+        <v>25.28852275578878</v>
+      </c>
+      <c r="D41" s="6">
         <f>IF(ISNUMBER(I11),I11,NA())</f>
-        <v>#N/A</v>
+        <v>43.929927772800724</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
@@ -5346,13 +5379,13 @@
       <c r="B42" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C42" s="5" t="e">
+      <c r="C42" s="5">
         <f>IF(ISNUMBER(J6),J6,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D42" s="5" t="e">
+        <v>28.936138504618729</v>
+      </c>
+      <c r="D42" s="5">
         <f>IF(ISNUMBER(J9),J9,NA())</f>
-        <v>#N/A</v>
+        <v>50.520636777799808</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
@@ -5369,13 +5402,13 @@
       <c r="B43" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C43" s="6" t="e">
+      <c r="C43" s="6">
         <f>IF(ISNUMBER(J7),J7,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D43" s="6" t="e">
+        <v>35.424413992032278</v>
+      </c>
+      <c r="D43" s="6">
         <f>IF(ISNUMBER(J10),J10,NA())</f>
-        <v>#N/A</v>
+        <v>62.820919515601688</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
@@ -5392,13 +5425,13 @@
       <c r="B44" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C44" s="5" t="e">
+      <c r="C44" s="5">
         <f>IF(ISNUMBER(J8),J8,NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D44" s="5" t="e">
+        <v>47.441271723562288</v>
+      </c>
+      <c r="D44" s="5">
         <f>IF(ISNUMBER(J11),J11,NA())</f>
-        <v>#N/A</v>
+        <v>82.348747539484549</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -5472,13 +5505,13 @@
     </row>
     <row r="49" spans="1:13" ht="26.1" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="44" t="s">
+      <c r="B49" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="C49" s="44" t="s">
+      <c r="C49" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="D49" s="44" t="s">
+      <c r="D49" s="43" t="s">
         <v>35</v>
       </c>
       <c r="E49" s="1"/>
@@ -6210,7 +6243,7 @@
     <mergeCell ref="B2:K3"/>
     <mergeCell ref="B49:D49"/>
   </mergeCells>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/arb_stiffness.xlsx
+++ b/docs/arb_stiffness.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B39674A-0F99-4379-9495-B7ACE30517CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comparison" sheetId="1" r:id="rId1"/>
@@ -260,11 +260,11 @@
   </si>
   <si>
     <t>Front</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>M</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -277,7 +277,7 @@
     <numFmt numFmtId="178" formatCode="0.000"/>
     <numFmt numFmtId="179" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -287,20 +287,6 @@
       <color rgb="FF283C50"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF667B91"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF667B91"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -556,22 +542,22 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -604,97 +590,91 @@
     <xf numFmtId="179" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="7" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="1" fontId="5" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="1" fontId="5" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="5" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="176" fontId="5" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="18" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="16" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="14" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="16" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="14" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="20" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="16" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="14" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="16" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="14" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2642,7 +2622,7 @@
     <mergeCell ref="B5:N5"/>
     <mergeCell ref="B49:N49"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2682,56 +2662,56 @@
     </row>
     <row r="2" spans="1:10" ht="27" customHeight="1">
       <c r="A2" s="15"/>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="38" t="s">
+      <c r="F2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="38" t="s">
+      <c r="G2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="38" t="s">
+      <c r="H2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="38" t="s">
+      <c r="I2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10" ht="27" customHeight="1">
       <c r="A3" s="15"/>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="38" t="s">
+      <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="38" t="s">
+      <c r="F3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="38" t="s">
+      <c r="G3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="38" t="s">
+      <c r="H3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="38" t="s">
+      <c r="I3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="J3" s="15"/>
@@ -2741,25 +2721,25 @@
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="39" t="s">
+      <c r="F4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="39" t="s">
+      <c r="G4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="39" t="s">
+      <c r="H4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="39" t="s">
+      <c r="I4" s="37" t="s">
         <v>4</v>
       </c>
       <c r="J4" s="15"/>
@@ -2935,56 +2915,56 @@
     </row>
     <row r="14" spans="1:10" ht="27" customHeight="1">
       <c r="A14" s="15"/>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="40" t="s">
+      <c r="D14" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="40" t="s">
+      <c r="E14" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="40" t="s">
+      <c r="F14" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="40" t="s">
+      <c r="G14" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="40" t="s">
+      <c r="H14" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="I14" s="40" t="s">
+      <c r="I14" s="38" t="s">
         <v>11</v>
       </c>
       <c r="J14" s="15"/>
     </row>
     <row r="15" spans="1:10" ht="27" customHeight="1">
       <c r="A15" s="15"/>
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="41" t="s">
+      <c r="C15" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="41" t="s">
+      <c r="D15" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="41" t="s">
+      <c r="E15" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="41" t="s">
+      <c r="F15" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="41" t="s">
+      <c r="G15" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="H15" s="41" t="s">
+      <c r="H15" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="41" t="s">
+      <c r="I15" s="39" t="s">
         <v>12</v>
       </c>
       <c r="J15" s="15"/>
@@ -3042,44 +3022,44 @@
     </row>
     <row r="20" spans="1:14" ht="27" customHeight="1">
       <c r="A20" s="15"/>
-      <c r="B20" s="40" t="s">
+      <c r="B20" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="40" t="s">
+      <c r="C20" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="40" t="s">
+      <c r="D20" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="40" t="s">
+      <c r="E20" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="40" t="s">
+      <c r="F20" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="G20" s="40" t="s">
+      <c r="G20" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H20" s="40" t="s">
+      <c r="H20" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="I20" s="40" t="s">
+      <c r="I20" s="38" t="s">
         <v>18</v>
       </c>
       <c r="J20" s="15"/>
     </row>
     <row r="21" spans="1:14" ht="27" customHeight="1">
       <c r="A21" s="15"/>
-      <c r="B21" s="42" t="s">
+      <c r="B21" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="42"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
       <c r="J21" s="15"/>
     </row>
     <row r="22" spans="1:14" ht="42" customHeight="1">
@@ -3494,28 +3474,28 @@
     </row>
     <row r="38" spans="1:14" ht="27" customHeight="1">
       <c r="A38" s="15"/>
-      <c r="B38" s="37" t="s">
+      <c r="B38" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="37" t="s">
+      <c r="C38" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D38" s="37" t="s">
+      <c r="D38" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E38" s="37" t="s">
+      <c r="E38" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F38" s="37" t="s">
+      <c r="F38" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G38" s="37" t="s">
+      <c r="G38" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H38" s="37" t="s">
+      <c r="H38" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I38" s="37" t="s">
+      <c r="I38" s="3" t="s">
         <v>27</v>
       </c>
       <c r="J38" s="15"/>
@@ -4037,7 +4017,7 @@
     <mergeCell ref="B20:I20"/>
     <mergeCell ref="B21:I21"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5505,13 +5485,13 @@
     </row>
     <row r="49" spans="1:13" ht="26.1" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="43" t="s">
+      <c r="B49" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="C49" s="43" t="s">
+      <c r="C49" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="D49" s="43" t="s">
+      <c r="D49" s="41" t="s">
         <v>35</v>
       </c>
       <c r="E49" s="1"/>
@@ -6243,7 +6223,7 @@
     <mergeCell ref="B2:K3"/>
     <mergeCell ref="B49:D49"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/arb_stiffness.xlsx
+++ b/docs/arb_stiffness.xlsx
@@ -542,11 +542,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -632,19 +632,19 @@
     <xf numFmtId="0" fontId="13" fillId="11" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="18" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="18" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -662,7 +662,10 @@
     <xf numFmtId="176" fontId="17" fillId="14" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
@@ -672,9 +675,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1780,65 +1780,65 @@
     </row>
     <row r="4" spans="1:15" ht="26.1" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="O4" s="1"/>
     </row>
     <row r="5" spans="1:15" ht="26.1" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="1" t="str">
+      <c r="B5" s="37" t="str">
         <f>IF(COUNT(Samples!H6:J17)=0,"待补节点坐标；暂无刚度结果。","")</f>
         <v/>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="37"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="26.1" customHeight="1">
@@ -2574,43 +2574,43 @@
     </row>
     <row r="49" spans="1:15" ht="26.1" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="H49" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="I49" s="1" t="s">
+      <c r="I49" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="J49" s="1" t="s">
+      <c r="J49" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="K49" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="L49" s="1" t="s">
+      <c r="L49" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="M49" s="1" t="s">
+      <c r="M49" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="N49" s="1" t="s">
+      <c r="N49" s="37" t="s">
         <v>2</v>
       </c>
       <c r="O49" s="1"/>
@@ -2662,56 +2662,56 @@
     </row>
     <row r="2" spans="1:10" ht="27" customHeight="1">
       <c r="A2" s="15"/>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10" ht="27" customHeight="1">
       <c r="A3" s="15"/>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="J3" s="15"/>
@@ -2721,25 +2721,25 @@
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="37" t="s">
+      <c r="E4" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="37" t="s">
+      <c r="F4" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="37" t="s">
+      <c r="G4" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="37" t="s">
+      <c r="H4" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="37" t="s">
+      <c r="I4" s="38" t="s">
         <v>4</v>
       </c>
       <c r="J4" s="15"/>
@@ -2915,56 +2915,56 @@
     </row>
     <row r="14" spans="1:10" ht="27" customHeight="1">
       <c r="A14" s="15"/>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="38" t="s">
+      <c r="E14" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="38" t="s">
+      <c r="F14" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="38" t="s">
+      <c r="G14" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="38" t="s">
+      <c r="H14" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="I14" s="38" t="s">
+      <c r="I14" s="39" t="s">
         <v>11</v>
       </c>
       <c r="J14" s="15"/>
     </row>
     <row r="15" spans="1:10" ht="27" customHeight="1">
       <c r="A15" s="15"/>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="39" t="s">
+      <c r="E15" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="39" t="s">
+      <c r="F15" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="39" t="s">
+      <c r="G15" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="H15" s="39" t="s">
+      <c r="H15" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="39" t="s">
+      <c r="I15" s="40" t="s">
         <v>12</v>
       </c>
       <c r="J15" s="15"/>
@@ -3022,44 +3022,44 @@
     </row>
     <row r="20" spans="1:14" ht="27" customHeight="1">
       <c r="A20" s="15"/>
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="D20" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="38" t="s">
+      <c r="E20" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="38" t="s">
+      <c r="F20" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="G20" s="38" t="s">
+      <c r="G20" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="H20" s="38" t="s">
+      <c r="H20" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="I20" s="38" t="s">
+      <c r="I20" s="39" t="s">
         <v>18</v>
       </c>
       <c r="J20" s="15"/>
     </row>
     <row r="21" spans="1:14" ht="27" customHeight="1">
       <c r="A21" s="15"/>
-      <c r="B21" s="40" t="s">
+      <c r="B21" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="40"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41"/>
       <c r="J21" s="15"/>
     </row>
     <row r="22" spans="1:14" ht="42" customHeight="1">
@@ -5485,13 +5485,13 @@
     </row>
     <row r="49" spans="1:13" ht="26.1" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="41" t="s">
+      <c r="B49" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C49" s="41" t="s">
+      <c r="C49" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D49" s="41" t="s">
+      <c r="D49" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E49" s="1"/>

--- a/docs/arb_stiffness.xlsx
+++ b/docs/arb_stiffness.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\UserSpace\Games\Steam_Library\common\BeamNG_Userdata\current\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B39674A-0F99-4379-9495-B7ACE30517CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F7043D-D7E2-42C5-B526-2B87F246579A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -260,11 +260,11 @@
   </si>
   <si>
     <t>Front</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>M</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -277,7 +277,7 @@
     <numFmt numFmtId="178" formatCode="0.000"/>
     <numFmt numFmtId="179" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -294,14 +294,6 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF667B91"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -400,7 +392,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -420,11 +412,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF5F7FA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDF2F7"/>
       </patternFill>
     </fill>
     <fill>
@@ -542,17 +529,17 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -590,91 +577,88 @@
     <xf numFmtId="179" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="7" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="7" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="177" fontId="17" fillId="14" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="14" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="13" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="16" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="16" fillId="13" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="18" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="18" fillId="15" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="16" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="14" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="16" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="14" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -781,31 +765,31 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>9.0145383497721205</c:v>
+                  <c:v>8.6385052748859135</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10.603232186754845</c:v>
+                  <c:v>10.160928227504549</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12.572445303571339</c:v>
+                  <c:v>12.047997452455359</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>16.700545198921954</c:v>
+                  <c:v>16.003897503858848</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>19.643796666974055</c:v>
+                  <c:v>18.824373977035812</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>23.292007078607082</c:v>
+                  <c:v>22.320402687766435</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>31.330224796635314</c:v>
+                  <c:v>30.023313637124545</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>36.85176490378413</c:v>
+                  <c:v>35.314527839159076</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>43.695808073660181</c:v>
+                  <c:v>41.87307811988596</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -870,31 +854,31 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>13.838466461259268</c:v>
+                  <c:v>13.261207716193466</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16.853552276273707</c:v>
+                  <c:v>16.15052203342573</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>21.242835430841463</c:v>
+                  <c:v>20.35671032754508</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>26.445946096343832</c:v>
+                  <c:v>25.342778075639309</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>32.207913808802836</c:v>
+                  <c:v>30.864390669262328</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>40.596035862084598</c:v>
+                  <c:v>38.902610020283568</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>49.574188917265118</c:v>
+                  <c:v>47.50624777926771</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>60.375272564339298</c:v>
+                  <c:v>57.856774277620552</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>76.0992079386142</c:v>
+                  <c:v>72.924800326461153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1130,31 +1114,31 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>8.3256960949803513</c:v>
+                  <c:v>7.9783974334529209</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10.192545394173928</c:v>
+                  <c:v>9.7673728521340628</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>13.650114740317481</c:v>
+                  <c:v>13.080712911938672</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>15.424379879666526</c:v>
+                  <c:v>14.780966232808993</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>18.882948681644748</c:v>
+                  <c:v>18.095264057078605</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>25.28852275578878</c:v>
+                  <c:v>24.233635572195013</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>28.936138504618729</c:v>
+                  <c:v>27.729094425927766</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>35.424413992032278</c:v>
+                  <c:v>33.946717541852699</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>47.441271723562288</c:v>
+                  <c:v>45.462303240592291</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1219,31 +1203,31 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>14.102664166988719</c:v>
+                  <c:v>13.514384660591768</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>17.536246316263107</c:v>
+                  <c:v>16.804738127112959</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>22.987373184334313</c:v>
+                  <c:v>22.02847631278453</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>26.950840067367189</c:v>
+                  <c:v>25.826610864708716</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>33.512573529039784</c:v>
+                  <c:v>32.114627723884531</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>43.929927772800724</c:v>
+                  <c:v>42.097431733738119</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>50.520636777799808</c:v>
+                  <c:v>48.413215448426278</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>62.820919515601688</c:v>
+                  <c:v>60.200403343164751</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>82.348747539484549</c:v>
+                  <c:v>78.913646201091169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1823,22 +1807,22 @@
     </row>
     <row r="5" spans="1:15" ht="26.1" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="37" t="str">
+      <c r="B5" s="1" t="str">
         <f>IF(COUNT(Samples!H6:J17)=0,"待补节点坐标；暂无刚度结果。","")</f>
         <v/>
       </c>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="37"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="26.1" customHeight="1">
@@ -2574,43 +2558,43 @@
     </row>
     <row r="49" spans="1:15" ht="26.1" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="37" t="s">
+      <c r="B49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C49" s="37" t="s">
+      <c r="C49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D49" s="37" t="s">
+      <c r="D49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E49" s="37" t="s">
+      <c r="E49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F49" s="37" t="s">
+      <c r="F49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G49" s="37" t="s">
+      <c r="G49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H49" s="37" t="s">
+      <c r="H49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I49" s="37" t="s">
+      <c r="I49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J49" s="37" t="s">
+      <c r="J49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K49" s="37" t="s">
+      <c r="K49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L49" s="37" t="s">
+      <c r="L49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M49" s="37" t="s">
+      <c r="M49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="N49" s="37" t="s">
+      <c r="N49" s="1" t="s">
         <v>2</v>
       </c>
       <c r="O49" s="1"/>
@@ -2622,7 +2606,7 @@
     <mergeCell ref="B5:N5"/>
     <mergeCell ref="B49:N49"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2721,25 +2705,25 @@
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="38" t="s">
+      <c r="E4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="38" t="s">
+      <c r="F4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="38" t="s">
+      <c r="G4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="38" t="s">
+      <c r="H4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="38" t="s">
+      <c r="I4" s="37" t="s">
         <v>4</v>
       </c>
       <c r="J4" s="15"/>
@@ -2789,7 +2773,7 @@
       </c>
       <c r="E7" s="21">
         <f>$E$8*(D7/$D$8)^4</f>
-        <v>1423.3869221157856</v>
+        <v>1364.0116618075808</v>
       </c>
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
@@ -2809,7 +2793,7 @@
         <v>18.2</v>
       </c>
       <c r="E8" s="20">
-        <v>2637</v>
+        <v>2527</v>
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
@@ -2830,7 +2814,7 @@
       </c>
       <c r="E9" s="21">
         <f>$E$8*(D9/$D$8)^4</f>
-        <v>4947.0123163440448</v>
+        <v>4740.6523031480474</v>
       </c>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
@@ -2851,7 +2835,7 @@
       </c>
       <c r="E10" s="22">
         <f>$E$8*(D10/$D$8)^4</f>
-        <v>1781.3955155995275</v>
+        <v>1707.0862601137678</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
@@ -2872,7 +2856,7 @@
       </c>
       <c r="E11" s="21">
         <f>$E$8*(D11/$D$8)^4</f>
-        <v>3404.3287898771091</v>
+        <v>3262.3203837768124</v>
       </c>
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
@@ -2893,7 +2877,7 @@
       </c>
       <c r="E12" s="22">
         <f>$E$8*(D12/$D$8)^4</f>
-        <v>6381.5768946600283</v>
+        <v>6115.3753556336333</v>
       </c>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
@@ -2915,56 +2899,56 @@
     </row>
     <row r="14" spans="1:10" ht="27" customHeight="1">
       <c r="A14" s="15"/>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="39" t="s">
+      <c r="E14" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="39" t="s">
+      <c r="F14" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="39" t="s">
+      <c r="G14" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="39" t="s">
+      <c r="H14" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="I14" s="39" t="s">
+      <c r="I14" s="38" t="s">
         <v>11</v>
       </c>
       <c r="J14" s="15"/>
     </row>
     <row r="15" spans="1:10" ht="27" customHeight="1">
       <c r="A15" s="15"/>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="40" t="s">
+      <c r="D15" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="40" t="s">
+      <c r="E15" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="40" t="s">
+      <c r="F15" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="40" t="s">
+      <c r="G15" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="H15" s="40" t="s">
+      <c r="H15" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="40" t="s">
+      <c r="I15" s="39" t="s">
         <v>12</v>
       </c>
       <c r="J15" s="15"/>
@@ -3022,44 +3006,44 @@
     </row>
     <row r="20" spans="1:14" ht="27" customHeight="1">
       <c r="A20" s="15"/>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="39" t="s">
+      <c r="C20" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="39" t="s">
+      <c r="D20" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="39" t="s">
+      <c r="E20" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="39" t="s">
+      <c r="F20" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="G20" s="39" t="s">
+      <c r="G20" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H20" s="39" t="s">
+      <c r="H20" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="I20" s="39" t="s">
+      <c r="I20" s="38" t="s">
         <v>18</v>
       </c>
       <c r="J20" s="15"/>
     </row>
     <row r="21" spans="1:14" ht="27" customHeight="1">
       <c r="A21" s="15"/>
-      <c r="B21" s="41" t="s">
+      <c r="B21" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="41"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
       <c r="J21" s="15"/>
     </row>
     <row r="22" spans="1:14" ht="42" customHeight="1">
@@ -4017,7 +4001,7 @@
     <mergeCell ref="B20:I20"/>
     <mergeCell ref="B21:I21"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4215,15 +4199,15 @@
       </c>
       <c r="H6" s="5">
         <f>IF(ISNUMBER(G6),1000*Parameters!E7*G6^2,"")</f>
-        <v>8.3256960949803513</v>
+        <v>7.9783974334529209</v>
       </c>
       <c r="I6" s="5">
         <f>IF(ISNUMBER(G6),1000*Parameters!E8*G6^2,"")</f>
-        <v>15.424379879666526</v>
+        <v>14.780966232808993</v>
       </c>
       <c r="J6" s="5">
         <f>IF(ISNUMBER(G6),1000*Parameters!E9*G6^2,"")</f>
-        <v>28.936138504618729</v>
+        <v>27.729094425927766</v>
       </c>
       <c r="K6" s="13" t="str">
         <f>IF(COUNT(Parameters!C17:D17,Parameters!F23:I23)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E6)),"待填轮行程",IF(E6&lt;=0,"轮行程须大于0",IF(COUNT(L6:M6)&lt;2,"无效半径",""))))</f>
@@ -4271,15 +4255,15 @@
       </c>
       <c r="H7" s="6">
         <f>IF(ISNUMBER(G7),1000*Parameters!E7*G7^2,"")</f>
-        <v>10.192545394173928</v>
+        <v>9.7673728521340628</v>
       </c>
       <c r="I7" s="6">
         <f>IF(ISNUMBER(G7),1000*Parameters!E8*G7^2,"")</f>
-        <v>18.882948681644748</v>
+        <v>18.095264057078605</v>
       </c>
       <c r="J7" s="6">
         <f>IF(ISNUMBER(G7),1000*Parameters!E9*G7^2,"")</f>
-        <v>35.424413992032278</v>
+        <v>33.946717541852699</v>
       </c>
       <c r="K7" s="14" t="str">
         <f>IF(COUNT(Parameters!C17:D17,Parameters!F24:I24)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E7)),"待填轮行程",IF(E7&lt;=0,"轮行程须大于0",IF(COUNT(L7:M7)&lt;2,"无效半径",""))))</f>
@@ -4327,15 +4311,15 @@
       </c>
       <c r="H8" s="5">
         <f>IF(ISNUMBER(G8),1000*Parameters!E7*G8^2,"")</f>
-        <v>13.650114740317481</v>
+        <v>13.080712911938672</v>
       </c>
       <c r="I8" s="5">
         <f>IF(ISNUMBER(G8),1000*Parameters!E8*G8^2,"")</f>
-        <v>25.28852275578878</v>
+        <v>24.233635572195013</v>
       </c>
       <c r="J8" s="5">
         <f>IF(ISNUMBER(G8),1000*Parameters!E9*G8^2,"")</f>
-        <v>47.441271723562288</v>
+        <v>45.462303240592291</v>
       </c>
       <c r="K8" s="13" t="str">
         <f>IF(COUNT(Parameters!C17:D17,Parameters!F25:I25)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E8)),"待填轮行程",IF(E8&lt;=0,"轮行程须大于0",IF(COUNT(L8:M8)&lt;2,"无效半径",""))))</f>
@@ -4383,15 +4367,15 @@
       </c>
       <c r="H9" s="6">
         <f>IF(ISNUMBER(G9),1000*Parameters!E10*G9^2,"")</f>
-        <v>14.102664166988719</v>
+        <v>13.514384660591768</v>
       </c>
       <c r="I9" s="6">
         <f>IF(ISNUMBER(G9),1000*Parameters!E11*G9^2,"")</f>
-        <v>26.950840067367189</v>
+        <v>25.826610864708716</v>
       </c>
       <c r="J9" s="6">
         <f>IF(ISNUMBER(G9),1000*Parameters!E12*G9^2,"")</f>
-        <v>50.520636777799808</v>
+        <v>48.413215448426278</v>
       </c>
       <c r="K9" s="14" t="str">
         <f>IF(COUNT(Parameters!C18:D18,Parameters!F26:I26)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E9)),"待填轮行程",IF(E9&lt;=0,"轮行程须大于0",IF(COUNT(L9:M9)&lt;2,"无效半径",""))))</f>
@@ -4439,15 +4423,15 @@
       </c>
       <c r="H10" s="5">
         <f>IF(ISNUMBER(G10),1000*Parameters!E10*G10^2,"")</f>
-        <v>17.536246316263107</v>
+        <v>16.804738127112959</v>
       </c>
       <c r="I10" s="5">
         <f>IF(ISNUMBER(G10),1000*Parameters!E11*G10^2,"")</f>
-        <v>33.512573529039784</v>
+        <v>32.114627723884531</v>
       </c>
       <c r="J10" s="5">
         <f>IF(ISNUMBER(G10),1000*Parameters!E12*G10^2,"")</f>
-        <v>62.820919515601688</v>
+        <v>60.200403343164751</v>
       </c>
       <c r="K10" s="13" t="str">
         <f>IF(COUNT(Parameters!C18:D18,Parameters!F27:I27)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E10)),"待填轮行程",IF(E10&lt;=0,"轮行程须大于0",IF(COUNT(L10:M10)&lt;2,"无效半径",""))))</f>
@@ -4495,15 +4479,15 @@
       </c>
       <c r="H11" s="6">
         <f>IF(ISNUMBER(G11),1000*Parameters!E10*G11^2,"")</f>
-        <v>22.987373184334313</v>
+        <v>22.02847631278453</v>
       </c>
       <c r="I11" s="6">
         <f>IF(ISNUMBER(G11),1000*Parameters!E11*G11^2,"")</f>
-        <v>43.929927772800724</v>
+        <v>42.097431733738119</v>
       </c>
       <c r="J11" s="6">
         <f>IF(ISNUMBER(G11),1000*Parameters!E12*G11^2,"")</f>
-        <v>82.348747539484549</v>
+        <v>78.913646201091169</v>
       </c>
       <c r="K11" s="14" t="str">
         <f>IF(COUNT(Parameters!C18:D18,Parameters!F28:I28)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E11)),"待填轮行程",IF(E11&lt;=0,"轮行程须大于0",IF(COUNT(L11:M11)&lt;2,"无效半径",""))))</f>
@@ -4551,15 +4535,15 @@
       </c>
       <c r="H12" s="5">
         <f>IF(ISNUMBER(G12),1000*Parameters!E7*G12^2,"")</f>
-        <v>9.0145383497721205</v>
+        <v>8.6385052748859135</v>
       </c>
       <c r="I12" s="5">
         <f>IF(ISNUMBER(G12),1000*Parameters!E8*G12^2,"")</f>
-        <v>16.700545198921954</v>
+        <v>16.003897503858848</v>
       </c>
       <c r="J12" s="5">
         <f>IF(ISNUMBER(G12),1000*Parameters!E9*G12^2,"")</f>
-        <v>31.330224796635314</v>
+        <v>30.023313637124545</v>
       </c>
       <c r="K12" s="13" t="str">
         <f>IF(COUNT(Parameters!C17:D17,Parameters!F29:I29)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E12)),"待填轮行程",IF(E12&lt;=0,"轮行程须大于0",IF(COUNT(L12:M12)&lt;2,"无效半径",""))))</f>
@@ -4607,15 +4591,15 @@
       </c>
       <c r="H13" s="6">
         <f>IF(ISNUMBER(G13),1000*Parameters!E7*G13^2,"")</f>
-        <v>10.603232186754845</v>
+        <v>10.160928227504549</v>
       </c>
       <c r="I13" s="6">
         <f>IF(ISNUMBER(G13),1000*Parameters!E8*G13^2,"")</f>
-        <v>19.643796666974055</v>
+        <v>18.824373977035812</v>
       </c>
       <c r="J13" s="6">
         <f>IF(ISNUMBER(G13),1000*Parameters!E9*G13^2,"")</f>
-        <v>36.85176490378413</v>
+        <v>35.314527839159076</v>
       </c>
       <c r="K13" s="14" t="str">
         <f>IF(COUNT(Parameters!C17:D17,Parameters!F30:I30)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E13)),"待填轮行程",IF(E13&lt;=0,"轮行程须大于0",IF(COUNT(L13:M13)&lt;2,"无效半径",""))))</f>
@@ -4663,15 +4647,15 @@
       </c>
       <c r="H14" s="5">
         <f>IF(ISNUMBER(G14),1000*Parameters!E7*G14^2,"")</f>
-        <v>12.572445303571339</v>
+        <v>12.047997452455359</v>
       </c>
       <c r="I14" s="5">
         <f>IF(ISNUMBER(G14),1000*Parameters!E8*G14^2,"")</f>
-        <v>23.292007078607082</v>
+        <v>22.320402687766435</v>
       </c>
       <c r="J14" s="5">
         <f>IF(ISNUMBER(G14),1000*Parameters!E9*G14^2,"")</f>
-        <v>43.695808073660181</v>
+        <v>41.87307811988596</v>
       </c>
       <c r="K14" s="13" t="str">
         <f>IF(COUNT(Parameters!C17:D17,Parameters!F31:I31)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E14)),"待填轮行程",IF(E14&lt;=0,"轮行程须大于0",IF(COUNT(L14:M14)&lt;2,"无效半径",""))))</f>
@@ -4719,15 +4703,15 @@
       </c>
       <c r="H15" s="6">
         <f>IF(ISNUMBER(G15),1000*Parameters!E10*G15^2,"")</f>
-        <v>13.838466461259268</v>
+        <v>13.261207716193466</v>
       </c>
       <c r="I15" s="6">
         <f>IF(ISNUMBER(G15),1000*Parameters!E11*G15^2,"")</f>
-        <v>26.445946096343832</v>
+        <v>25.342778075639309</v>
       </c>
       <c r="J15" s="6">
         <f>IF(ISNUMBER(G15),1000*Parameters!E12*G15^2,"")</f>
-        <v>49.574188917265118</v>
+        <v>47.50624777926771</v>
       </c>
       <c r="K15" s="14" t="str">
         <f>IF(COUNT(Parameters!C18:D18,Parameters!F32:I32)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E15)),"待填轮行程",IF(E15&lt;=0,"轮行程须大于0",IF(COUNT(L15:M15)&lt;2,"无效半径",""))))</f>
@@ -4775,15 +4759,15 @@
       </c>
       <c r="H16" s="5">
         <f>IF(ISNUMBER(G16),1000*Parameters!E10*G16^2,"")</f>
-        <v>16.853552276273707</v>
+        <v>16.15052203342573</v>
       </c>
       <c r="I16" s="5">
         <f>IF(ISNUMBER(G16),1000*Parameters!E11*G16^2,"")</f>
-        <v>32.207913808802836</v>
+        <v>30.864390669262328</v>
       </c>
       <c r="J16" s="5">
         <f>IF(ISNUMBER(G16),1000*Parameters!E12*G16^2,"")</f>
-        <v>60.375272564339298</v>
+        <v>57.856774277620552</v>
       </c>
       <c r="K16" s="13" t="str">
         <f>IF(COUNT(Parameters!C18:D18,Parameters!F33:I33)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E16)),"待填轮行程",IF(E16&lt;=0,"轮行程须大于0",IF(COUNT(L16:M16)&lt;2,"无效半径",""))))</f>
@@ -4831,15 +4815,15 @@
       </c>
       <c r="H17" s="6">
         <f>IF(ISNUMBER(G17),1000*Parameters!E10*G17^2,"")</f>
-        <v>21.242835430841463</v>
+        <v>20.35671032754508</v>
       </c>
       <c r="I17" s="6">
         <f>IF(ISNUMBER(G17),1000*Parameters!E11*G17^2,"")</f>
-        <v>40.596035862084598</v>
+        <v>38.902610020283568</v>
       </c>
       <c r="J17" s="6">
         <f>IF(ISNUMBER(G17),1000*Parameters!E12*G17^2,"")</f>
-        <v>76.0992079386142</v>
+        <v>72.924800326461153</v>
       </c>
       <c r="K17" s="14" t="str">
         <f>IF(COUNT(Parameters!C18:D18,Parameters!F34:I34)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E17)),"待填轮行程",IF(E17&lt;=0,"轮行程须大于0",IF(COUNT(L17:M17)&lt;2,"无效半径",""))))</f>
@@ -4950,11 +4934,11 @@
       </c>
       <c r="C23" s="6">
         <f>IF(ISNUMBER(H12),H12,NA())</f>
-        <v>9.0145383497721205</v>
+        <v>8.6385052748859135</v>
       </c>
       <c r="D23" s="6">
         <f>IF(ISNUMBER(H15),H15,NA())</f>
-        <v>13.838466461259268</v>
+        <v>13.261207716193466</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -4973,11 +4957,11 @@
       </c>
       <c r="C24" s="5">
         <f>IF(ISNUMBER(H13),H13,NA())</f>
-        <v>10.603232186754845</v>
+        <v>10.160928227504549</v>
       </c>
       <c r="D24" s="5">
         <f>IF(ISNUMBER(H16),H16,NA())</f>
-        <v>16.853552276273707</v>
+        <v>16.15052203342573</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
@@ -4996,11 +4980,11 @@
       </c>
       <c r="C25" s="6">
         <f>IF(ISNUMBER(H14),H14,NA())</f>
-        <v>12.572445303571339</v>
+        <v>12.047997452455359</v>
       </c>
       <c r="D25" s="6">
         <f>IF(ISNUMBER(H17),H17,NA())</f>
-        <v>21.242835430841463</v>
+        <v>20.35671032754508</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -5019,11 +5003,11 @@
       </c>
       <c r="C26" s="5">
         <f>IF(ISNUMBER(I12),I12,NA())</f>
-        <v>16.700545198921954</v>
+        <v>16.003897503858848</v>
       </c>
       <c r="D26" s="5">
         <f>IF(ISNUMBER(I15),I15,NA())</f>
-        <v>26.445946096343832</v>
+        <v>25.342778075639309</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
@@ -5042,11 +5026,11 @@
       </c>
       <c r="C27" s="6">
         <f>IF(ISNUMBER(I13),I13,NA())</f>
-        <v>19.643796666974055</v>
+        <v>18.824373977035812</v>
       </c>
       <c r="D27" s="6">
         <f>IF(ISNUMBER(I16),I16,NA())</f>
-        <v>32.207913808802836</v>
+        <v>30.864390669262328</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -5065,11 +5049,11 @@
       </c>
       <c r="C28" s="5">
         <f>IF(ISNUMBER(I14),I14,NA())</f>
-        <v>23.292007078607082</v>
+        <v>22.320402687766435</v>
       </c>
       <c r="D28" s="5">
         <f>IF(ISNUMBER(I17),I17,NA())</f>
-        <v>40.596035862084598</v>
+        <v>38.902610020283568</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
@@ -5088,11 +5072,11 @@
       </c>
       <c r="C29" s="6">
         <f>IF(ISNUMBER(J12),J12,NA())</f>
-        <v>31.330224796635314</v>
+        <v>30.023313637124545</v>
       </c>
       <c r="D29" s="6">
         <f>IF(ISNUMBER(J15),J15,NA())</f>
-        <v>49.574188917265118</v>
+        <v>47.50624777926771</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
@@ -5111,11 +5095,11 @@
       </c>
       <c r="C30" s="5">
         <f>IF(ISNUMBER(J13),J13,NA())</f>
-        <v>36.85176490378413</v>
+        <v>35.314527839159076</v>
       </c>
       <c r="D30" s="5">
         <f>IF(ISNUMBER(J16),J16,NA())</f>
-        <v>60.375272564339298</v>
+        <v>57.856774277620552</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -5134,11 +5118,11 @@
       </c>
       <c r="C31" s="6">
         <f>IF(ISNUMBER(J14),J14,NA())</f>
-        <v>43.695808073660181</v>
+        <v>41.87307811988596</v>
       </c>
       <c r="D31" s="6">
         <f>IF(ISNUMBER(J17),J17,NA())</f>
-        <v>76.0992079386142</v>
+        <v>72.924800326461153</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -5223,11 +5207,11 @@
       </c>
       <c r="C36" s="5">
         <f>IF(ISNUMBER(H6),H6,NA())</f>
-        <v>8.3256960949803513</v>
+        <v>7.9783974334529209</v>
       </c>
       <c r="D36" s="5">
         <f>IF(ISNUMBER(H9),H9,NA())</f>
-        <v>14.102664166988719</v>
+        <v>13.514384660591768</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
@@ -5246,11 +5230,11 @@
       </c>
       <c r="C37" s="6">
         <f>IF(ISNUMBER(H7),H7,NA())</f>
-        <v>10.192545394173928</v>
+        <v>9.7673728521340628</v>
       </c>
       <c r="D37" s="6">
         <f>IF(ISNUMBER(H10),H10,NA())</f>
-        <v>17.536246316263107</v>
+        <v>16.804738127112959</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
@@ -5269,11 +5253,11 @@
       </c>
       <c r="C38" s="5">
         <f>IF(ISNUMBER(H8),H8,NA())</f>
-        <v>13.650114740317481</v>
+        <v>13.080712911938672</v>
       </c>
       <c r="D38" s="5">
         <f>IF(ISNUMBER(H11),H11,NA())</f>
-        <v>22.987373184334313</v>
+        <v>22.02847631278453</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
@@ -5292,11 +5276,11 @@
       </c>
       <c r="C39" s="6">
         <f>IF(ISNUMBER(I6),I6,NA())</f>
-        <v>15.424379879666526</v>
+        <v>14.780966232808993</v>
       </c>
       <c r="D39" s="6">
         <f>IF(ISNUMBER(I9),I9,NA())</f>
-        <v>26.950840067367189</v>
+        <v>25.826610864708716</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
@@ -5315,11 +5299,11 @@
       </c>
       <c r="C40" s="5">
         <f>IF(ISNUMBER(I7),I7,NA())</f>
-        <v>18.882948681644748</v>
+        <v>18.095264057078605</v>
       </c>
       <c r="D40" s="5">
         <f>IF(ISNUMBER(I10),I10,NA())</f>
-        <v>33.512573529039784</v>
+        <v>32.114627723884531</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
@@ -5338,11 +5322,11 @@
       </c>
       <c r="C41" s="6">
         <f>IF(ISNUMBER(I8),I8,NA())</f>
-        <v>25.28852275578878</v>
+        <v>24.233635572195013</v>
       </c>
       <c r="D41" s="6">
         <f>IF(ISNUMBER(I11),I11,NA())</f>
-        <v>43.929927772800724</v>
+        <v>42.097431733738119</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
@@ -5361,11 +5345,11 @@
       </c>
       <c r="C42" s="5">
         <f>IF(ISNUMBER(J6),J6,NA())</f>
-        <v>28.936138504618729</v>
+        <v>27.729094425927766</v>
       </c>
       <c r="D42" s="5">
         <f>IF(ISNUMBER(J9),J9,NA())</f>
-        <v>50.520636777799808</v>
+        <v>48.413215448426278</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
@@ -5384,11 +5368,11 @@
       </c>
       <c r="C43" s="6">
         <f>IF(ISNUMBER(J7),J7,NA())</f>
-        <v>35.424413992032278</v>
+        <v>33.946717541852699</v>
       </c>
       <c r="D43" s="6">
         <f>IF(ISNUMBER(J10),J10,NA())</f>
-        <v>62.820919515601688</v>
+        <v>60.200403343164751</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
@@ -5407,11 +5391,11 @@
       </c>
       <c r="C44" s="5">
         <f>IF(ISNUMBER(J8),J8,NA())</f>
-        <v>47.441271723562288</v>
+        <v>45.462303240592291</v>
       </c>
       <c r="D44" s="5">
         <f>IF(ISNUMBER(J11),J11,NA())</f>
-        <v>82.348747539484549</v>
+        <v>78.913646201091169</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -6223,7 +6207,7 @@
     <mergeCell ref="B2:K3"/>
     <mergeCell ref="B49:D49"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/arb_stiffness.xlsx
+++ b/docs/arb_stiffness.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\UserSpace\Games\Steam_Library\common\BeamNG_Userdata\current\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F7043D-D7E2-42C5-B526-2B87F246579A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB5A578-E02C-49BD-B82C-4B513DC64073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comparison" sheetId="1" r:id="rId1"/>
@@ -583,16 +583,16 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -601,37 +601,37 @@
     <xf numFmtId="1" fontId="6" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="7" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="7" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="6" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="7" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="7" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="17" fillId="14" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="17" fillId="14" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -649,7 +649,7 @@
     <xf numFmtId="176" fontId="16" fillId="13" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">

--- a/docs/arb_stiffness.xlsx
+++ b/docs/arb_stiffness.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\UserSpace\Games\Steam_Library\common\BeamNG_Userdata\current\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB5A578-E02C-49BD-B82C-4B513DC64073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A03DC9-06E4-4D77-91B4-B1E6675F803D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -529,17 +529,17 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -660,6 +660,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1764,65 +1767,65 @@
     </row>
     <row r="4" spans="1:15" ht="26.1" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="M4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="N4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="O4" s="1"/>
     </row>
     <row r="5" spans="1:15" ht="26.1" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="1" t="str">
+      <c r="B5" s="2" t="str">
         <f>IF(COUNT(Samples!H6:J17)=0,"待补节点坐标；暂无刚度结果。","")</f>
         <v/>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="26.1" customHeight="1">
@@ -2558,43 +2561,43 @@
     </row>
     <row r="49" spans="1:15" ht="26.1" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="H49" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I49" s="1" t="s">
+      <c r="I49" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="J49" s="1" t="s">
+      <c r="J49" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="K49" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="L49" s="1" t="s">
+      <c r="L49" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="M49" s="1" t="s">
+      <c r="M49" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="N49" s="1" t="s">
+      <c r="N49" s="2" t="s">
         <v>2</v>
       </c>
       <c r="O49" s="1"/>
@@ -2646,56 +2649,56 @@
     </row>
     <row r="2" spans="1:10" ht="27" customHeight="1">
       <c r="A2" s="15"/>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10" ht="27" customHeight="1">
       <c r="A3" s="15"/>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="J3" s="15"/>
@@ -2705,7 +2708,7 @@
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="37" t="s">
@@ -5469,13 +5472,13 @@
     </row>
     <row r="49" spans="1:13" ht="26.1" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="41" t="s">
         <v>35</v>
       </c>
       <c r="E49" s="1"/>

--- a/docs/arb_stiffness.xlsx
+++ b/docs/arb_stiffness.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\UserSpace\Games\Steam_Library\common\BeamNG_Userdata\current\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\.codex\visualizations\2026\09\05\01a07025-ed7a-7f60-89f7-3275b6531400\xlsx-locale-20261027\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A03DC9-06E4-4D77-91B4-B1E6675F803D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E51F443B-77A7-4BE7-9B97-A0E6A49A2D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comparison" sheetId="1" r:id="rId1"/>
     <sheet name="Parameters" sheetId="5" r:id="rId2"/>
-    <sheet name="Samples" sheetId="7" r:id="rId3"/>
+    <sheet name="Locale" sheetId="8" state="hidden" r:id="rId3"/>
+    <sheet name="Samples" sheetId="7" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="174">
   <si>
     <t>Astral · Anti-Roll Bar Stiffness</t>
   </si>
@@ -259,11 +260,336 @@
     <t>#3 H</t>
   </si>
   <si>
-    <t>Front</t>
+    <t>M</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>M</t>
+    <t>Language / 语言</t>
+  </si>
+  <si>
+    <t>简体中文</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>en-US</t>
+  </si>
+  <si>
+    <t>zh-CN</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>label.angularMotionRatio</t>
+  </si>
+  <si>
+    <t>角运动比
+(rad/mm)</t>
+  </si>
+  <si>
+    <t>label.arb1EndYM</t>
+  </si>
+  <si>
+    <t>arb1 终点 Y
+(m)</t>
+  </si>
+  <si>
+    <t>label.arb1EndZM</t>
+  </si>
+  <si>
+    <t>arb1 终点 Z
+(m)</t>
+  </si>
+  <si>
+    <t>label.arb1StartYM</t>
+  </si>
+  <si>
+    <t>arb1 起点 Y
+(m)</t>
+  </si>
+  <si>
+    <t>label.arb1StartZM</t>
+  </si>
+  <si>
+    <t>arb1 起点 Z
+(m)</t>
+  </si>
+  <si>
+    <t>label.arbBar</t>
+  </si>
+  <si>
+    <t>防倾杆</t>
+  </si>
+  <si>
+    <t>label.arbDeltaZ</t>
+  </si>
+  <si>
+    <t>防倾杆 ΔZ (mm)</t>
+  </si>
+  <si>
+    <t>label.armDeltaAngle</t>
+  </si>
+  <si>
+    <t>摇臂 Δθ
+(°)</t>
+  </si>
+  <si>
+    <t>label.axle</t>
+  </si>
+  <si>
+    <t>车轴</t>
+  </si>
+  <si>
+    <t>label.diameterMm</t>
+  </si>
+  <si>
+    <t>直径
+(mm)</t>
+  </si>
+  <si>
+    <t>label.endAngleDeg</t>
+  </si>
+  <si>
+    <t>终点角度
+(°)</t>
+  </si>
+  <si>
+    <t>label.endRadiusMm</t>
+  </si>
+  <si>
+    <t>终点半径
+(mm)</t>
+  </si>
+  <si>
+    <t>label.equivalentWheelRate</t>
+  </si>
+  <si>
+    <t>Equivalent wheel rate (N/mm)</t>
+  </si>
+  <si>
+    <t>等效轮端刚度 (N/mm)</t>
+  </si>
+  <si>
+    <t>label.fixedPivotAxis</t>
+  </si>
+  <si>
+    <t>Fixed pivot axis</t>
+  </si>
+  <si>
+    <t>label.front</t>
+  </si>
+  <si>
+    <t>前轴</t>
+  </si>
+  <si>
+    <t>label.gravel</t>
+  </si>
+  <si>
+    <t>砂石</t>
+  </si>
+  <si>
+    <t>label.input</t>
+  </si>
+  <si>
+    <t>输入</t>
+  </si>
+  <si>
+    <t>label.originalArmMm</t>
+  </si>
+  <si>
+    <t>原始臂长 (mm)</t>
+  </si>
+  <si>
+    <t>label.originalTableValue</t>
+  </si>
+  <si>
+    <t>Original table value</t>
+  </si>
+  <si>
+    <t>label.position</t>
+  </si>
+  <si>
+    <t>位置</t>
+  </si>
+  <si>
+    <t>label.rear</t>
+  </si>
+  <si>
+    <t>后轴</t>
+  </si>
+  <si>
+    <t>label.setting</t>
+  </si>
+  <si>
+    <t>设定</t>
+  </si>
+  <si>
+    <t>label.startAngleDegMultiline</t>
+  </si>
+  <si>
+    <t>起点角度
+(°)</t>
+  </si>
+  <si>
+    <t>label.startRadiusMmMultiline</t>
+  </si>
+  <si>
+    <t>起点半径
+(mm)</t>
+  </si>
+  <si>
+    <t>label.surface</t>
+  </si>
+  <si>
+    <t>路面</t>
+  </si>
+  <si>
+    <t>label.tarmac</t>
+  </si>
+  <si>
+    <t>柏油</t>
+  </si>
+  <si>
+    <t>label.torsionNmRadMultiline</t>
+  </si>
+  <si>
+    <t>扭转刚度
+(N·m/rad)</t>
+  </si>
+  <si>
+    <t>label.wheelDeltaZMmMultiline</t>
+  </si>
+  <si>
+    <t>车轮 ΔZ
+(mm)</t>
+  </si>
+  <si>
+    <t>note.bodyCoordinatesYzRadius</t>
+  </si>
+  <si>
+    <t>Nodes use body-relative coordinates (m); rotation radius is calculated from Y/Z.</t>
+  </si>
+  <si>
+    <t>note.bodyRelativeCoordinates</t>
+  </si>
+  <si>
+    <t>Nodes use body-relative coordinates (m).</t>
+  </si>
+  <si>
+    <t>note.enterTravelArb1End</t>
+  </si>
+  <si>
+    <t>Measurements · enter wheel travel and arb1 end position for each set</t>
+  </si>
+  <si>
+    <t>note.intervalMotionRatio</t>
+  </si>
+  <si>
+    <t>Converted using the full-interval angular motion ratio; does not represent instantaneous stiffness at every travel position.</t>
+  </si>
+  <si>
+    <t>note.intervalWheelStiffness</t>
+  </si>
+  <si>
+    <t>Interval equivalent wheel stiffness · full-interval angular motion ratio · opposite wheel fixed</t>
+  </si>
+  <si>
+    <t>note.originalZMeasurements</t>
+  </si>
+  <si>
+    <t>Original Z measurements (excluded from stiffness calculation)</t>
+  </si>
+  <si>
+    <t>note.wheeljackStartPosition</t>
+  </si>
+  <si>
+    <t>Start position is recorded after lifting with wheeljack and stabilizing at full extension; wheel travel uses the same start position.</t>
+  </si>
+  <si>
+    <t>note.yellowInputs</t>
+  </si>
+  <si>
+    <t>Yellow cells are manual inputs.</t>
+  </si>
+  <si>
+    <t>status.coordinatesNeeded</t>
+  </si>
+  <si>
+    <t>Coordinates needed</t>
+  </si>
+  <si>
+    <t>待补坐标</t>
+  </si>
+  <si>
+    <t>status.invalidRadius</t>
+  </si>
+  <si>
+    <t>Invalid radius</t>
+  </si>
+  <si>
+    <t>无效半径</t>
+  </si>
+  <si>
+    <t>status.nodeCoordinatesNeeded</t>
+  </si>
+  <si>
+    <t>Node coordinates needed; no stiffness result yet.</t>
+  </si>
+  <si>
+    <t>待补节点坐标；暂无刚度结果。</t>
+  </si>
+  <si>
+    <t>status.positiveWheelTravel</t>
+  </si>
+  <si>
+    <t>Wheel travel must be greater than 0</t>
+  </si>
+  <si>
+    <t>轮行程须大于0</t>
+  </si>
+  <si>
+    <t>status.wheelTravelNeeded</t>
+  </si>
+  <si>
+    <t>Enter wheel travel</t>
+  </si>
+  <si>
+    <t>待填轮行程</t>
+  </si>
+  <si>
+    <t>title.arbCalculations</t>
+  </si>
+  <si>
+    <t>Astral · 防倾杆计算</t>
+  </si>
+  <si>
+    <t>title.arbParameters</t>
+  </si>
+  <si>
+    <t>Astral · 防倾杆参数</t>
+  </si>
+  <si>
+    <t>title.arbStiffness</t>
+  </si>
+  <si>
+    <t>Astral · 防倾杆刚度</t>
+  </si>
+  <si>
+    <t>title.fixedGeometry</t>
+  </si>
+  <si>
+    <t>Fixed geometry · spawn position / pivot axis</t>
+  </si>
+  <si>
+    <t>title.settingMeasurements</t>
+  </si>
+  <si>
+    <t>Measurements · start / end of each setting</t>
+  </si>
+  <si>
+    <t>简体中文</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -277,7 +603,7 @@
     <numFmt numFmtId="178" formatCode="0.000"/>
     <numFmt numFmtId="179" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -391,8 +717,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -469,8 +808,21 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -526,20 +878,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -583,16 +942,16 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -604,7 +963,7 @@
     <xf numFmtId="1" fontId="4" fillId="7" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="1" fontId="4" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="6" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -613,25 +972,25 @@
     <xf numFmtId="176" fontId="4" fillId="7" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="17" fillId="14" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="17" fillId="14" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -649,6 +1008,14 @@
     <xf numFmtId="176" fontId="16" fillId="13" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -661,12 +1028,9 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -684,28 +1048,37 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="zh-CN"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr lang="en-US" sz="1125">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
-                <a:cs typeface="Arial"/>
-              </a:rPr>
-              <a:t>Gravel</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
+        <c:strRef>
+          <c:f>Locale!$D$17</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>砂石</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
       </c:tx>
       <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1125">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Microsoft YaHei"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -718,7 +1091,15 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Front</c:v>
+            <c:strRef>
+              <c:f>Locale!$D$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>前轴</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -807,7 +1188,15 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>Rear</c:v>
+            <c:strRef>
+              <c:f>Locale!$D$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>后轴</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -922,7 +1311,7 @@
             <a:pPr>
               <a:defRPr sz="750">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -956,18 +1345,27 @@
         </c:majorGridlines>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Equivalent wheel rate (N/mm)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>等效轮端刚度 (N/mm)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US"/>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -980,7 +1378,7 @@
             <a:pPr>
               <a:defRPr sz="825">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -1002,7 +1400,7 @@
           <a:pPr>
             <a:defRPr sz="825">
               <a:latin typeface="Arial"/>
-              <a:ea typeface="Arial"/>
+              <a:ea typeface="Microsoft YaHei"/>
               <a:cs typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
@@ -1033,28 +1431,37 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="zh-CN"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr lang="en-US" sz="1125">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
-                <a:cs typeface="Arial"/>
-              </a:rPr>
-              <a:t>Tarmac</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
+        <c:strRef>
+          <c:f>Locale!$D$27</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>柏油</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
       </c:tx>
       <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1125">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Microsoft YaHei"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -1067,7 +1474,15 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Front</c:v>
+            <c:strRef>
+              <c:f>Locale!$D$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>前轴</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1156,7 +1571,15 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>Rear</c:v>
+            <c:strRef>
+              <c:f>Locale!$D$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>后轴</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1271,7 +1694,7 @@
             <a:pPr>
               <a:defRPr sz="750">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -1305,18 +1728,27 @@
         </c:majorGridlines>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Equivalent wheel rate (N/mm)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>等效轮端刚度 (N/mm)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US"/>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -1329,7 +1761,7 @@
             <a:pPr>
               <a:defRPr sz="825">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -1351,7 +1783,7 @@
           <a:pPr>
             <a:defRPr sz="825">
               <a:latin typeface="Arial"/>
-              <a:ea typeface="Arial"/>
+              <a:ea typeface="Microsoft YaHei"/>
               <a:cs typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
@@ -1374,7 +1806,7 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -1650,26 +2082,38 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88E5B481-2775-4575-8B9C-179779A44002}">
   <sheetPr>
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O49"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.75" customWidth="1"/>
     <col min="2" max="14" width="10" customWidth="1"/>
     <col min="15" max="15" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="26.1" customHeight="1">
+    <row r="1" spans="1:15" ht="22" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="F1" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="39" t="s">
+        <v>70</v>
+      </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -1679,139 +2123,178 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="26.1" customHeight="1">
+    <row r="2" spans="1:15" ht="26.15" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>0</v>
+      <c r="B2" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="C2" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="D2" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="E2" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="F2" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="G2" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="H2" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="I2" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="J2" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="K2" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="L2" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="M2" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="N2" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
       </c>
       <c r="O2" s="1"/>
     </row>
-    <row r="3" spans="1:15" ht="26.1" customHeight="1">
+    <row r="3" spans="1:15" ht="26.15" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>0</v>
+      <c r="B3" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="C3" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="D3" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="E3" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="F3" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="G3" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="H3" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="I3" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="J3" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="K3" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="L3" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="M3" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+      <c r="N3" s="3" t="str">
+        <f>VLOOKUP("title.arbStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆刚度</v>
       </c>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="26.1" customHeight="1">
+    <row r="4" spans="1:15" ht="26.15" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>1</v>
+      <c r="B4" s="2" t="str">
+        <f>VLOOKUP("note.intervalWheelStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>区间等效轮端刚度 · 整段角运动比 · 对侧轮固定</v>
+      </c>
+      <c r="C4" s="2" t="str">
+        <f>VLOOKUP("note.intervalWheelStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>区间等效轮端刚度 · 整段角运动比 · 对侧轮固定</v>
+      </c>
+      <c r="D4" s="2" t="str">
+        <f>VLOOKUP("note.intervalWheelStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>区间等效轮端刚度 · 整段角运动比 · 对侧轮固定</v>
+      </c>
+      <c r="E4" s="2" t="str">
+        <f>VLOOKUP("note.intervalWheelStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>区间等效轮端刚度 · 整段角运动比 · 对侧轮固定</v>
+      </c>
+      <c r="F4" s="2" t="str">
+        <f>VLOOKUP("note.intervalWheelStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>区间等效轮端刚度 · 整段角运动比 · 对侧轮固定</v>
+      </c>
+      <c r="G4" s="2" t="str">
+        <f>VLOOKUP("note.intervalWheelStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>区间等效轮端刚度 · 整段角运动比 · 对侧轮固定</v>
+      </c>
+      <c r="H4" s="2" t="str">
+        <f>VLOOKUP("note.intervalWheelStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>区间等效轮端刚度 · 整段角运动比 · 对侧轮固定</v>
+      </c>
+      <c r="I4" s="2" t="str">
+        <f>VLOOKUP("note.intervalWheelStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>区间等效轮端刚度 · 整段角运动比 · 对侧轮固定</v>
+      </c>
+      <c r="J4" s="2" t="str">
+        <f>VLOOKUP("note.intervalWheelStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>区间等效轮端刚度 · 整段角运动比 · 对侧轮固定</v>
+      </c>
+      <c r="K4" s="2" t="str">
+        <f>VLOOKUP("note.intervalWheelStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>区间等效轮端刚度 · 整段角运动比 · 对侧轮固定</v>
+      </c>
+      <c r="L4" s="2" t="str">
+        <f>VLOOKUP("note.intervalWheelStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>区间等效轮端刚度 · 整段角运动比 · 对侧轮固定</v>
+      </c>
+      <c r="M4" s="2" t="str">
+        <f>VLOOKUP("note.intervalWheelStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>区间等效轮端刚度 · 整段角运动比 · 对侧轮固定</v>
+      </c>
+      <c r="N4" s="2" t="str">
+        <f>VLOOKUP("note.intervalWheelStiffness",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>区间等效轮端刚度 · 整段角运动比 · 对侧轮固定</v>
       </c>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15" ht="26.1" customHeight="1">
+    <row r="5" spans="1:15" ht="26.15" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="str">
-        <f>IF(COUNT(Samples!H6:J17)=0,"待补节点坐标；暂无刚度结果。","")</f>
+        <f>IF(COUNT(Samples!H6:J17)=0,VLOOKUP("status.nodeCoordinatesNeeded",Locale!$A$2:$D$47,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="C5" s="2"/>
@@ -1828,7 +2311,7 @@
       <c r="N5" s="2"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="1:15" ht="26.1" customHeight="1">
+    <row r="6" spans="1:15" ht="26.15" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1845,7 +2328,7 @@
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="1:15" ht="26.1" customHeight="1">
+    <row r="7" spans="1:15" ht="26.15" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1862,7 +2345,7 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="1:15" ht="26.1" customHeight="1">
+    <row r="8" spans="1:15" ht="26.15" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1879,7 +2362,7 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
     </row>
-    <row r="9" spans="1:15" ht="26.1" customHeight="1">
+    <row r="9" spans="1:15" ht="26.15" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1896,7 +2379,7 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:15" ht="26.1" customHeight="1">
+    <row r="10" spans="1:15" ht="26.15" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1913,7 +2396,7 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:15" ht="26.1" customHeight="1">
+    <row r="11" spans="1:15" ht="26.15" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1930,7 +2413,7 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:15" ht="26.1" customHeight="1">
+    <row r="12" spans="1:15" ht="26.15" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1947,7 +2430,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:15" ht="26.1" customHeight="1">
+    <row r="13" spans="1:15" ht="26.15" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1964,7 +2447,7 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:15" ht="26.1" customHeight="1">
+    <row r="14" spans="1:15" ht="26.15" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1981,7 +2464,7 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="1:15" ht="26.1" customHeight="1">
+    <row r="15" spans="1:15" ht="26.15" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1998,7 +2481,7 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="1:15" ht="26.1" customHeight="1">
+    <row r="16" spans="1:15" ht="26.15" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -2015,7 +2498,7 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:15" ht="26.1" customHeight="1">
+    <row r="17" spans="1:15" ht="26.15" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -2032,7 +2515,7 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="1:15" ht="26.1" customHeight="1">
+    <row r="18" spans="1:15" ht="26.15" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -2049,7 +2532,7 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
     </row>
-    <row r="19" spans="1:15" ht="26.1" customHeight="1">
+    <row r="19" spans="1:15" ht="26.15" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -2066,7 +2549,7 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
     </row>
-    <row r="20" spans="1:15" ht="26.1" customHeight="1">
+    <row r="20" spans="1:15" ht="26.15" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -2083,7 +2566,7 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
     </row>
-    <row r="21" spans="1:15" ht="26.1" customHeight="1">
+    <row r="21" spans="1:15" ht="26.15" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -2100,7 +2583,7 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
     </row>
-    <row r="22" spans="1:15" ht="26.1" customHeight="1">
+    <row r="22" spans="1:15" ht="26.15" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -2117,7 +2600,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" ht="26.1" customHeight="1">
+    <row r="23" spans="1:15" ht="26.15" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -2134,7 +2617,7 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="26.1" customHeight="1">
+    <row r="24" spans="1:15" ht="26.15" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -2151,7 +2634,7 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:15" ht="26.1" customHeight="1">
+    <row r="25" spans="1:15" ht="26.15" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -2168,7 +2651,7 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" ht="26.1" customHeight="1">
+    <row r="26" spans="1:15" ht="26.15" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -2185,7 +2668,7 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" ht="26.1" customHeight="1">
+    <row r="27" spans="1:15" ht="26.15" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -2202,7 +2685,7 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" ht="26.1" customHeight="1">
+    <row r="28" spans="1:15" ht="26.15" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2219,7 +2702,7 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" ht="26.1" customHeight="1">
+    <row r="29" spans="1:15" ht="26.15" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2236,7 +2719,7 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" ht="26.1" customHeight="1">
+    <row r="30" spans="1:15" ht="26.15" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2253,7 +2736,7 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" ht="26.1" customHeight="1">
+    <row r="31" spans="1:15" ht="26.15" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2270,7 +2753,7 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" ht="26.1" customHeight="1">
+    <row r="32" spans="1:15" ht="26.15" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2287,7 +2770,7 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" ht="26.1" customHeight="1">
+    <row r="33" spans="1:15" ht="26.15" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2304,7 +2787,7 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" ht="26.1" customHeight="1">
+    <row r="34" spans="1:15" ht="26.15" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2321,7 +2804,7 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:15" ht="26.1" customHeight="1">
+    <row r="35" spans="1:15" ht="26.15" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2338,7 +2821,7 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:15" ht="26.1" customHeight="1">
+    <row r="36" spans="1:15" ht="26.15" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2355,7 +2838,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:15" ht="26.1" customHeight="1">
+    <row r="37" spans="1:15" ht="26.15" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2372,7 +2855,7 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:15" ht="26.1" customHeight="1">
+    <row r="38" spans="1:15" ht="26.15" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2389,7 +2872,7 @@
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:15" ht="26.1" customHeight="1">
+    <row r="39" spans="1:15" ht="26.15" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2406,7 +2889,7 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:15" ht="26.1" customHeight="1">
+    <row r="40" spans="1:15" ht="26.15" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2423,7 +2906,7 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:15" ht="26.1" customHeight="1">
+    <row r="41" spans="1:15" ht="26.15" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2440,7 +2923,7 @@
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
-    <row r="42" spans="1:15" ht="26.1" customHeight="1">
+    <row r="42" spans="1:15" ht="26.15" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2457,7 +2940,7 @@
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
     </row>
-    <row r="43" spans="1:15" ht="26.1" customHeight="1">
+    <row r="43" spans="1:15" ht="26.15" customHeight="1">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2474,7 +2957,7 @@
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
     </row>
-    <row r="44" spans="1:15" ht="26.1" customHeight="1">
+    <row r="44" spans="1:15" ht="26.15" customHeight="1">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2491,7 +2974,7 @@
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
     </row>
-    <row r="45" spans="1:15" ht="26.1" customHeight="1">
+    <row r="45" spans="1:15" ht="26.15" customHeight="1">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2508,7 +2991,7 @@
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
     </row>
-    <row r="46" spans="1:15" ht="26.1" customHeight="1">
+    <row r="46" spans="1:15" ht="26.15" customHeight="1">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2525,7 +3008,7 @@
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
     </row>
-    <row r="47" spans="1:15" ht="26.1" customHeight="1">
+    <row r="47" spans="1:15" ht="26.15" customHeight="1">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2542,7 +3025,7 @@
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
     </row>
-    <row r="48" spans="1:15" ht="26.1" customHeight="1">
+    <row r="48" spans="1:15" ht="26.15" customHeight="1">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2559,77 +3042,98 @@
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
     </row>
-    <row r="49" spans="1:15" ht="26.1" customHeight="1">
+    <row r="49" spans="1:15" ht="26.15" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="L49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="M49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="N49" s="2" t="s">
-        <v>2</v>
+      <c r="B49" s="2" t="str">
+        <f>VLOOKUP("note.intervalMotionRatio",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>整段角运动比换算值；不代表行程内每一位置的瞬时刚度。</v>
+      </c>
+      <c r="C49" s="2" t="str">
+        <f>VLOOKUP("note.intervalMotionRatio",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>整段角运动比换算值；不代表行程内每一位置的瞬时刚度。</v>
+      </c>
+      <c r="D49" s="2" t="str">
+        <f>VLOOKUP("note.intervalMotionRatio",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>整段角运动比换算值；不代表行程内每一位置的瞬时刚度。</v>
+      </c>
+      <c r="E49" s="2" t="str">
+        <f>VLOOKUP("note.intervalMotionRatio",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>整段角运动比换算值；不代表行程内每一位置的瞬时刚度。</v>
+      </c>
+      <c r="F49" s="2" t="str">
+        <f>VLOOKUP("note.intervalMotionRatio",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>整段角运动比换算值；不代表行程内每一位置的瞬时刚度。</v>
+      </c>
+      <c r="G49" s="2" t="str">
+        <f>VLOOKUP("note.intervalMotionRatio",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>整段角运动比换算值；不代表行程内每一位置的瞬时刚度。</v>
+      </c>
+      <c r="H49" s="2" t="str">
+        <f>VLOOKUP("note.intervalMotionRatio",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>整段角运动比换算值；不代表行程内每一位置的瞬时刚度。</v>
+      </c>
+      <c r="I49" s="2" t="str">
+        <f>VLOOKUP("note.intervalMotionRatio",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>整段角运动比换算值；不代表行程内每一位置的瞬时刚度。</v>
+      </c>
+      <c r="J49" s="2" t="str">
+        <f>VLOOKUP("note.intervalMotionRatio",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>整段角运动比换算值；不代表行程内每一位置的瞬时刚度。</v>
+      </c>
+      <c r="K49" s="2" t="str">
+        <f>VLOOKUP("note.intervalMotionRatio",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>整段角运动比换算值；不代表行程内每一位置的瞬时刚度。</v>
+      </c>
+      <c r="L49" s="2" t="str">
+        <f>VLOOKUP("note.intervalMotionRatio",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>整段角运动比换算值；不代表行程内每一位置的瞬时刚度。</v>
+      </c>
+      <c r="M49" s="2" t="str">
+        <f>VLOOKUP("note.intervalMotionRatio",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>整段角运动比换算值；不代表行程内每一位置的瞬时刚度。</v>
+      </c>
+      <c r="N49" s="2" t="str">
+        <f>VLOOKUP("note.intervalMotionRatio",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>整段角运动比换算值；不代表行程内每一位置的瞬时刚度。</v>
       </c>
       <c r="O49" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="B2:N3"/>
     <mergeCell ref="B4:N4"/>
     <mergeCell ref="B5:N5"/>
     <mergeCell ref="B49:N49"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="E1:G1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"English,简体中文"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F2D244E-AB5E-4B38-9AA1-584347E594FD}">
   <sheetPr>
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:N118"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.75" customWidth="1"/>
     <col min="2" max="2" width="13.5" customWidth="1"/>
     <col min="3" max="3" width="13.75" customWidth="1"/>
     <col min="4" max="4" width="15.5" customWidth="1"/>
-    <col min="5" max="5" width="18.125" customWidth="1"/>
+    <col min="5" max="5" width="18.08203125" customWidth="1"/>
     <col min="6" max="7" width="16.5" customWidth="1"/>
-    <col min="8" max="9" width="15.625" customWidth="1"/>
+    <col min="8" max="9" width="15.58203125" customWidth="1"/>
     <col min="10" max="10" width="2.75" customWidth="1"/>
     <col min="11" max="14" width="10" customWidth="1"/>
     <col min="15" max="15" width="10.5" customWidth="1"/>
@@ -2649,85 +3153,109 @@
     </row>
     <row r="2" spans="1:10" ht="27" customHeight="1">
       <c r="A2" s="15"/>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>3</v>
+      <c r="B2" s="2" t="str">
+        <f>VLOOKUP("title.arbParameters",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆参数</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <f>VLOOKUP("title.arbParameters",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆参数</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <f>VLOOKUP("title.arbParameters",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆参数</v>
+      </c>
+      <c r="E2" s="2" t="str">
+        <f>VLOOKUP("title.arbParameters",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆参数</v>
+      </c>
+      <c r="F2" s="2" t="str">
+        <f>VLOOKUP("title.arbParameters",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆参数</v>
+      </c>
+      <c r="G2" s="2" t="str">
+        <f>VLOOKUP("title.arbParameters",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆参数</v>
+      </c>
+      <c r="H2" s="2" t="str">
+        <f>VLOOKUP("title.arbParameters",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆参数</v>
+      </c>
+      <c r="I2" s="2" t="str">
+        <f>VLOOKUP("title.arbParameters",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆参数</v>
       </c>
       <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10" ht="27" customHeight="1">
       <c r="A3" s="15"/>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>3</v>
+      <c r="B3" s="2" t="str">
+        <f>VLOOKUP("title.arbParameters",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆参数</v>
+      </c>
+      <c r="C3" s="2" t="str">
+        <f>VLOOKUP("title.arbParameters",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆参数</v>
+      </c>
+      <c r="D3" s="2" t="str">
+        <f>VLOOKUP("title.arbParameters",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆参数</v>
+      </c>
+      <c r="E3" s="2" t="str">
+        <f>VLOOKUP("title.arbParameters",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆参数</v>
+      </c>
+      <c r="F3" s="2" t="str">
+        <f>VLOOKUP("title.arbParameters",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆参数</v>
+      </c>
+      <c r="G3" s="2" t="str">
+        <f>VLOOKUP("title.arbParameters",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆参数</v>
+      </c>
+      <c r="H3" s="2" t="str">
+        <f>VLOOKUP("title.arbParameters",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆参数</v>
+      </c>
+      <c r="I3" s="2" t="str">
+        <f>VLOOKUP("title.arbParameters",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆参数</v>
       </c>
       <c r="J3" s="15"/>
     </row>
     <row r="4" spans="1:10" ht="27" customHeight="1">
       <c r="A4" s="15"/>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="I4" s="37" t="s">
-        <v>4</v>
+      <c r="B4" s="3" t="str">
+        <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>黄色单元格为手动输入。</v>
+      </c>
+      <c r="C4" s="40" t="str">
+        <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>黄色单元格为手动输入。</v>
+      </c>
+      <c r="D4" s="41" t="str">
+        <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>黄色单元格为手动输入。</v>
+      </c>
+      <c r="E4" s="41" t="str">
+        <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>黄色单元格为手动输入。</v>
+      </c>
+      <c r="F4" s="41" t="str">
+        <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>黄色单元格为手动输入。</v>
+      </c>
+      <c r="G4" s="41" t="str">
+        <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>黄色单元格为手动输入。</v>
+      </c>
+      <c r="H4" s="41" t="str">
+        <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>黄色单元格为手动输入。</v>
+      </c>
+      <c r="I4" s="41" t="str">
+        <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>黄色单元格为手动输入。</v>
       </c>
       <c r="J4" s="15"/>
     </row>
@@ -2745,17 +3273,23 @@
     </row>
     <row r="6" spans="1:10" ht="42" customHeight="1">
       <c r="A6" s="15"/>
-      <c r="B6" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>8</v>
+      <c r="B6" s="16" t="str">
+        <f>VLOOKUP("label.axle",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>车轴</v>
+      </c>
+      <c r="C6" s="16" t="str">
+        <f>VLOOKUP("label.arbBar",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>防倾杆</v>
+      </c>
+      <c r="D6" s="16" t="str">
+        <f>VLOOKUP("label.diameterMm",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>直径
+(mm)</v>
+      </c>
+      <c r="E6" s="16" t="str">
+        <f>VLOOKUP("label.torsionNmRadMultiline",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>扭转刚度
+(N·m/rad)</v>
       </c>
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
@@ -2765,8 +3299,9 @@
     </row>
     <row r="7" spans="1:10" ht="27" customHeight="1">
       <c r="A7" s="15"/>
-      <c r="B7" s="17" t="s">
-        <v>9</v>
+      <c r="B7" s="17" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>44</v>
@@ -2786,8 +3321,9 @@
     </row>
     <row r="8" spans="1:10" ht="27" customHeight="1">
       <c r="A8" s="15"/>
-      <c r="B8" s="18" t="s">
-        <v>9</v>
+      <c r="B8" s="18" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>45</v>
@@ -2806,8 +3342,9 @@
     </row>
     <row r="9" spans="1:10" ht="27" customHeight="1">
       <c r="A9" s="15"/>
-      <c r="B9" s="17" t="s">
-        <v>9</v>
+      <c r="B9" s="17" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>46</v>
@@ -2827,8 +3364,9 @@
     </row>
     <row r="10" spans="1:10" ht="27" customHeight="1">
       <c r="A10" s="15"/>
-      <c r="B10" s="18" t="s">
-        <v>10</v>
+      <c r="B10" s="18" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>44</v>
@@ -2848,8 +3386,9 @@
     </row>
     <row r="11" spans="1:10" ht="27" customHeight="1">
       <c r="A11" s="15"/>
-      <c r="B11" s="17" t="s">
-        <v>10</v>
+      <c r="B11" s="17" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="C11" s="17" t="s">
         <v>45</v>
@@ -2869,8 +3408,9 @@
     </row>
     <row r="12" spans="1:10" ht="27" customHeight="1">
       <c r="A12" s="15"/>
-      <c r="B12" s="18" t="s">
-        <v>10</v>
+      <c r="B12" s="18" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>46</v>
@@ -2902,64 +3442,81 @@
     </row>
     <row r="14" spans="1:10" ht="27" customHeight="1">
       <c r="A14" s="15"/>
-      <c r="B14" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="38" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="38" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="38" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="38" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" s="38" t="s">
-        <v>11</v>
-      </c>
-      <c r="I14" s="38" t="s">
-        <v>11</v>
+      <c r="B14" s="42" t="str">
+        <f>VLOOKUP("label.fixedPivotAxis",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>固定转轴</v>
+      </c>
+      <c r="C14" s="42" t="str">
+        <f>VLOOKUP("title.fixedGeometry",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>固定几何 · 生成位置 / 转轴</v>
+      </c>
+      <c r="D14" s="42" t="str">
+        <f>VLOOKUP("title.fixedGeometry",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>固定几何 · 生成位置 / 转轴</v>
+      </c>
+      <c r="E14" s="42" t="str">
+        <f>VLOOKUP("title.fixedGeometry",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>固定几何 · 生成位置 / 转轴</v>
+      </c>
+      <c r="F14" s="42" t="str">
+        <f>VLOOKUP("title.fixedGeometry",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>固定几何 · 生成位置 / 转轴</v>
+      </c>
+      <c r="G14" s="42" t="str">
+        <f>VLOOKUP("title.fixedGeometry",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>固定几何 · 生成位置 / 转轴</v>
+      </c>
+      <c r="H14" s="42" t="str">
+        <f>VLOOKUP("title.fixedGeometry",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>固定几何 · 生成位置 / 转轴</v>
+      </c>
+      <c r="I14" s="42" t="str">
+        <f>VLOOKUP("title.fixedGeometry",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>固定几何 · 生成位置 / 转轴</v>
       </c>
       <c r="J14" s="15"/>
     </row>
     <row r="15" spans="1:10" ht="27" customHeight="1">
       <c r="A15" s="15"/>
-      <c r="B15" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="I15" s="39" t="s">
-        <v>12</v>
+      <c r="B15" s="43" t="str">
+        <f>VLOOKUP("note.bodyRelativeCoordinates",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>节点使用车身相对坐标（m）。</v>
+      </c>
+      <c r="C15" s="43" t="str">
+        <f>VLOOKUP("note.bodyCoordinatesYzRadius",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</v>
+      </c>
+      <c r="D15" s="43" t="str">
+        <f>VLOOKUP("note.bodyCoordinatesYzRadius",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</v>
+      </c>
+      <c r="E15" s="43" t="str">
+        <f>VLOOKUP("note.bodyCoordinatesYzRadius",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</v>
+      </c>
+      <c r="F15" s="43" t="str">
+        <f>VLOOKUP("note.bodyCoordinatesYzRadius",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</v>
+      </c>
+      <c r="G15" s="43" t="str">
+        <f>VLOOKUP("note.bodyCoordinatesYzRadius",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</v>
+      </c>
+      <c r="H15" s="43" t="str">
+        <f>VLOOKUP("note.bodyCoordinatesYzRadius",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</v>
+      </c>
+      <c r="I15" s="43" t="str">
+        <f>VLOOKUP("note.bodyCoordinatesYzRadius",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</v>
       </c>
       <c r="J15" s="15"/>
     </row>
     <row r="16" spans="1:10" ht="42" customHeight="1">
       <c r="A16" s="15"/>
-      <c r="B16" s="27" t="s">
-        <v>5</v>
+      <c r="B16" s="27" t="str">
+        <f>VLOOKUP("label.axle",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>车轴</v>
       </c>
       <c r="C16" s="27" t="s">
         <v>15</v>
@@ -2971,8 +3528,9 @@
     </row>
     <row r="17" spans="1:14" ht="27" customHeight="1">
       <c r="A17" s="15"/>
-      <c r="B17" s="28" t="s">
-        <v>9</v>
+      <c r="B17" s="28" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
       </c>
       <c r="C17" s="29">
         <v>-0.91500000000000004</v>
@@ -2984,8 +3542,9 @@
     </row>
     <row r="18" spans="1:14" ht="27" customHeight="1">
       <c r="A18" s="15"/>
-      <c r="B18" s="30" t="s">
-        <v>10</v>
+      <c r="B18" s="30" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="C18" s="29">
         <v>1.4590000000000001</v>
@@ -3009,81 +3568,105 @@
     </row>
     <row r="20" spans="1:14" ht="27" customHeight="1">
       <c r="A20" s="15"/>
-      <c r="B20" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="G20" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="H20" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="I20" s="38" t="s">
-        <v>18</v>
+      <c r="B20" s="42" t="str">
+        <f>VLOOKUP("title.settingMeasurements",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>测量 · 各档起点 / 终点</v>
+      </c>
+      <c r="C20" s="42" t="str">
+        <f>VLOOKUP("note.enterTravelArb1End",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>测量 · 每组填写轮行程和 arb1 终点</v>
+      </c>
+      <c r="D20" s="42" t="str">
+        <f>VLOOKUP("note.enterTravelArb1End",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>测量 · 每组填写轮行程和 arb1 终点</v>
+      </c>
+      <c r="E20" s="42" t="str">
+        <f>VLOOKUP("note.enterTravelArb1End",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>测量 · 每组填写轮行程和 arb1 终点</v>
+      </c>
+      <c r="F20" s="42" t="str">
+        <f>VLOOKUP("note.enterTravelArb1End",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>测量 · 每组填写轮行程和 arb1 终点</v>
+      </c>
+      <c r="G20" s="42" t="str">
+        <f>VLOOKUP("note.enterTravelArb1End",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>测量 · 每组填写轮行程和 arb1 终点</v>
+      </c>
+      <c r="H20" s="42" t="str">
+        <f>VLOOKUP("note.enterTravelArb1End",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>测量 · 每组填写轮行程和 arb1 终点</v>
+      </c>
+      <c r="I20" s="42" t="str">
+        <f>VLOOKUP("note.enterTravelArb1End",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>测量 · 每组填写轮行程和 arb1 终点</v>
       </c>
       <c r="J20" s="15"/>
     </row>
     <row r="21" spans="1:14" ht="27" customHeight="1">
       <c r="A21" s="15"/>
-      <c r="B21" s="40" t="s">
-        <v>50</v>
-      </c>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="40"/>
+      <c r="B21" s="44" t="str">
+        <f>VLOOKUP("note.wheeljackStartPosition",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>起点为 wheeljack 架起、全伸展稳定后的位置；轮行程从同一起点计算。</v>
+      </c>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="44"/>
       <c r="J21" s="15"/>
     </row>
     <row r="22" spans="1:14" ht="42" customHeight="1">
       <c r="A22" s="15"/>
-      <c r="B22" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="I22" s="27" t="s">
-        <v>23</v>
+      <c r="B22" s="27" t="str">
+        <f>VLOOKUP("label.surface",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>路面</v>
+      </c>
+      <c r="C22" s="27" t="str">
+        <f>VLOOKUP("label.axle",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>车轴</v>
+      </c>
+      <c r="D22" s="27" t="str">
+        <f>VLOOKUP("label.position",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>位置</v>
+      </c>
+      <c r="E22" s="27" t="str">
+        <f>VLOOKUP("label.wheelDeltaZMmMultiline",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>车轮 ΔZ
+(mm)</v>
+      </c>
+      <c r="F22" s="27" t="str">
+        <f>VLOOKUP("label.arb1StartYM",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>arb1 起点 Y
+(m)</v>
+      </c>
+      <c r="G22" s="27" t="str">
+        <f>VLOOKUP("label.arb1StartZM",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>arb1 起点 Z
+(m)</v>
+      </c>
+      <c r="H22" s="27" t="str">
+        <f>VLOOKUP("label.arb1EndYM",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>arb1 终点 Y
+(m)</v>
+      </c>
+      <c r="I22" s="27" t="str">
+        <f>VLOOKUP("label.arb1EndZM",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>arb1 终点 Z
+(m)</v>
       </c>
       <c r="J22" s="15"/>
     </row>
     <row r="23" spans="1:14" ht="27" customHeight="1">
       <c r="A23" s="15"/>
-      <c r="B23" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="28" t="s">
-        <v>9</v>
+      <c r="B23" s="28" t="str">
+        <f>VLOOKUP("label.tarmac",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>柏油</v>
+      </c>
+      <c r="C23" s="28" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
       </c>
       <c r="D23" s="28" t="s">
         <v>51</v>
@@ -3107,11 +3690,13 @@
     </row>
     <row r="24" spans="1:14" ht="27" customHeight="1">
       <c r="A24" s="15"/>
-      <c r="B24" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>9</v>
+      <c r="B24" s="30" t="str">
+        <f>VLOOKUP("label.tarmac",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>柏油</v>
+      </c>
+      <c r="C24" s="30" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
       </c>
       <c r="D24" s="30" t="s">
         <v>52</v>
@@ -3137,11 +3722,13 @@
     </row>
     <row r="25" spans="1:14" ht="27" customHeight="1">
       <c r="A25" s="15"/>
-      <c r="B25" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="28" t="s">
-        <v>9</v>
+      <c r="B25" s="28" t="str">
+        <f>VLOOKUP("label.tarmac",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>柏油</v>
+      </c>
+      <c r="C25" s="28" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
       </c>
       <c r="D25" s="28" t="s">
         <v>53</v>
@@ -3165,11 +3752,13 @@
     </row>
     <row r="26" spans="1:14" ht="27" customHeight="1">
       <c r="A26" s="15"/>
-      <c r="B26" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>10</v>
+      <c r="B26" s="30" t="str">
+        <f>VLOOKUP("label.tarmac",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>柏油</v>
+      </c>
+      <c r="C26" s="30" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="D26" s="30" t="s">
         <v>51</v>
@@ -3193,11 +3782,13 @@
     </row>
     <row r="27" spans="1:14" ht="27" customHeight="1">
       <c r="A27" s="15"/>
-      <c r="B27" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="28" t="s">
-        <v>10</v>
+      <c r="B27" s="28" t="str">
+        <f>VLOOKUP("label.tarmac",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>柏油</v>
+      </c>
+      <c r="C27" s="28" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="D27" s="28" t="s">
         <v>52</v>
@@ -3223,11 +3814,13 @@
     </row>
     <row r="28" spans="1:14" ht="27" customHeight="1">
       <c r="A28" s="15"/>
-      <c r="B28" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>10</v>
+      <c r="B28" s="30" t="str">
+        <f>VLOOKUP("label.tarmac",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>柏油</v>
+      </c>
+      <c r="C28" s="30" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="D28" s="30" t="s">
         <v>53</v>
@@ -3251,11 +3844,13 @@
     </row>
     <row r="29" spans="1:14" ht="27" customHeight="1">
       <c r="A29" s="15"/>
-      <c r="B29" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" s="28" t="s">
-        <v>9</v>
+      <c r="B29" s="28" t="str">
+        <f>VLOOKUP("label.gravel",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>砂石</v>
+      </c>
+      <c r="C29" s="28" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
       </c>
       <c r="D29" s="28" t="s">
         <v>51</v>
@@ -3281,11 +3876,13 @@
     </row>
     <row r="30" spans="1:14" ht="27" customHeight="1">
       <c r="A30" s="15"/>
-      <c r="B30" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="C30" s="30" t="s">
-        <v>9</v>
+      <c r="B30" s="30" t="str">
+        <f>VLOOKUP("label.gravel",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>砂石</v>
+      </c>
+      <c r="C30" s="30" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
       </c>
       <c r="D30" s="30" t="s">
         <v>52</v>
@@ -3309,11 +3906,13 @@
     </row>
     <row r="31" spans="1:14" ht="27" customHeight="1">
       <c r="A31" s="15"/>
-      <c r="B31" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="C31" s="28" t="s">
-        <v>9</v>
+      <c r="B31" s="28" t="str">
+        <f>VLOOKUP("label.gravel",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>砂石</v>
+      </c>
+      <c r="C31" s="28" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
       </c>
       <c r="D31" s="28" t="s">
         <v>53</v>
@@ -3337,11 +3936,13 @@
     </row>
     <row r="32" spans="1:14" ht="27" customHeight="1">
       <c r="A32" s="15"/>
-      <c r="B32" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" s="30" t="s">
-        <v>10</v>
+      <c r="B32" s="30" t="str">
+        <f>VLOOKUP("label.gravel",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>砂石</v>
+      </c>
+      <c r="C32" s="30" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="D32" s="30" t="s">
         <v>51</v>
@@ -3365,11 +3966,13 @@
     </row>
     <row r="33" spans="1:14" ht="27" customHeight="1">
       <c r="A33" s="15"/>
-      <c r="B33" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="C33" s="28" t="s">
-        <v>10</v>
+      <c r="B33" s="28" t="str">
+        <f>VLOOKUP("label.gravel",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>砂石</v>
+      </c>
+      <c r="C33" s="28" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="D33" s="28" t="s">
         <v>52</v>
@@ -3395,11 +3998,13 @@
     </row>
     <row r="34" spans="1:14" ht="27" customHeight="1">
       <c r="A34" s="15"/>
-      <c r="B34" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="C34" s="30" t="s">
-        <v>10</v>
+      <c r="B34" s="30" t="str">
+        <f>VLOOKUP("label.gravel",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>砂石</v>
+      </c>
+      <c r="C34" s="30" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="D34" s="30" t="s">
         <v>53</v>
@@ -3461,48 +4066,61 @@
     </row>
     <row r="38" spans="1:14" ht="27" customHeight="1">
       <c r="A38" s="15"/>
-      <c r="B38" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>27</v>
+      <c r="B38" s="3" t="str">
+        <f>VLOOKUP("note.originalZMeasurements",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>原 Z 测量记录（不参与刚度计算）</v>
+      </c>
+      <c r="C38" s="3" t="str">
+        <f>VLOOKUP("note.originalZMeasurements",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>原 Z 测量记录（不参与刚度计算）</v>
+      </c>
+      <c r="D38" s="3" t="str">
+        <f>VLOOKUP("note.originalZMeasurements",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>原 Z 测量记录（不参与刚度计算）</v>
+      </c>
+      <c r="E38" s="3" t="str">
+        <f>VLOOKUP("note.originalZMeasurements",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>原 Z 测量记录（不参与刚度计算）</v>
+      </c>
+      <c r="F38" s="3" t="str">
+        <f>VLOOKUP("note.originalZMeasurements",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>原 Z 测量记录（不参与刚度计算）</v>
+      </c>
+      <c r="G38" s="3" t="str">
+        <f>VLOOKUP("note.originalZMeasurements",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>原 Z 测量记录（不参与刚度计算）</v>
+      </c>
+      <c r="H38" s="3" t="str">
+        <f>VLOOKUP("note.originalZMeasurements",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>原 Z 测量记录（不参与刚度计算）</v>
+      </c>
+      <c r="I38" s="3" t="str">
+        <f>VLOOKUP("note.originalZMeasurements",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>原 Z 测量记录（不参与刚度计算）</v>
       </c>
       <c r="J38" s="15"/>
     </row>
     <row r="39" spans="1:14" ht="42" customHeight="1">
       <c r="A39" s="15"/>
-      <c r="B39" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E39" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="F39" s="16" t="s">
-        <v>29</v>
+      <c r="B39" s="16" t="str">
+        <f>VLOOKUP("label.surface",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>路面</v>
+      </c>
+      <c r="C39" s="16" t="str">
+        <f>VLOOKUP("label.axle",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>车轴</v>
+      </c>
+      <c r="D39" s="16" t="str">
+        <f>VLOOKUP("label.position",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>位置</v>
+      </c>
+      <c r="E39" s="16" t="str">
+        <f>VLOOKUP("label.arbDeltaZ",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>防倾杆 ΔZ (mm)</v>
+      </c>
+      <c r="F39" s="16" t="str">
+        <f>VLOOKUP("label.originalArmMm",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>原始臂长 (mm)</v>
       </c>
       <c r="G39" s="15"/>
       <c r="H39" s="15"/>
@@ -3511,11 +4129,13 @@
     </row>
     <row r="40" spans="1:14" ht="27" customHeight="1">
       <c r="A40" s="15"/>
-      <c r="B40" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="18" t="s">
-        <v>9</v>
+      <c r="B40" s="18" t="str">
+        <f>VLOOKUP("label.tarmac",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>柏油</v>
+      </c>
+      <c r="C40" s="18" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
       </c>
       <c r="D40" s="18" t="s">
         <v>51</v>
@@ -3533,11 +4153,13 @@
     </row>
     <row r="41" spans="1:14" ht="27" customHeight="1">
       <c r="A41" s="15"/>
-      <c r="B41" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="17" t="s">
-        <v>9</v>
+      <c r="B41" s="17" t="str">
+        <f>VLOOKUP("label.tarmac",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>柏油</v>
+      </c>
+      <c r="C41" s="17" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
       </c>
       <c r="D41" s="17" t="s">
         <v>52</v>
@@ -3555,11 +4177,13 @@
     </row>
     <row r="42" spans="1:14" ht="27" customHeight="1">
       <c r="A42" s="15"/>
-      <c r="B42" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C42" s="18" t="s">
-        <v>9</v>
+      <c r="B42" s="18" t="str">
+        <f>VLOOKUP("label.tarmac",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>柏油</v>
+      </c>
+      <c r="C42" s="18" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
       </c>
       <c r="D42" s="18" t="s">
         <v>53</v>
@@ -3577,11 +4201,13 @@
     </row>
     <row r="43" spans="1:14" ht="27" customHeight="1">
       <c r="A43" s="15"/>
-      <c r="B43" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C43" s="17" t="s">
-        <v>10</v>
+      <c r="B43" s="17" t="str">
+        <f>VLOOKUP("label.tarmac",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>柏油</v>
+      </c>
+      <c r="C43" s="17" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="D43" s="17" t="s">
         <v>51</v>
@@ -3599,11 +4225,13 @@
     </row>
     <row r="44" spans="1:14" ht="27" customHeight="1">
       <c r="A44" s="15"/>
-      <c r="B44" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C44" s="18" t="s">
-        <v>10</v>
+      <c r="B44" s="18" t="str">
+        <f>VLOOKUP("label.tarmac",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>柏油</v>
+      </c>
+      <c r="C44" s="18" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="D44" s="18" t="s">
         <v>52</v>
@@ -3621,11 +4249,13 @@
     </row>
     <row r="45" spans="1:14" ht="27" customHeight="1">
       <c r="A45" s="15"/>
-      <c r="B45" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C45" s="17" t="s">
-        <v>10</v>
+      <c r="B45" s="17" t="str">
+        <f>VLOOKUP("label.tarmac",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>柏油</v>
+      </c>
+      <c r="C45" s="17" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="D45" s="17" t="s">
         <v>53</v>
@@ -3643,11 +4273,13 @@
     </row>
     <row r="46" spans="1:14" ht="27" customHeight="1">
       <c r="A46" s="15"/>
-      <c r="B46" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="C46" s="18" t="s">
-        <v>9</v>
+      <c r="B46" s="18" t="str">
+        <f>VLOOKUP("label.gravel",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>砂石</v>
+      </c>
+      <c r="C46" s="18" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
       </c>
       <c r="D46" s="18" t="s">
         <v>51</v>
@@ -3665,11 +4297,13 @@
     </row>
     <row r="47" spans="1:14" ht="27" customHeight="1">
       <c r="A47" s="15"/>
-      <c r="B47" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C47" s="17" t="s">
-        <v>9</v>
+      <c r="B47" s="17" t="str">
+        <f>VLOOKUP("label.gravel",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>砂石</v>
+      </c>
+      <c r="C47" s="17" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
       </c>
       <c r="D47" s="17" t="s">
         <v>52</v>
@@ -3687,11 +4321,13 @@
     </row>
     <row r="48" spans="1:14" ht="27" customHeight="1">
       <c r="A48" s="15"/>
-      <c r="B48" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="C48" s="18" t="s">
-        <v>9</v>
+      <c r="B48" s="18" t="str">
+        <f>VLOOKUP("label.gravel",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>砂石</v>
+      </c>
+      <c r="C48" s="18" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
       </c>
       <c r="D48" s="18" t="s">
         <v>53</v>
@@ -3709,11 +4345,13 @@
     </row>
     <row r="49" spans="1:10" ht="27" customHeight="1">
       <c r="A49" s="15"/>
-      <c r="B49" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C49" s="17" t="s">
-        <v>10</v>
+      <c r="B49" s="17" t="str">
+        <f>VLOOKUP("label.gravel",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>砂石</v>
+      </c>
+      <c r="C49" s="17" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="D49" s="17" t="s">
         <v>51</v>
@@ -3731,11 +4369,13 @@
     </row>
     <row r="50" spans="1:10" ht="27" customHeight="1">
       <c r="A50" s="15"/>
-      <c r="B50" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="C50" s="18" t="s">
-        <v>10</v>
+      <c r="B50" s="18" t="str">
+        <f>VLOOKUP("label.gravel",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>砂石</v>
+      </c>
+      <c r="C50" s="18" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="D50" s="18" t="s">
         <v>52</v>
@@ -3753,11 +4393,13 @@
     </row>
     <row r="51" spans="1:10" ht="27" customHeight="1">
       <c r="A51" s="15"/>
-      <c r="B51" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C51" s="17" t="s">
-        <v>10</v>
+      <c r="B51" s="17" t="str">
+        <f>VLOOKUP("label.gravel",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>砂石</v>
+      </c>
+      <c r="C51" s="17" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="D51" s="17" t="s">
         <v>53</v>
@@ -3941,59 +4583,59 @@
       <c r="I65" s="15"/>
       <c r="J65" s="15"/>
     </row>
-    <row r="66" spans="1:10" ht="26.1" customHeight="1"/>
-    <row r="67" spans="1:10" ht="26.1" customHeight="1"/>
-    <row r="68" spans="1:10" ht="39.950000000000003" customHeight="1"/>
-    <row r="69" spans="1:10" ht="26.1" customHeight="1"/>
-    <row r="70" spans="1:10" ht="26.1" customHeight="1"/>
-    <row r="71" spans="1:10" ht="26.1" customHeight="1"/>
-    <row r="72" spans="1:10" ht="26.1" customHeight="1"/>
-    <row r="73" spans="1:10" ht="26.1" customHeight="1"/>
-    <row r="74" spans="1:10" ht="26.1" customHeight="1"/>
-    <row r="75" spans="1:10" ht="39.950000000000003" customHeight="1"/>
-    <row r="76" spans="1:10" ht="26.1" customHeight="1"/>
-    <row r="77" spans="1:10" ht="26.1" customHeight="1"/>
-    <row r="78" spans="1:10" ht="26.1" customHeight="1"/>
-    <row r="79" spans="1:10" ht="26.1" customHeight="1"/>
-    <row r="80" spans="1:10" ht="26.1" customHeight="1"/>
-    <row r="81" ht="26.1" customHeight="1"/>
-    <row r="82" ht="39.950000000000003" customHeight="1"/>
-    <row r="83" ht="26.1" customHeight="1"/>
-    <row r="84" ht="26.1" customHeight="1"/>
-    <row r="85" ht="26.1" customHeight="1"/>
-    <row r="86" ht="26.1" customHeight="1"/>
-    <row r="87" ht="26.1" customHeight="1"/>
-    <row r="88" ht="26.1" customHeight="1"/>
-    <row r="89" ht="39.950000000000003" customHeight="1"/>
-    <row r="90" ht="26.1" customHeight="1"/>
-    <row r="91" ht="26.1" customHeight="1"/>
-    <row r="92" ht="26.1" customHeight="1"/>
-    <row r="93" ht="26.1" customHeight="1"/>
-    <row r="94" ht="26.1" customHeight="1"/>
-    <row r="95" ht="26.1" customHeight="1"/>
-    <row r="96" ht="39.950000000000003" customHeight="1"/>
-    <row r="97" ht="26.1" customHeight="1"/>
-    <row r="98" ht="26.1" customHeight="1"/>
-    <row r="99" ht="26.1" customHeight="1"/>
-    <row r="100" ht="26.1" customHeight="1"/>
-    <row r="101" ht="26.1" customHeight="1"/>
-    <row r="102" ht="26.1" customHeight="1"/>
-    <row r="103" ht="39.950000000000003" customHeight="1"/>
-    <row r="104" ht="26.1" customHeight="1"/>
-    <row r="105" ht="26.1" customHeight="1"/>
-    <row r="106" ht="26.1" customHeight="1"/>
-    <row r="107" ht="26.1" customHeight="1"/>
-    <row r="108" ht="26.1" customHeight="1"/>
-    <row r="109" ht="26.1" customHeight="1"/>
-    <row r="110" ht="26.1" customHeight="1"/>
-    <row r="111" ht="26.1" customHeight="1"/>
-    <row r="112" ht="26.1" customHeight="1"/>
-    <row r="113" ht="26.1" customHeight="1"/>
-    <row r="114" ht="26.1" customHeight="1"/>
-    <row r="115" ht="26.1" customHeight="1"/>
-    <row r="116" ht="26.1" customHeight="1"/>
-    <row r="117" ht="26.1" customHeight="1"/>
-    <row r="118" ht="26.1" customHeight="1"/>
+    <row r="66" spans="1:10" ht="26.15" customHeight="1"/>
+    <row r="67" spans="1:10" ht="26.15" customHeight="1"/>
+    <row r="68" spans="1:10" ht="40" customHeight="1"/>
+    <row r="69" spans="1:10" ht="26.15" customHeight="1"/>
+    <row r="70" spans="1:10" ht="26.15" customHeight="1"/>
+    <row r="71" spans="1:10" ht="26.15" customHeight="1"/>
+    <row r="72" spans="1:10" ht="26.15" customHeight="1"/>
+    <row r="73" spans="1:10" ht="26.15" customHeight="1"/>
+    <row r="74" spans="1:10" ht="26.15" customHeight="1"/>
+    <row r="75" spans="1:10" ht="40" customHeight="1"/>
+    <row r="76" spans="1:10" ht="26.15" customHeight="1"/>
+    <row r="77" spans="1:10" ht="26.15" customHeight="1"/>
+    <row r="78" spans="1:10" ht="26.15" customHeight="1"/>
+    <row r="79" spans="1:10" ht="26.15" customHeight="1"/>
+    <row r="80" spans="1:10" ht="26.15" customHeight="1"/>
+    <row r="81" ht="26.15" customHeight="1"/>
+    <row r="82" ht="40" customHeight="1"/>
+    <row r="83" ht="26.15" customHeight="1"/>
+    <row r="84" ht="26.15" customHeight="1"/>
+    <row r="85" ht="26.15" customHeight="1"/>
+    <row r="86" ht="26.15" customHeight="1"/>
+    <row r="87" ht="26.15" customHeight="1"/>
+    <row r="88" ht="26.15" customHeight="1"/>
+    <row r="89" ht="40" customHeight="1"/>
+    <row r="90" ht="26.15" customHeight="1"/>
+    <row r="91" ht="26.15" customHeight="1"/>
+    <row r="92" ht="26.15" customHeight="1"/>
+    <row r="93" ht="26.15" customHeight="1"/>
+    <row r="94" ht="26.15" customHeight="1"/>
+    <row r="95" ht="26.15" customHeight="1"/>
+    <row r="96" ht="40" customHeight="1"/>
+    <row r="97" ht="26.15" customHeight="1"/>
+    <row r="98" ht="26.15" customHeight="1"/>
+    <row r="99" ht="26.15" customHeight="1"/>
+    <row r="100" ht="26.15" customHeight="1"/>
+    <row r="101" ht="26.15" customHeight="1"/>
+    <row r="102" ht="26.15" customHeight="1"/>
+    <row r="103" ht="40" customHeight="1"/>
+    <row r="104" ht="26.15" customHeight="1"/>
+    <row r="105" ht="26.15" customHeight="1"/>
+    <row r="106" ht="26.15" customHeight="1"/>
+    <row r="107" ht="26.15" customHeight="1"/>
+    <row r="108" ht="26.15" customHeight="1"/>
+    <row r="109" ht="26.15" customHeight="1"/>
+    <row r="110" ht="26.15" customHeight="1"/>
+    <row r="111" ht="26.15" customHeight="1"/>
+    <row r="112" ht="26.15" customHeight="1"/>
+    <row r="113" ht="26.15" customHeight="1"/>
+    <row r="114" ht="26.15" customHeight="1"/>
+    <row r="115" ht="26.15" customHeight="1"/>
+    <row r="116" ht="26.15" customHeight="1"/>
+    <row r="117" ht="26.15" customHeight="1"/>
+    <row r="118" ht="26.15" customHeight="1"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="B38:I38"/>
@@ -4006,16 +4648,745 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A9FE79E-695D-4F08-8015-DFBE75C1B903}">
+  <dimension ref="A1:D47"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="38" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B2,C2)</f>
+        <v>角运动比
+(rad/mm)</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B3,C3)</f>
+        <v>arb1 终点 Y
+(m)</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B4,C4)</f>
+        <v>arb1 终点 Z
+(m)</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B5,C5)</f>
+        <v>arb1 起点 Y
+(m)</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B6,C6)</f>
+        <v>arb1 起点 Z
+(m)</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B7,C7)</f>
+        <v>防倾杆</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B8,C8)</f>
+        <v>防倾杆 ΔZ (mm)</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B9,C9)</f>
+        <v>摇臂 Δθ
+(°)</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B10,C10)</f>
+        <v>车轴</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B11,C11)</f>
+        <v>直径
+(mm)</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B12,C12)</f>
+        <v>终点角度
+(°)</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B13,C13)</f>
+        <v>终点半径
+(mm)</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="B14" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B14,C14)</f>
+        <v>等效轮端刚度 (N/mm)</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B15,C15)</f>
+        <v>固定转轴</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B16,C16)</f>
+        <v>前轴</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B17,C17)</f>
+        <v>砂石</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B18,C18)</f>
+        <v>输入</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B19,C19)</f>
+        <v>原始臂长 (mm)</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B20,C20)</f>
+        <v>旧表原值</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="D21" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B21,C21)</f>
+        <v>位置</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="B22" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B22,C22)</f>
+        <v>后轴</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="D23" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B23,C23)</f>
+        <v>设定</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="37" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="D24" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B24,C24)</f>
+        <v>起点角度
+(°)</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B25,C25)</f>
+        <v>起点半径
+(mm)</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="B26" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="D26" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B26,C26)</f>
+        <v>路面</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="37" t="s">
+        <v>127</v>
+      </c>
+      <c r="D27" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B27,C27)</f>
+        <v>柏油</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="B28" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B28,C28)</f>
+        <v>扭转刚度
+(N·m/rad)</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="37" t="s">
+        <v>130</v>
+      </c>
+      <c r="B29" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="D29" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B29,C29)</f>
+        <v>车轮 ΔZ
+(mm)</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="B30" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="C30" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B30,C30)</f>
+        <v>节点使用车身相对坐标（m）；旋转半径按 Y/Z 计算。</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="B31" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="C31" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B31,C31)</f>
+        <v>节点使用车身相对坐标（m）。</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="B32" s="37" t="s">
+        <v>137</v>
+      </c>
+      <c r="C32" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B32,C32)</f>
+        <v>测量 · 每组填写轮行程和 arb1 终点</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="B33" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="C33" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B33,C33)</f>
+        <v>整段角运动比换算值；不代表行程内每一位置的瞬时刚度。</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="37" t="s">
+        <v>140</v>
+      </c>
+      <c r="B34" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="C34" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="D34" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B34,C34)</f>
+        <v>区间等效轮端刚度 · 整段角运动比 · 对侧轮固定</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="B35" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="C35" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B35,C35)</f>
+        <v>原 Z 测量记录（不参与刚度计算）</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="B36" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="C36" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="D36" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B36,C36)</f>
+        <v>起点为 wheeljack 架起、全伸展稳定后的位置；轮行程从同一起点计算。</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="37" t="s">
+        <v>146</v>
+      </c>
+      <c r="B37" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="C37" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B37,C37)</f>
+        <v>黄色单元格为手动输入。</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="B38" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="C38" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="D38" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B38,C38)</f>
+        <v>待补坐标</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="B39" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="C39" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="D39" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B39,C39)</f>
+        <v>无效半径</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="B40" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="C40" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="D40" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B40,C40)</f>
+        <v>待补节点坐标；暂无刚度结果。</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="B41" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="C41" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="D41" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B41,C41)</f>
+        <v>轮行程须大于0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="B42" s="37" t="s">
+        <v>161</v>
+      </c>
+      <c r="C42" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="D42" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B42,C42)</f>
+        <v>待填轮行程</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="B43" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="D43" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B43,C43)</f>
+        <v>Astral · 防倾杆计算</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="37" t="s">
+        <v>165</v>
+      </c>
+      <c r="B44" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C44" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="D44" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B44,C44)</f>
+        <v>Astral · 防倾杆参数</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="B45" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="C45" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="D45" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B45,C45)</f>
+        <v>Astral · 防倾杆刚度</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="B46" s="37" t="s">
+        <v>170</v>
+      </c>
+      <c r="C46" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B46,C46)</f>
+        <v>固定几何 · 生成位置 / 转轴</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="B47" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="C47" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="D47" s="37" t="str">
+        <f>IF(Comparison!$E$1="English",B47,C47)</f>
+        <v>测量 · 各档起点 / 终点</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41BA758-A778-4052-B774-1845C020535F}">
   <sheetPr>
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O157"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.75" customWidth="1"/>
     <col min="2" max="2" width="12.5" customWidth="1"/>
@@ -4023,16 +5394,16 @@
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="13.5" customWidth="1"/>
     <col min="6" max="6" width="13.75" customWidth="1"/>
-    <col min="7" max="7" width="15.625" customWidth="1"/>
+    <col min="7" max="7" width="15.58203125" customWidth="1"/>
     <col min="8" max="10" width="12.5" customWidth="1"/>
-    <col min="11" max="11" width="18.125" customWidth="1"/>
+    <col min="11" max="11" width="18.08203125" customWidth="1"/>
     <col min="12" max="15" width="16" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
     <col min="17" max="17" width="12" customWidth="1"/>
     <col min="18" max="22" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="26.1" customHeight="1">
+    <row r="1" spans="1:15" ht="26.15" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4047,77 +5418,97 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="26.1" customHeight="1">
+    <row r="2" spans="1:15" ht="26.15" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>30</v>
+      <c r="B2" s="3" t="str">
+        <f>VLOOKUP("title.arbCalculations",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆计算</v>
+      </c>
+      <c r="C2" s="3" t="str">
+        <f>VLOOKUP("title.arbCalculations",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆计算</v>
+      </c>
+      <c r="D2" s="3" t="str">
+        <f>VLOOKUP("title.arbCalculations",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆计算</v>
+      </c>
+      <c r="E2" s="3" t="str">
+        <f>VLOOKUP("title.arbCalculations",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆计算</v>
+      </c>
+      <c r="F2" s="3" t="str">
+        <f>VLOOKUP("title.arbCalculations",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆计算</v>
+      </c>
+      <c r="G2" s="3" t="str">
+        <f>VLOOKUP("title.arbCalculations",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆计算</v>
+      </c>
+      <c r="H2" s="3" t="str">
+        <f>VLOOKUP("title.arbCalculations",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆计算</v>
+      </c>
+      <c r="I2" s="3" t="str">
+        <f>VLOOKUP("title.arbCalculations",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆计算</v>
+      </c>
+      <c r="J2" s="3" t="str">
+        <f>VLOOKUP("title.arbCalculations",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆计算</v>
+      </c>
+      <c r="K2" s="3" t="str">
+        <f>VLOOKUP("title.arbCalculations",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆计算</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:15" ht="26.1" customHeight="1">
+    <row r="3" spans="1:15" ht="26.15" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>30</v>
+      <c r="B3" s="3" t="str">
+        <f>VLOOKUP("title.arbCalculations",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆计算</v>
+      </c>
+      <c r="C3" s="3" t="str">
+        <f>VLOOKUP("title.arbCalculations",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆计算</v>
+      </c>
+      <c r="D3" s="3" t="str">
+        <f>VLOOKUP("title.arbCalculations",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆计算</v>
+      </c>
+      <c r="E3" s="3" t="str">
+        <f>VLOOKUP("title.arbCalculations",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆计算</v>
+      </c>
+      <c r="F3" s="3" t="str">
+        <f>VLOOKUP("title.arbCalculations",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆计算</v>
+      </c>
+      <c r="G3" s="3" t="str">
+        <f>VLOOKUP("title.arbCalculations",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆计算</v>
+      </c>
+      <c r="H3" s="3" t="str">
+        <f>VLOOKUP("title.arbCalculations",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆计算</v>
+      </c>
+      <c r="I3" s="3" t="str">
+        <f>VLOOKUP("title.arbCalculations",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆计算</v>
+      </c>
+      <c r="J3" s="3" t="str">
+        <f>VLOOKUP("title.arbCalculations",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆计算</v>
+      </c>
+      <c r="K3" s="3" t="str">
+        <f>VLOOKUP("title.arbCalculations",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>Astral · 防倾杆计算</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="26.1" customHeight="1">
+    <row r="4" spans="1:15" ht="26.15" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -4132,25 +5523,34 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="1:15" ht="39.950000000000003" customHeight="1">
+    <row r="5" spans="1:15" ht="40" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>32</v>
+      <c r="B5" s="2" t="str">
+        <f>VLOOKUP("label.surface",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>路面</v>
+      </c>
+      <c r="C5" s="2" t="str">
+        <f>VLOOKUP("label.axle",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>车轴</v>
+      </c>
+      <c r="D5" s="2" t="str">
+        <f>VLOOKUP("label.position",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>位置</v>
+      </c>
+      <c r="E5" s="2" t="str">
+        <f>VLOOKUP("label.wheelDeltaZMmMultiline",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>车轮 ΔZ
+(mm)</v>
+      </c>
+      <c r="F5" s="2" t="str">
+        <f>VLOOKUP("label.armDeltaAngle",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>摇臂 Δθ
+(°)</v>
+      </c>
+      <c r="G5" s="2" t="str">
+        <f>VLOOKUP("label.angularMotionRatio",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>角运动比
+(rad/mm)</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>54</v>
@@ -4161,29 +5561,40 @@
       <c r="J5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L5" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="M5" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="N5" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="O5" s="27" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="26.1" customHeight="1">
+      <c r="K5" s="2" t="str">
+        <f>VLOOKUP("label.input",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>输入</v>
+      </c>
+      <c r="L5" s="31" t="str">
+        <f>VLOOKUP("label.startAngleDegMultiline",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>起点角度
+(°)</v>
+      </c>
+      <c r="M5" s="31" t="str">
+        <f>VLOOKUP("label.endAngleDeg",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>终点角度
+(°)</v>
+      </c>
+      <c r="N5" s="27" t="str">
+        <f>VLOOKUP("label.startRadiusMmMultiline",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>起点半径
+(mm)</v>
+      </c>
+      <c r="O5" s="27" t="str">
+        <f>VLOOKUP("label.endRadiusMm",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>终点半径
+(mm)</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="26.15" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>9</v>
+      <c r="B6" s="4" t="str">
+        <f>VLOOKUP("label.tarmac",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>柏油</v>
+      </c>
+      <c r="C6" s="4" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>51</v>
@@ -4213,7 +5624,7 @@
         <v>27.729094425927766</v>
       </c>
       <c r="K6" s="13" t="str">
-        <f>IF(COUNT(Parameters!C17:D17,Parameters!F23:I23)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E6)),"待填轮行程",IF(E6&lt;=0,"轮行程须大于0",IF(COUNT(L6:M6)&lt;2,"无效半径",""))))</f>
+        <f>IF(COUNT(Parameters!C17:D17,Parameters!F23:I23)&lt;6,VLOOKUP("status.coordinatesNeeded",Locale!$A$2:$D$47,4,FALSE),IF(NOT(ISNUMBER(E6)),VLOOKUP("status.wheelTravelNeeded",Locale!$A$2:$D$47,4,FALSE),IF(E6&lt;=0,VLOOKUP("status.positiveWheelTravel",Locale!$A$2:$D$47,4,FALSE),IF(COUNT(L6:M6)&lt;2,VLOOKUP("status.invalidRadius",Locale!$A$2:$D$47,4,FALSE),""))))</f>
         <v/>
       </c>
       <c r="L6" s="33">
@@ -4233,13 +5644,15 @@
         <v>167.96725871431008</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="26.1" customHeight="1">
+    <row r="7" spans="1:15" ht="26.15" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>9</v>
+      <c r="B7" s="3" t="str">
+        <f>VLOOKUP("label.tarmac",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>柏油</v>
+      </c>
+      <c r="C7" s="3" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>52</v>
@@ -4269,7 +5682,7 @@
         <v>33.946717541852699</v>
       </c>
       <c r="K7" s="14" t="str">
-        <f>IF(COUNT(Parameters!C17:D17,Parameters!F24:I24)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E7)),"待填轮行程",IF(E7&lt;=0,"轮行程须大于0",IF(COUNT(L7:M7)&lt;2,"无效半径",""))))</f>
+        <f>IF(COUNT(Parameters!C17:D17,Parameters!F24:I24)&lt;6,VLOOKUP("status.coordinatesNeeded",Locale!$A$2:$D$47,4,FALSE),IF(NOT(ISNUMBER(E7)),VLOOKUP("status.wheelTravelNeeded",Locale!$A$2:$D$47,4,FALSE),IF(E7&lt;=0,VLOOKUP("status.positiveWheelTravel",Locale!$A$2:$D$47,4,FALSE),IF(COUNT(L7:M7)&lt;2,VLOOKUP("status.invalidRadius",Locale!$A$2:$D$47,4,FALSE),""))))</f>
         <v/>
       </c>
       <c r="L7" s="34">
@@ -4289,13 +5702,15 @@
         <v>151.16216457830976</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="26.1" customHeight="1">
+    <row r="8" spans="1:15" ht="26.15" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>9</v>
+      <c r="B8" s="4" t="str">
+        <f>VLOOKUP("label.tarmac",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>柏油</v>
+      </c>
+      <c r="C8" s="4" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>53</v>
@@ -4325,7 +5740,7 @@
         <v>45.462303240592291</v>
       </c>
       <c r="K8" s="13" t="str">
-        <f>IF(COUNT(Parameters!C17:D17,Parameters!F25:I25)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E8)),"待填轮行程",IF(E8&lt;=0,"轮行程须大于0",IF(COUNT(L8:M8)&lt;2,"无效半径",""))))</f>
+        <f>IF(COUNT(Parameters!C17:D17,Parameters!F25:I25)&lt;6,VLOOKUP("status.coordinatesNeeded",Locale!$A$2:$D$47,4,FALSE),IF(NOT(ISNUMBER(E8)),VLOOKUP("status.wheelTravelNeeded",Locale!$A$2:$D$47,4,FALSE),IF(E8&lt;=0,VLOOKUP("status.positiveWheelTravel",Locale!$A$2:$D$47,4,FALSE),IF(COUNT(L8:M8)&lt;2,VLOOKUP("status.invalidRadius",Locale!$A$2:$D$47,4,FALSE),""))))</f>
         <v/>
       </c>
       <c r="L8" s="33">
@@ -4345,13 +5760,15 @@
         <v>134.20134127496638</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="26.1" customHeight="1">
+    <row r="9" spans="1:15" ht="26.15" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>10</v>
+      <c r="B9" s="3" t="str">
+        <f>VLOOKUP("label.tarmac",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>柏油</v>
+      </c>
+      <c r="C9" s="3" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>51</v>
@@ -4381,7 +5798,7 @@
         <v>48.413215448426278</v>
       </c>
       <c r="K9" s="14" t="str">
-        <f>IF(COUNT(Parameters!C18:D18,Parameters!F26:I26)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E9)),"待填轮行程",IF(E9&lt;=0,"轮行程须大于0",IF(COUNT(L9:M9)&lt;2,"无效半径",""))))</f>
+        <f>IF(COUNT(Parameters!C18:D18,Parameters!F26:I26)&lt;6,VLOOKUP("status.coordinatesNeeded",Locale!$A$2:$D$47,4,FALSE),IF(NOT(ISNUMBER(E9)),VLOOKUP("status.wheelTravelNeeded",Locale!$A$2:$D$47,4,FALSE),IF(E9&lt;=0,VLOOKUP("status.positiveWheelTravel",Locale!$A$2:$D$47,4,FALSE),IF(COUNT(L9:M9)&lt;2,VLOOKUP("status.invalidRadius",Locale!$A$2:$D$47,4,FALSE),""))))</f>
         <v/>
       </c>
       <c r="L9" s="34">
@@ -4401,13 +5818,15 @@
         <v>160.79800993793438</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="26.1" customHeight="1">
+    <row r="10" spans="1:15" ht="26.15" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>10</v>
+      <c r="B10" s="4" t="str">
+        <f>VLOOKUP("label.tarmac",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>柏油</v>
+      </c>
+      <c r="C10" s="4" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>52</v>
@@ -4437,7 +5856,7 @@
         <v>60.200403343164751</v>
       </c>
       <c r="K10" s="13" t="str">
-        <f>IF(COUNT(Parameters!C18:D18,Parameters!F27:I27)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E10)),"待填轮行程",IF(E10&lt;=0,"轮行程须大于0",IF(COUNT(L10:M10)&lt;2,"无效半径",""))))</f>
+        <f>IF(COUNT(Parameters!C18:D18,Parameters!F27:I27)&lt;6,VLOOKUP("status.coordinatesNeeded",Locale!$A$2:$D$47,4,FALSE),IF(NOT(ISNUMBER(E10)),VLOOKUP("status.wheelTravelNeeded",Locale!$A$2:$D$47,4,FALSE),IF(E10&lt;=0,VLOOKUP("status.positiveWheelTravel",Locale!$A$2:$D$47,4,FALSE),IF(COUNT(L10:M10)&lt;2,VLOOKUP("status.invalidRadius",Locale!$A$2:$D$47,4,FALSE),""))))</f>
         <v/>
       </c>
       <c r="L10" s="33">
@@ -4457,13 +5876,15 @@
         <v>146.98639392814576</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="26.1" customHeight="1">
+    <row r="11" spans="1:15" ht="26.15" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>10</v>
+      <c r="B11" s="3" t="str">
+        <f>VLOOKUP("label.tarmac",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>柏油</v>
+      </c>
+      <c r="C11" s="3" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>53</v>
@@ -4493,7 +5914,7 @@
         <v>78.913646201091169</v>
       </c>
       <c r="K11" s="14" t="str">
-        <f>IF(COUNT(Parameters!C18:D18,Parameters!F28:I28)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E11)),"待填轮行程",IF(E11&lt;=0,"轮行程须大于0",IF(COUNT(L11:M11)&lt;2,"无效半径",""))))</f>
+        <f>IF(COUNT(Parameters!C18:D18,Parameters!F28:I28)&lt;6,VLOOKUP("status.coordinatesNeeded",Locale!$A$2:$D$47,4,FALSE),IF(NOT(ISNUMBER(E11)),VLOOKUP("status.wheelTravelNeeded",Locale!$A$2:$D$47,4,FALSE),IF(E11&lt;=0,VLOOKUP("status.positiveWheelTravel",Locale!$A$2:$D$47,4,FALSE),IF(COUNT(L11:M11)&lt;2,VLOOKUP("status.invalidRadius",Locale!$A$2:$D$47,4,FALSE),""))))</f>
         <v/>
       </c>
       <c r="L11" s="34">
@@ -4513,13 +5934,15 @@
         <v>133.09019498069733</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="26.1" customHeight="1">
+    <row r="12" spans="1:15" ht="26.15" customHeight="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>68</v>
+      <c r="B12" s="4" t="str">
+        <f>VLOOKUP("label.gravel",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>砂石</v>
+      </c>
+      <c r="C12" s="4" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>51</v>
@@ -4549,7 +5972,7 @@
         <v>30.023313637124545</v>
       </c>
       <c r="K12" s="13" t="str">
-        <f>IF(COUNT(Parameters!C17:D17,Parameters!F29:I29)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E12)),"待填轮行程",IF(E12&lt;=0,"轮行程须大于0",IF(COUNT(L12:M12)&lt;2,"无效半径",""))))</f>
+        <f>IF(COUNT(Parameters!C17:D17,Parameters!F29:I29)&lt;6,VLOOKUP("status.coordinatesNeeded",Locale!$A$2:$D$47,4,FALSE),IF(NOT(ISNUMBER(E12)),VLOOKUP("status.wheelTravelNeeded",Locale!$A$2:$D$47,4,FALSE),IF(E12&lt;=0,VLOOKUP("status.positiveWheelTravel",Locale!$A$2:$D$47,4,FALSE),IF(COUNT(L12:M12)&lt;2,VLOOKUP("status.invalidRadius",Locale!$A$2:$D$47,4,FALSE),""))))</f>
         <v/>
       </c>
       <c r="L12" s="33">
@@ -4569,16 +5992,18 @@
         <v>167.86303941010956</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="26.1" customHeight="1">
+    <row r="13" spans="1:15" ht="26.15" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>9</v>
+      <c r="B13" s="3" t="str">
+        <f>VLOOKUP("label.gravel",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>砂石</v>
+      </c>
+      <c r="C13" s="3" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E13" s="8">
         <f>IF(ISNUMBER(Parameters!E30),Parameters!E30,"")</f>
@@ -4605,7 +6030,7 @@
         <v>35.314527839159076</v>
       </c>
       <c r="K13" s="14" t="str">
-        <f>IF(COUNT(Parameters!C17:D17,Parameters!F30:I30)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E13)),"待填轮行程",IF(E13&lt;=0,"轮行程须大于0",IF(COUNT(L13:M13)&lt;2,"无效半径",""))))</f>
+        <f>IF(COUNT(Parameters!C17:D17,Parameters!F30:I30)&lt;6,VLOOKUP("status.coordinatesNeeded",Locale!$A$2:$D$47,4,FALSE),IF(NOT(ISNUMBER(E13)),VLOOKUP("status.wheelTravelNeeded",Locale!$A$2:$D$47,4,FALSE),IF(E13&lt;=0,VLOOKUP("status.positiveWheelTravel",Locale!$A$2:$D$47,4,FALSE),IF(COUNT(L13:M13)&lt;2,VLOOKUP("status.invalidRadius",Locale!$A$2:$D$47,4,FALSE),""))))</f>
         <v/>
       </c>
       <c r="L13" s="34">
@@ -4625,13 +6050,15 @@
         <v>151.23822268196622</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="26.1" customHeight="1">
+    <row r="14" spans="1:15" ht="26.15" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>9</v>
+      <c r="B14" s="4" t="str">
+        <f>VLOOKUP("label.gravel",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>砂石</v>
+      </c>
+      <c r="C14" s="4" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>53</v>
@@ -4661,7 +6088,7 @@
         <v>41.87307811988596</v>
       </c>
       <c r="K14" s="13" t="str">
-        <f>IF(COUNT(Parameters!C17:D17,Parameters!F31:I31)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E14)),"待填轮行程",IF(E14&lt;=0,"轮行程须大于0",IF(COUNT(L14:M14)&lt;2,"无效半径",""))))</f>
+        <f>IF(COUNT(Parameters!C17:D17,Parameters!F31:I31)&lt;6,VLOOKUP("status.coordinatesNeeded",Locale!$A$2:$D$47,4,FALSE),IF(NOT(ISNUMBER(E14)),VLOOKUP("status.wheelTravelNeeded",Locale!$A$2:$D$47,4,FALSE),IF(E14&lt;=0,VLOOKUP("status.positiveWheelTravel",Locale!$A$2:$D$47,4,FALSE),IF(COUNT(L14:M14)&lt;2,VLOOKUP("status.invalidRadius",Locale!$A$2:$D$47,4,FALSE),""))))</f>
         <v/>
       </c>
       <c r="L14" s="33">
@@ -4681,13 +6108,15 @@
         <v>133.70115930686603</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="26.1" customHeight="1">
+    <row r="15" spans="1:15" ht="26.15" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>10</v>
+      <c r="B15" s="3" t="str">
+        <f>VLOOKUP("label.gravel",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>砂石</v>
+      </c>
+      <c r="C15" s="3" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>51</v>
@@ -4717,7 +6146,7 @@
         <v>47.50624777926771</v>
       </c>
       <c r="K15" s="14" t="str">
-        <f>IF(COUNT(Parameters!C18:D18,Parameters!F32:I32)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E15)),"待填轮行程",IF(E15&lt;=0,"轮行程须大于0",IF(COUNT(L15:M15)&lt;2,"无效半径",""))))</f>
+        <f>IF(COUNT(Parameters!C18:D18,Parameters!F32:I32)&lt;6,VLOOKUP("status.coordinatesNeeded",Locale!$A$2:$D$47,4,FALSE),IF(NOT(ISNUMBER(E15)),VLOOKUP("status.wheelTravelNeeded",Locale!$A$2:$D$47,4,FALSE),IF(E15&lt;=0,VLOOKUP("status.positiveWheelTravel",Locale!$A$2:$D$47,4,FALSE),IF(COUNT(L15:M15)&lt;2,VLOOKUP("status.invalidRadius",Locale!$A$2:$D$47,4,FALSE),""))))</f>
         <v/>
       </c>
       <c r="L15" s="34">
@@ -4737,13 +6166,15 @@
         <v>161.18622769951543</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="26.1" customHeight="1">
+    <row r="16" spans="1:15" ht="26.15" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>10</v>
+      <c r="B16" s="4" t="str">
+        <f>VLOOKUP("label.gravel",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>砂石</v>
+      </c>
+      <c r="C16" s="4" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>52</v>
@@ -4773,7 +6204,7 @@
         <v>57.856774277620552</v>
       </c>
       <c r="K16" s="13" t="str">
-        <f>IF(COUNT(Parameters!C18:D18,Parameters!F33:I33)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E16)),"待填轮行程",IF(E16&lt;=0,"轮行程须大于0",IF(COUNT(L16:M16)&lt;2,"无效半径",""))))</f>
+        <f>IF(COUNT(Parameters!C18:D18,Parameters!F33:I33)&lt;6,VLOOKUP("status.coordinatesNeeded",Locale!$A$2:$D$47,4,FALSE),IF(NOT(ISNUMBER(E16)),VLOOKUP("status.wheelTravelNeeded",Locale!$A$2:$D$47,4,FALSE),IF(E16&lt;=0,VLOOKUP("status.positiveWheelTravel",Locale!$A$2:$D$47,4,FALSE),IF(COUNT(L16:M16)&lt;2,VLOOKUP("status.invalidRadius",Locale!$A$2:$D$47,4,FALSE),""))))</f>
         <v/>
       </c>
       <c r="L16" s="33">
@@ -4793,13 +6224,15 @@
         <v>146.41379716406522</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="26.1" customHeight="1">
+    <row r="17" spans="1:15" ht="26.15" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>10</v>
+      <c r="B17" s="3" t="str">
+        <f>VLOOKUP("label.gravel",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>砂石</v>
+      </c>
+      <c r="C17" s="3" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>53</v>
@@ -4829,7 +6262,7 @@
         <v>72.924800326461153</v>
       </c>
       <c r="K17" s="14" t="str">
-        <f>IF(COUNT(Parameters!C18:D18,Parameters!F34:I34)&lt;6,"待补坐标",IF(NOT(ISNUMBER(E17)),"待填轮行程",IF(E17&lt;=0,"轮行程须大于0",IF(COUNT(L17:M17)&lt;2,"无效半径",""))))</f>
+        <f>IF(COUNT(Parameters!C18:D18,Parameters!F34:I34)&lt;6,VLOOKUP("status.coordinatesNeeded",Locale!$A$2:$D$47,4,FALSE),IF(NOT(ISNUMBER(E17)),VLOOKUP("status.wheelTravelNeeded",Locale!$A$2:$D$47,4,FALSE),IF(E17&lt;=0,VLOOKUP("status.positiveWheelTravel",Locale!$A$2:$D$47,4,FALSE),IF(COUNT(L17:M17)&lt;2,VLOOKUP("status.invalidRadius",Locale!$A$2:$D$47,4,FALSE),""))))</f>
         <v/>
       </c>
       <c r="L17" s="34">
@@ -4849,7 +6282,7 @@
         <v>132.38202294873727</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="26.1" customHeight="1">
+    <row r="18" spans="1:15" ht="26.15" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -4864,7 +6297,7 @@
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
     </row>
-    <row r="19" spans="1:15" ht="26.1" customHeight="1">
+    <row r="19" spans="1:15" ht="26.15" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -4879,7 +6312,7 @@
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
     </row>
-    <row r="20" spans="1:15" ht="26.1" customHeight="1">
+    <row r="20" spans="1:15" ht="26.15" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -4894,7 +6327,7 @@
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
     </row>
-    <row r="21" spans="1:15" ht="26.1" customHeight="1">
+    <row r="21" spans="1:15" ht="26.15" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -4909,16 +6342,19 @@
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
     </row>
-    <row r="22" spans="1:15" ht="39.950000000000003" customHeight="1">
+    <row r="22" spans="1:15" ht="40" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>10</v>
+      <c r="B22" s="2" t="str">
+        <f>VLOOKUP("label.setting",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>设定</v>
+      </c>
+      <c r="C22" s="2" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
+      </c>
+      <c r="D22" s="2" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -4930,7 +6366,7 @@
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
     </row>
-    <row r="23" spans="1:15" ht="26.1" customHeight="1">
+    <row r="23" spans="1:15" ht="26.15" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="3" t="s">
         <v>59</v>
@@ -4953,7 +6389,7 @@
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="26.1" customHeight="1">
+    <row r="24" spans="1:15" ht="26.15" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="4" t="s">
         <v>60</v>
@@ -4976,7 +6412,7 @@
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
     </row>
-    <row r="25" spans="1:15" ht="26.1" customHeight="1">
+    <row r="25" spans="1:15" ht="26.15" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="3" t="s">
         <v>61</v>
@@ -4999,7 +6435,7 @@
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
     </row>
-    <row r="26" spans="1:15" ht="26.1" customHeight="1">
+    <row r="26" spans="1:15" ht="26.15" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="4" t="s">
         <v>62</v>
@@ -5022,7 +6458,7 @@
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
     </row>
-    <row r="27" spans="1:15" ht="26.1" customHeight="1">
+    <row r="27" spans="1:15" ht="26.15" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="3" t="s">
         <v>63</v>
@@ -5045,7 +6481,7 @@
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
     </row>
-    <row r="28" spans="1:15" ht="26.1" customHeight="1">
+    <row r="28" spans="1:15" ht="26.15" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="4" t="s">
         <v>64</v>
@@ -5068,7 +6504,7 @@
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
     </row>
-    <row r="29" spans="1:15" ht="26.1" customHeight="1">
+    <row r="29" spans="1:15" ht="26.15" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="3" t="s">
         <v>65</v>
@@ -5091,7 +6527,7 @@
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
     </row>
-    <row r="30" spans="1:15" ht="26.1" customHeight="1">
+    <row r="30" spans="1:15" ht="26.15" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="4" t="s">
         <v>66</v>
@@ -5114,7 +6550,7 @@
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
     </row>
-    <row r="31" spans="1:15" ht="26.1" customHeight="1">
+    <row r="31" spans="1:15" ht="26.15" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="3" t="s">
         <v>67</v>
@@ -5137,7 +6573,7 @@
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
     </row>
-    <row r="32" spans="1:15" ht="26.1" customHeight="1">
+    <row r="32" spans="1:15" ht="26.15" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -5152,7 +6588,7 @@
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
     </row>
-    <row r="33" spans="1:13" ht="26.1" customHeight="1">
+    <row r="33" spans="1:13" ht="26.15" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -5167,7 +6603,7 @@
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
     </row>
-    <row r="34" spans="1:13" ht="26.1" customHeight="1">
+    <row r="34" spans="1:13" ht="26.15" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -5182,16 +6618,19 @@
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
     </row>
-    <row r="35" spans="1:13" ht="39.950000000000003" customHeight="1">
+    <row r="35" spans="1:13" ht="40" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>10</v>
+      <c r="B35" s="2" t="str">
+        <f>VLOOKUP("label.setting",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>设定</v>
+      </c>
+      <c r="C35" s="2" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>前轴</v>
+      </c>
+      <c r="D35" s="2" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
@@ -5203,7 +6642,7 @@
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
     </row>
-    <row r="36" spans="1:13" ht="26.1" customHeight="1">
+    <row r="36" spans="1:13" ht="26.15" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="4" t="s">
         <v>59</v>
@@ -5226,7 +6665,7 @@
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
     </row>
-    <row r="37" spans="1:13" ht="26.1" customHeight="1">
+    <row r="37" spans="1:13" ht="26.15" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="3" t="s">
         <v>60</v>
@@ -5249,7 +6688,7 @@
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
     </row>
-    <row r="38" spans="1:13" ht="26.1" customHeight="1">
+    <row r="38" spans="1:13" ht="26.15" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="4" t="s">
         <v>61</v>
@@ -5272,7 +6711,7 @@
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
     </row>
-    <row r="39" spans="1:13" ht="26.1" customHeight="1">
+    <row r="39" spans="1:13" ht="26.15" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="3" t="s">
         <v>62</v>
@@ -5295,7 +6734,7 @@
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
     </row>
-    <row r="40" spans="1:13" ht="26.1" customHeight="1">
+    <row r="40" spans="1:13" ht="26.15" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="4" t="s">
         <v>63</v>
@@ -5318,7 +6757,7 @@
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
     </row>
-    <row r="41" spans="1:13" ht="26.1" customHeight="1">
+    <row r="41" spans="1:13" ht="26.15" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="3" t="s">
         <v>64</v>
@@ -5341,7 +6780,7 @@
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
     </row>
-    <row r="42" spans="1:13" ht="26.1" customHeight="1">
+    <row r="42" spans="1:13" ht="26.15" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="4" t="s">
         <v>65</v>
@@ -5364,7 +6803,7 @@
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
     </row>
-    <row r="43" spans="1:13" ht="26.1" customHeight="1">
+    <row r="43" spans="1:13" ht="26.15" customHeight="1">
       <c r="A43" s="1"/>
       <c r="B43" s="3" t="s">
         <v>66</v>
@@ -5387,7 +6826,7 @@
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
     </row>
-    <row r="44" spans="1:13" ht="26.1" customHeight="1">
+    <row r="44" spans="1:13" ht="26.15" customHeight="1">
       <c r="A44" s="1"/>
       <c r="B44" s="4" t="s">
         <v>67</v>
@@ -5410,7 +6849,7 @@
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
     </row>
-    <row r="45" spans="1:13" ht="26.1" customHeight="1">
+    <row r="45" spans="1:13" ht="26.15" customHeight="1">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -5425,7 +6864,7 @@
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
     </row>
-    <row r="46" spans="1:13" ht="26.1" customHeight="1">
+    <row r="46" spans="1:13" ht="26.15" customHeight="1">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -5440,7 +6879,7 @@
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
     </row>
-    <row r="47" spans="1:13" ht="26.1" customHeight="1">
+    <row r="47" spans="1:13" ht="26.15" customHeight="1">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -5455,7 +6894,7 @@
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
     </row>
-    <row r="48" spans="1:13" ht="26.1" customHeight="1">
+    <row r="48" spans="1:13" ht="26.15" customHeight="1">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -5470,16 +6909,19 @@
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
     </row>
-    <row r="49" spans="1:13" ht="26.1" customHeight="1">
+    <row r="49" spans="1:13" ht="26.15" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="C49" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="D49" s="41" t="s">
-        <v>35</v>
+      <c r="B49" s="2" t="str">
+        <f>VLOOKUP("label.originalTableValue",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>旧表原值</v>
+      </c>
+      <c r="C49" s="2" t="str">
+        <f>VLOOKUP("label.originalTableValue",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>旧表原值</v>
+      </c>
+      <c r="D49" s="2" t="str">
+        <f>VLOOKUP("label.originalTableValue",Locale!$A$2:$D$47,4,FALSE)</f>
+        <v>旧表原值</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -5491,7 +6933,7 @@
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
     </row>
-    <row r="50" spans="1:13" ht="26.1" customHeight="1">
+    <row r="50" spans="1:13" ht="26.15" customHeight="1">
       <c r="A50" s="1"/>
       <c r="B50" s="1" t="s">
         <v>36</v>
@@ -5510,7 +6952,7 @@
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
     </row>
-    <row r="51" spans="1:13" ht="26.1" customHeight="1">
+    <row r="51" spans="1:13" ht="26.15" customHeight="1">
       <c r="A51" s="1"/>
       <c r="B51" s="1" t="s">
         <v>37</v>
@@ -5529,7 +6971,7 @@
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
     </row>
-    <row r="52" spans="1:13" ht="26.1" customHeight="1">
+    <row r="52" spans="1:13" ht="26.15" customHeight="1">
       <c r="A52" s="1"/>
       <c r="B52" s="1" t="s">
         <v>38</v>
@@ -5548,7 +6990,7 @@
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
     </row>
-    <row r="53" spans="1:13" ht="26.1" customHeight="1">
+    <row r="53" spans="1:13" ht="26.15" customHeight="1">
       <c r="A53" s="1"/>
       <c r="B53" s="1" t="s">
         <v>39</v>
@@ -5567,7 +7009,7 @@
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
     </row>
-    <row r="54" spans="1:13" ht="26.1" customHeight="1">
+    <row r="54" spans="1:13" ht="26.15" customHeight="1">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
         <v>40</v>
@@ -5586,7 +7028,7 @@
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
     </row>
-    <row r="55" spans="1:13" ht="26.1" customHeight="1">
+    <row r="55" spans="1:13" ht="26.15" customHeight="1">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="s">
         <v>41</v>
@@ -5605,7 +7047,7 @@
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
     </row>
-    <row r="56" spans="1:13" ht="26.1" customHeight="1">
+    <row r="56" spans="1:13" ht="26.15" customHeight="1">
       <c r="A56" s="1"/>
       <c r="B56" s="1" t="s">
         <v>42</v>
@@ -5624,7 +7066,7 @@
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
     </row>
-    <row r="57" spans="1:13" ht="26.1" customHeight="1">
+    <row r="57" spans="1:13" ht="26.15" customHeight="1">
       <c r="A57" s="1"/>
       <c r="B57" s="1" t="s">
         <v>43</v>
@@ -5643,7 +7085,7 @@
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
     </row>
-    <row r="58" spans="1:13" ht="26.1" customHeight="1">
+    <row r="58" spans="1:13" ht="26.15" customHeight="1">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -5658,7 +7100,7 @@
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
     </row>
-    <row r="59" spans="1:13" ht="26.1" customHeight="1">
+    <row r="59" spans="1:13" ht="26.15" customHeight="1">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -5673,7 +7115,7 @@
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
     </row>
-    <row r="60" spans="1:13" ht="26.1" customHeight="1">
+    <row r="60" spans="1:13" ht="26.15" customHeight="1">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -5688,7 +7130,7 @@
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
     </row>
-    <row r="61" spans="1:13" ht="26.1" customHeight="1">
+    <row r="61" spans="1:13" ht="26.15" customHeight="1">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -5703,7 +7145,7 @@
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
     </row>
-    <row r="62" spans="1:13" ht="26.1" customHeight="1">
+    <row r="62" spans="1:13" ht="26.15" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -5718,7 +7160,7 @@
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
     </row>
-    <row r="63" spans="1:13" ht="26.1" customHeight="1">
+    <row r="63" spans="1:13" ht="26.15" customHeight="1">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -5733,7 +7175,7 @@
       <c r="L63" s="1"/>
       <c r="M63" s="1"/>
     </row>
-    <row r="64" spans="1:13" ht="26.1" customHeight="1">
+    <row r="64" spans="1:13" ht="26.15" customHeight="1">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -5748,7 +7190,7 @@
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
     </row>
-    <row r="65" spans="1:13" ht="26.1" customHeight="1">
+    <row r="65" spans="1:13" ht="26.15" customHeight="1">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -5763,7 +7205,7 @@
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
     </row>
-    <row r="66" spans="1:13" ht="26.1" customHeight="1">
+    <row r="66" spans="1:13" ht="26.15" customHeight="1">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -5778,7 +7220,7 @@
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
     </row>
-    <row r="67" spans="1:13" ht="26.1" customHeight="1">
+    <row r="67" spans="1:13" ht="26.15" customHeight="1">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -5793,7 +7235,7 @@
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
     </row>
-    <row r="68" spans="1:13" ht="26.1" customHeight="1">
+    <row r="68" spans="1:13" ht="26.15" customHeight="1">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -5808,7 +7250,7 @@
       <c r="L68" s="1"/>
       <c r="M68" s="1"/>
     </row>
-    <row r="69" spans="1:13" ht="26.1" customHeight="1">
+    <row r="69" spans="1:13" ht="26.15" customHeight="1">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -5823,7 +7265,7 @@
       <c r="L69" s="1"/>
       <c r="M69" s="1"/>
     </row>
-    <row r="70" spans="1:13" ht="26.1" customHeight="1">
+    <row r="70" spans="1:13" ht="26.15" customHeight="1">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -5838,7 +7280,7 @@
       <c r="L70" s="1"/>
       <c r="M70" s="1"/>
     </row>
-    <row r="71" spans="1:13" ht="26.1" customHeight="1">
+    <row r="71" spans="1:13" ht="26.15" customHeight="1">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -5853,7 +7295,7 @@
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
     </row>
-    <row r="72" spans="1:13" ht="26.1" customHeight="1">
+    <row r="72" spans="1:13" ht="26.15" customHeight="1">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -5868,7 +7310,7 @@
       <c r="L72" s="1"/>
       <c r="M72" s="1"/>
     </row>
-    <row r="73" spans="1:13" ht="26.1" customHeight="1">
+    <row r="73" spans="1:13" ht="26.15" customHeight="1">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -5883,7 +7325,7 @@
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
     </row>
-    <row r="74" spans="1:13" ht="26.1" customHeight="1">
+    <row r="74" spans="1:13" ht="26.15" customHeight="1">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -5898,7 +7340,7 @@
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
     </row>
-    <row r="75" spans="1:13" ht="26.1" customHeight="1">
+    <row r="75" spans="1:13" ht="26.15" customHeight="1">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -5913,7 +7355,7 @@
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
     </row>
-    <row r="76" spans="1:13" ht="26.1" customHeight="1">
+    <row r="76" spans="1:13" ht="26.15" customHeight="1">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -5928,7 +7370,7 @@
       <c r="L76" s="1"/>
       <c r="M76" s="1"/>
     </row>
-    <row r="77" spans="1:13" ht="26.1" customHeight="1">
+    <row r="77" spans="1:13" ht="26.15" customHeight="1">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -5943,7 +7385,7 @@
       <c r="L77" s="1"/>
       <c r="M77" s="1"/>
     </row>
-    <row r="78" spans="1:13" ht="26.1" customHeight="1">
+    <row r="78" spans="1:13" ht="26.15" customHeight="1">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -5958,7 +7400,7 @@
       <c r="L78" s="1"/>
       <c r="M78" s="1"/>
     </row>
-    <row r="79" spans="1:13" ht="26.1" customHeight="1">
+    <row r="79" spans="1:13" ht="26.15" customHeight="1">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -5973,7 +7415,7 @@
       <c r="L79" s="1"/>
       <c r="M79" s="1"/>
     </row>
-    <row r="80" spans="1:13" ht="26.1" customHeight="1">
+    <row r="80" spans="1:13" ht="26.15" customHeight="1">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -5988,7 +7430,7 @@
       <c r="L80" s="1"/>
       <c r="M80" s="1"/>
     </row>
-    <row r="81" spans="1:13" ht="26.1" customHeight="1">
+    <row r="81" spans="1:13" ht="26.15" customHeight="1">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -6003,7 +7445,7 @@
       <c r="L81" s="1"/>
       <c r="M81" s="1"/>
     </row>
-    <row r="82" spans="1:13" ht="26.1" customHeight="1">
+    <row r="82" spans="1:13" ht="26.15" customHeight="1">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -6018,7 +7460,7 @@
       <c r="L82" s="1"/>
       <c r="M82" s="1"/>
     </row>
-    <row r="83" spans="1:13" ht="26.1" customHeight="1">
+    <row r="83" spans="1:13" ht="26.15" customHeight="1">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -6033,7 +7475,7 @@
       <c r="L83" s="1"/>
       <c r="M83" s="1"/>
     </row>
-    <row r="84" spans="1:13" ht="26.1" customHeight="1">
+    <row r="84" spans="1:13" ht="26.15" customHeight="1">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -6048,7 +7490,7 @@
       <c r="L84" s="1"/>
       <c r="M84" s="1"/>
     </row>
-    <row r="85" spans="1:13" ht="26.1" customHeight="1">
+    <row r="85" spans="1:13" ht="26.15" customHeight="1">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -6063,7 +7505,7 @@
       <c r="L85" s="1"/>
       <c r="M85" s="1"/>
     </row>
-    <row r="86" spans="1:13" ht="26.1" customHeight="1">
+    <row r="86" spans="1:13" ht="26.15" customHeight="1">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -6078,7 +7520,7 @@
       <c r="L86" s="1"/>
       <c r="M86" s="1"/>
     </row>
-    <row r="87" spans="1:13" ht="26.1" customHeight="1">
+    <row r="87" spans="1:13" ht="26.15" customHeight="1">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -6093,7 +7535,7 @@
       <c r="L87" s="1"/>
       <c r="M87" s="1"/>
     </row>
-    <row r="88" spans="1:13" ht="26.1" customHeight="1">
+    <row r="88" spans="1:13" ht="26.15" customHeight="1">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -6108,7 +7550,7 @@
       <c r="L88" s="1"/>
       <c r="M88" s="1"/>
     </row>
-    <row r="89" spans="1:13" ht="26.1" customHeight="1">
+    <row r="89" spans="1:13" ht="26.15" customHeight="1">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -6123,7 +7565,7 @@
       <c r="L89" s="1"/>
       <c r="M89" s="1"/>
     </row>
-    <row r="90" spans="1:13" ht="26.1" customHeight="1">
+    <row r="90" spans="1:13" ht="26.15" customHeight="1">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -6138,73 +7580,73 @@
       <c r="L90" s="1"/>
       <c r="M90" s="1"/>
     </row>
-    <row r="91" spans="1:13" ht="21.95" customHeight="1"/>
-    <row r="92" spans="1:13" ht="21.95" customHeight="1"/>
-    <row r="93" spans="1:13" ht="21.95" customHeight="1"/>
-    <row r="94" spans="1:13" ht="21.95" customHeight="1"/>
-    <row r="95" spans="1:13" ht="21.95" customHeight="1"/>
-    <row r="96" spans="1:13" ht="21.95" customHeight="1"/>
-    <row r="97" ht="21.95" customHeight="1"/>
-    <row r="98" ht="21.95" customHeight="1"/>
-    <row r="99" ht="21.95" customHeight="1"/>
-    <row r="100" ht="21.95" customHeight="1"/>
-    <row r="101" ht="21.95" customHeight="1"/>
-    <row r="102" ht="21.95" customHeight="1"/>
-    <row r="103" ht="21.95" customHeight="1"/>
-    <row r="104" ht="21.95" customHeight="1"/>
-    <row r="105" ht="21.95" customHeight="1"/>
-    <row r="106" ht="21.95" customHeight="1"/>
-    <row r="107" ht="21.95" customHeight="1"/>
-    <row r="108" ht="21.95" customHeight="1"/>
-    <row r="109" ht="21.95" customHeight="1"/>
-    <row r="110" ht="21.95" customHeight="1"/>
-    <row r="111" ht="21.95" customHeight="1"/>
-    <row r="112" ht="21.95" customHeight="1"/>
-    <row r="113" ht="21.95" customHeight="1"/>
-    <row r="114" ht="21.95" customHeight="1"/>
-    <row r="115" ht="21.95" customHeight="1"/>
-    <row r="116" ht="21.95" customHeight="1"/>
-    <row r="117" ht="21.95" customHeight="1"/>
-    <row r="118" ht="21.95" customHeight="1"/>
-    <row r="119" ht="21.95" customHeight="1"/>
-    <row r="120" ht="21.95" customHeight="1"/>
-    <row r="121" ht="21.95" customHeight="1"/>
-    <row r="122" ht="21.95" customHeight="1"/>
-    <row r="123" ht="21.95" customHeight="1"/>
-    <row r="124" ht="35.1" customHeight="1"/>
-    <row r="125" ht="21.95" customHeight="1"/>
-    <row r="126" ht="21.95" customHeight="1"/>
-    <row r="127" ht="21.95" customHeight="1"/>
-    <row r="128" ht="21.95" customHeight="1"/>
-    <row r="129" ht="21.95" customHeight="1"/>
-    <row r="130" ht="21.95" customHeight="1"/>
-    <row r="131" ht="21.95" customHeight="1"/>
-    <row r="132" ht="21.95" customHeight="1"/>
-    <row r="133" ht="21.95" customHeight="1"/>
-    <row r="134" ht="21.95" customHeight="1"/>
-    <row r="135" ht="21.95" customHeight="1"/>
-    <row r="136" ht="21.95" customHeight="1"/>
-    <row r="137" ht="21.95" customHeight="1"/>
-    <row r="138" ht="21.95" customHeight="1"/>
-    <row r="139" ht="21.95" customHeight="1"/>
-    <row r="140" ht="21.95" customHeight="1"/>
-    <row r="141" ht="21.95" customHeight="1"/>
-    <row r="142" ht="21.95" customHeight="1"/>
-    <row r="143" ht="21.95" customHeight="1"/>
-    <row r="144" ht="21.95" customHeight="1"/>
-    <row r="145" ht="21.95" customHeight="1"/>
-    <row r="146" ht="21.95" customHeight="1"/>
-    <row r="147" ht="21.95" customHeight="1"/>
-    <row r="148" ht="21.95" customHeight="1"/>
-    <row r="149" ht="21.95" customHeight="1"/>
-    <row r="150" ht="21.95" customHeight="1"/>
-    <row r="151" ht="21.95" customHeight="1"/>
-    <row r="152" ht="21.95" customHeight="1"/>
-    <row r="153" ht="21.95" customHeight="1"/>
-    <row r="154" ht="21.95" customHeight="1"/>
-    <row r="155" ht="21.95" customHeight="1"/>
-    <row r="156" ht="21.95" customHeight="1"/>
-    <row r="157" ht="21.95" customHeight="1"/>
+    <row r="91" spans="1:13" ht="22" customHeight="1"/>
+    <row r="92" spans="1:13" ht="22" customHeight="1"/>
+    <row r="93" spans="1:13" ht="22" customHeight="1"/>
+    <row r="94" spans="1:13" ht="22" customHeight="1"/>
+    <row r="95" spans="1:13" ht="22" customHeight="1"/>
+    <row r="96" spans="1:13" ht="22" customHeight="1"/>
+    <row r="97" ht="22" customHeight="1"/>
+    <row r="98" ht="22" customHeight="1"/>
+    <row r="99" ht="22" customHeight="1"/>
+    <row r="100" ht="22" customHeight="1"/>
+    <row r="101" ht="22" customHeight="1"/>
+    <row r="102" ht="22" customHeight="1"/>
+    <row r="103" ht="22" customHeight="1"/>
+    <row r="104" ht="22" customHeight="1"/>
+    <row r="105" ht="22" customHeight="1"/>
+    <row r="106" ht="22" customHeight="1"/>
+    <row r="107" ht="22" customHeight="1"/>
+    <row r="108" ht="22" customHeight="1"/>
+    <row r="109" ht="22" customHeight="1"/>
+    <row r="110" ht="22" customHeight="1"/>
+    <row r="111" ht="22" customHeight="1"/>
+    <row r="112" ht="22" customHeight="1"/>
+    <row r="113" ht="22" customHeight="1"/>
+    <row r="114" ht="22" customHeight="1"/>
+    <row r="115" ht="22" customHeight="1"/>
+    <row r="116" ht="22" customHeight="1"/>
+    <row r="117" ht="22" customHeight="1"/>
+    <row r="118" ht="22" customHeight="1"/>
+    <row r="119" ht="22" customHeight="1"/>
+    <row r="120" ht="22" customHeight="1"/>
+    <row r="121" ht="22" customHeight="1"/>
+    <row r="122" ht="22" customHeight="1"/>
+    <row r="123" ht="22" customHeight="1"/>
+    <row r="124" ht="35.15" customHeight="1"/>
+    <row r="125" ht="22" customHeight="1"/>
+    <row r="126" ht="22" customHeight="1"/>
+    <row r="127" ht="22" customHeight="1"/>
+    <row r="128" ht="22" customHeight="1"/>
+    <row r="129" ht="22" customHeight="1"/>
+    <row r="130" ht="22" customHeight="1"/>
+    <row r="131" ht="22" customHeight="1"/>
+    <row r="132" ht="22" customHeight="1"/>
+    <row r="133" ht="22" customHeight="1"/>
+    <row r="134" ht="22" customHeight="1"/>
+    <row r="135" ht="22" customHeight="1"/>
+    <row r="136" ht="22" customHeight="1"/>
+    <row r="137" ht="22" customHeight="1"/>
+    <row r="138" ht="22" customHeight="1"/>
+    <row r="139" ht="22" customHeight="1"/>
+    <row r="140" ht="22" customHeight="1"/>
+    <row r="141" ht="22" customHeight="1"/>
+    <row r="142" ht="22" customHeight="1"/>
+    <row r="143" ht="22" customHeight="1"/>
+    <row r="144" ht="22" customHeight="1"/>
+    <row r="145" ht="22" customHeight="1"/>
+    <row r="146" ht="22" customHeight="1"/>
+    <row r="147" ht="22" customHeight="1"/>
+    <row r="148" ht="22" customHeight="1"/>
+    <row r="149" ht="22" customHeight="1"/>
+    <row r="150" ht="22" customHeight="1"/>
+    <row r="151" ht="22" customHeight="1"/>
+    <row r="152" ht="22" customHeight="1"/>
+    <row r="153" ht="22" customHeight="1"/>
+    <row r="154" ht="22" customHeight="1"/>
+    <row r="155" ht="22" customHeight="1"/>
+    <row r="156" ht="22" customHeight="1"/>
+    <row r="157" ht="22" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:K3"/>
@@ -6212,5 +7654,6 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/arb_stiffness.xlsx
+++ b/docs/arb_stiffness.xlsx
@@ -3122,7 +3122,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F2D244E-AB5E-4B38-9AA1-584347E594FD}">
   <sheetPr>
-    <tabColor rgb="FF31475E"/>
+    <tabColor rgb="FFC49A32"/>
   </sheetPr>
   <dimension ref="A1:N118"/>
   <sheetFormatPr defaultRowHeight="14"/>
@@ -5383,7 +5383,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41BA758-A778-4052-B774-1845C020535F}">
   <sheetPr>
-    <tabColor rgb="FF31475E"/>
+    <tabColor rgb="FF93A0AC"/>
   </sheetPr>
   <dimension ref="A1:O157"/>
   <sheetFormatPr defaultRowHeight="14"/>
